--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -963,22 +963,22 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.61631944444444</v>
+        <v>22.49007936507936</v>
       </c>
       <c r="D7" t="n">
-        <v>181.2152777777778</v>
+        <v>181.2103174603174</v>
       </c>
       <c r="E7" t="n">
-        <v>1.107638888888889</v>
+        <v>1.10515873015873</v>
       </c>
       <c r="F7" t="n">
-        <v>71.19791666666666</v>
+        <v>71.04761904761905</v>
       </c>
       <c r="G7" t="n">
-        <v>9185972.222222222</v>
+        <v>9051468.253968254</v>
       </c>
       <c r="H7" t="n">
-        <v>77.24131944444444</v>
+        <v>77.32936507936508</v>
       </c>
       <c r="I7" t="n">
         <v>25.82291666666667</v>
@@ -999,22 +999,22 @@
         <v>85.62326388888889</v>
       </c>
       <c r="O7" t="n">
-        <v>23.93213716108453</v>
+        <v>24.06839114832535</v>
       </c>
       <c r="P7" t="n">
-        <v>180.335225943647</v>
+        <v>180.5613397129187</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.078989898989899</v>
+        <v>1.088863636363636</v>
       </c>
       <c r="R7" t="n">
-        <v>71.26668793195108</v>
+        <v>71.26712918660286</v>
       </c>
       <c r="S7" t="n">
-        <v>5512095.95959596</v>
+        <v>5610976.375598086</v>
       </c>
       <c r="T7" t="n">
-        <v>76.5253110047847</v>
+        <v>76.3475538277512</v>
       </c>
       <c r="U7" t="n">
         <v>23.60959682638745</v>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -565,22 +565,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.29382716049383</v>
+        <v>25.33055555555556</v>
       </c>
       <c r="D2" t="n">
-        <v>182.8719135802469</v>
+        <v>182.7934027777778</v>
       </c>
       <c r="E2" t="n">
-        <v>1.514814814814815</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>78.88672839506172</v>
+        <v>78.86006944444443</v>
       </c>
       <c r="G2" t="n">
-        <v>23387500</v>
+        <v>23348437.5</v>
       </c>
       <c r="H2" t="n">
-        <v>82.15833333333333</v>
+        <v>82.090625</v>
       </c>
       <c r="I2" t="n">
         <v>26.28993055555555</v>
@@ -601,22 +601,22 @@
         <v>79.30381944444444</v>
       </c>
       <c r="O2" t="n">
-        <v>25.26073692103104</v>
+        <v>25.07173812706901</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7650546077017</v>
+        <v>181.8265955245735</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.354055258467023</v>
+        <v>1.347175802139037</v>
       </c>
       <c r="R2" t="n">
-        <v>75.40366975072858</v>
+        <v>75.1245830150242</v>
       </c>
       <c r="S2" t="n">
-        <v>13228080.94955154</v>
+        <v>12794659.25006366</v>
       </c>
       <c r="T2" t="n">
-        <v>79.78000311235606</v>
+        <v>79.74682168321874</v>
       </c>
       <c r="U2" t="n">
         <v>24.57832341269841</v>
@@ -935,22 +935,22 @@
         <v>76.74345290126541</v>
       </c>
       <c r="U6" t="n">
-        <v>26.58624806565983</v>
+        <v>26.68631478815302</v>
       </c>
       <c r="V6" t="n">
-        <v>181.8278145873734</v>
+        <v>181.9848628393665</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>68.26875844743492</v>
+        <v>68.33806753907857</v>
       </c>
       <c r="Y6" t="n">
-        <v>1745110.349209614</v>
+        <v>1739365.214289387</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.52199148890325</v>
+        <v>72.5425975678733</v>
       </c>
     </row>
     <row r="7">
@@ -1127,22 +1127,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.7020202020202</v>
+        <v>27.81477272727273</v>
       </c>
       <c r="D9" t="n">
-        <v>183.1858585858586</v>
+        <v>182.9340909090909</v>
       </c>
       <c r="E9" t="n">
-        <v>1.286868686868687</v>
+        <v>1.285227272727273</v>
       </c>
       <c r="F9" t="n">
-        <v>75.77474747474747</v>
+        <v>75.8215909090909</v>
       </c>
       <c r="G9" t="n">
-        <v>9570101.010101011</v>
+        <v>9508863.636363637</v>
       </c>
       <c r="H9" t="n">
-        <v>77.64444444444445</v>
+        <v>77.61250000000001</v>
       </c>
       <c r="I9" t="n">
         <v>25.46157407407408</v>
@@ -1163,22 +1163,22 @@
         <v>87.10732323232325</v>
       </c>
       <c r="O9" t="n">
-        <v>27.23065823065823</v>
+        <v>27.22377622377623</v>
       </c>
       <c r="P9" t="n">
-        <v>181.042402042402</v>
+        <v>181.0030594405594</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.114080364080364</v>
+        <v>1.114947552447553</v>
       </c>
       <c r="R9" t="n">
-        <v>74.57303807303806</v>
+        <v>74.51966783216783</v>
       </c>
       <c r="S9" t="n">
-        <v>7789054.834054834</v>
+        <v>7759517.045454545</v>
       </c>
       <c r="T9" t="n">
-        <v>76.64912864912864</v>
+        <v>76.64991258741259</v>
       </c>
       <c r="U9" t="n">
         <v>25.10080790919606</v>
@@ -1245,40 +1245,40 @@
         <v>75.1388888888889</v>
       </c>
       <c r="O10" t="n">
-        <v>25.78370976336663</v>
+        <v>25.80667348378746</v>
       </c>
       <c r="P10" t="n">
-        <v>180.1519886068905</v>
+        <v>180.1397371827518</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.174720123739732</v>
+        <v>1.184060139207198</v>
       </c>
       <c r="R10" t="n">
-        <v>69.73968855218855</v>
+        <v>69.73839962121212</v>
       </c>
       <c r="S10" t="n">
-        <v>2330018.579822501</v>
+        <v>2331427.152300314</v>
       </c>
       <c r="T10" t="n">
-        <v>74.46470140244649</v>
+        <v>74.49778907775232</v>
       </c>
       <c r="U10" t="n">
-        <v>27.06654325438262</v>
+        <v>26.96097741447006</v>
       </c>
       <c r="V10" t="n">
-        <v>179.4667789601048</v>
+        <v>179.4167883178913</v>
       </c>
       <c r="W10" t="n">
-        <v>1.069652801949182</v>
+        <v>1.064346091000503</v>
       </c>
       <c r="X10" t="n">
-        <v>71.31638703804994</v>
+        <v>71.20941929122075</v>
       </c>
       <c r="Y10" t="n">
-        <v>2857680.553483721</v>
+        <v>2820265.044051809</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.77954001127077</v>
+        <v>73.78894612332113</v>
       </c>
     </row>
     <row r="11">
@@ -1373,22 +1373,22 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.29382716049383</v>
+        <v>25.33055555555556</v>
       </c>
       <c r="D12" t="n">
-        <v>182.8719135802469</v>
+        <v>182.7934027777778</v>
       </c>
       <c r="E12" t="n">
-        <v>1.514814814814815</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>78.88672839506172</v>
+        <v>78.86006944444443</v>
       </c>
       <c r="G12" t="n">
-        <v>23387500</v>
+        <v>23348437.5</v>
       </c>
       <c r="H12" t="n">
-        <v>82.15833333333333</v>
+        <v>82.090625</v>
       </c>
       <c r="I12" t="n">
         <v>25.82291666666667</v>
@@ -1409,22 +1409,22 @@
         <v>85.62326388888889</v>
       </c>
       <c r="O12" t="n">
-        <v>25.26073692103104</v>
+        <v>25.07173812706901</v>
       </c>
       <c r="P12" t="n">
-        <v>181.7650546077017</v>
+        <v>181.8265955245735</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.354055258467023</v>
+        <v>1.347175802139037</v>
       </c>
       <c r="R12" t="n">
-        <v>75.40366975072858</v>
+        <v>75.1245830150242</v>
       </c>
       <c r="S12" t="n">
-        <v>13228080.94955154</v>
+        <v>12794659.25006366</v>
       </c>
       <c r="T12" t="n">
-        <v>79.78000311235606</v>
+        <v>79.74682168321874</v>
       </c>
       <c r="U12" t="n">
         <v>23.60959682638745</v>
@@ -1473,22 +1473,22 @@
         <v>87.10732323232325</v>
       </c>
       <c r="I13" t="n">
-        <v>27.7020202020202</v>
+        <v>27.81477272727273</v>
       </c>
       <c r="J13" t="n">
-        <v>183.1858585858586</v>
+        <v>182.9340909090909</v>
       </c>
       <c r="K13" t="n">
-        <v>1.286868686868687</v>
+        <v>1.285227272727273</v>
       </c>
       <c r="L13" t="n">
-        <v>75.77474747474747</v>
+        <v>75.8215909090909</v>
       </c>
       <c r="M13" t="n">
-        <v>9570101.010101011</v>
+        <v>9508863.636363637</v>
       </c>
       <c r="N13" t="n">
-        <v>77.64444444444445</v>
+        <v>77.61250000000001</v>
       </c>
       <c r="O13" t="n">
         <v>25.10080790919606</v>
@@ -1509,22 +1509,22 @@
         <v>87.42271092394448</v>
       </c>
       <c r="U13" t="n">
-        <v>27.23065823065823</v>
+        <v>27.22377622377623</v>
       </c>
       <c r="V13" t="n">
-        <v>181.042402042402</v>
+        <v>181.0030594405594</v>
       </c>
       <c r="W13" t="n">
-        <v>1.114080364080364</v>
+        <v>1.114947552447553</v>
       </c>
       <c r="X13" t="n">
-        <v>74.57303807303806</v>
+        <v>74.51966783216783</v>
       </c>
       <c r="Y13" t="n">
-        <v>7789054.834054834</v>
+        <v>7759517.045454545</v>
       </c>
       <c r="Z13" t="n">
-        <v>76.64912864912864</v>
+        <v>76.64991258741259</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,22 +565,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.29382716049383</v>
+        <v>25.33055555555556</v>
       </c>
       <c r="D2" t="n">
-        <v>182.8719135802469</v>
+        <v>182.7934027777778</v>
       </c>
       <c r="E2" t="n">
-        <v>1.514814814814815</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>78.88672839506172</v>
+        <v>78.86006944444443</v>
       </c>
       <c r="G2" t="n">
-        <v>23387500</v>
+        <v>23348437.5</v>
       </c>
       <c r="H2" t="n">
-        <v>82.15833333333333</v>
+        <v>82.090625</v>
       </c>
       <c r="I2" t="n">
         <v>26.28993055555555</v>
@@ -601,22 +601,22 @@
         <v>79.30381944444444</v>
       </c>
       <c r="O2" t="n">
-        <v>25.26073692103104</v>
+        <v>25.07173812706901</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7650546077017</v>
+        <v>181.8265955245735</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.354055258467023</v>
+        <v>1.347175802139037</v>
       </c>
       <c r="R2" t="n">
-        <v>75.40366975072858</v>
+        <v>75.1245830150242</v>
       </c>
       <c r="S2" t="n">
-        <v>13228080.94955154</v>
+        <v>12794659.25006366</v>
       </c>
       <c r="T2" t="n">
-        <v>79.78000311235606</v>
+        <v>79.74682168321874</v>
       </c>
       <c r="U2" t="n">
         <v>24.57832341269841</v>
@@ -935,22 +935,22 @@
         <v>76.74345290126541</v>
       </c>
       <c r="U6" t="n">
-        <v>26.58624806565983</v>
+        <v>26.68631478815302</v>
       </c>
       <c r="V6" t="n">
-        <v>181.8278145873734</v>
+        <v>181.9848628393665</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>68.26875844743492</v>
+        <v>68.33806753907857</v>
       </c>
       <c r="Y6" t="n">
-        <v>1745110.349209614</v>
+        <v>1739365.214289387</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.52199148890325</v>
+        <v>72.5425975678733</v>
       </c>
     </row>
     <row r="7">
@@ -1127,22 +1127,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.7020202020202</v>
+        <v>27.81477272727273</v>
       </c>
       <c r="D9" t="n">
-        <v>183.1858585858586</v>
+        <v>182.9340909090909</v>
       </c>
       <c r="E9" t="n">
-        <v>1.286868686868687</v>
+        <v>1.285227272727273</v>
       </c>
       <c r="F9" t="n">
-        <v>75.77474747474747</v>
+        <v>75.8215909090909</v>
       </c>
       <c r="G9" t="n">
-        <v>9570101.010101011</v>
+        <v>9508863.636363637</v>
       </c>
       <c r="H9" t="n">
-        <v>77.64444444444445</v>
+        <v>77.61250000000001</v>
       </c>
       <c r="I9" t="n">
         <v>25.46157407407408</v>
@@ -1163,22 +1163,22 @@
         <v>87.10732323232325</v>
       </c>
       <c r="O9" t="n">
-        <v>27.23065823065823</v>
+        <v>27.22377622377623</v>
       </c>
       <c r="P9" t="n">
-        <v>181.042402042402</v>
+        <v>181.0030594405594</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.114080364080364</v>
+        <v>1.114947552447553</v>
       </c>
       <c r="R9" t="n">
-        <v>74.57303807303806</v>
+        <v>74.51966783216783</v>
       </c>
       <c r="S9" t="n">
-        <v>7789054.834054834</v>
+        <v>7759517.045454545</v>
       </c>
       <c r="T9" t="n">
-        <v>76.64912864912864</v>
+        <v>76.64991258741259</v>
       </c>
       <c r="U9" t="n">
         <v>25.10080790919606</v>
@@ -1245,40 +1245,40 @@
         <v>75.1388888888889</v>
       </c>
       <c r="O10" t="n">
-        <v>25.78370976336663</v>
+        <v>25.80667348378746</v>
       </c>
       <c r="P10" t="n">
-        <v>180.1519886068905</v>
+        <v>180.1397371827518</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.174720123739732</v>
+        <v>1.184060139207198</v>
       </c>
       <c r="R10" t="n">
-        <v>69.73968855218855</v>
+        <v>69.73839962121212</v>
       </c>
       <c r="S10" t="n">
-        <v>2330018.579822501</v>
+        <v>2331427.152300314</v>
       </c>
       <c r="T10" t="n">
-        <v>74.46470140244649</v>
+        <v>74.49778907775232</v>
       </c>
       <c r="U10" t="n">
-        <v>27.06654325438262</v>
+        <v>26.96097741447006</v>
       </c>
       <c r="V10" t="n">
-        <v>179.4667789601048</v>
+        <v>179.4167883178913</v>
       </c>
       <c r="W10" t="n">
-        <v>1.069652801949182</v>
+        <v>1.064346091000503</v>
       </c>
       <c r="X10" t="n">
-        <v>71.31638703804994</v>
+        <v>71.20941929122075</v>
       </c>
       <c r="Y10" t="n">
-        <v>2857680.553483721</v>
+        <v>2820265.044051809</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.77954001127077</v>
+        <v>73.78894612332113</v>
       </c>
     </row>
     <row r="11">
@@ -1366,165 +1366,1219 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.29382716049383</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>182.8719135802469</v>
+        <v>182.2539682539683</v>
       </c>
       <c r="E12" t="n">
-        <v>1.514814814814815</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="F12" t="n">
-        <v>78.88672839506172</v>
+        <v>75.03968253968254</v>
       </c>
       <c r="G12" t="n">
-        <v>23387500</v>
+        <v>8103174.603174603</v>
       </c>
       <c r="H12" t="n">
-        <v>82.15833333333333</v>
+        <v>78.16507936507936</v>
       </c>
       <c r="I12" t="n">
-        <v>25.82291666666667</v>
+        <v>22.49007936507936</v>
       </c>
       <c r="J12" t="n">
-        <v>181.9045138888889</v>
+        <v>181.2103174603174</v>
       </c>
       <c r="K12" t="n">
-        <v>2.703125</v>
+        <v>1.10515873015873</v>
       </c>
       <c r="L12" t="n">
-        <v>81.27951388888889</v>
+        <v>71.04761904761905</v>
       </c>
       <c r="M12" t="n">
-        <v>44854861.1111111</v>
+        <v>9051468.253968254</v>
       </c>
       <c r="N12" t="n">
-        <v>85.62326388888889</v>
+        <v>77.32936507936508</v>
       </c>
       <c r="O12" t="n">
-        <v>25.26073692103104</v>
+        <v>25.30606060606061</v>
       </c>
       <c r="P12" t="n">
-        <v>181.7650546077017</v>
+        <v>180.0204816017316</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.354055258467023</v>
+        <v>1.191044372294372</v>
       </c>
       <c r="R12" t="n">
-        <v>75.40366975072858</v>
+        <v>73.72873376623377</v>
       </c>
       <c r="S12" t="n">
-        <v>13228080.94955154</v>
+        <v>6829829.545454545</v>
       </c>
       <c r="T12" t="n">
-        <v>79.78000311235606</v>
+        <v>77.36168831168831</v>
       </c>
       <c r="U12" t="n">
-        <v>23.60959682638745</v>
+        <v>24.06839114832535</v>
       </c>
       <c r="V12" t="n">
-        <v>180.5017145857893</v>
+        <v>180.5613397129187</v>
       </c>
       <c r="W12" t="n">
-        <v>2.318392015116844</v>
+        <v>1.088863636363636</v>
       </c>
       <c r="X12" t="n">
-        <v>79.44544067679081</v>
+        <v>71.26712918660286</v>
       </c>
       <c r="Y12" t="n">
-        <v>40567152.92224303</v>
+        <v>5610976.375598086</v>
       </c>
       <c r="Z12" t="n">
-        <v>85.261088863463</v>
+        <v>76.3475538277512</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>184.9385416666667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.04375</v>
+      </c>
+      <c r="F13" t="n">
+        <v>77.81041666666667</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13975069.44444444</v>
+      </c>
+      <c r="H13" t="n">
+        <v>80.16354166666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="J13" t="n">
+        <v>185.1064814814815</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.518518518518519</v>
+      </c>
+      <c r="L13" t="n">
+        <v>75.62037037037037</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9920833.333333334</v>
+      </c>
+      <c r="N13" t="n">
+        <v>78.84722222222223</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25.41943703301305</v>
+      </c>
+      <c r="P13" t="n">
+        <v>183.3490060669577</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.627527551829275</v>
+      </c>
+      <c r="R13" t="n">
+        <v>75.61303539913295</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11723820.80654535</v>
+      </c>
+      <c r="T13" t="n">
+        <v>80.07666880062476</v>
+      </c>
+      <c r="U13" t="n">
+        <v>27.91926645658264</v>
+      </c>
+      <c r="V13" t="n">
+        <v>183.1641104139024</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.644544265074451</v>
+      </c>
+      <c r="X13" t="n">
+        <v>76.55679571170573</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9335421.060694015</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>79.17320622327878</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="D14" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>78</v>
+      </c>
+      <c r="I14" t="n">
+        <v>27.81477272727273</v>
+      </c>
+      <c r="J14" t="n">
+        <v>182.9340909090909</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.285227272727273</v>
+      </c>
+      <c r="L14" t="n">
+        <v>75.8215909090909</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9508863.636363637</v>
+      </c>
+      <c r="N14" t="n">
+        <v>77.61250000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25.9863710941836</v>
+      </c>
+      <c r="P14" t="n">
+        <v>181.3564177142302</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.047224476911977</v>
+      </c>
+      <c r="R14" t="n">
+        <v>72.84928144771894</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7850698.108315296</v>
+      </c>
+      <c r="T14" t="n">
+        <v>76.74345290126541</v>
+      </c>
+      <c r="U14" t="n">
+        <v>27.22377622377623</v>
+      </c>
+      <c r="V14" t="n">
+        <v>181.0030594405594</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.114947552447553</v>
+      </c>
+      <c r="X14" t="n">
+        <v>74.51966783216783</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7759517.045454545</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>76.64991258741259</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.82291666666667</v>
+      </c>
+      <c r="D15" t="n">
+        <v>181.9045138888889</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.703125</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81.27951388888889</v>
+      </c>
+      <c r="G15" t="n">
+        <v>44854861.1111111</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85.62326388888889</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.33055555555556</v>
+      </c>
+      <c r="J15" t="n">
+        <v>182.7934027777778</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.541666666666667</v>
+      </c>
+      <c r="L15" t="n">
+        <v>78.86006944444443</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23348437.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>82.090625</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23.60959682638745</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180.5017145857893</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.318392015116844</v>
+      </c>
+      <c r="R15" t="n">
+        <v>79.44544067679081</v>
+      </c>
+      <c r="S15" t="n">
+        <v>40567152.92224303</v>
+      </c>
+      <c r="T15" t="n">
+        <v>85.261088863463</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.07173812706901</v>
+      </c>
+      <c r="V15" t="n">
+        <v>181.8265955245735</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.347175802139037</v>
+      </c>
+      <c r="X15" t="n">
+        <v>75.1245830150242</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12794659.25006366</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.74682168321874</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>27.06944444444444</v>
+      </c>
+      <c r="D16" t="n">
+        <v>182.5462962962963</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.162037037037037</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71.84722222222223</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3919444.444444444</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75.1388888888889</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25.82361111111111</v>
+      </c>
+      <c r="J16" t="n">
+        <v>181.7444444444444</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.683585858585858</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79.13017676767677</v>
+      </c>
+      <c r="M16" t="n">
+        <v>24644318.18181818</v>
+      </c>
+      <c r="N16" t="n">
+        <v>82.18472222222221</v>
+      </c>
+      <c r="O16" t="n">
+        <v>26.96097741447006</v>
+      </c>
+      <c r="P16" t="n">
+        <v>179.4167883178913</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.064346091000503</v>
+      </c>
+      <c r="R16" t="n">
+        <v>71.20941929122075</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2820265.044051809</v>
+      </c>
+      <c r="T16" t="n">
+        <v>73.78894612332113</v>
+      </c>
+      <c r="U16" t="n">
+        <v>24.47144915772633</v>
+      </c>
+      <c r="V16" t="n">
+        <v>180.5634263833992</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.655547713156409</v>
+      </c>
+      <c r="X16" t="n">
+        <v>75.58595485130812</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16626390.73675419</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.28526079898363</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.28993055555555</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183.5694444444444</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.321180555555555</v>
+      </c>
+      <c r="F17" t="n">
+        <v>76.14409722222223</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12212456.59722222</v>
+      </c>
+      <c r="H17" t="n">
+        <v>79.30381944444444</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28.96006944444444</v>
+      </c>
+      <c r="J17" t="n">
+        <v>179.8767361111111</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.307291666666667</v>
+      </c>
+      <c r="L17" t="n">
+        <v>75.40104166666667</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6664756.944444444</v>
+      </c>
+      <c r="N17" t="n">
+        <v>76.58159722222223</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.57832341269841</v>
+      </c>
+      <c r="P17" t="n">
+        <v>184.7292162698413</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.121081349206349</v>
+      </c>
+      <c r="R17" t="n">
+        <v>71.78727678571428</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5391410.590277778</v>
+      </c>
+      <c r="T17" t="n">
+        <v>77.2749255952381</v>
+      </c>
+      <c r="U17" t="n">
+        <v>28.98191833751044</v>
+      </c>
+      <c r="V17" t="n">
+        <v>180.2723292606516</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.387305503341687</v>
+      </c>
+      <c r="X17" t="n">
+        <v>74.64022034252297</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5440179.485171262</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>75.37856881787803</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.46157407407408</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.8776515151515</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.829040404040404</v>
+      </c>
+      <c r="F18" t="n">
+        <v>83.26292087542087</v>
+      </c>
+      <c r="G18" t="n">
+        <v>62781355.21885522</v>
+      </c>
+      <c r="H18" t="n">
+        <v>87.10732323232325</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.52777777777778</v>
+      </c>
+      <c r="J18" t="n">
+        <v>179.7673611111111</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="L18" t="n">
+        <v>70.22222222222221</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2883333.333333333</v>
+      </c>
+      <c r="N18" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25.10080790919606</v>
+      </c>
+      <c r="P18" t="n">
+        <v>180.1463379000385</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.853098792654714</v>
+      </c>
+      <c r="R18" t="n">
+        <v>83.29487480721033</v>
+      </c>
+      <c r="S18" t="n">
+        <v>65050253.78952187</v>
+      </c>
+      <c r="T18" t="n">
+        <v>87.42271092394448</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.80667348378746</v>
+      </c>
+      <c r="V18" t="n">
+        <v>180.1397371827518</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.184060139207198</v>
+      </c>
+      <c r="X18" t="n">
+        <v>69.73839962121212</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2331427.152300314</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>74.49778907775232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>24.88293650793651</v>
+      </c>
+      <c r="J19" t="n">
+        <v>179.6071428571429</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.035714285714286</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74.91269841269842</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10446230.15873016</v>
+      </c>
+      <c r="N19" t="n">
+        <v>78.62103174603173</v>
+      </c>
+      <c r="O19" t="n">
+        <v>26.68631478815302</v>
+      </c>
+      <c r="P19" t="n">
+        <v>181.9848628393665</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>68.33806753907857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1739365.214289387</v>
+      </c>
+      <c r="T19" t="n">
+        <v>72.5425975678733</v>
+      </c>
+      <c r="U19" t="n">
+        <v>26.44866684920276</v>
+      </c>
+      <c r="V19" t="n">
+        <v>178.9288127608023</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.127813987567151</v>
+      </c>
+      <c r="X19" t="n">
+        <v>73.06314045693168</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5660047.953964194</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>75.2452737429484</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="H20" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27.79365079365079</v>
+      </c>
+      <c r="J20" t="n">
+        <v>182.0119047619048</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.871031746031746</v>
+      </c>
+      <c r="L20" t="n">
+        <v>76.39682539682541</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11400793.65079365</v>
+      </c>
+      <c r="N20" t="n">
+        <v>78.75396825396827</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23.54257246376812</v>
+      </c>
+      <c r="P20" t="n">
+        <v>180.9154589371981</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>70.68184955141476</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3850310.559006211</v>
+      </c>
+      <c r="T20" t="n">
+        <v>76.42809696342304</v>
+      </c>
+      <c r="U20" t="n">
+        <v>28.12487599206349</v>
+      </c>
+      <c r="V20" t="n">
+        <v>183.1067708333333</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.020833333333333</v>
+      </c>
+      <c r="X20" t="n">
+        <v>76.16133432539682</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11012524.8015873</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>79.10391865079364</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28.65798611111111</v>
+      </c>
+      <c r="D21" t="n">
+        <v>179.828125</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>82.203125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33149305.55555556</v>
+      </c>
+      <c r="H21" t="n">
+        <v>83.67013888888889</v>
+      </c>
+      <c r="I21" t="n">
+        <v>24.975</v>
+      </c>
+      <c r="J21" t="n">
+        <v>182.3375</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>78.55</v>
+      </c>
+      <c r="M21" t="n">
+        <v>25057500</v>
+      </c>
+      <c r="N21" t="n">
+        <v>82.72499999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>26.96886702049241</v>
+      </c>
+      <c r="P21" t="n">
+        <v>180.7552091011843</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.904880460956312</v>
+      </c>
+      <c r="R21" t="n">
+        <v>78.70829709076612</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20010981.16000786</v>
+      </c>
+      <c r="T21" t="n">
+        <v>81.61007420512064</v>
+      </c>
+      <c r="U21" t="n">
+        <v>23.97150178435219</v>
+      </c>
+      <c r="V21" t="n">
+        <v>178.3522263539283</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.119713175602049</v>
+      </c>
+      <c r="X21" t="n">
+        <v>75.24845503704914</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15947498.63789909</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>80.95702367331373</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185.1064814814815</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.518518518518519</v>
+      </c>
+      <c r="F22" t="n">
+        <v>75.62037037037037</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9920833.333333334</v>
+      </c>
+      <c r="H22" t="n">
+        <v>78.84722222222223</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27</v>
+      </c>
+      <c r="J22" t="n">
+        <v>182.2539682539683</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="L22" t="n">
+        <v>75.03968253968254</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8103174.603174603</v>
+      </c>
+      <c r="N22" t="n">
+        <v>78.16507936507936</v>
+      </c>
+      <c r="O22" t="n">
+        <v>27.91926645658264</v>
+      </c>
+      <c r="P22" t="n">
+        <v>183.1641104139024</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.644544265074451</v>
+      </c>
+      <c r="R22" t="n">
+        <v>76.55679571170573</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9335421.060694015</v>
+      </c>
+      <c r="T22" t="n">
+        <v>79.17320622327878</v>
+      </c>
+      <c r="U22" t="n">
+        <v>25.30606060606061</v>
+      </c>
+      <c r="V22" t="n">
+        <v>180.0204816017316</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.191044372294372</v>
+      </c>
+      <c r="X22" t="n">
+        <v>73.72873376623377</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6829829.545454545</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>77.36168831168831</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27.81477272727273</v>
+      </c>
+      <c r="D23" t="n">
+        <v>182.9340909090909</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.285227272727273</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75.8215909090909</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9508863.636363637</v>
+      </c>
+      <c r="H23" t="n">
+        <v>77.61250000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>184.9385416666667</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.04375</v>
+      </c>
+      <c r="L23" t="n">
+        <v>77.81041666666667</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13975069.44444444</v>
+      </c>
+      <c r="N23" t="n">
+        <v>80.16354166666667</v>
+      </c>
+      <c r="O23" t="n">
+        <v>27.22377622377623</v>
+      </c>
+      <c r="P23" t="n">
+        <v>181.0030594405594</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.114947552447553</v>
+      </c>
+      <c r="R23" t="n">
+        <v>74.51966783216783</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7759517.045454545</v>
+      </c>
+      <c r="T23" t="n">
+        <v>76.64991258741259</v>
+      </c>
+      <c r="U23" t="n">
+        <v>25.41943703301305</v>
+      </c>
+      <c r="V23" t="n">
+        <v>183.3490060669577</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.627527551829275</v>
+      </c>
+      <c r="X23" t="n">
+        <v>75.61303539913295</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11723820.80654535</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>80.07666880062476</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>28.96006944444444</v>
+      </c>
+      <c r="D24" t="n">
+        <v>179.8767361111111</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.307291666666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>75.40104166666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6664756.944444444</v>
+      </c>
+      <c r="H24" t="n">
+        <v>76.58159722222223</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25.82291666666667</v>
+      </c>
+      <c r="J24" t="n">
+        <v>181.9045138888889</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.703125</v>
+      </c>
+      <c r="L24" t="n">
+        <v>81.27951388888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>44854861.1111111</v>
+      </c>
+      <c r="N24" t="n">
+        <v>85.62326388888889</v>
+      </c>
+      <c r="O24" t="n">
+        <v>28.98191833751044</v>
+      </c>
+      <c r="P24" t="n">
+        <v>180.2723292606516</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.387305503341687</v>
+      </c>
+      <c r="R24" t="n">
+        <v>74.64022034252297</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5440179.485171262</v>
+      </c>
+      <c r="T24" t="n">
+        <v>75.37856881787803</v>
+      </c>
+      <c r="U24" t="n">
+        <v>23.60959682638745</v>
+      </c>
+      <c r="V24" t="n">
+        <v>180.5017145857893</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.318392015116844</v>
+      </c>
+      <c r="X24" t="n">
+        <v>79.44544067679081</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>40567152.92224303</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>85.261088863463</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>25.33055555555556</v>
+      </c>
+      <c r="D25" t="n">
+        <v>182.7934027777778</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.541666666666667</v>
+      </c>
+      <c r="F25" t="n">
+        <v>78.86006944444443</v>
+      </c>
+      <c r="G25" t="n">
+        <v>23348437.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>82.090625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.82291666666667</v>
+      </c>
+      <c r="J25" t="n">
+        <v>181.9045138888889</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.703125</v>
+      </c>
+      <c r="L25" t="n">
+        <v>81.27951388888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>44854861.1111111</v>
+      </c>
+      <c r="N25" t="n">
+        <v>85.62326388888889</v>
+      </c>
+      <c r="O25" t="n">
+        <v>25.07173812706901</v>
+      </c>
+      <c r="P25" t="n">
+        <v>181.8265955245735</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.347175802139037</v>
+      </c>
+      <c r="R25" t="n">
+        <v>75.1245830150242</v>
+      </c>
+      <c r="S25" t="n">
+        <v>12794659.25006366</v>
+      </c>
+      <c r="T25" t="n">
+        <v>79.74682168321874</v>
+      </c>
+      <c r="U25" t="n">
+        <v>23.60959682638745</v>
+      </c>
+      <c r="V25" t="n">
+        <v>180.5017145857893</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.318392015116844</v>
+      </c>
+      <c r="X25" t="n">
+        <v>79.44544067679081</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>40567152.92224303</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>85.261088863463</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>25.46157407407408</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D26" t="n">
         <v>181.8776515151515</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E26" t="n">
         <v>2.829040404040404</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F26" t="n">
         <v>83.26292087542087</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G26" t="n">
         <v>62781355.21885522</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H26" t="n">
         <v>87.10732323232325</v>
       </c>
-      <c r="I13" t="n">
-        <v>27.7020202020202</v>
-      </c>
-      <c r="J13" t="n">
-        <v>183.1858585858586</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.286868686868687</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75.77474747474747</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9570101.010101011</v>
-      </c>
-      <c r="N13" t="n">
-        <v>77.64444444444445</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="I26" t="n">
+        <v>27.81477272727273</v>
+      </c>
+      <c r="J26" t="n">
+        <v>182.9340909090909</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.285227272727273</v>
+      </c>
+      <c r="L26" t="n">
+        <v>75.8215909090909</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9508863.636363637</v>
+      </c>
+      <c r="N26" t="n">
+        <v>77.61250000000001</v>
+      </c>
+      <c r="O26" t="n">
         <v>25.10080790919606</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P26" t="n">
         <v>180.1463379000385</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q26" t="n">
         <v>2.853098792654714</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R26" t="n">
         <v>83.29487480721033</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S26" t="n">
         <v>65050253.78952187</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T26" t="n">
         <v>87.42271092394448</v>
       </c>
-      <c r="U13" t="n">
-        <v>27.23065823065823</v>
-      </c>
-      <c r="V13" t="n">
-        <v>181.042402042402</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.114080364080364</v>
-      </c>
-      <c r="X13" t="n">
-        <v>74.57303807303806</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>7789054.834054834</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>76.64912864912864</v>
+      <c r="U26" t="n">
+        <v>27.22377622377623</v>
+      </c>
+      <c r="V26" t="n">
+        <v>181.0030594405594</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.114947552447553</v>
+      </c>
+      <c r="X26" t="n">
+        <v>74.51966783216783</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7759517.045454545</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>76.64991258741259</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,1054 +1530,164 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>26.875</v>
+        <v>25.33055555555556</v>
       </c>
       <c r="D14" t="n">
-        <v>181.875</v>
+        <v>182.7934027777778</v>
       </c>
       <c r="E14" t="n">
-        <v>1.25</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>74.625</v>
+        <v>78.86006944444443</v>
       </c>
       <c r="G14" t="n">
-        <v>11100000</v>
+        <v>23348437.5</v>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>82.090625</v>
       </c>
       <c r="I14" t="n">
-        <v>27.81477272727273</v>
+        <v>25.82291666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>182.9340909090909</v>
+        <v>181.9045138888889</v>
       </c>
       <c r="K14" t="n">
-        <v>1.285227272727273</v>
+        <v>2.703125</v>
       </c>
       <c r="L14" t="n">
-        <v>75.8215909090909</v>
+        <v>81.27951388888889</v>
       </c>
       <c r="M14" t="n">
-        <v>9508863.636363637</v>
+        <v>44854861.1111111</v>
       </c>
       <c r="N14" t="n">
-        <v>77.61250000000001</v>
+        <v>85.62326388888889</v>
       </c>
       <c r="O14" t="n">
-        <v>25.9863710941836</v>
+        <v>25.07173812706901</v>
       </c>
       <c r="P14" t="n">
-        <v>181.3564177142302</v>
+        <v>181.8265955245735</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.047224476911977</v>
+        <v>1.347175802139037</v>
       </c>
       <c r="R14" t="n">
-        <v>72.84928144771894</v>
+        <v>75.1245830150242</v>
       </c>
       <c r="S14" t="n">
-        <v>7850698.108315296</v>
+        <v>12794659.25006366</v>
       </c>
       <c r="T14" t="n">
-        <v>76.74345290126541</v>
+        <v>79.74682168321874</v>
       </c>
       <c r="U14" t="n">
-        <v>27.22377622377623</v>
+        <v>23.60959682638745</v>
       </c>
       <c r="V14" t="n">
-        <v>181.0030594405594</v>
+        <v>180.5017145857893</v>
       </c>
       <c r="W14" t="n">
-        <v>1.114947552447553</v>
+        <v>2.318392015116844</v>
       </c>
       <c r="X14" t="n">
-        <v>74.51966783216783</v>
+        <v>79.44544067679081</v>
       </c>
       <c r="Y14" t="n">
-        <v>7759517.045454545</v>
+        <v>40567152.92224303</v>
       </c>
       <c r="Z14" t="n">
-        <v>76.64991258741259</v>
+        <v>85.261088863463</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.82291666666667</v>
+        <v>25.46157407407408</v>
       </c>
       <c r="D15" t="n">
-        <v>181.9045138888889</v>
+        <v>181.8776515151515</v>
       </c>
       <c r="E15" t="n">
-        <v>2.703125</v>
+        <v>2.829040404040404</v>
       </c>
       <c r="F15" t="n">
-        <v>81.27951388888889</v>
+        <v>83.26292087542087</v>
       </c>
       <c r="G15" t="n">
-        <v>44854861.1111111</v>
+        <v>62781355.21885522</v>
       </c>
       <c r="H15" t="n">
-        <v>85.62326388888889</v>
+        <v>87.10732323232325</v>
       </c>
       <c r="I15" t="n">
-        <v>25.33055555555556</v>
+        <v>27.81477272727273</v>
       </c>
       <c r="J15" t="n">
-        <v>182.7934027777778</v>
+        <v>182.9340909090909</v>
       </c>
       <c r="K15" t="n">
-        <v>1.541666666666667</v>
+        <v>1.285227272727273</v>
       </c>
       <c r="L15" t="n">
-        <v>78.86006944444443</v>
+        <v>75.8215909090909</v>
       </c>
       <c r="M15" t="n">
-        <v>23348437.5</v>
+        <v>9508863.636363637</v>
       </c>
       <c r="N15" t="n">
-        <v>82.090625</v>
+        <v>77.61250000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>23.60959682638745</v>
+        <v>25.10080790919606</v>
       </c>
       <c r="P15" t="n">
-        <v>180.5017145857893</v>
+        <v>180.1463379000385</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.318392015116844</v>
+        <v>2.853098792654714</v>
       </c>
       <c r="R15" t="n">
-        <v>79.44544067679081</v>
+        <v>83.29487480721033</v>
       </c>
       <c r="S15" t="n">
-        <v>40567152.92224303</v>
+        <v>65050253.78952187</v>
       </c>
       <c r="T15" t="n">
-        <v>85.261088863463</v>
+        <v>87.42271092394448</v>
       </c>
       <c r="U15" t="n">
-        <v>25.07173812706901</v>
+        <v>27.22377622377623</v>
       </c>
       <c r="V15" t="n">
-        <v>181.8265955245735</v>
+        <v>181.0030594405594</v>
       </c>
       <c r="W15" t="n">
-        <v>1.347175802139037</v>
+        <v>1.114947552447553</v>
       </c>
       <c r="X15" t="n">
-        <v>75.1245830150242</v>
+        <v>74.51966783216783</v>
       </c>
       <c r="Y15" t="n">
-        <v>12794659.25006366</v>
+        <v>7759517.045454545</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.74682168321874</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>27.06944444444444</v>
-      </c>
-      <c r="D16" t="n">
-        <v>182.5462962962963</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.162037037037037</v>
-      </c>
-      <c r="F16" t="n">
-        <v>71.84722222222223</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3919444.444444444</v>
-      </c>
-      <c r="H16" t="n">
-        <v>75.1388888888889</v>
-      </c>
-      <c r="I16" t="n">
-        <v>25.82361111111111</v>
-      </c>
-      <c r="J16" t="n">
-        <v>181.7444444444444</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.683585858585858</v>
-      </c>
-      <c r="L16" t="n">
-        <v>79.13017676767677</v>
-      </c>
-      <c r="M16" t="n">
-        <v>24644318.18181818</v>
-      </c>
-      <c r="N16" t="n">
-        <v>82.18472222222221</v>
-      </c>
-      <c r="O16" t="n">
-        <v>26.96097741447006</v>
-      </c>
-      <c r="P16" t="n">
-        <v>179.4167883178913</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.064346091000503</v>
-      </c>
-      <c r="R16" t="n">
-        <v>71.20941929122075</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2820265.044051809</v>
-      </c>
-      <c r="T16" t="n">
-        <v>73.78894612332113</v>
-      </c>
-      <c r="U16" t="n">
-        <v>24.47144915772633</v>
-      </c>
-      <c r="V16" t="n">
-        <v>180.5634263833992</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.655547713156409</v>
-      </c>
-      <c r="X16" t="n">
-        <v>75.58595485130812</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16626390.73675419</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>80.28526079898363</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>26.28993055555555</v>
-      </c>
-      <c r="D17" t="n">
-        <v>183.5694444444444</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.321180555555555</v>
-      </c>
-      <c r="F17" t="n">
-        <v>76.14409722222223</v>
-      </c>
-      <c r="G17" t="n">
-        <v>12212456.59722222</v>
-      </c>
-      <c r="H17" t="n">
-        <v>79.30381944444444</v>
-      </c>
-      <c r="I17" t="n">
-        <v>28.96006944444444</v>
-      </c>
-      <c r="J17" t="n">
-        <v>179.8767361111111</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.307291666666667</v>
-      </c>
-      <c r="L17" t="n">
-        <v>75.40104166666667</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6664756.944444444</v>
-      </c>
-      <c r="N17" t="n">
-        <v>76.58159722222223</v>
-      </c>
-      <c r="O17" t="n">
-        <v>24.57832341269841</v>
-      </c>
-      <c r="P17" t="n">
-        <v>184.7292162698413</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.121081349206349</v>
-      </c>
-      <c r="R17" t="n">
-        <v>71.78727678571428</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5391410.590277778</v>
-      </c>
-      <c r="T17" t="n">
-        <v>77.2749255952381</v>
-      </c>
-      <c r="U17" t="n">
-        <v>28.98191833751044</v>
-      </c>
-      <c r="V17" t="n">
-        <v>180.2723292606516</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.387305503341687</v>
-      </c>
-      <c r="X17" t="n">
-        <v>74.64022034252297</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>5440179.485171262</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>75.37856881787803</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>25.46157407407408</v>
-      </c>
-      <c r="D18" t="n">
-        <v>181.8776515151515</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.829040404040404</v>
-      </c>
-      <c r="F18" t="n">
-        <v>83.26292087542087</v>
-      </c>
-      <c r="G18" t="n">
-        <v>62781355.21885522</v>
-      </c>
-      <c r="H18" t="n">
-        <v>87.10732323232325</v>
-      </c>
-      <c r="I18" t="n">
-        <v>25.52777777777778</v>
-      </c>
-      <c r="J18" t="n">
-        <v>179.7673611111111</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="L18" t="n">
-        <v>70.22222222222221</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2883333.333333333</v>
-      </c>
-      <c r="N18" t="n">
-        <v>75.55555555555556</v>
-      </c>
-      <c r="O18" t="n">
-        <v>25.10080790919606</v>
-      </c>
-      <c r="P18" t="n">
-        <v>180.1463379000385</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.853098792654714</v>
-      </c>
-      <c r="R18" t="n">
-        <v>83.29487480721033</v>
-      </c>
-      <c r="S18" t="n">
-        <v>65050253.78952187</v>
-      </c>
-      <c r="T18" t="n">
-        <v>87.42271092394448</v>
-      </c>
-      <c r="U18" t="n">
-        <v>25.80667348378746</v>
-      </c>
-      <c r="V18" t="n">
-        <v>180.1397371827518</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.184060139207198</v>
-      </c>
-      <c r="X18" t="n">
-        <v>69.73839962121212</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2331427.152300314</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>74.49778907775232</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>24.88293650793651</v>
-      </c>
-      <c r="J19" t="n">
-        <v>179.6071428571429</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.035714285714286</v>
-      </c>
-      <c r="L19" t="n">
-        <v>74.91269841269842</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10446230.15873016</v>
-      </c>
-      <c r="N19" t="n">
-        <v>78.62103174603173</v>
-      </c>
-      <c r="O19" t="n">
-        <v>26.68631478815302</v>
-      </c>
-      <c r="P19" t="n">
-        <v>181.9848628393665</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>68.33806753907857</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1739365.214289387</v>
-      </c>
-      <c r="T19" t="n">
-        <v>72.5425975678733</v>
-      </c>
-      <c r="U19" t="n">
-        <v>26.44866684920276</v>
-      </c>
-      <c r="V19" t="n">
-        <v>178.9288127608023</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.127813987567151</v>
-      </c>
-      <c r="X19" t="n">
-        <v>73.06314045693168</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>5660047.953964194</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>75.2452737429484</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>23.64814814814815</v>
-      </c>
-      <c r="D20" t="n">
-        <v>182.0972222222223</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>71.25462962962963</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4062500</v>
-      </c>
-      <c r="H20" t="n">
-        <v>77.19907407407408</v>
-      </c>
-      <c r="I20" t="n">
-        <v>27.79365079365079</v>
-      </c>
-      <c r="J20" t="n">
-        <v>182.0119047619048</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.871031746031746</v>
-      </c>
-      <c r="L20" t="n">
-        <v>76.39682539682541</v>
-      </c>
-      <c r="M20" t="n">
-        <v>11400793.65079365</v>
-      </c>
-      <c r="N20" t="n">
-        <v>78.75396825396827</v>
-      </c>
-      <c r="O20" t="n">
-        <v>23.54257246376812</v>
-      </c>
-      <c r="P20" t="n">
-        <v>180.9154589371981</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>70.68184955141476</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3850310.559006211</v>
-      </c>
-      <c r="T20" t="n">
-        <v>76.42809696342304</v>
-      </c>
-      <c r="U20" t="n">
-        <v>28.12487599206349</v>
-      </c>
-      <c r="V20" t="n">
-        <v>183.1067708333333</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.020833333333333</v>
-      </c>
-      <c r="X20" t="n">
-        <v>76.16133432539682</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>11012524.8015873</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>79.10391865079364</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>28.65798611111111</v>
-      </c>
-      <c r="D21" t="n">
-        <v>179.828125</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.416666666666667</v>
-      </c>
-      <c r="F21" t="n">
-        <v>82.203125</v>
-      </c>
-      <c r="G21" t="n">
-        <v>33149305.55555556</v>
-      </c>
-      <c r="H21" t="n">
-        <v>83.67013888888889</v>
-      </c>
-      <c r="I21" t="n">
-        <v>24.975</v>
-      </c>
-      <c r="J21" t="n">
-        <v>182.3375</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L21" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="M21" t="n">
-        <v>25057500</v>
-      </c>
-      <c r="N21" t="n">
-        <v>82.72499999999999</v>
-      </c>
-      <c r="O21" t="n">
-        <v>26.96886702049241</v>
-      </c>
-      <c r="P21" t="n">
-        <v>180.7552091011843</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.904880460956312</v>
-      </c>
-      <c r="R21" t="n">
-        <v>78.70829709076612</v>
-      </c>
-      <c r="S21" t="n">
-        <v>20010981.16000786</v>
-      </c>
-      <c r="T21" t="n">
-        <v>81.61007420512064</v>
-      </c>
-      <c r="U21" t="n">
-        <v>23.97150178435219</v>
-      </c>
-      <c r="V21" t="n">
-        <v>178.3522263539283</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.119713175602049</v>
-      </c>
-      <c r="X21" t="n">
-        <v>75.24845503704914</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15947498.63789909</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>80.95702367331373</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>26.22222222222222</v>
-      </c>
-      <c r="D22" t="n">
-        <v>185.1064814814815</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.518518518518519</v>
-      </c>
-      <c r="F22" t="n">
-        <v>75.62037037037037</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9920833.333333334</v>
-      </c>
-      <c r="H22" t="n">
-        <v>78.84722222222223</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27</v>
-      </c>
-      <c r="J22" t="n">
-        <v>182.2539682539683</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.388888888888889</v>
-      </c>
-      <c r="L22" t="n">
-        <v>75.03968253968254</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8103174.603174603</v>
-      </c>
-      <c r="N22" t="n">
-        <v>78.16507936507936</v>
-      </c>
-      <c r="O22" t="n">
-        <v>27.91926645658264</v>
-      </c>
-      <c r="P22" t="n">
-        <v>183.1641104139024</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.644544265074451</v>
-      </c>
-      <c r="R22" t="n">
-        <v>76.55679571170573</v>
-      </c>
-      <c r="S22" t="n">
-        <v>9335421.060694015</v>
-      </c>
-      <c r="T22" t="n">
-        <v>79.17320622327878</v>
-      </c>
-      <c r="U22" t="n">
-        <v>25.30606060606061</v>
-      </c>
-      <c r="V22" t="n">
-        <v>180.0204816017316</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.191044372294372</v>
-      </c>
-      <c r="X22" t="n">
-        <v>73.72873376623377</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>6829829.545454545</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>77.36168831168831</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27.81477272727273</v>
-      </c>
-      <c r="D23" t="n">
-        <v>182.9340909090909</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.285227272727273</v>
-      </c>
-      <c r="F23" t="n">
-        <v>75.8215909090909</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9508863.636363637</v>
-      </c>
-      <c r="H23" t="n">
-        <v>77.61250000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>184.9385416666667</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.04375</v>
-      </c>
-      <c r="L23" t="n">
-        <v>77.81041666666667</v>
-      </c>
-      <c r="M23" t="n">
-        <v>13975069.44444444</v>
-      </c>
-      <c r="N23" t="n">
-        <v>80.16354166666667</v>
-      </c>
-      <c r="O23" t="n">
-        <v>27.22377622377623</v>
-      </c>
-      <c r="P23" t="n">
-        <v>181.0030594405594</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.114947552447553</v>
-      </c>
-      <c r="R23" t="n">
-        <v>74.51966783216783</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7759517.045454545</v>
-      </c>
-      <c r="T23" t="n">
-        <v>76.64991258741259</v>
-      </c>
-      <c r="U23" t="n">
-        <v>25.41943703301305</v>
-      </c>
-      <c r="V23" t="n">
-        <v>183.3490060669577</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.627527551829275</v>
-      </c>
-      <c r="X23" t="n">
-        <v>75.61303539913295</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>11723820.80654535</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>80.07666880062476</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>28.96006944444444</v>
-      </c>
-      <c r="D24" t="n">
-        <v>179.8767361111111</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.307291666666667</v>
-      </c>
-      <c r="F24" t="n">
-        <v>75.40104166666667</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6664756.944444444</v>
-      </c>
-      <c r="H24" t="n">
-        <v>76.58159722222223</v>
-      </c>
-      <c r="I24" t="n">
-        <v>25.82291666666667</v>
-      </c>
-      <c r="J24" t="n">
-        <v>181.9045138888889</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.703125</v>
-      </c>
-      <c r="L24" t="n">
-        <v>81.27951388888889</v>
-      </c>
-      <c r="M24" t="n">
-        <v>44854861.1111111</v>
-      </c>
-      <c r="N24" t="n">
-        <v>85.62326388888889</v>
-      </c>
-      <c r="O24" t="n">
-        <v>28.98191833751044</v>
-      </c>
-      <c r="P24" t="n">
-        <v>180.2723292606516</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.387305503341687</v>
-      </c>
-      <c r="R24" t="n">
-        <v>74.64022034252297</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5440179.485171262</v>
-      </c>
-      <c r="T24" t="n">
-        <v>75.37856881787803</v>
-      </c>
-      <c r="U24" t="n">
-        <v>23.60959682638745</v>
-      </c>
-      <c r="V24" t="n">
-        <v>180.5017145857893</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.318392015116844</v>
-      </c>
-      <c r="X24" t="n">
-        <v>79.44544067679081</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>40567152.92224303</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>85.261088863463</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>25.33055555555556</v>
-      </c>
-      <c r="D25" t="n">
-        <v>182.7934027777778</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.541666666666667</v>
-      </c>
-      <c r="F25" t="n">
-        <v>78.86006944444443</v>
-      </c>
-      <c r="G25" t="n">
-        <v>23348437.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>82.090625</v>
-      </c>
-      <c r="I25" t="n">
-        <v>25.82291666666667</v>
-      </c>
-      <c r="J25" t="n">
-        <v>181.9045138888889</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.703125</v>
-      </c>
-      <c r="L25" t="n">
-        <v>81.27951388888889</v>
-      </c>
-      <c r="M25" t="n">
-        <v>44854861.1111111</v>
-      </c>
-      <c r="N25" t="n">
-        <v>85.62326388888889</v>
-      </c>
-      <c r="O25" t="n">
-        <v>25.07173812706901</v>
-      </c>
-      <c r="P25" t="n">
-        <v>181.8265955245735</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.347175802139037</v>
-      </c>
-      <c r="R25" t="n">
-        <v>75.1245830150242</v>
-      </c>
-      <c r="S25" t="n">
-        <v>12794659.25006366</v>
-      </c>
-      <c r="T25" t="n">
-        <v>79.74682168321874</v>
-      </c>
-      <c r="U25" t="n">
-        <v>23.60959682638745</v>
-      </c>
-      <c r="V25" t="n">
-        <v>180.5017145857893</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.318392015116844</v>
-      </c>
-      <c r="X25" t="n">
-        <v>79.44544067679081</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>40567152.92224303</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>85.261088863463</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>25.46157407407408</v>
-      </c>
-      <c r="D26" t="n">
-        <v>181.8776515151515</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.829040404040404</v>
-      </c>
-      <c r="F26" t="n">
-        <v>83.26292087542087</v>
-      </c>
-      <c r="G26" t="n">
-        <v>62781355.21885522</v>
-      </c>
-      <c r="H26" t="n">
-        <v>87.10732323232325</v>
-      </c>
-      <c r="I26" t="n">
-        <v>27.81477272727273</v>
-      </c>
-      <c r="J26" t="n">
-        <v>182.9340909090909</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.285227272727273</v>
-      </c>
-      <c r="L26" t="n">
-        <v>75.8215909090909</v>
-      </c>
-      <c r="M26" t="n">
-        <v>9508863.636363637</v>
-      </c>
-      <c r="N26" t="n">
-        <v>77.61250000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>25.10080790919606</v>
-      </c>
-      <c r="P26" t="n">
-        <v>180.1463379000385</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.853098792654714</v>
-      </c>
-      <c r="R26" t="n">
-        <v>83.29487480721033</v>
-      </c>
-      <c r="S26" t="n">
-        <v>65050253.78952187</v>
-      </c>
-      <c r="T26" t="n">
-        <v>87.42271092394448</v>
-      </c>
-      <c r="U26" t="n">
-        <v>27.22377622377623</v>
-      </c>
-      <c r="V26" t="n">
-        <v>181.0030594405594</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.114947552447553</v>
-      </c>
-      <c r="X26" t="n">
-        <v>74.51966783216783</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>7759517.045454545</v>
-      </c>
-      <c r="Z26" t="n">
         <v>76.64991258741259</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,22 +565,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.33055555555556</v>
+        <v>25.20631313131313</v>
       </c>
       <c r="D2" t="n">
-        <v>182.7934027777778</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="E2" t="n">
-        <v>1.541666666666667</v>
+        <v>1.478030303030303</v>
       </c>
       <c r="F2" t="n">
-        <v>78.86006944444443</v>
+        <v>78.86186868686868</v>
       </c>
       <c r="G2" t="n">
-        <v>23348437.5</v>
+        <v>23356818.18181818</v>
       </c>
       <c r="H2" t="n">
-        <v>82.090625</v>
+        <v>82.16363636363636</v>
       </c>
       <c r="I2" t="n">
         <v>26.28993055555555</v>
@@ -601,40 +601,40 @@
         <v>79.30381944444444</v>
       </c>
       <c r="O2" t="n">
-        <v>25.07173812706901</v>
+        <v>25.33190728321512</v>
       </c>
       <c r="P2" t="n">
-        <v>181.8265955245735</v>
+        <v>181.6462106869338</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.347175802139037</v>
+        <v>1.340570903172624</v>
       </c>
       <c r="R2" t="n">
-        <v>75.1245830150242</v>
+        <v>75.61980094229571</v>
       </c>
       <c r="S2" t="n">
-        <v>12794659.25006366</v>
+        <v>13677224.33421806</v>
       </c>
       <c r="T2" t="n">
-        <v>79.74682168321874</v>
+        <v>79.89114879153243</v>
       </c>
       <c r="U2" t="n">
-        <v>24.57832341269841</v>
+        <v>24.67694444444444</v>
       </c>
       <c r="V2" t="n">
-        <v>184.7292162698413</v>
+        <v>184.7762301587302</v>
       </c>
       <c r="W2" t="n">
-        <v>1.121081349206349</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="X2" t="n">
-        <v>71.78727678571428</v>
+        <v>72.03696428571429</v>
       </c>
       <c r="Y2" t="n">
-        <v>5391410.590277778</v>
+        <v>5435271.329365079</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.2749255952381</v>
+        <v>77.33422619047619</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27.79365079365079</v>
+        <v>27.78395061728395</v>
       </c>
       <c r="D3" t="n">
-        <v>182.0119047619048</v>
+        <v>182.037037037037</v>
       </c>
       <c r="E3" t="n">
-        <v>1.871031746031746</v>
+        <v>1.871913580246914</v>
       </c>
       <c r="F3" t="n">
-        <v>76.39682539682541</v>
+        <v>76.6141975308642</v>
       </c>
       <c r="G3" t="n">
-        <v>11400793.65079365</v>
+        <v>12136728.39506173</v>
       </c>
       <c r="H3" t="n">
-        <v>78.75396825396827</v>
+        <v>78.90586419753087</v>
       </c>
       <c r="I3" t="n">
-        <v>24.975</v>
+        <v>25.12666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>182.3375</v>
+        <v>181.6877777777778</v>
       </c>
       <c r="K3" t="n">
-        <v>1.35</v>
+        <v>1.353333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55</v>
+        <v>78.54888888888888</v>
       </c>
       <c r="M3" t="n">
-        <v>25057500</v>
+        <v>24666444.44444444</v>
       </c>
       <c r="N3" t="n">
-        <v>82.72499999999999</v>
+        <v>82.65777777777778</v>
       </c>
       <c r="O3" t="n">
-        <v>28.12487599206349</v>
+        <v>28.1894246031746</v>
       </c>
       <c r="P3" t="n">
-        <v>183.1067708333333</v>
+        <v>183.5720833333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.020833333333333</v>
+        <v>2.023333333333333</v>
       </c>
       <c r="R3" t="n">
-        <v>76.16133432539682</v>
+        <v>75.9471626984127</v>
       </c>
       <c r="S3" t="n">
-        <v>11012524.8015873</v>
+        <v>10458496.03174603</v>
       </c>
       <c r="T3" t="n">
-        <v>79.10391865079364</v>
+        <v>79.1536111111111</v>
       </c>
       <c r="U3" t="n">
-        <v>23.97150178435219</v>
+        <v>23.86767761795794</v>
       </c>
       <c r="V3" t="n">
-        <v>178.3522263539283</v>
+        <v>179.5817810831426</v>
       </c>
       <c r="W3" t="n">
-        <v>1.119713175602049</v>
+        <v>1.129103873814972</v>
       </c>
       <c r="X3" t="n">
-        <v>75.24845503704914</v>
+        <v>74.76543069630597</v>
       </c>
       <c r="Y3" t="n">
-        <v>15947498.63789909</v>
+        <v>14949427.48174785</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.95702367331373</v>
+        <v>80.84180941484145</v>
       </c>
     </row>
     <row r="4">
@@ -729,22 +729,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>27.07407407407407</v>
       </c>
       <c r="D4" t="n">
-        <v>182.2539682539683</v>
+        <v>182.1604938271605</v>
       </c>
       <c r="E4" t="n">
-        <v>1.388888888888889</v>
+        <v>1.41358024691358</v>
       </c>
       <c r="F4" t="n">
-        <v>75.03968253968254</v>
+        <v>75.2037037037037</v>
       </c>
       <c r="G4" t="n">
-        <v>8103174.603174603</v>
+        <v>8313580.246913578</v>
       </c>
       <c r="H4" t="n">
-        <v>78.16507936507936</v>
+        <v>78.30123456790122</v>
       </c>
       <c r="I4" t="n">
         <v>23.64814814814815</v>
@@ -765,40 +765,40 @@
         <v>77.19907407407408</v>
       </c>
       <c r="O4" t="n">
-        <v>25.30606060606061</v>
+        <v>25.47484848484849</v>
       </c>
       <c r="P4" t="n">
-        <v>180.0204816017316</v>
+        <v>180.1052741702742</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.191044372294372</v>
+        <v>1.162835497835498</v>
       </c>
       <c r="R4" t="n">
-        <v>73.72873376623377</v>
+        <v>73.58965367965368</v>
       </c>
       <c r="S4" t="n">
-        <v>6829829.545454545</v>
+        <v>6629696.96969697</v>
       </c>
       <c r="T4" t="n">
-        <v>77.36168831168831</v>
+        <v>76.97379509379509</v>
       </c>
       <c r="U4" t="n">
-        <v>23.54257246376812</v>
+        <v>23.53052261747914</v>
       </c>
       <c r="V4" t="n">
-        <v>180.9154589371981</v>
+        <v>180.7263065436979</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>70.68184955141476</v>
+        <v>70.54598469163686</v>
       </c>
       <c r="Y4" t="n">
-        <v>3850310.559006211</v>
+        <v>3713771.174477696</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.42809696342304</v>
+        <v>76.28237656063743</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.88293650793651</v>
+        <v>24.91666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>179.6071428571429</v>
+        <v>179.6219135802469</v>
       </c>
       <c r="E5" t="n">
-        <v>1.035714285714286</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="F5" t="n">
-        <v>74.91269841269842</v>
+        <v>74.98456790123457</v>
       </c>
       <c r="G5" t="n">
-        <v>10446230.15873016</v>
+        <v>10353395.0617284</v>
       </c>
       <c r="H5" t="n">
-        <v>78.62103174603173</v>
+        <v>78.64351851851853</v>
       </c>
       <c r="I5" t="n">
-        <v>28.3</v>
+        <v>28.57333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>184.9385416666667</v>
+        <v>184.7841666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>2.04375</v>
+        <v>2.079444444444444</v>
       </c>
       <c r="L5" t="n">
-        <v>77.81041666666667</v>
+        <v>78.08166666666666</v>
       </c>
       <c r="M5" t="n">
-        <v>13975069.44444444</v>
+        <v>14353388.88888889</v>
       </c>
       <c r="N5" t="n">
-        <v>80.16354166666667</v>
+        <v>80.13083333333334</v>
       </c>
       <c r="O5" t="n">
-        <v>26.44866684920276</v>
+        <v>26.42893347936221</v>
       </c>
       <c r="P5" t="n">
-        <v>178.9288127608023</v>
+        <v>178.9630502086418</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.127813987567151</v>
+        <v>1.132251190053721</v>
       </c>
       <c r="R5" t="n">
-        <v>73.06314045693168</v>
+        <v>73.06551236554535</v>
       </c>
       <c r="S5" t="n">
-        <v>5660047.953964194</v>
+        <v>5814538.363171356</v>
       </c>
       <c r="T5" t="n">
-        <v>75.2452737429484</v>
+        <v>75.27621899435871</v>
       </c>
       <c r="U5" t="n">
-        <v>25.41943703301305</v>
+        <v>25.37854479549257</v>
       </c>
       <c r="V5" t="n">
-        <v>183.3490060669577</v>
+        <v>183.5299294912473</v>
       </c>
       <c r="W5" t="n">
-        <v>1.627527551829275</v>
+        <v>1.629558273347478</v>
       </c>
       <c r="X5" t="n">
-        <v>75.61303539913295</v>
+        <v>75.69042831930636</v>
       </c>
       <c r="Y5" t="n">
-        <v>11723820.80654535</v>
+        <v>11843066.30707203</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.07666880062476</v>
+        <v>80.09128673132106</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +893,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.875</v>
+        <v>27.41666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>181.875</v>
+        <v>183.4166666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>1.25</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>74.625</v>
+        <v>75.25</v>
       </c>
       <c r="G6" t="n">
-        <v>11100000</v>
+        <v>10925000</v>
       </c>
       <c r="H6" t="n">
-        <v>78</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -917,40 +917,40 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>25.9863710941836</v>
+        <v>26.13074255990923</v>
       </c>
       <c r="P6" t="n">
-        <v>181.3564177142302</v>
+        <v>181.0787205078872</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.047224476911977</v>
+        <v>1.057850328683662</v>
       </c>
       <c r="R6" t="n">
-        <v>72.84928144771894</v>
+        <v>73.15174223924224</v>
       </c>
       <c r="S6" t="n">
-        <v>7850698.108315296</v>
+        <v>8064906.255010421</v>
       </c>
       <c r="T6" t="n">
-        <v>76.74345290126541</v>
+        <v>76.91481527731528</v>
       </c>
       <c r="U6" t="n">
-        <v>26.68631478815302</v>
+        <v>26.18199269412505</v>
       </c>
       <c r="V6" t="n">
-        <v>181.9848628393665</v>
+        <v>181.7001773893318</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>68.33806753907857</v>
+        <v>67.97260641727554</v>
       </c>
       <c r="Y6" t="n">
-        <v>1739365.214289387</v>
+        <v>1721028.091427908</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.5425975678733</v>
+        <v>72.42437760360555</v>
       </c>
     </row>
     <row r="7">
@@ -963,76 +963,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.49007936507936</v>
+        <v>22.925</v>
       </c>
       <c r="D7" t="n">
-        <v>181.2103174603174</v>
+        <v>181.5819444444444</v>
       </c>
       <c r="E7" t="n">
-        <v>1.10515873015873</v>
+        <v>1.134722222222222</v>
       </c>
       <c r="F7" t="n">
-        <v>71.04761904761905</v>
+        <v>71.63333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>9051468.253968254</v>
+        <v>9446666.666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>77.32936507936508</v>
+        <v>77.25277777777778</v>
       </c>
       <c r="I7" t="n">
-        <v>25.82291666666667</v>
+        <v>25.87361111111111</v>
       </c>
       <c r="J7" t="n">
-        <v>181.9045138888889</v>
+        <v>181.775</v>
       </c>
       <c r="K7" t="n">
-        <v>2.703125</v>
+        <v>2.715277777777778</v>
       </c>
       <c r="L7" t="n">
-        <v>81.27951388888889</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>44854861.1111111</v>
+        <v>43920694.44444444</v>
       </c>
       <c r="N7" t="n">
-        <v>85.62326388888889</v>
+        <v>85.49027777777778</v>
       </c>
       <c r="O7" t="n">
-        <v>24.06839114832535</v>
+        <v>23.76410067869398</v>
       </c>
       <c r="P7" t="n">
-        <v>180.5613397129187</v>
+        <v>180.3781718759709</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.088863636363636</v>
+        <v>1.064628099173554</v>
       </c>
       <c r="R7" t="n">
-        <v>71.26712918660286</v>
+        <v>70.95124395009562</v>
       </c>
       <c r="S7" t="n">
-        <v>5610976.375598086</v>
+        <v>5228807.22812541</v>
       </c>
       <c r="T7" t="n">
-        <v>76.3475538277512</v>
+        <v>76.45144493465068</v>
       </c>
       <c r="U7" t="n">
-        <v>23.60959682638745</v>
+        <v>23.46750939388307</v>
       </c>
       <c r="V7" t="n">
-        <v>180.5017145857893</v>
+        <v>180.6559935173709</v>
       </c>
       <c r="W7" t="n">
-        <v>2.318392015116844</v>
+        <v>2.183285040664904</v>
       </c>
       <c r="X7" t="n">
-        <v>79.44544067679081</v>
+        <v>78.51349539857549</v>
       </c>
       <c r="Y7" t="n">
-        <v>40567152.92224303</v>
+        <v>36364898.80838265</v>
       </c>
       <c r="Z7" t="n">
-        <v>85.261088863463</v>
+        <v>84.76769462018217</v>
       </c>
     </row>
     <row r="8">
@@ -1045,76 +1045,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.82361111111111</v>
+        <v>25.84343434343434</v>
       </c>
       <c r="D8" t="n">
-        <v>181.7444444444444</v>
+        <v>181.5691919191919</v>
       </c>
       <c r="E8" t="n">
-        <v>1.683585858585858</v>
+        <v>1.698686868686869</v>
       </c>
       <c r="F8" t="n">
-        <v>79.13017676767677</v>
+        <v>79.43323232323232</v>
       </c>
       <c r="G8" t="n">
-        <v>24644318.18181818</v>
+        <v>25763181.81818182</v>
       </c>
       <c r="H8" t="n">
-        <v>82.18472222222221</v>
+        <v>82.44686868686868</v>
       </c>
       <c r="I8" t="n">
-        <v>28.96006944444444</v>
+        <v>28.70694444444445</v>
       </c>
       <c r="J8" t="n">
-        <v>179.8767361111111</v>
+        <v>179.6513888888889</v>
       </c>
       <c r="K8" t="n">
-        <v>1.307291666666667</v>
+        <v>1.268055555555555</v>
       </c>
       <c r="L8" t="n">
-        <v>75.40104166666667</v>
+        <v>75.35277777777779</v>
       </c>
       <c r="M8" t="n">
-        <v>6664756.944444444</v>
+        <v>6780972.222222222</v>
       </c>
       <c r="N8" t="n">
-        <v>76.58159722222223</v>
+        <v>76.55694444444445</v>
       </c>
       <c r="O8" t="n">
-        <v>24.47144915772633</v>
+        <v>24.39584619486794</v>
       </c>
       <c r="P8" t="n">
-        <v>180.5634263833992</v>
+        <v>180.8557916117699</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.655547713156409</v>
+        <v>1.646155342242299</v>
       </c>
       <c r="R8" t="n">
-        <v>75.58595485130812</v>
+        <v>75.20563256791517</v>
       </c>
       <c r="S8" t="n">
-        <v>16626390.73675419</v>
+        <v>15812387.8419286</v>
       </c>
       <c r="T8" t="n">
-        <v>80.28526079898363</v>
+        <v>80.07366318464145</v>
       </c>
       <c r="U8" t="n">
-        <v>28.98191833751044</v>
+        <v>29.1236299081036</v>
       </c>
       <c r="V8" t="n">
-        <v>180.2723292606516</v>
+        <v>180.5778634085213</v>
       </c>
       <c r="W8" t="n">
-        <v>1.387305503341687</v>
+        <v>1.393653926482874</v>
       </c>
       <c r="X8" t="n">
-        <v>74.64022034252297</v>
+        <v>74.63693817878028</v>
       </c>
       <c r="Y8" t="n">
-        <v>5440179.485171262</v>
+        <v>5295762.635756057</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.37856881787803</v>
+        <v>75.45333124477861</v>
       </c>
     </row>
     <row r="9">
@@ -1127,76 +1127,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.81477272727273</v>
+        <v>27.74545454545455</v>
       </c>
       <c r="D9" t="n">
-        <v>182.9340909090909</v>
+        <v>183.3537190082644</v>
       </c>
       <c r="E9" t="n">
-        <v>1.285227272727273</v>
+        <v>1.269421487603306</v>
       </c>
       <c r="F9" t="n">
-        <v>75.8215909090909</v>
+        <v>75.69338842975206</v>
       </c>
       <c r="G9" t="n">
-        <v>9508863.636363637</v>
+        <v>9326611.570247935</v>
       </c>
       <c r="H9" t="n">
-        <v>77.61250000000001</v>
+        <v>77.49090909090908</v>
       </c>
       <c r="I9" t="n">
-        <v>25.46157407407408</v>
+        <v>25.50299873737374</v>
       </c>
       <c r="J9" t="n">
-        <v>181.8776515151515</v>
+        <v>181.7230113636363</v>
       </c>
       <c r="K9" t="n">
-        <v>2.829040404040404</v>
+        <v>2.787689393939394</v>
       </c>
       <c r="L9" t="n">
-        <v>83.26292087542087</v>
+        <v>83.56650883838384</v>
       </c>
       <c r="M9" t="n">
-        <v>62781355.21885522</v>
+        <v>63154198.23232324</v>
       </c>
       <c r="N9" t="n">
-        <v>87.10732323232325</v>
+        <v>87.18503787878788</v>
       </c>
       <c r="O9" t="n">
-        <v>27.22377622377623</v>
+        <v>27.29139042775406</v>
       </c>
       <c r="P9" t="n">
-        <v>181.0030594405594</v>
+        <v>180.8754427390791</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.114947552447553</v>
+        <v>1.105099446008537</v>
       </c>
       <c r="R9" t="n">
-        <v>74.51966783216783</v>
+        <v>74.46884933248569</v>
       </c>
       <c r="S9" t="n">
-        <v>7759517.045454545</v>
+        <v>7590431.386795023</v>
       </c>
       <c r="T9" t="n">
-        <v>76.64991258741259</v>
+        <v>76.58514213059667</v>
       </c>
       <c r="U9" t="n">
-        <v>25.10080790919606</v>
+        <v>25.13281690693971</v>
       </c>
       <c r="V9" t="n">
-        <v>180.1463379000385</v>
+        <v>179.9695843062071</v>
       </c>
       <c r="W9" t="n">
-        <v>2.853098792654714</v>
+        <v>2.832384111989375</v>
       </c>
       <c r="X9" t="n">
-        <v>83.29487480721033</v>
+        <v>82.99050600147092</v>
       </c>
       <c r="Y9" t="n">
-        <v>65050253.78952187</v>
+        <v>63210719.4178466</v>
       </c>
       <c r="Z9" t="n">
-        <v>87.42271092394448</v>
+        <v>87.23376773486423</v>
       </c>
     </row>
     <row r="10">
@@ -1209,76 +1209,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.52777777777778</v>
+        <v>25.9074074074074</v>
       </c>
       <c r="D10" t="n">
-        <v>179.7673611111111</v>
+        <v>180.0069444444445</v>
       </c>
       <c r="E10" t="n">
-        <v>1.166666666666667</v>
+        <v>1.189814814814815</v>
       </c>
       <c r="F10" t="n">
-        <v>70.22222222222221</v>
+        <v>70.3912037037037</v>
       </c>
       <c r="G10" t="n">
-        <v>2883333.333333333</v>
+        <v>2919155.092592593</v>
       </c>
       <c r="H10" t="n">
-        <v>75.55555555555556</v>
+        <v>75.54398148148148</v>
       </c>
       <c r="I10" t="n">
-        <v>27.06944444444444</v>
+        <v>26.91666666666666</v>
       </c>
       <c r="J10" t="n">
-        <v>182.5462962962963</v>
+        <v>182.8777777777778</v>
       </c>
       <c r="K10" t="n">
-        <v>1.162037037037037</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="L10" t="n">
-        <v>71.84722222222223</v>
+        <v>71.95833333333334</v>
       </c>
       <c r="M10" t="n">
-        <v>3919444.444444444</v>
+        <v>3914166.666666667</v>
       </c>
       <c r="N10" t="n">
-        <v>75.1388888888889</v>
+        <v>75.25833333333334</v>
       </c>
       <c r="O10" t="n">
-        <v>25.80667348378746</v>
+        <v>25.91150027124292</v>
       </c>
       <c r="P10" t="n">
-        <v>180.1397371827518</v>
+        <v>180.617196583373</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.184060139207198</v>
+        <v>1.179574891339597</v>
       </c>
       <c r="R10" t="n">
-        <v>69.73839962121212</v>
+        <v>69.96502282439782</v>
       </c>
       <c r="S10" t="n">
-        <v>2331427.152300314</v>
+        <v>2379828.495306436</v>
       </c>
       <c r="T10" t="n">
-        <v>74.49778907775232</v>
+        <v>74.48039418370301</v>
       </c>
       <c r="U10" t="n">
-        <v>26.96097741447006</v>
+        <v>27.23790339052287</v>
       </c>
       <c r="V10" t="n">
-        <v>179.4167883178913</v>
+        <v>179.7714282347554</v>
       </c>
       <c r="W10" t="n">
-        <v>1.064346091000503</v>
+        <v>1.090361216602026</v>
       </c>
       <c r="X10" t="n">
-        <v>71.20941929122075</v>
+        <v>71.40358461493572</v>
       </c>
       <c r="Y10" t="n">
-        <v>2820265.044051809</v>
+        <v>2888474.881939956</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.78894612332113</v>
+        <v>73.70217204670328</v>
       </c>
     </row>
     <row r="11">
@@ -1291,76 +1291,76 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.22222222222222</v>
+        <v>26.69166666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>185.1064814814815</v>
+        <v>185.6166666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>1.518518518518519</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>75.62037037037037</v>
+        <v>75.84166666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>9920833.333333334</v>
+        <v>9787222.222222222</v>
       </c>
       <c r="H11" t="n">
-        <v>78.84722222222223</v>
+        <v>78.84166666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>28.65798611111111</v>
+        <v>28.59876543209877</v>
       </c>
       <c r="J11" t="n">
-        <v>179.828125</v>
+        <v>179.9027777777778</v>
       </c>
       <c r="K11" t="n">
-        <v>2.416666666666667</v>
+        <v>2.439814814814815</v>
       </c>
       <c r="L11" t="n">
-        <v>82.203125</v>
+        <v>82.20833333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>33149305.55555556</v>
+        <v>33334104.9382716</v>
       </c>
       <c r="N11" t="n">
-        <v>83.67013888888889</v>
+        <v>83.73456790123457</v>
       </c>
       <c r="O11" t="n">
-        <v>27.91926645658264</v>
+        <v>27.69999649859944</v>
       </c>
       <c r="P11" t="n">
-        <v>183.1641104139024</v>
+        <v>183.2354549977886</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.644544265074451</v>
+        <v>1.644802078726227</v>
       </c>
       <c r="R11" t="n">
-        <v>76.55679571170573</v>
+        <v>76.30585323603125</v>
       </c>
       <c r="S11" t="n">
-        <v>9335421.060694015</v>
+        <v>9400003.515221879</v>
       </c>
       <c r="T11" t="n">
-        <v>79.17320622327878</v>
+        <v>79.02398164528969</v>
       </c>
       <c r="U11" t="n">
-        <v>26.96886702049241</v>
+        <v>27.16231583861615</v>
       </c>
       <c r="V11" t="n">
-        <v>180.7552091011843</v>
+        <v>180.7869450587253</v>
       </c>
       <c r="W11" t="n">
-        <v>1.904880460956312</v>
+        <v>2.008348813209494</v>
       </c>
       <c r="X11" t="n">
-        <v>78.70829709076612</v>
+        <v>78.72997100594623</v>
       </c>
       <c r="Y11" t="n">
-        <v>20010981.16000786</v>
+        <v>20172007.15022851</v>
       </c>
       <c r="Z11" t="n">
-        <v>81.61007420512064</v>
+        <v>81.55250380854096</v>
       </c>
     </row>
     <row r="12">
@@ -1373,76 +1373,76 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>27.07407407407407</v>
       </c>
       <c r="D12" t="n">
-        <v>182.2539682539683</v>
+        <v>182.1604938271605</v>
       </c>
       <c r="E12" t="n">
-        <v>1.388888888888889</v>
+        <v>1.41358024691358</v>
       </c>
       <c r="F12" t="n">
-        <v>75.03968253968254</v>
+        <v>75.2037037037037</v>
       </c>
       <c r="G12" t="n">
-        <v>8103174.603174603</v>
+        <v>8313580.246913578</v>
       </c>
       <c r="H12" t="n">
-        <v>78.16507936507936</v>
+        <v>78.30123456790122</v>
       </c>
       <c r="I12" t="n">
-        <v>22.49007936507936</v>
+        <v>22.925</v>
       </c>
       <c r="J12" t="n">
-        <v>181.2103174603174</v>
+        <v>181.5819444444444</v>
       </c>
       <c r="K12" t="n">
-        <v>1.10515873015873</v>
+        <v>1.134722222222222</v>
       </c>
       <c r="L12" t="n">
-        <v>71.04761904761905</v>
+        <v>71.63333333333333</v>
       </c>
       <c r="M12" t="n">
-        <v>9051468.253968254</v>
+        <v>9446666.666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>77.32936507936508</v>
+        <v>77.25277777777778</v>
       </c>
       <c r="O12" t="n">
-        <v>25.30606060606061</v>
+        <v>25.47484848484849</v>
       </c>
       <c r="P12" t="n">
-        <v>180.0204816017316</v>
+        <v>180.1052741702742</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.191044372294372</v>
+        <v>1.162835497835498</v>
       </c>
       <c r="R12" t="n">
-        <v>73.72873376623377</v>
+        <v>73.58965367965368</v>
       </c>
       <c r="S12" t="n">
-        <v>6829829.545454545</v>
+        <v>6629696.96969697</v>
       </c>
       <c r="T12" t="n">
-        <v>77.36168831168831</v>
+        <v>76.97379509379509</v>
       </c>
       <c r="U12" t="n">
-        <v>24.06839114832535</v>
+        <v>23.76410067869398</v>
       </c>
       <c r="V12" t="n">
-        <v>180.5613397129187</v>
+        <v>180.3781718759709</v>
       </c>
       <c r="W12" t="n">
-        <v>1.088863636363636</v>
+        <v>1.064628099173554</v>
       </c>
       <c r="X12" t="n">
-        <v>71.26712918660286</v>
+        <v>70.95124395009562</v>
       </c>
       <c r="Y12" t="n">
-        <v>5610976.375598086</v>
+        <v>5228807.22812541</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.3475538277512</v>
+        <v>76.45144493465068</v>
       </c>
     </row>
     <row r="13">
@@ -1455,240 +1455,802 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>28.3</v>
+        <v>28.57333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>184.9385416666667</v>
+        <v>184.7841666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>2.04375</v>
+        <v>2.079444444444444</v>
       </c>
       <c r="F13" t="n">
-        <v>77.81041666666667</v>
+        <v>78.08166666666666</v>
       </c>
       <c r="G13" t="n">
-        <v>13975069.44444444</v>
+        <v>14353388.88888889</v>
       </c>
       <c r="H13" t="n">
-        <v>80.16354166666667</v>
+        <v>80.13083333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>26.22222222222222</v>
+        <v>26.69166666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>185.1064814814815</v>
+        <v>185.6166666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>1.518518518518519</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="L13" t="n">
-        <v>75.62037037037037</v>
+        <v>75.84166666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>9920833.333333334</v>
+        <v>9787222.222222222</v>
       </c>
       <c r="N13" t="n">
-        <v>78.84722222222223</v>
+        <v>78.84166666666667</v>
       </c>
       <c r="O13" t="n">
-        <v>25.41943703301305</v>
+        <v>25.37854479549257</v>
       </c>
       <c r="P13" t="n">
-        <v>183.3490060669577</v>
+        <v>183.5299294912473</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.627527551829275</v>
+        <v>1.629558273347478</v>
       </c>
       <c r="R13" t="n">
-        <v>75.61303539913295</v>
+        <v>75.69042831930636</v>
       </c>
       <c r="S13" t="n">
-        <v>11723820.80654535</v>
+        <v>11843066.30707203</v>
       </c>
       <c r="T13" t="n">
-        <v>80.07666880062476</v>
+        <v>80.09128673132106</v>
       </c>
       <c r="U13" t="n">
-        <v>27.91926645658264</v>
+        <v>27.69999649859944</v>
       </c>
       <c r="V13" t="n">
-        <v>183.1641104139024</v>
+        <v>183.2354549977886</v>
       </c>
       <c r="W13" t="n">
-        <v>1.644544265074451</v>
+        <v>1.644802078726227</v>
       </c>
       <c r="X13" t="n">
-        <v>76.55679571170573</v>
+        <v>76.30585323603125</v>
       </c>
       <c r="Y13" t="n">
-        <v>9335421.060694015</v>
+        <v>9400003.515221879</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.17320622327878</v>
+        <v>79.02398164528969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.33055555555556</v>
+        <v>27.41666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>182.7934027777778</v>
+        <v>183.4166666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>1.541666666666667</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>78.86006944444443</v>
+        <v>75.25</v>
       </c>
       <c r="G14" t="n">
-        <v>23348437.5</v>
+        <v>10925000</v>
       </c>
       <c r="H14" t="n">
-        <v>82.090625</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>25.82291666666667</v>
+        <v>27.74545454545455</v>
       </c>
       <c r="J14" t="n">
-        <v>181.9045138888889</v>
+        <v>183.3537190082644</v>
       </c>
       <c r="K14" t="n">
-        <v>2.703125</v>
+        <v>1.269421487603306</v>
       </c>
       <c r="L14" t="n">
-        <v>81.27951388888889</v>
+        <v>75.69338842975206</v>
       </c>
       <c r="M14" t="n">
-        <v>44854861.1111111</v>
+        <v>9326611.570247935</v>
       </c>
       <c r="N14" t="n">
-        <v>85.62326388888889</v>
+        <v>77.49090909090908</v>
       </c>
       <c r="O14" t="n">
-        <v>25.07173812706901</v>
+        <v>26.13074255990923</v>
       </c>
       <c r="P14" t="n">
-        <v>181.8265955245735</v>
+        <v>181.0787205078872</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.347175802139037</v>
+        <v>1.057850328683662</v>
       </c>
       <c r="R14" t="n">
-        <v>75.1245830150242</v>
+        <v>73.15174223924224</v>
       </c>
       <c r="S14" t="n">
-        <v>12794659.25006366</v>
+        <v>8064906.255010421</v>
       </c>
       <c r="T14" t="n">
-        <v>79.74682168321874</v>
+        <v>76.91481527731528</v>
       </c>
       <c r="U14" t="n">
-        <v>23.60959682638745</v>
+        <v>27.29139042775406</v>
       </c>
       <c r="V14" t="n">
-        <v>180.5017145857893</v>
+        <v>180.8754427390791</v>
       </c>
       <c r="W14" t="n">
-        <v>2.318392015116844</v>
+        <v>1.105099446008537</v>
       </c>
       <c r="X14" t="n">
-        <v>79.44544067679081</v>
+        <v>74.46884933248569</v>
       </c>
       <c r="Y14" t="n">
-        <v>40567152.92224303</v>
+        <v>7590431.386795023</v>
       </c>
       <c r="Z14" t="n">
-        <v>85.261088863463</v>
+        <v>76.58514213059667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.87361111111111</v>
+      </c>
+      <c r="D15" t="n">
+        <v>181.775</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.715277777777778</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>43920694.44444444</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85.49027777777778</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.20631313131313</v>
+      </c>
+      <c r="J15" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.478030303030303</v>
+      </c>
+      <c r="L15" t="n">
+        <v>78.86186868686868</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23356818.18181818</v>
+      </c>
+      <c r="N15" t="n">
+        <v>82.16363636363636</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23.46750939388307</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180.6559935173709</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.183285040664904</v>
+      </c>
+      <c r="R15" t="n">
+        <v>78.51349539857549</v>
+      </c>
+      <c r="S15" t="n">
+        <v>36364898.80838265</v>
+      </c>
+      <c r="T15" t="n">
+        <v>84.76769462018217</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.33190728321512</v>
+      </c>
+      <c r="V15" t="n">
+        <v>181.6462106869338</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.340570903172624</v>
+      </c>
+      <c r="X15" t="n">
+        <v>75.61980094229571</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13677224.33421806</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.89114879153243</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26.91666666666666</v>
+      </c>
+      <c r="D16" t="n">
+        <v>182.8777777777778</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.122222222222222</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71.95833333333334</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3914166.666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75.25833333333334</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25.84343434343434</v>
+      </c>
+      <c r="J16" t="n">
+        <v>181.5691919191919</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.698686868686869</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79.43323232323232</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25763181.81818182</v>
+      </c>
+      <c r="N16" t="n">
+        <v>82.44686868686868</v>
+      </c>
+      <c r="O16" t="n">
+        <v>27.23790339052287</v>
+      </c>
+      <c r="P16" t="n">
+        <v>179.7714282347554</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.090361216602026</v>
+      </c>
+      <c r="R16" t="n">
+        <v>71.40358461493572</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2888474.881939956</v>
+      </c>
+      <c r="T16" t="n">
+        <v>73.70217204670328</v>
+      </c>
+      <c r="U16" t="n">
+        <v>24.39584619486794</v>
+      </c>
+      <c r="V16" t="n">
+        <v>180.8557916117699</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.646155342242299</v>
+      </c>
+      <c r="X16" t="n">
+        <v>75.20563256791517</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15812387.8419286</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.07366318464145</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.28993055555555</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183.5694444444444</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.321180555555555</v>
+      </c>
+      <c r="F17" t="n">
+        <v>76.14409722222223</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12212456.59722222</v>
+      </c>
+      <c r="H17" t="n">
+        <v>79.30381944444444</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28.70694444444445</v>
+      </c>
+      <c r="J17" t="n">
+        <v>179.6513888888889</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.268055555555555</v>
+      </c>
+      <c r="L17" t="n">
+        <v>75.35277777777779</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6780972.222222222</v>
+      </c>
+      <c r="N17" t="n">
+        <v>76.55694444444445</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.67694444444444</v>
+      </c>
+      <c r="P17" t="n">
+        <v>184.7762301587302</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.096865079365079</v>
+      </c>
+      <c r="R17" t="n">
+        <v>72.03696428571429</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5435271.329365079</v>
+      </c>
+      <c r="T17" t="n">
+        <v>77.33422619047619</v>
+      </c>
+      <c r="U17" t="n">
+        <v>29.1236299081036</v>
+      </c>
+      <c r="V17" t="n">
+        <v>180.5778634085213</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.393653926482874</v>
+      </c>
+      <c r="X17" t="n">
+        <v>74.63693817878028</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5295762.635756057</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>75.45333124477861</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.50299873737374</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.7230113636363</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.787689393939394</v>
+      </c>
+      <c r="F18" t="n">
+        <v>83.56650883838384</v>
+      </c>
+      <c r="G18" t="n">
+        <v>63154198.23232324</v>
+      </c>
+      <c r="H18" t="n">
+        <v>87.18503787878788</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.9074074074074</v>
+      </c>
+      <c r="J18" t="n">
+        <v>180.0069444444445</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.189814814814815</v>
+      </c>
+      <c r="L18" t="n">
+        <v>70.3912037037037</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2919155.092592593</v>
+      </c>
+      <c r="N18" t="n">
+        <v>75.54398148148148</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25.13281690693971</v>
+      </c>
+      <c r="P18" t="n">
+        <v>179.9695843062071</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.832384111989375</v>
+      </c>
+      <c r="R18" t="n">
+        <v>82.99050600147092</v>
+      </c>
+      <c r="S18" t="n">
+        <v>63210719.4178466</v>
+      </c>
+      <c r="T18" t="n">
+        <v>87.23376773486423</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.91150027124292</v>
+      </c>
+      <c r="V18" t="n">
+        <v>180.617196583373</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.179574891339597</v>
+      </c>
+      <c r="X18" t="n">
+        <v>69.96502282439782</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2379828.495306436</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>74.48039418370301</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>179.6219135802469</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.027777777777778</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74.98456790123457</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10353395.0617284</v>
+      </c>
+      <c r="N19" t="n">
+        <v>78.64351851851853</v>
+      </c>
+      <c r="O19" t="n">
+        <v>26.18199269412505</v>
+      </c>
+      <c r="P19" t="n">
+        <v>181.7001773893318</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>67.97260641727554</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1721028.091427908</v>
+      </c>
+      <c r="T19" t="n">
+        <v>72.42437760360555</v>
+      </c>
+      <c r="U19" t="n">
+        <v>26.42893347936221</v>
+      </c>
+      <c r="V19" t="n">
+        <v>178.9630502086418</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.132251190053721</v>
+      </c>
+      <c r="X19" t="n">
+        <v>73.06551236554535</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5814538.363171356</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>75.27621899435871</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="H20" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27.78395061728395</v>
+      </c>
+      <c r="J20" t="n">
+        <v>182.037037037037</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.871913580246914</v>
+      </c>
+      <c r="L20" t="n">
+        <v>76.6141975308642</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12136728.39506173</v>
+      </c>
+      <c r="N20" t="n">
+        <v>78.90586419753087</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23.53052261747914</v>
+      </c>
+      <c r="P20" t="n">
+        <v>180.7263065436979</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>70.54598469163686</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3713771.174477696</v>
+      </c>
+      <c r="T20" t="n">
+        <v>76.28237656063743</v>
+      </c>
+      <c r="U20" t="n">
+        <v>28.1894246031746</v>
+      </c>
+      <c r="V20" t="n">
+        <v>183.5720833333333</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.023333333333333</v>
+      </c>
+      <c r="X20" t="n">
+        <v>75.9471626984127</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10458496.03174603</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>79.1536111111111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25.20631313131313</v>
+      </c>
+      <c r="D21" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.478030303030303</v>
+      </c>
+      <c r="F21" t="n">
+        <v>78.86186868686868</v>
+      </c>
+      <c r="G21" t="n">
+        <v>23356818.18181818</v>
+      </c>
+      <c r="H21" t="n">
+        <v>82.16363636363636</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25.87361111111111</v>
+      </c>
+      <c r="J21" t="n">
+        <v>181.775</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.715277777777778</v>
+      </c>
+      <c r="L21" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>43920694.44444444</v>
+      </c>
+      <c r="N21" t="n">
+        <v>85.49027777777778</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25.33190728321512</v>
+      </c>
+      <c r="P21" t="n">
+        <v>181.6462106869338</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.340570903172624</v>
+      </c>
+      <c r="R21" t="n">
+        <v>75.61980094229571</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13677224.33421806</v>
+      </c>
+      <c r="T21" t="n">
+        <v>79.89114879153243</v>
+      </c>
+      <c r="U21" t="n">
+        <v>23.46750939388307</v>
+      </c>
+      <c r="V21" t="n">
+        <v>180.6559935173709</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.183285040664904</v>
+      </c>
+      <c r="X21" t="n">
+        <v>78.51349539857549</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>36364898.80838265</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>84.76769462018217</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>25.46157407407408</v>
-      </c>
-      <c r="D15" t="n">
-        <v>181.8776515151515</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.829040404040404</v>
-      </c>
-      <c r="F15" t="n">
-        <v>83.26292087542087</v>
-      </c>
-      <c r="G15" t="n">
-        <v>62781355.21885522</v>
-      </c>
-      <c r="H15" t="n">
-        <v>87.10732323232325</v>
-      </c>
-      <c r="I15" t="n">
-        <v>27.81477272727273</v>
-      </c>
-      <c r="J15" t="n">
-        <v>182.9340909090909</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.285227272727273</v>
-      </c>
-      <c r="L15" t="n">
-        <v>75.8215909090909</v>
-      </c>
-      <c r="M15" t="n">
-        <v>9508863.636363637</v>
-      </c>
-      <c r="N15" t="n">
-        <v>77.61250000000001</v>
-      </c>
-      <c r="O15" t="n">
-        <v>25.10080790919606</v>
-      </c>
-      <c r="P15" t="n">
-        <v>180.1463379000385</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.853098792654714</v>
-      </c>
-      <c r="R15" t="n">
-        <v>83.29487480721033</v>
-      </c>
-      <c r="S15" t="n">
-        <v>65050253.78952187</v>
-      </c>
-      <c r="T15" t="n">
-        <v>87.42271092394448</v>
-      </c>
-      <c r="U15" t="n">
-        <v>27.22377622377623</v>
-      </c>
-      <c r="V15" t="n">
-        <v>181.0030594405594</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.114947552447553</v>
-      </c>
-      <c r="X15" t="n">
-        <v>74.51966783216783</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7759517.045454545</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>76.64991258741259</v>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.50299873737374</v>
+      </c>
+      <c r="D22" t="n">
+        <v>181.7230113636363</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.787689393939394</v>
+      </c>
+      <c r="F22" t="n">
+        <v>83.56650883838384</v>
+      </c>
+      <c r="G22" t="n">
+        <v>63154198.23232324</v>
+      </c>
+      <c r="H22" t="n">
+        <v>87.18503787878788</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27.74545454545455</v>
+      </c>
+      <c r="J22" t="n">
+        <v>183.3537190082644</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.269421487603306</v>
+      </c>
+      <c r="L22" t="n">
+        <v>75.69338842975206</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9326611.570247935</v>
+      </c>
+      <c r="N22" t="n">
+        <v>77.49090909090908</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25.13281690693971</v>
+      </c>
+      <c r="P22" t="n">
+        <v>179.9695843062071</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.832384111989375</v>
+      </c>
+      <c r="R22" t="n">
+        <v>82.99050600147092</v>
+      </c>
+      <c r="S22" t="n">
+        <v>63210719.4178466</v>
+      </c>
+      <c r="T22" t="n">
+        <v>87.23376773486423</v>
+      </c>
+      <c r="U22" t="n">
+        <v>27.29139042775406</v>
+      </c>
+      <c r="V22" t="n">
+        <v>180.8754427390791</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.105099446008537</v>
+      </c>
+      <c r="X22" t="n">
+        <v>74.46884933248569</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7590431.386795023</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>76.58514213059667</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1699 +558,2671 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.20631313131313</v>
+        <v>25.9074074074074</v>
       </c>
       <c r="D2" t="n">
-        <v>183.1111111111111</v>
+        <v>180.0069444444445</v>
       </c>
       <c r="E2" t="n">
-        <v>1.478030303030303</v>
+        <v>1.189814814814815</v>
       </c>
       <c r="F2" t="n">
-        <v>78.86186868686868</v>
+        <v>70.3912037037037</v>
       </c>
       <c r="G2" t="n">
-        <v>23356818.18181818</v>
+        <v>2919155.092592593</v>
       </c>
       <c r="H2" t="n">
-        <v>82.16363636363636</v>
+        <v>75.54398148148148</v>
       </c>
       <c r="I2" t="n">
-        <v>26.28993055555555</v>
+        <v>27.08333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>183.5694444444444</v>
+        <v>182.8159722222222</v>
       </c>
       <c r="K2" t="n">
-        <v>1.321180555555555</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>76.14409722222223</v>
+        <v>71.88541666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>12212456.59722222</v>
+        <v>3805208.333333333</v>
       </c>
       <c r="N2" t="n">
-        <v>79.30381944444444</v>
+        <v>75.07291666666667</v>
       </c>
       <c r="O2" t="n">
-        <v>25.33190728321512</v>
+        <v>25.81254575044682</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6462106869338</v>
+        <v>180.4525261429004</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.340570903172624</v>
+        <v>1.169925855487353</v>
       </c>
       <c r="R2" t="n">
-        <v>75.61980094229571</v>
+        <v>69.87093399025217</v>
       </c>
       <c r="S2" t="n">
-        <v>13677224.33421806</v>
+        <v>2364033.683191437</v>
       </c>
       <c r="T2" t="n">
-        <v>79.89114879153243</v>
+        <v>74.43315729131237</v>
       </c>
       <c r="U2" t="n">
-        <v>24.67694444444444</v>
+        <v>27.27598583877996</v>
       </c>
       <c r="V2" t="n">
-        <v>184.7762301587302</v>
+        <v>179.6228567837391</v>
       </c>
       <c r="W2" t="n">
-        <v>1.096865079365079</v>
+        <v>1.085274186597716</v>
       </c>
       <c r="X2" t="n">
-        <v>72.03696428571429</v>
+        <v>71.47493470037588</v>
       </c>
       <c r="Y2" t="n">
-        <v>5435271.329365079</v>
+        <v>2935484.31851373</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.33422619047619</v>
+        <v>73.7378724053724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27.78395061728395</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>182.037037037037</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="E3" t="n">
-        <v>1.871913580246914</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>76.6141975308642</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>12136728.39506173</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="H3" t="n">
-        <v>78.90586419753087</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="I3" t="n">
-        <v>25.12666666666667</v>
+        <v>28.59876543209877</v>
       </c>
       <c r="J3" t="n">
-        <v>181.6877777777778</v>
+        <v>179.9027777777778</v>
       </c>
       <c r="K3" t="n">
-        <v>1.353333333333333</v>
+        <v>2.439814814814815</v>
       </c>
       <c r="L3" t="n">
-        <v>78.54888888888888</v>
+        <v>82.20833333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>24666444.44444444</v>
+        <v>33334104.9382716</v>
       </c>
       <c r="N3" t="n">
-        <v>82.65777777777778</v>
+        <v>83.73456790123457</v>
       </c>
       <c r="O3" t="n">
-        <v>28.1894246031746</v>
+        <v>27.90740351696234</v>
       </c>
       <c r="P3" t="n">
-        <v>183.5720833333333</v>
+        <v>183.1319870345799</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.023333333333333</v>
+        <v>1.642372680066178</v>
       </c>
       <c r="R3" t="n">
-        <v>75.9471626984127</v>
+        <v>76.54354063262731</v>
       </c>
       <c r="S3" t="n">
-        <v>10458496.03174603</v>
+        <v>9359263.165061347</v>
       </c>
       <c r="T3" t="n">
-        <v>79.1536111111111</v>
+        <v>79.00812775402558</v>
       </c>
       <c r="U3" t="n">
-        <v>23.86767761795794</v>
+        <v>27.15565957377103</v>
       </c>
       <c r="V3" t="n">
-        <v>179.5817810831426</v>
+        <v>180.7879636454972</v>
       </c>
       <c r="W3" t="n">
-        <v>1.129103873814972</v>
+        <v>1.959893743072278</v>
       </c>
       <c r="X3" t="n">
-        <v>74.76543069630597</v>
+        <v>78.77404185845879</v>
       </c>
       <c r="Y3" t="n">
-        <v>14949427.48174785</v>
+        <v>19966427.69778477</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.84180941484145</v>
+        <v>81.56451040455168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.07407407407407</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="D4" t="n">
-        <v>182.1604938271605</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="E4" t="n">
-        <v>1.41358024691358</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="F4" t="n">
-        <v>75.2037037037037</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="G4" t="n">
-        <v>8313580.246913578</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="H4" t="n">
-        <v>78.30123456790122</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="I4" t="n">
-        <v>23.64814814814815</v>
+        <v>22.65</v>
       </c>
       <c r="J4" t="n">
-        <v>182.0972222222223</v>
+        <v>181.5194444444444</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="L4" t="n">
-        <v>71.25462962962963</v>
+        <v>71.55833333333332</v>
       </c>
       <c r="M4" t="n">
-        <v>4062500</v>
+        <v>9487916.666666666</v>
       </c>
       <c r="N4" t="n">
-        <v>77.19907407407408</v>
+        <v>77.56527777777778</v>
       </c>
       <c r="O4" t="n">
-        <v>25.47484848484849</v>
+        <v>25.42484848484849</v>
       </c>
       <c r="P4" t="n">
-        <v>180.1052741702742</v>
+        <v>180.1719408369408</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.162835497835498</v>
+        <v>1.190613275613276</v>
       </c>
       <c r="R4" t="n">
-        <v>73.58965367965368</v>
+        <v>73.70076479076479</v>
       </c>
       <c r="S4" t="n">
-        <v>6629696.96969697</v>
+        <v>7235113.636363636</v>
       </c>
       <c r="T4" t="n">
-        <v>76.97379509379509</v>
+        <v>77.20712842712842</v>
       </c>
       <c r="U4" t="n">
-        <v>23.53052261747914</v>
+        <v>23.81081785041115</v>
       </c>
       <c r="V4" t="n">
-        <v>180.7263065436979</v>
+        <v>180.1849900577891</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.070309917355372</v>
       </c>
       <c r="X4" t="n">
-        <v>70.54598469163686</v>
+        <v>70.76879445514614</v>
       </c>
       <c r="Y4" t="n">
-        <v>3713771.174477696</v>
+        <v>5187711.899842582</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.28237656063743</v>
+        <v>76.25636917707492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.91666666666667</v>
+        <v>28.06222222222222</v>
       </c>
       <c r="D5" t="n">
-        <v>179.6219135802469</v>
+        <v>185.0286111111111</v>
       </c>
       <c r="E5" t="n">
-        <v>1.027777777777778</v>
+        <v>1.990555555555555</v>
       </c>
       <c r="F5" t="n">
-        <v>74.98456790123457</v>
+        <v>77.65944444444445</v>
       </c>
       <c r="G5" t="n">
-        <v>10353395.0617284</v>
+        <v>13911166.66666667</v>
       </c>
       <c r="H5" t="n">
-        <v>78.64351851851853</v>
+        <v>80.0975</v>
       </c>
       <c r="I5" t="n">
-        <v>28.57333333333333</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="J5" t="n">
-        <v>184.7841666666667</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="K5" t="n">
-        <v>2.079444444444444</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>78.08166666666666</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="M5" t="n">
-        <v>14353388.88888889</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="N5" t="n">
-        <v>80.13083333333334</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="O5" t="n">
-        <v>26.42893347936221</v>
+        <v>25.56743368438146</v>
       </c>
       <c r="P5" t="n">
-        <v>178.9630502086418</v>
+        <v>182.996596157914</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.132251190053721</v>
+        <v>1.640669384458589</v>
       </c>
       <c r="R5" t="n">
-        <v>73.06551236554535</v>
+        <v>75.67931720819526</v>
       </c>
       <c r="S5" t="n">
-        <v>5814538.363171356</v>
+        <v>11720844.08484981</v>
       </c>
       <c r="T5" t="n">
-        <v>75.27621899435871</v>
+        <v>80.21350895354327</v>
       </c>
       <c r="U5" t="n">
-        <v>25.37854479549257</v>
+        <v>27.90740351696234</v>
       </c>
       <c r="V5" t="n">
-        <v>183.5299294912473</v>
+        <v>183.1319870345799</v>
       </c>
       <c r="W5" t="n">
-        <v>1.629558273347478</v>
+        <v>1.642372680066178</v>
       </c>
       <c r="X5" t="n">
-        <v>75.69042831930636</v>
+        <v>76.54354063262731</v>
       </c>
       <c r="Y5" t="n">
-        <v>11843066.30707203</v>
+        <v>9359263.165061347</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.09128673132106</v>
+        <v>79.00812775402558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>27.41666666666667</v>
+        <v>26.8125</v>
       </c>
       <c r="D6" t="n">
-        <v>183.4166666666667</v>
+        <v>182.4375</v>
       </c>
       <c r="E6" t="n">
-        <v>1.166666666666667</v>
+        <v>1.1875</v>
       </c>
       <c r="F6" t="n">
-        <v>75.25</v>
+        <v>74.4375</v>
       </c>
       <c r="G6" t="n">
-        <v>10925000</v>
+        <v>10537500</v>
       </c>
       <c r="H6" t="n">
-        <v>77.83333333333333</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>77.875</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27.74242424242425</v>
+      </c>
+      <c r="J6" t="n">
+        <v>183.4183654729109</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.281542699724518</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75.81662075298438</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9759742.883379249</v>
+      </c>
+      <c r="N6" t="n">
+        <v>77.65858585858585</v>
+      </c>
       <c r="O6" t="n">
-        <v>26.13074255990923</v>
+        <v>26.0051683039183</v>
       </c>
       <c r="P6" t="n">
-        <v>181.0787205078872</v>
+        <v>180.7583484570985</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.057850328683662</v>
+        <v>1.052065295815296</v>
       </c>
       <c r="R6" t="n">
-        <v>73.15174223924224</v>
+        <v>73.06781801531801</v>
       </c>
       <c r="S6" t="n">
-        <v>8064906.255010421</v>
+        <v>8045446.87950938</v>
       </c>
       <c r="T6" t="n">
-        <v>76.91481527731528</v>
+        <v>77.04208374958375</v>
       </c>
       <c r="U6" t="n">
-        <v>26.18199269412505</v>
+        <v>27.13480060609247</v>
       </c>
       <c r="V6" t="n">
-        <v>181.7001773893318</v>
+        <v>181.1055427825763</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.101619672193835</v>
       </c>
       <c r="X6" t="n">
-        <v>67.97260641727554</v>
+        <v>74.44492588750963</v>
       </c>
       <c r="Y6" t="n">
-        <v>1721028.091427908</v>
+        <v>7526368.750866359</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.42437760360555</v>
+        <v>76.6142852362948</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.925</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="D7" t="n">
-        <v>181.5819444444444</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="E7" t="n">
-        <v>1.134722222222222</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>71.63333333333333</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="G7" t="n">
-        <v>9446666.666666666</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="H7" t="n">
-        <v>77.25277777777778</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="I7" t="n">
-        <v>25.87361111111111</v>
+        <v>25.33383838383838</v>
       </c>
       <c r="J7" t="n">
-        <v>181.775</v>
+        <v>183.270202020202</v>
       </c>
       <c r="K7" t="n">
-        <v>2.715277777777778</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="L7" t="n">
-        <v>81.15000000000001</v>
+        <v>78.66742424242423</v>
       </c>
       <c r="M7" t="n">
-        <v>43920694.44444444</v>
+        <v>22654797.97979798</v>
       </c>
       <c r="N7" t="n">
-        <v>85.49027777777778</v>
+        <v>81.9729797979798</v>
       </c>
       <c r="O7" t="n">
-        <v>23.76410067869398</v>
+        <v>23.21304510816878</v>
       </c>
       <c r="P7" t="n">
-        <v>180.3781718759709</v>
+        <v>180.7381363745138</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.064628099173554</v>
+        <v>2.223463612093475</v>
       </c>
       <c r="R7" t="n">
-        <v>70.95124395009562</v>
+        <v>78.53135254143265</v>
       </c>
       <c r="S7" t="n">
-        <v>5228807.22812541</v>
+        <v>38380836.30838265</v>
       </c>
       <c r="T7" t="n">
-        <v>76.45144493465068</v>
+        <v>84.88019462018217</v>
       </c>
       <c r="U7" t="n">
-        <v>23.46750939388307</v>
+        <v>25.2314288143156</v>
       </c>
       <c r="V7" t="n">
-        <v>180.6559935173709</v>
+        <v>181.6767130792783</v>
       </c>
       <c r="W7" t="n">
-        <v>2.183285040664904</v>
+        <v>1.372269467765925</v>
       </c>
       <c r="X7" t="n">
-        <v>78.51349539857549</v>
+        <v>75.65688228200862</v>
       </c>
       <c r="Y7" t="n">
-        <v>36364898.80838265</v>
+        <v>13939784.1428305</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.76769462018217</v>
+        <v>80.02033539440323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.84343434343434</v>
+        <v>27.08333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>181.5691919191919</v>
+        <v>182.8159722222222</v>
       </c>
       <c r="E8" t="n">
-        <v>1.698686868686869</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="F8" t="n">
-        <v>79.43323232323232</v>
+        <v>71.88541666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>25763181.81818182</v>
+        <v>3805208.333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>82.44686868686868</v>
+        <v>75.07291666666667</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70694444444445</v>
+        <v>25.77777777777778</v>
       </c>
       <c r="J8" t="n">
-        <v>179.6513888888889</v>
+        <v>181.6055555555556</v>
       </c>
       <c r="K8" t="n">
-        <v>1.268055555555555</v>
+        <v>1.705757575757576</v>
       </c>
       <c r="L8" t="n">
-        <v>75.35277777777779</v>
+        <v>79.09080808080807</v>
       </c>
       <c r="M8" t="n">
-        <v>6780972.222222222</v>
+        <v>24896010.1010101</v>
       </c>
       <c r="N8" t="n">
-        <v>76.55694444444445</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>24.39584619486794</v>
+        <v>27.27598583877996</v>
       </c>
       <c r="P8" t="n">
-        <v>180.8557916117699</v>
+        <v>179.6228567837391</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.646155342242299</v>
+        <v>1.085274186597716</v>
       </c>
       <c r="R8" t="n">
-        <v>75.20563256791517</v>
+        <v>71.47493470037588</v>
       </c>
       <c r="S8" t="n">
-        <v>15812387.8419286</v>
+        <v>2935484.31851373</v>
       </c>
       <c r="T8" t="n">
-        <v>80.07366318464145</v>
+        <v>73.7378724053724</v>
       </c>
       <c r="U8" t="n">
-        <v>29.1236299081036</v>
+        <v>24.33056841709016</v>
       </c>
       <c r="V8" t="n">
-        <v>180.5778634085213</v>
+        <v>180.5030138339921</v>
       </c>
       <c r="W8" t="n">
-        <v>1.393653926482874</v>
+        <v>1.639210897797855</v>
       </c>
       <c r="X8" t="n">
-        <v>74.63693817878028</v>
+        <v>75.37785479013739</v>
       </c>
       <c r="Y8" t="n">
-        <v>5295762.635756057</v>
+        <v>16504748.95303971</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.45333124477861</v>
+        <v>80.29241318464145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.74545454545455</v>
+        <v>26.34413580246913</v>
       </c>
       <c r="D9" t="n">
-        <v>183.3537190082644</v>
+        <v>183.1604938271605</v>
       </c>
       <c r="E9" t="n">
-        <v>1.269421487603306</v>
+        <v>1.322530864197531</v>
       </c>
       <c r="F9" t="n">
-        <v>75.69338842975206</v>
+        <v>75.97993827160494</v>
       </c>
       <c r="G9" t="n">
-        <v>9326611.570247935</v>
+        <v>11894714.50617284</v>
       </c>
       <c r="H9" t="n">
-        <v>77.49090909090908</v>
+        <v>79.08487654320987</v>
       </c>
       <c r="I9" t="n">
-        <v>25.50299873737374</v>
+        <v>28.73055555555555</v>
       </c>
       <c r="J9" t="n">
-        <v>181.7230113636363</v>
+        <v>179.5638888888889</v>
       </c>
       <c r="K9" t="n">
-        <v>2.787689393939394</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>83.56650883838384</v>
+        <v>75.32083333333334</v>
       </c>
       <c r="M9" t="n">
-        <v>63154198.23232324</v>
+        <v>6703055.555555555</v>
       </c>
       <c r="N9" t="n">
-        <v>87.18503787878788</v>
+        <v>76.56527777777778</v>
       </c>
       <c r="O9" t="n">
-        <v>27.29139042775406</v>
+        <v>24.49551587301588</v>
       </c>
       <c r="P9" t="n">
-        <v>180.8754427390791</v>
+        <v>184.1648015873016</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.105099446008537</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="R9" t="n">
-        <v>74.46884933248569</v>
+        <v>71.97553571428571</v>
       </c>
       <c r="S9" t="n">
-        <v>7590431.386795023</v>
+        <v>5478414.186507936</v>
       </c>
       <c r="T9" t="n">
-        <v>76.58514213059667</v>
+        <v>77.42136904761905</v>
       </c>
       <c r="U9" t="n">
-        <v>25.13281690693971</v>
+        <v>28.85886800334168</v>
       </c>
       <c r="V9" t="n">
-        <v>179.9695843062071</v>
+        <v>180.164530075188</v>
       </c>
       <c r="W9" t="n">
-        <v>2.832384111989375</v>
+        <v>1.34984440267335</v>
       </c>
       <c r="X9" t="n">
-        <v>82.99050600147092</v>
+        <v>74.55217627401836</v>
       </c>
       <c r="Y9" t="n">
-        <v>63210719.4178466</v>
+        <v>5359476.921470342</v>
       </c>
       <c r="Z9" t="n">
-        <v>87.23376773486423</v>
+        <v>75.46285505430242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D10" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F10" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G10" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H10" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I10" t="n">
         <v>25.9074074074074</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>180.0069444444445</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>1.189814814814815</v>
       </c>
-      <c r="F10" t="n">
+      <c r="L10" t="n">
         <v>70.3912037037037</v>
       </c>
-      <c r="G10" t="n">
+      <c r="M10" t="n">
         <v>2919155.092592593</v>
       </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
         <v>75.54398148148148</v>
       </c>
-      <c r="I10" t="n">
-        <v>26.91666666666666</v>
-      </c>
-      <c r="J10" t="n">
-        <v>182.8777777777778</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.122222222222222</v>
-      </c>
-      <c r="L10" t="n">
-        <v>71.95833333333334</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3914166.666666667</v>
-      </c>
-      <c r="N10" t="n">
-        <v>75.25833333333334</v>
-      </c>
       <c r="O10" t="n">
-        <v>25.91150027124292</v>
+        <v>25.07216679519311</v>
       </c>
       <c r="P10" t="n">
-        <v>180.617196583373</v>
+        <v>179.6831521913759</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.179574891339597</v>
+        <v>2.754408858685175</v>
       </c>
       <c r="R10" t="n">
-        <v>69.96502282439782</v>
+        <v>82.48092908553436</v>
       </c>
       <c r="S10" t="n">
-        <v>2379828.495306436</v>
+        <v>60388463.26553564</v>
       </c>
       <c r="T10" t="n">
-        <v>74.48039418370301</v>
+        <v>86.84723306664095</v>
       </c>
       <c r="U10" t="n">
-        <v>27.23790339052287</v>
+        <v>25.81254575044682</v>
       </c>
       <c r="V10" t="n">
-        <v>179.7714282347554</v>
+        <v>180.4525261429004</v>
       </c>
       <c r="W10" t="n">
-        <v>1.090361216602026</v>
+        <v>1.169925855487353</v>
       </c>
       <c r="X10" t="n">
-        <v>71.40358461493572</v>
+        <v>69.87093399025217</v>
       </c>
       <c r="Y10" t="n">
-        <v>2888474.881939956</v>
+        <v>2364033.683191437</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.70217204670328</v>
+        <v>74.43315729131237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
-        <v>26.69166666666667</v>
-      </c>
-      <c r="D11" t="n">
-        <v>185.6166666666667</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.541666666666667</v>
-      </c>
-      <c r="F11" t="n">
-        <v>75.84166666666667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9787222.222222222</v>
-      </c>
-      <c r="H11" t="n">
-        <v>78.84166666666667</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>28.59876543209877</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="J11" t="n">
-        <v>179.9027777777778</v>
+        <v>179.671875</v>
       </c>
       <c r="K11" t="n">
-        <v>2.439814814814815</v>
+        <v>1.03125</v>
       </c>
       <c r="L11" t="n">
-        <v>82.20833333333333</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="M11" t="n">
-        <v>33334104.9382716</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="N11" t="n">
-        <v>83.73456790123457</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="O11" t="n">
-        <v>27.69999649859944</v>
+        <v>26.20995322044084</v>
       </c>
       <c r="P11" t="n">
-        <v>183.2354549977886</v>
+        <v>181.8257256349458</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.644802078726227</v>
+        <v>1.004385964912281</v>
       </c>
       <c r="R11" t="n">
-        <v>76.30585323603125</v>
+        <v>68.38324238218782</v>
       </c>
       <c r="S11" t="n">
-        <v>9400003.515221879</v>
+        <v>2025701.885287557</v>
       </c>
       <c r="T11" t="n">
-        <v>79.02398164528969</v>
+        <v>72.72207497202659</v>
       </c>
       <c r="U11" t="n">
-        <v>27.16231583861615</v>
+        <v>26.25620620663493</v>
       </c>
       <c r="V11" t="n">
-        <v>180.7869450587253</v>
+        <v>178.6930502086418</v>
       </c>
       <c r="W11" t="n">
-        <v>2.008348813209494</v>
+        <v>1.13134209914463</v>
       </c>
       <c r="X11" t="n">
-        <v>78.72997100594623</v>
+        <v>73.17096691099989</v>
       </c>
       <c r="Y11" t="n">
-        <v>20172007.15022851</v>
+        <v>6018265.635898629</v>
       </c>
       <c r="Z11" t="n">
-        <v>81.55250380854096</v>
+        <v>75.4571280852678</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>27.07407407407407</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="D12" t="n">
-        <v>182.1604938271605</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="E12" t="n">
-        <v>1.41358024691358</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>75.2037037037037</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="G12" t="n">
-        <v>8313580.246913578</v>
+        <v>4062500</v>
       </c>
       <c r="H12" t="n">
-        <v>78.30123456790122</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="I12" t="n">
-        <v>22.925</v>
+        <v>27.86631944444444</v>
       </c>
       <c r="J12" t="n">
-        <v>181.5819444444444</v>
+        <v>181.9479166666667</v>
       </c>
       <c r="K12" t="n">
-        <v>1.134722222222222</v>
+        <v>1.887152777777778</v>
       </c>
       <c r="L12" t="n">
-        <v>71.63333333333333</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="M12" t="n">
-        <v>9446666.666666666</v>
+        <v>11931944.44444444</v>
       </c>
       <c r="N12" t="n">
-        <v>77.25277777777778</v>
+        <v>78.83159722222223</v>
       </c>
       <c r="O12" t="n">
-        <v>25.47484848484849</v>
+        <v>23.60128285139727</v>
       </c>
       <c r="P12" t="n">
-        <v>180.1052741702742</v>
+        <v>180.8280609296627</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.162835497835498</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>73.58965367965368</v>
+        <v>70.67347007175383</v>
       </c>
       <c r="S12" t="n">
-        <v>6629696.96969697</v>
+        <v>3797718.542898749</v>
       </c>
       <c r="T12" t="n">
-        <v>76.97379509379509</v>
+        <v>76.33266895829824</v>
       </c>
       <c r="U12" t="n">
-        <v>23.76410067869398</v>
+        <v>27.65425976800977</v>
       </c>
       <c r="V12" t="n">
-        <v>180.3781718759709</v>
+        <v>183.4720833333333</v>
       </c>
       <c r="W12" t="n">
-        <v>1.064628099173554</v>
+        <v>1.954102564102564</v>
       </c>
       <c r="X12" t="n">
-        <v>70.95124395009562</v>
+        <v>75.75265720390721</v>
       </c>
       <c r="Y12" t="n">
-        <v>5228807.22812541</v>
+        <v>10349814.71306472</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.45144493465068</v>
+        <v>79.18877594627595</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>28.57333333333333</v>
+        <v>28.59876543209877</v>
       </c>
       <c r="D13" t="n">
-        <v>184.7841666666667</v>
+        <v>179.9027777777778</v>
       </c>
       <c r="E13" t="n">
-        <v>2.079444444444444</v>
+        <v>2.439814814814815</v>
       </c>
       <c r="F13" t="n">
-        <v>78.08166666666666</v>
+        <v>82.20833333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>14353388.88888889</v>
+        <v>33334104.9382716</v>
       </c>
       <c r="H13" t="n">
-        <v>80.13083333333334</v>
+        <v>83.73456790123457</v>
       </c>
       <c r="I13" t="n">
-        <v>26.69166666666667</v>
+        <v>25.1225</v>
       </c>
       <c r="J13" t="n">
-        <v>185.6166666666667</v>
+        <v>182.185</v>
       </c>
       <c r="K13" t="n">
-        <v>1.541666666666667</v>
+        <v>1.345</v>
       </c>
       <c r="L13" t="n">
-        <v>75.84166666666667</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>9787222.222222222</v>
+        <v>24073250</v>
       </c>
       <c r="N13" t="n">
-        <v>78.84166666666667</v>
+        <v>82.5175</v>
       </c>
       <c r="O13" t="n">
-        <v>25.37854479549257</v>
+        <v>27.15565957377103</v>
       </c>
       <c r="P13" t="n">
-        <v>183.5299294912473</v>
+        <v>180.7879636454972</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.629558273347478</v>
+        <v>1.959893743072278</v>
       </c>
       <c r="R13" t="n">
-        <v>75.69042831930636</v>
+        <v>78.77404185845879</v>
       </c>
       <c r="S13" t="n">
-        <v>11843066.30707203</v>
+        <v>19966427.69778477</v>
       </c>
       <c r="T13" t="n">
-        <v>80.09128673132106</v>
+        <v>81.56451040455168</v>
       </c>
       <c r="U13" t="n">
-        <v>27.69999649859944</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="V13" t="n">
-        <v>183.2354549977886</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="W13" t="n">
-        <v>1.644802078726227</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="X13" t="n">
-        <v>76.30585323603125</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="Y13" t="n">
-        <v>9400003.515221879</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.02398164528969</v>
+        <v>80.79895227198431</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>27.41666666666667</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="D14" t="n">
-        <v>183.4166666666667</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="E14" t="n">
-        <v>1.166666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>75.25</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>10925000</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="H14" t="n">
-        <v>77.83333333333333</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="I14" t="n">
-        <v>27.74545454545455</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="J14" t="n">
-        <v>183.3537190082644</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="K14" t="n">
-        <v>1.269421487603306</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="L14" t="n">
-        <v>75.69338842975206</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="M14" t="n">
-        <v>9326611.570247935</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="N14" t="n">
-        <v>77.49090909090908</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="O14" t="n">
-        <v>26.13074255990923</v>
+        <v>27.90740351696234</v>
       </c>
       <c r="P14" t="n">
-        <v>181.0787205078872</v>
+        <v>183.1319870345799</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.057850328683662</v>
+        <v>1.642372680066178</v>
       </c>
       <c r="R14" t="n">
-        <v>73.15174223924224</v>
+        <v>76.54354063262731</v>
       </c>
       <c r="S14" t="n">
-        <v>8064906.255010421</v>
+        <v>9359263.165061347</v>
       </c>
       <c r="T14" t="n">
-        <v>76.91481527731528</v>
+        <v>79.00812775402558</v>
       </c>
       <c r="U14" t="n">
-        <v>27.29139042775406</v>
+        <v>25.42484848484849</v>
       </c>
       <c r="V14" t="n">
-        <v>180.8754427390791</v>
+        <v>180.1719408369408</v>
       </c>
       <c r="W14" t="n">
-        <v>1.105099446008537</v>
+        <v>1.190613275613276</v>
       </c>
       <c r="X14" t="n">
-        <v>74.46884933248569</v>
+        <v>73.70076479076479</v>
       </c>
       <c r="Y14" t="n">
-        <v>7590431.386795023</v>
+        <v>7235113.636363636</v>
       </c>
       <c r="Z14" t="n">
-        <v>76.58514213059667</v>
+        <v>77.20712842712842</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.87361111111111</v>
+        <v>27.74242424242425</v>
       </c>
       <c r="D15" t="n">
-        <v>181.775</v>
+        <v>183.4183654729109</v>
       </c>
       <c r="E15" t="n">
-        <v>2.715277777777778</v>
+        <v>1.281542699724518</v>
       </c>
       <c r="F15" t="n">
-        <v>81.15000000000001</v>
+        <v>75.81662075298438</v>
       </c>
       <c r="G15" t="n">
-        <v>43920694.44444444</v>
+        <v>9759742.883379249</v>
       </c>
       <c r="H15" t="n">
-        <v>85.49027777777778</v>
+        <v>77.65858585858585</v>
       </c>
       <c r="I15" t="n">
-        <v>25.20631313131313</v>
+        <v>28.06222222222222</v>
       </c>
       <c r="J15" t="n">
-        <v>183.1111111111111</v>
+        <v>185.0286111111111</v>
       </c>
       <c r="K15" t="n">
-        <v>1.478030303030303</v>
+        <v>1.990555555555555</v>
       </c>
       <c r="L15" t="n">
-        <v>78.86186868686868</v>
+        <v>77.65944444444445</v>
       </c>
       <c r="M15" t="n">
-        <v>23356818.18181818</v>
+        <v>13911166.66666667</v>
       </c>
       <c r="N15" t="n">
-        <v>82.16363636363636</v>
+        <v>80.0975</v>
       </c>
       <c r="O15" t="n">
-        <v>23.46750939388307</v>
+        <v>27.13480060609247</v>
       </c>
       <c r="P15" t="n">
-        <v>180.6559935173709</v>
+        <v>181.1055427825763</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.183285040664904</v>
+        <v>1.101619672193835</v>
       </c>
       <c r="R15" t="n">
-        <v>78.51349539857549</v>
+        <v>74.44492588750963</v>
       </c>
       <c r="S15" t="n">
-        <v>36364898.80838265</v>
+        <v>7526368.750866359</v>
       </c>
       <c r="T15" t="n">
-        <v>84.76769462018217</v>
+        <v>76.6142852362948</v>
       </c>
       <c r="U15" t="n">
-        <v>25.33190728321512</v>
+        <v>25.56743368438146</v>
       </c>
       <c r="V15" t="n">
-        <v>181.6462106869338</v>
+        <v>182.996596157914</v>
       </c>
       <c r="W15" t="n">
-        <v>1.340570903172624</v>
+        <v>1.640669384458589</v>
       </c>
       <c r="X15" t="n">
-        <v>75.61980094229571</v>
+        <v>75.67931720819526</v>
       </c>
       <c r="Y15" t="n">
-        <v>13677224.33421806</v>
+        <v>11720844.08484981</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.89114879153243</v>
+        <v>80.21350895354327</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>26.91666666666666</v>
+        <v>28.73055555555555</v>
       </c>
       <c r="D16" t="n">
-        <v>182.8777777777778</v>
+        <v>179.5638888888889</v>
       </c>
       <c r="E16" t="n">
-        <v>1.122222222222222</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>71.95833333333334</v>
+        <v>75.32083333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>3914166.666666667</v>
+        <v>6703055.555555555</v>
       </c>
       <c r="H16" t="n">
-        <v>75.25833333333334</v>
+        <v>76.56527777777778</v>
       </c>
       <c r="I16" t="n">
-        <v>25.84343434343434</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="J16" t="n">
-        <v>181.5691919191919</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="K16" t="n">
-        <v>1.698686868686869</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="L16" t="n">
-        <v>79.43323232323232</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="M16" t="n">
-        <v>25763181.81818182</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="N16" t="n">
-        <v>82.44686868686868</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="O16" t="n">
-        <v>27.23790339052287</v>
+        <v>28.85886800334168</v>
       </c>
       <c r="P16" t="n">
-        <v>179.7714282347554</v>
+        <v>180.164530075188</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.090361216602026</v>
+        <v>1.34984440267335</v>
       </c>
       <c r="R16" t="n">
-        <v>71.40358461493572</v>
+        <v>74.55217627401836</v>
       </c>
       <c r="S16" t="n">
-        <v>2888474.881939956</v>
+        <v>5359476.921470342</v>
       </c>
       <c r="T16" t="n">
-        <v>73.70217204670328</v>
+        <v>75.46285505430242</v>
       </c>
       <c r="U16" t="n">
-        <v>24.39584619486794</v>
+        <v>23.21304510816878</v>
       </c>
       <c r="V16" t="n">
-        <v>180.8557916117699</v>
+        <v>180.7381363745138</v>
       </c>
       <c r="W16" t="n">
-        <v>1.646155342242299</v>
+        <v>2.223463612093475</v>
       </c>
       <c r="X16" t="n">
-        <v>75.20563256791517</v>
+        <v>78.53135254143265</v>
       </c>
       <c r="Y16" t="n">
-        <v>15812387.8419286</v>
+        <v>38380836.30838265</v>
       </c>
       <c r="Z16" t="n">
-        <v>80.07366318464145</v>
+        <v>84.88019462018217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.28993055555555</v>
+        <v>25.33383838383838</v>
       </c>
       <c r="D17" t="n">
-        <v>183.5694444444444</v>
+        <v>183.270202020202</v>
       </c>
       <c r="E17" t="n">
-        <v>1.321180555555555</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="F17" t="n">
-        <v>76.14409722222223</v>
+        <v>78.66742424242423</v>
       </c>
       <c r="G17" t="n">
-        <v>12212456.59722222</v>
+        <v>22654797.97979798</v>
       </c>
       <c r="H17" t="n">
-        <v>79.30381944444444</v>
+        <v>81.9729797979798</v>
       </c>
       <c r="I17" t="n">
-        <v>28.70694444444445</v>
+        <v>22.65</v>
       </c>
       <c r="J17" t="n">
-        <v>179.6513888888889</v>
+        <v>181.5194444444444</v>
       </c>
       <c r="K17" t="n">
-        <v>1.268055555555555</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="L17" t="n">
-        <v>75.35277777777779</v>
+        <v>71.55833333333332</v>
       </c>
       <c r="M17" t="n">
-        <v>6780972.222222222</v>
+        <v>9487916.666666666</v>
       </c>
       <c r="N17" t="n">
-        <v>76.55694444444445</v>
+        <v>77.56527777777778</v>
       </c>
       <c r="O17" t="n">
-        <v>24.67694444444444</v>
+        <v>25.2314288143156</v>
       </c>
       <c r="P17" t="n">
-        <v>184.7762301587302</v>
+        <v>181.6767130792783</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.096865079365079</v>
+        <v>1.372269467765925</v>
       </c>
       <c r="R17" t="n">
-        <v>72.03696428571429</v>
+        <v>75.65688228200862</v>
       </c>
       <c r="S17" t="n">
-        <v>5435271.329365079</v>
+        <v>13939784.1428305</v>
       </c>
       <c r="T17" t="n">
-        <v>77.33422619047619</v>
+        <v>80.02033539440323</v>
       </c>
       <c r="U17" t="n">
-        <v>29.1236299081036</v>
+        <v>23.81081785041115</v>
       </c>
       <c r="V17" t="n">
-        <v>180.5778634085213</v>
+        <v>180.1849900577891</v>
       </c>
       <c r="W17" t="n">
-        <v>1.393653926482874</v>
+        <v>1.070309917355372</v>
       </c>
       <c r="X17" t="n">
-        <v>74.63693817878028</v>
+        <v>70.76879445514614</v>
       </c>
       <c r="Y17" t="n">
-        <v>5295762.635756057</v>
+        <v>5187711.899842582</v>
       </c>
       <c r="Z17" t="n">
-        <v>75.45333124477861</v>
+        <v>76.25636917707492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.50299873737374</v>
+        <v>25.9074074074074</v>
       </c>
       <c r="D18" t="n">
-        <v>181.7230113636363</v>
+        <v>180.0069444444445</v>
       </c>
       <c r="E18" t="n">
-        <v>2.787689393939394</v>
+        <v>1.189814814814815</v>
       </c>
       <c r="F18" t="n">
-        <v>83.56650883838384</v>
+        <v>70.3912037037037</v>
       </c>
       <c r="G18" t="n">
-        <v>63154198.23232324</v>
+        <v>2919155.092592593</v>
       </c>
       <c r="H18" t="n">
-        <v>87.18503787878788</v>
-      </c>
-      <c r="I18" t="n">
-        <v>25.9074074074074</v>
-      </c>
-      <c r="J18" t="n">
-        <v>180.0069444444445</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.189814814814815</v>
-      </c>
-      <c r="L18" t="n">
-        <v>70.3912037037037</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2919155.092592593</v>
-      </c>
-      <c r="N18" t="n">
         <v>75.54398148148148</v>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>25.13281690693971</v>
+        <v>25.81254575044682</v>
       </c>
       <c r="P18" t="n">
-        <v>179.9695843062071</v>
+        <v>180.4525261429004</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.832384111989375</v>
+        <v>1.169925855487353</v>
       </c>
       <c r="R18" t="n">
-        <v>82.99050600147092</v>
+        <v>69.87093399025217</v>
       </c>
       <c r="S18" t="n">
-        <v>63210719.4178466</v>
+        <v>2364033.683191437</v>
       </c>
       <c r="T18" t="n">
-        <v>87.23376773486423</v>
+        <v>74.43315729131237</v>
       </c>
       <c r="U18" t="n">
-        <v>25.91150027124292</v>
+        <v>26.20995322044084</v>
       </c>
       <c r="V18" t="n">
-        <v>180.617196583373</v>
+        <v>181.8257256349458</v>
       </c>
       <c r="W18" t="n">
-        <v>1.179574891339597</v>
+        <v>1.004385964912281</v>
       </c>
       <c r="X18" t="n">
-        <v>69.96502282439782</v>
+        <v>68.38324238218782</v>
       </c>
       <c r="Y18" t="n">
-        <v>2379828.495306436</v>
+        <v>2025701.885287557</v>
       </c>
       <c r="Z18" t="n">
-        <v>74.48039418370301</v>
+        <v>72.72207497202659</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>28.59876543209877</v>
+      </c>
+      <c r="D19" t="n">
+        <v>179.9027777777778</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.439814814814815</v>
+      </c>
+      <c r="F19" t="n">
+        <v>82.20833333333333</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33334104.9382716</v>
+      </c>
+      <c r="H19" t="n">
+        <v>83.73456790123457</v>
+      </c>
       <c r="I19" t="n">
-        <v>24.91666666666667</v>
+        <v>27.08333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>179.6219135802469</v>
+        <v>182.8159722222222</v>
       </c>
       <c r="K19" t="n">
-        <v>1.027777777777778</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="L19" t="n">
-        <v>74.98456790123457</v>
+        <v>71.88541666666667</v>
       </c>
       <c r="M19" t="n">
-        <v>10353395.0617284</v>
+        <v>3805208.333333333</v>
       </c>
       <c r="N19" t="n">
-        <v>78.64351851851853</v>
+        <v>75.07291666666667</v>
       </c>
       <c r="O19" t="n">
-        <v>26.18199269412505</v>
+        <v>27.15565957377103</v>
       </c>
       <c r="P19" t="n">
-        <v>181.7001773893318</v>
+        <v>180.7879636454972</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>1.959893743072278</v>
       </c>
       <c r="R19" t="n">
-        <v>67.97260641727554</v>
+        <v>78.77404185845879</v>
       </c>
       <c r="S19" t="n">
-        <v>1721028.091427908</v>
+        <v>19966427.69778477</v>
       </c>
       <c r="T19" t="n">
-        <v>72.42437760360555</v>
+        <v>81.56451040455168</v>
       </c>
       <c r="U19" t="n">
-        <v>26.42893347936221</v>
+        <v>27.27598583877996</v>
       </c>
       <c r="V19" t="n">
-        <v>178.9630502086418</v>
+        <v>179.6228567837391</v>
       </c>
       <c r="W19" t="n">
-        <v>1.132251190053721</v>
+        <v>1.085274186597716</v>
       </c>
       <c r="X19" t="n">
-        <v>73.06551236554535</v>
+        <v>71.47493470037588</v>
       </c>
       <c r="Y19" t="n">
-        <v>5814538.363171356</v>
+        <v>2935484.31851373</v>
       </c>
       <c r="Z19" t="n">
-        <v>75.27621899435871</v>
+        <v>73.7378724053724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="D20" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="F20" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="H20" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="I20" t="n">
         <v>23.64814814814815</v>
       </c>
-      <c r="D20" t="n">
+      <c r="J20" t="n">
         <v>182.0972222222223</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>71.25462962962963</v>
       </c>
-      <c r="G20" t="n">
+      <c r="M20" t="n">
         <v>4062500</v>
       </c>
-      <c r="H20" t="n">
+      <c r="N20" t="n">
         <v>77.19907407407408</v>
       </c>
-      <c r="I20" t="n">
-        <v>27.78395061728395</v>
-      </c>
-      <c r="J20" t="n">
-        <v>182.037037037037</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.871913580246914</v>
-      </c>
-      <c r="L20" t="n">
-        <v>76.6141975308642</v>
-      </c>
-      <c r="M20" t="n">
-        <v>12136728.39506173</v>
-      </c>
-      <c r="N20" t="n">
-        <v>78.90586419753087</v>
-      </c>
       <c r="O20" t="n">
-        <v>23.53052261747914</v>
+        <v>24.33056841709016</v>
       </c>
       <c r="P20" t="n">
-        <v>180.7263065436979</v>
+        <v>180.5030138339921</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>1.639210897797855</v>
       </c>
       <c r="R20" t="n">
-        <v>70.54598469163686</v>
+        <v>75.37785479013739</v>
       </c>
       <c r="S20" t="n">
-        <v>3713771.174477696</v>
+        <v>16504748.95303971</v>
       </c>
       <c r="T20" t="n">
-        <v>76.28237656063743</v>
+        <v>80.29241318464145</v>
       </c>
       <c r="U20" t="n">
-        <v>28.1894246031746</v>
+        <v>23.60128285139727</v>
       </c>
       <c r="V20" t="n">
-        <v>183.5720833333333</v>
+        <v>180.8280609296627</v>
       </c>
       <c r="W20" t="n">
-        <v>2.023333333333333</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>75.9471626984127</v>
+        <v>70.67347007175383</v>
       </c>
       <c r="Y20" t="n">
-        <v>10458496.03174603</v>
+        <v>3797718.542898749</v>
       </c>
       <c r="Z20" t="n">
-        <v>79.1536111111111</v>
+        <v>76.33266895829824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>25.20631313131313</v>
+        <v>25.1225</v>
       </c>
       <c r="D21" t="n">
-        <v>183.1111111111111</v>
+        <v>182.185</v>
       </c>
       <c r="E21" t="n">
-        <v>1.478030303030303</v>
+        <v>1.345</v>
       </c>
       <c r="F21" t="n">
-        <v>78.86186868686868</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>23356818.18181818</v>
+        <v>24073250</v>
       </c>
       <c r="H21" t="n">
-        <v>82.16363636363636</v>
+        <v>82.5175</v>
       </c>
       <c r="I21" t="n">
-        <v>25.87361111111111</v>
+        <v>26.8125</v>
       </c>
       <c r="J21" t="n">
-        <v>181.775</v>
+        <v>182.4375</v>
       </c>
       <c r="K21" t="n">
-        <v>2.715277777777778</v>
+        <v>1.1875</v>
       </c>
       <c r="L21" t="n">
-        <v>81.15000000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="M21" t="n">
-        <v>43920694.44444444</v>
+        <v>10537500</v>
       </c>
       <c r="N21" t="n">
-        <v>85.49027777777778</v>
+        <v>77.875</v>
       </c>
       <c r="O21" t="n">
-        <v>25.33190728321512</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="P21" t="n">
-        <v>181.6462106869338</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.340570903172624</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="R21" t="n">
-        <v>75.61980094229571</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="S21" t="n">
-        <v>13677224.33421806</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="T21" t="n">
-        <v>79.89114879153243</v>
+        <v>80.79895227198431</v>
       </c>
       <c r="U21" t="n">
-        <v>23.46750939388307</v>
+        <v>26.0051683039183</v>
       </c>
       <c r="V21" t="n">
-        <v>180.6559935173709</v>
+        <v>180.7583484570985</v>
       </c>
       <c r="W21" t="n">
-        <v>2.183285040664904</v>
+        <v>1.052065295815296</v>
       </c>
       <c r="X21" t="n">
-        <v>78.51349539857549</v>
+        <v>73.06781801531801</v>
       </c>
       <c r="Y21" t="n">
-        <v>36364898.80838265</v>
+        <v>8045446.87950938</v>
       </c>
       <c r="Z21" t="n">
-        <v>84.76769462018217</v>
+        <v>77.04208374958375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24.97569444444444</v>
+      </c>
+      <c r="D22" t="n">
+        <v>179.671875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.03125</v>
+      </c>
+      <c r="F22" t="n">
+        <v>74.95486111111111</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10317013.88888889</v>
+      </c>
+      <c r="H22" t="n">
+        <v>78.54340277777777</v>
+      </c>
+      <c r="I22" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="J22" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="L22" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="M22" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="N22" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="O22" t="n">
+        <v>26.25620620663493</v>
+      </c>
+      <c r="P22" t="n">
+        <v>178.6930502086418</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.13134209914463</v>
+      </c>
+      <c r="R22" t="n">
+        <v>73.17096691099989</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6018265.635898629</v>
+      </c>
+      <c r="T22" t="n">
+        <v>75.4571280852678</v>
+      </c>
+      <c r="U22" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="V22" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="X22" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>86.84723306664095</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.99537037037037</v>
+      </c>
+      <c r="D23" t="n">
+        <v>181.7623456790124</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>81.29012345679013</v>
+      </c>
+      <c r="G23" t="n">
+        <v>44161265.43209876</v>
+      </c>
+      <c r="H23" t="n">
+        <v>85.47067901234567</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25.9074074074074</v>
+      </c>
+      <c r="J23" t="n">
+        <v>180.0069444444445</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.189814814814815</v>
+      </c>
+      <c r="L23" t="n">
+        <v>70.3912037037037</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2919155.092592593</v>
+      </c>
+      <c r="N23" t="n">
+        <v>75.54398148148148</v>
+      </c>
+      <c r="O23" t="n">
+        <v>23.21304510816878</v>
+      </c>
+      <c r="P23" t="n">
+        <v>180.7381363745138</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.223463612093475</v>
+      </c>
+      <c r="R23" t="n">
+        <v>78.53135254143265</v>
+      </c>
+      <c r="S23" t="n">
+        <v>38380836.30838265</v>
+      </c>
+      <c r="T23" t="n">
+        <v>84.88019462018217</v>
+      </c>
+      <c r="U23" t="n">
+        <v>25.81254575044682</v>
+      </c>
+      <c r="V23" t="n">
+        <v>180.4525261429004</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.169925855487353</v>
+      </c>
+      <c r="X23" t="n">
+        <v>69.87093399025217</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2364033.683191437</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>74.43315729131237</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.33383838383838</v>
+      </c>
+      <c r="D24" t="n">
+        <v>183.270202020202</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="F24" t="n">
+        <v>78.66742424242423</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22654797.97979798</v>
+      </c>
+      <c r="H24" t="n">
+        <v>81.9729797979798</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28.59876543209877</v>
+      </c>
+      <c r="J24" t="n">
+        <v>179.9027777777778</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.439814814814815</v>
+      </c>
+      <c r="L24" t="n">
+        <v>82.20833333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>33334104.9382716</v>
+      </c>
+      <c r="N24" t="n">
+        <v>83.73456790123457</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25.2314288143156</v>
+      </c>
+      <c r="P24" t="n">
+        <v>181.6767130792783</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.372269467765925</v>
+      </c>
+      <c r="R24" t="n">
+        <v>75.65688228200862</v>
+      </c>
+      <c r="S24" t="n">
+        <v>13939784.1428305</v>
+      </c>
+      <c r="T24" t="n">
+        <v>80.02033539440323</v>
+      </c>
+      <c r="U24" t="n">
+        <v>27.15565957377103</v>
+      </c>
+      <c r="V24" t="n">
+        <v>180.7879636454972</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.959893743072278</v>
+      </c>
+      <c r="X24" t="n">
+        <v>78.77404185845879</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19966427.69778477</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>81.56451040455168</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>27.08333333333333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>182.8159722222222</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.121527777777778</v>
+      </c>
+      <c r="F25" t="n">
+        <v>71.88541666666667</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3805208.333333333</v>
+      </c>
+      <c r="H25" t="n">
+        <v>75.07291666666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>28.73055555555555</v>
+      </c>
+      <c r="J25" t="n">
+        <v>179.5638888888889</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="L25" t="n">
+        <v>75.32083333333334</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6703055.555555555</v>
+      </c>
+      <c r="N25" t="n">
+        <v>76.56527777777778</v>
+      </c>
+      <c r="O25" t="n">
+        <v>27.27598583877996</v>
+      </c>
+      <c r="P25" t="n">
+        <v>179.6228567837391</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.085274186597716</v>
+      </c>
+      <c r="R25" t="n">
+        <v>71.47493470037588</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2935484.31851373</v>
+      </c>
+      <c r="T25" t="n">
+        <v>73.7378724053724</v>
+      </c>
+      <c r="U25" t="n">
+        <v>28.85886800334168</v>
+      </c>
+      <c r="V25" t="n">
+        <v>180.164530075188</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.34984440267335</v>
+      </c>
+      <c r="X25" t="n">
+        <v>74.55217627401836</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5359476.921470342</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>75.46285505430242</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>27.74242424242425</v>
+      </c>
+      <c r="J26" t="n">
+        <v>183.4183654729109</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.281542699724518</v>
+      </c>
+      <c r="L26" t="n">
+        <v>75.81662075298438</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9759742.883379249</v>
+      </c>
+      <c r="N26" t="n">
+        <v>77.65858585858585</v>
+      </c>
+      <c r="O26" t="n">
+        <v>26.20995322044084</v>
+      </c>
+      <c r="P26" t="n">
+        <v>181.8257256349458</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.004385964912281</v>
+      </c>
+      <c r="R26" t="n">
+        <v>68.38324238218782</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2025701.885287557</v>
+      </c>
+      <c r="T26" t="n">
+        <v>72.72207497202659</v>
+      </c>
+      <c r="U26" t="n">
+        <v>27.13480060609247</v>
+      </c>
+      <c r="V26" t="n">
+        <v>181.1055427825763</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.101619672193835</v>
+      </c>
+      <c r="X26" t="n">
+        <v>74.44492588750963</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7526368.750866359</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>76.6142852362948</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="D27" t="n">
+        <v>181.5194444444444</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.122222222222222</v>
+      </c>
+      <c r="F27" t="n">
+        <v>71.55833333333332</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9487916.666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>77.56527777777778</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="J27" t="n">
+        <v>185.5520833333334</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="L27" t="n">
+        <v>76.02083333333334</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10193402.77777778</v>
+      </c>
+      <c r="N27" t="n">
+        <v>79.05208333333334</v>
+      </c>
+      <c r="O27" t="n">
+        <v>23.81081785041115</v>
+      </c>
+      <c r="P27" t="n">
+        <v>180.1849900577891</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.070309917355372</v>
+      </c>
+      <c r="R27" t="n">
+        <v>70.76879445514614</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5187711.899842582</v>
+      </c>
+      <c r="T27" t="n">
+        <v>76.25636917707492</v>
+      </c>
+      <c r="U27" t="n">
+        <v>27.90740351696234</v>
+      </c>
+      <c r="V27" t="n">
+        <v>183.1319870345799</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.642372680066178</v>
+      </c>
+      <c r="X27" t="n">
+        <v>76.54354063262731</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9359263.165061347</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>79.00812775402558</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="D28" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="H28" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24.97569444444444</v>
+      </c>
+      <c r="J28" t="n">
+        <v>179.671875</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.03125</v>
+      </c>
+      <c r="L28" t="n">
+        <v>74.95486111111111</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10317013.88888889</v>
+      </c>
+      <c r="N28" t="n">
+        <v>78.54340277777777</v>
+      </c>
+      <c r="O28" t="n">
+        <v>23.60128285139727</v>
+      </c>
+      <c r="P28" t="n">
+        <v>180.8280609296627</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>70.67347007175383</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3797718.542898749</v>
+      </c>
+      <c r="T28" t="n">
+        <v>76.33266895829824</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26.25620620663493</v>
+      </c>
+      <c r="V28" t="n">
+        <v>178.6930502086418</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13134209914463</v>
+      </c>
+      <c r="X28" t="n">
+        <v>73.17096691099989</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6018265.635898629</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>75.4571280852678</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="D29" t="n">
+        <v>182.4375</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="F29" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10537500</v>
+      </c>
+      <c r="H29" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="I29" t="n">
+        <v>27.00925925925926</v>
+      </c>
+      <c r="J29" t="n">
+        <v>181.9737654320987</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="L29" t="n">
+        <v>75.12191358024693</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8219135.802469134</v>
+      </c>
+      <c r="N29" t="n">
+        <v>78.20555555555556</v>
+      </c>
+      <c r="O29" t="n">
+        <v>26.0051683039183</v>
+      </c>
+      <c r="P29" t="n">
+        <v>180.7583484570985</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.052065295815296</v>
+      </c>
+      <c r="R29" t="n">
+        <v>73.06781801531801</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8045446.87950938</v>
+      </c>
+      <c r="T29" t="n">
+        <v>77.04208374958375</v>
+      </c>
+      <c r="U29" t="n">
+        <v>25.42484848484849</v>
+      </c>
+      <c r="V29" t="n">
+        <v>180.1719408369408</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.190613275613276</v>
+      </c>
+      <c r="X29" t="n">
+        <v>73.70076479076479</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7235113.636363636</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>77.20712842712842</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>28.06222222222222</v>
+      </c>
+      <c r="D30" t="n">
+        <v>185.0286111111111</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.990555555555555</v>
+      </c>
+      <c r="F30" t="n">
+        <v>77.65944444444445</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13911166.66666667</v>
+      </c>
+      <c r="H30" t="n">
+        <v>80.0975</v>
+      </c>
+      <c r="I30" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="J30" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L30" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="N30" t="n">
+        <v>82.5175</v>
+      </c>
+      <c r="O30" t="n">
+        <v>25.56743368438146</v>
+      </c>
+      <c r="P30" t="n">
+        <v>182.996596157914</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.640669384458589</v>
+      </c>
+      <c r="R30" t="n">
+        <v>75.67931720819526</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11720844.08484981</v>
+      </c>
+      <c r="T30" t="n">
+        <v>80.21350895354327</v>
+      </c>
+      <c r="U30" t="n">
+        <v>24.0748204751008</v>
+      </c>
+      <c r="V30" t="n">
+        <v>179.0032096545712</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.136246730957829</v>
+      </c>
+      <c r="X30" t="n">
+        <v>74.80828783916313</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14677284.62460499</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>80.79895227198431</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>26.34413580246913</v>
+      </c>
+      <c r="D31" t="n">
+        <v>183.1604938271605</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.322530864197531</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75.97993827160494</v>
+      </c>
+      <c r="G31" t="n">
+        <v>11894714.50617284</v>
+      </c>
+      <c r="H31" t="n">
+        <v>79.08487654320987</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="J31" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="L31" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="M31" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="N31" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="O31" t="n">
+        <v>24.49551587301588</v>
+      </c>
+      <c r="P31" t="n">
+        <v>184.1648015873016</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.096865079365079</v>
+      </c>
+      <c r="R31" t="n">
+        <v>71.97553571428571</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5478414.186507936</v>
+      </c>
+      <c r="T31" t="n">
+        <v>77.42136904761905</v>
+      </c>
+      <c r="U31" t="n">
+        <v>24.33056841709016</v>
+      </c>
+      <c r="V31" t="n">
+        <v>180.5030138339921</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.639210897797855</v>
+      </c>
+      <c r="X31" t="n">
+        <v>75.37785479013739</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16504748.95303971</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>80.29241318464145</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D32" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F32" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G32" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H32" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I32" t="n">
+        <v>27.86631944444444</v>
+      </c>
+      <c r="J32" t="n">
+        <v>181.9479166666667</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.887152777777778</v>
+      </c>
+      <c r="L32" t="n">
+        <v>76.58159722222223</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11931944.44444444</v>
+      </c>
+      <c r="N32" t="n">
+        <v>78.83159722222223</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="P32" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="R32" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="S32" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="T32" t="n">
+        <v>86.84723306664095</v>
+      </c>
+      <c r="U32" t="n">
+        <v>27.65425976800977</v>
+      </c>
+      <c r="V32" t="n">
+        <v>183.4720833333333</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.954102564102564</v>
+      </c>
+      <c r="X32" t="n">
+        <v>75.75265720390721</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10349814.71306472</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>79.18877594627595</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>25.33383838383838</v>
+      </c>
+      <c r="D33" t="n">
+        <v>183.270202020202</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="F33" t="n">
+        <v>78.66742424242423</v>
+      </c>
+      <c r="G33" t="n">
+        <v>22654797.97979798</v>
+      </c>
+      <c r="H33" t="n">
+        <v>81.9729797979798</v>
+      </c>
+      <c r="I33" t="n">
+        <v>25.99537037037037</v>
+      </c>
+      <c r="J33" t="n">
+        <v>181.7623456790124</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="L33" t="n">
+        <v>81.29012345679013</v>
+      </c>
+      <c r="M33" t="n">
+        <v>44161265.43209876</v>
+      </c>
+      <c r="N33" t="n">
+        <v>85.47067901234567</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25.2314288143156</v>
+      </c>
+      <c r="P33" t="n">
+        <v>181.6767130792783</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.372269467765925</v>
+      </c>
+      <c r="R33" t="n">
+        <v>75.65688228200862</v>
+      </c>
+      <c r="S33" t="n">
+        <v>13939784.1428305</v>
+      </c>
+      <c r="T33" t="n">
+        <v>80.02033539440323</v>
+      </c>
+      <c r="U33" t="n">
+        <v>23.21304510816878</v>
+      </c>
+      <c r="V33" t="n">
+        <v>180.7381363745138</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.223463612093475</v>
+      </c>
+      <c r="X33" t="n">
+        <v>78.53135254143265</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>38380836.30838265</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>84.88019462018217</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>25.50299873737374</v>
-      </c>
-      <c r="D22" t="n">
-        <v>181.7230113636363</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.787689393939394</v>
-      </c>
-      <c r="F22" t="n">
-        <v>83.56650883838384</v>
-      </c>
-      <c r="G22" t="n">
-        <v>63154198.23232324</v>
-      </c>
-      <c r="H22" t="n">
-        <v>87.18503787878788</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27.74545454545455</v>
-      </c>
-      <c r="J22" t="n">
-        <v>183.3537190082644</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.269421487603306</v>
-      </c>
-      <c r="L22" t="n">
-        <v>75.69338842975206</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9326611.570247935</v>
-      </c>
-      <c r="N22" t="n">
-        <v>77.49090909090908</v>
-      </c>
-      <c r="O22" t="n">
-        <v>25.13281690693971</v>
-      </c>
-      <c r="P22" t="n">
-        <v>179.9695843062071</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.832384111989375</v>
-      </c>
-      <c r="R22" t="n">
-        <v>82.99050600147092</v>
-      </c>
-      <c r="S22" t="n">
-        <v>63210719.4178466</v>
-      </c>
-      <c r="T22" t="n">
-        <v>87.23376773486423</v>
-      </c>
-      <c r="U22" t="n">
-        <v>27.29139042775406</v>
-      </c>
-      <c r="V22" t="n">
-        <v>180.8754427390791</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.105099446008537</v>
-      </c>
-      <c r="X22" t="n">
-        <v>74.46884933248569</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>7590431.386795023</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>76.58514213059667</v>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D34" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F34" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G34" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H34" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I34" t="n">
+        <v>27.74242424242425</v>
+      </c>
+      <c r="J34" t="n">
+        <v>183.4183654729109</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.281542699724518</v>
+      </c>
+      <c r="L34" t="n">
+        <v>75.81662075298438</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9759742.883379249</v>
+      </c>
+      <c r="N34" t="n">
+        <v>77.65858585858585</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="P34" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="R34" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="S34" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="T34" t="n">
+        <v>86.84723306664095</v>
+      </c>
+      <c r="U34" t="n">
+        <v>27.13480060609247</v>
+      </c>
+      <c r="V34" t="n">
+        <v>181.1055427825763</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.101619672193835</v>
+      </c>
+      <c r="X34" t="n">
+        <v>74.44492588750963</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7526368.750866359</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>76.6142852362948</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1699 +558,2507 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.20631313131313</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="D2" t="n">
-        <v>183.1111111111111</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="E2" t="n">
-        <v>1.478030303030303</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="F2" t="n">
-        <v>78.86186868686868</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="G2" t="n">
-        <v>23356818.18181818</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="H2" t="n">
-        <v>82.16363636363636</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="I2" t="n">
-        <v>26.28993055555555</v>
+        <v>22.65</v>
       </c>
       <c r="J2" t="n">
-        <v>183.5694444444444</v>
+        <v>181.5194444444444</v>
       </c>
       <c r="K2" t="n">
-        <v>1.321180555555555</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="L2" t="n">
-        <v>76.14409722222223</v>
+        <v>71.55833333333332</v>
       </c>
       <c r="M2" t="n">
-        <v>12212456.59722222</v>
+        <v>9487916.666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>79.30381944444444</v>
+        <v>77.56527777777778</v>
       </c>
       <c r="O2" t="n">
-        <v>25.33190728321512</v>
+        <v>25.42484848484849</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6462106869338</v>
+        <v>180.1719408369408</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.340570903172624</v>
+        <v>1.190613275613276</v>
       </c>
       <c r="R2" t="n">
-        <v>75.61980094229571</v>
+        <v>73.70076479076479</v>
       </c>
       <c r="S2" t="n">
-        <v>13677224.33421806</v>
+        <v>7235113.636363636</v>
       </c>
       <c r="T2" t="n">
-        <v>79.89114879153243</v>
+        <v>77.20712842712842</v>
       </c>
       <c r="U2" t="n">
-        <v>24.67694444444444</v>
+        <v>23.81081785041115</v>
       </c>
       <c r="V2" t="n">
-        <v>184.7762301587302</v>
+        <v>180.1849900577891</v>
       </c>
       <c r="W2" t="n">
-        <v>1.096865079365079</v>
+        <v>1.070309917355372</v>
       </c>
       <c r="X2" t="n">
-        <v>72.03696428571429</v>
+        <v>70.76879445514614</v>
       </c>
       <c r="Y2" t="n">
-        <v>5435271.329365079</v>
+        <v>5187711.899842582</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.33422619047619</v>
+        <v>76.25636917707492</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27.78395061728395</v>
+        <v>28.06222222222222</v>
       </c>
       <c r="D3" t="n">
-        <v>182.037037037037</v>
+        <v>185.0286111111111</v>
       </c>
       <c r="E3" t="n">
-        <v>1.871913580246914</v>
+        <v>1.990555555555555</v>
       </c>
       <c r="F3" t="n">
-        <v>76.6141975308642</v>
+        <v>77.65944444444445</v>
       </c>
       <c r="G3" t="n">
-        <v>12136728.39506173</v>
+        <v>13911166.66666667</v>
       </c>
       <c r="H3" t="n">
-        <v>78.90586419753087</v>
+        <v>80.0975</v>
       </c>
       <c r="I3" t="n">
-        <v>25.12666666666667</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="J3" t="n">
-        <v>181.6877777777778</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="K3" t="n">
-        <v>1.353333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>78.54888888888888</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="M3" t="n">
-        <v>24666444.44444444</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="N3" t="n">
-        <v>82.65777777777778</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="O3" t="n">
-        <v>28.1894246031746</v>
+        <v>25.56743368438146</v>
       </c>
       <c r="P3" t="n">
-        <v>183.5720833333333</v>
+        <v>182.996596157914</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.023333333333333</v>
+        <v>1.640669384458589</v>
       </c>
       <c r="R3" t="n">
-        <v>75.9471626984127</v>
+        <v>75.67931720819526</v>
       </c>
       <c r="S3" t="n">
-        <v>10458496.03174603</v>
+        <v>11720844.0848498</v>
       </c>
       <c r="T3" t="n">
-        <v>79.1536111111111</v>
+        <v>80.21350895354327</v>
       </c>
       <c r="U3" t="n">
-        <v>23.86767761795794</v>
+        <v>27.46666316526611</v>
       </c>
       <c r="V3" t="n">
-        <v>179.5817810831426</v>
+        <v>182.7437883311219</v>
       </c>
       <c r="W3" t="n">
-        <v>1.129103873814972</v>
+        <v>1.619802078726227</v>
       </c>
       <c r="X3" t="n">
-        <v>74.76543069630597</v>
+        <v>76.36418656936459</v>
       </c>
       <c r="Y3" t="n">
-        <v>14949427.48174785</v>
+        <v>9585836.848555211</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.84180941484145</v>
+        <v>79.15731497862302</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.07407407407407</v>
+        <v>26.8125</v>
       </c>
       <c r="D4" t="n">
-        <v>182.1604938271605</v>
+        <v>182.4375</v>
       </c>
       <c r="E4" t="n">
-        <v>1.41358024691358</v>
+        <v>1.1875</v>
       </c>
       <c r="F4" t="n">
-        <v>75.2037037037037</v>
+        <v>74.4375</v>
       </c>
       <c r="G4" t="n">
-        <v>8313580.246913578</v>
+        <v>10537500</v>
       </c>
       <c r="H4" t="n">
-        <v>78.30123456790122</v>
+        <v>77.875</v>
       </c>
       <c r="I4" t="n">
-        <v>23.64814814814815</v>
+        <v>27.74242424242425</v>
       </c>
       <c r="J4" t="n">
-        <v>182.0972222222223</v>
+        <v>183.4183654729109</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.281542699724518</v>
       </c>
       <c r="L4" t="n">
-        <v>71.25462962962963</v>
+        <v>75.81662075298438</v>
       </c>
       <c r="M4" t="n">
-        <v>4062500</v>
+        <v>9759742.883379247</v>
       </c>
       <c r="N4" t="n">
-        <v>77.19907407407408</v>
+        <v>77.65858585858585</v>
       </c>
       <c r="O4" t="n">
-        <v>25.47484848484849</v>
+        <v>26.0051683039183</v>
       </c>
       <c r="P4" t="n">
-        <v>180.1052741702742</v>
+        <v>180.7583484570985</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.162835497835498</v>
+        <v>1.052065295815296</v>
       </c>
       <c r="R4" t="n">
-        <v>73.58965367965368</v>
+        <v>73.06781801531801</v>
       </c>
       <c r="S4" t="n">
-        <v>6629696.96969697</v>
+        <v>8045446.87950938</v>
       </c>
       <c r="T4" t="n">
-        <v>76.97379509379509</v>
+        <v>77.04208374958375</v>
       </c>
       <c r="U4" t="n">
-        <v>23.53052261747914</v>
+        <v>27.13480060609247</v>
       </c>
       <c r="V4" t="n">
-        <v>180.7263065436979</v>
+        <v>181.1055427825763</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.101619672193835</v>
       </c>
       <c r="X4" t="n">
-        <v>70.54598469163686</v>
+        <v>74.44492588750963</v>
       </c>
       <c r="Y4" t="n">
-        <v>3713771.174477696</v>
+        <v>7526368.750866359</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.28237656063743</v>
+        <v>76.6142852362948</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.91666666666667</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="D5" t="n">
-        <v>179.6219135802469</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="E5" t="n">
-        <v>1.027777777777778</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>74.98456790123457</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="G5" t="n">
-        <v>10353395.0617284</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="H5" t="n">
-        <v>78.64351851851853</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="I5" t="n">
-        <v>28.57333333333333</v>
+        <v>25.33383838383838</v>
       </c>
       <c r="J5" t="n">
-        <v>184.7841666666667</v>
+        <v>183.270202020202</v>
       </c>
       <c r="K5" t="n">
-        <v>2.079444444444444</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="L5" t="n">
-        <v>78.08166666666666</v>
+        <v>78.66742424242423</v>
       </c>
       <c r="M5" t="n">
-        <v>14353388.88888889</v>
+        <v>22654797.97979798</v>
       </c>
       <c r="N5" t="n">
-        <v>80.13083333333334</v>
+        <v>81.9729797979798</v>
       </c>
       <c r="O5" t="n">
-        <v>26.42893347936221</v>
+        <v>23.21304510816878</v>
       </c>
       <c r="P5" t="n">
-        <v>178.9630502086418</v>
+        <v>180.7381363745138</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.132251190053721</v>
+        <v>2.223463612093475</v>
       </c>
       <c r="R5" t="n">
-        <v>73.06551236554535</v>
+        <v>78.53135254143265</v>
       </c>
       <c r="S5" t="n">
-        <v>5814538.363171356</v>
+        <v>38380836.30838265</v>
       </c>
       <c r="T5" t="n">
-        <v>75.27621899435871</v>
+        <v>84.88019462018217</v>
       </c>
       <c r="U5" t="n">
-        <v>25.37854479549257</v>
+        <v>25.2314288143156</v>
       </c>
       <c r="V5" t="n">
-        <v>183.5299294912473</v>
+        <v>181.6767130792783</v>
       </c>
       <c r="W5" t="n">
-        <v>1.629558273347478</v>
+        <v>1.372269467765925</v>
       </c>
       <c r="X5" t="n">
-        <v>75.69042831930636</v>
+        <v>75.65688228200862</v>
       </c>
       <c r="Y5" t="n">
-        <v>11843066.30707203</v>
+        <v>13939784.1428305</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.09128673132106</v>
+        <v>80.02033539440323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>27.41666666666667</v>
+        <v>26.8</v>
       </c>
       <c r="D6" t="n">
-        <v>183.4166666666667</v>
+        <v>183.0083333333334</v>
       </c>
       <c r="E6" t="n">
-        <v>1.166666666666667</v>
+        <v>1.097222222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>75.25</v>
+        <v>71.93055555555556</v>
       </c>
       <c r="G6" t="n">
-        <v>10925000</v>
+        <v>3944166.666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>77.83333333333333</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>75.34722222222223</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="J6" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="L6" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="N6" t="n">
+        <v>82.26000000000001</v>
+      </c>
       <c r="O6" t="n">
-        <v>26.13074255990923</v>
+        <v>27.06555490567439</v>
       </c>
       <c r="P6" t="n">
-        <v>181.0787205078872</v>
+        <v>179.5725645983918</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.057850328683662</v>
+        <v>1.079944549935359</v>
       </c>
       <c r="R6" t="n">
-        <v>73.15174223924224</v>
+        <v>71.34866037251147</v>
       </c>
       <c r="S6" t="n">
-        <v>8064906.255010421</v>
+        <v>2953721.094061168</v>
       </c>
       <c r="T6" t="n">
-        <v>76.91481527731528</v>
+        <v>73.87925538003662</v>
       </c>
       <c r="U6" t="n">
-        <v>26.18199269412505</v>
+        <v>24.33056841709016</v>
       </c>
       <c r="V6" t="n">
-        <v>181.7001773893318</v>
+        <v>180.5030138339921</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.639210897797855</v>
       </c>
       <c r="X6" t="n">
-        <v>67.97260641727554</v>
+        <v>75.37785479013739</v>
       </c>
       <c r="Y6" t="n">
-        <v>1721028.091427908</v>
+        <v>16504748.95303971</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.42437760360555</v>
+        <v>80.29241318464145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>22.925</v>
+        <v>26.34413580246913</v>
       </c>
       <c r="D7" t="n">
-        <v>181.5819444444444</v>
+        <v>183.1604938271605</v>
       </c>
       <c r="E7" t="n">
-        <v>1.134722222222222</v>
+        <v>1.322530864197531</v>
       </c>
       <c r="F7" t="n">
-        <v>71.63333333333333</v>
+        <v>75.97993827160494</v>
       </c>
       <c r="G7" t="n">
-        <v>9446666.666666666</v>
+        <v>11894714.50617284</v>
       </c>
       <c r="H7" t="n">
-        <v>77.25277777777778</v>
+        <v>79.08487654320987</v>
       </c>
       <c r="I7" t="n">
-        <v>25.87361111111111</v>
+        <v>28.73055555555555</v>
       </c>
       <c r="J7" t="n">
-        <v>181.775</v>
+        <v>179.5638888888889</v>
       </c>
       <c r="K7" t="n">
-        <v>2.715277777777778</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>81.15000000000001</v>
+        <v>75.32083333333334</v>
       </c>
       <c r="M7" t="n">
-        <v>43920694.44444444</v>
+        <v>6703055.555555555</v>
       </c>
       <c r="N7" t="n">
-        <v>85.49027777777778</v>
+        <v>76.56527777777778</v>
       </c>
       <c r="O7" t="n">
-        <v>23.76410067869398</v>
+        <v>24.49551587301588</v>
       </c>
       <c r="P7" t="n">
-        <v>180.3781718759709</v>
+        <v>184.1648015873016</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.064628099173554</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="R7" t="n">
-        <v>70.95124395009562</v>
+        <v>71.97553571428571</v>
       </c>
       <c r="S7" t="n">
-        <v>5228807.22812541</v>
+        <v>5478414.186507936</v>
       </c>
       <c r="T7" t="n">
-        <v>76.45144493465068</v>
+        <v>77.42136904761905</v>
       </c>
       <c r="U7" t="n">
-        <v>23.46750939388307</v>
+        <v>28.85886800334168</v>
       </c>
       <c r="V7" t="n">
-        <v>180.6559935173709</v>
+        <v>180.164530075188</v>
       </c>
       <c r="W7" t="n">
-        <v>2.183285040664904</v>
+        <v>1.34984440267335</v>
       </c>
       <c r="X7" t="n">
-        <v>78.51349539857549</v>
+        <v>74.55217627401836</v>
       </c>
       <c r="Y7" t="n">
-        <v>36364898.80838265</v>
+        <v>5359476.921470342</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.76769462018217</v>
+        <v>75.46285505430242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.84343434343434</v>
+        <v>25.52118055555555</v>
       </c>
       <c r="D8" t="n">
-        <v>181.5691919191919</v>
+        <v>182.0582386363636</v>
       </c>
       <c r="E8" t="n">
-        <v>1.698686868686869</v>
+        <v>2.859280303030303</v>
       </c>
       <c r="F8" t="n">
-        <v>79.43323232323232</v>
+        <v>83.77219065656566</v>
       </c>
       <c r="G8" t="n">
-        <v>25763181.81818182</v>
+        <v>65004766.41414142</v>
       </c>
       <c r="H8" t="n">
-        <v>82.44686868686868</v>
+        <v>87.31799242424242</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70694444444445</v>
+        <v>25.76190476190476</v>
       </c>
       <c r="J8" t="n">
-        <v>179.6513888888889</v>
+        <v>179.8472222222222</v>
       </c>
       <c r="K8" t="n">
-        <v>1.268055555555555</v>
+        <v>1.162698412698413</v>
       </c>
       <c r="L8" t="n">
-        <v>75.35277777777779</v>
+        <v>70.54166666666666</v>
       </c>
       <c r="M8" t="n">
-        <v>6780972.222222222</v>
+        <v>3019593.253968254</v>
       </c>
       <c r="N8" t="n">
-        <v>76.55694444444445</v>
+        <v>75.54563492063492</v>
       </c>
       <c r="O8" t="n">
-        <v>24.39584619486794</v>
+        <v>25.07216679519311</v>
       </c>
       <c r="P8" t="n">
-        <v>180.8557916117699</v>
+        <v>179.6831521913759</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.646155342242299</v>
+        <v>2.754408858685175</v>
       </c>
       <c r="R8" t="n">
-        <v>75.20563256791517</v>
+        <v>82.48092908553436</v>
       </c>
       <c r="S8" t="n">
-        <v>15812387.8419286</v>
+        <v>60388463.26553564</v>
       </c>
       <c r="T8" t="n">
-        <v>80.07366318464145</v>
+        <v>86.84723306664095</v>
       </c>
       <c r="U8" t="n">
-        <v>29.1236299081036</v>
+        <v>25.69795860457625</v>
       </c>
       <c r="V8" t="n">
-        <v>180.5778634085213</v>
+        <v>180.4825239643254</v>
       </c>
       <c r="W8" t="n">
-        <v>1.393653926482874</v>
+        <v>1.160973700863407</v>
       </c>
       <c r="X8" t="n">
-        <v>74.63693817878028</v>
+        <v>69.87127282439782</v>
       </c>
       <c r="Y8" t="n">
-        <v>5295762.635756057</v>
+        <v>2449713.167925484</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.45333124477861</v>
+        <v>74.57414418370301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
-        <v>27.74545454545455</v>
-      </c>
-      <c r="D9" t="n">
-        <v>183.3537190082644</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.269421487603306</v>
-      </c>
-      <c r="F9" t="n">
-        <v>75.69338842975206</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9326611.570247935</v>
-      </c>
-      <c r="H9" t="n">
-        <v>77.49090909090908</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>25.50299873737374</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="J9" t="n">
-        <v>181.7230113636363</v>
+        <v>179.671875</v>
       </c>
       <c r="K9" t="n">
-        <v>2.787689393939394</v>
+        <v>1.03125</v>
       </c>
       <c r="L9" t="n">
-        <v>83.56650883838384</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="M9" t="n">
-        <v>63154198.23232324</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="N9" t="n">
-        <v>87.18503787878788</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="O9" t="n">
-        <v>27.29139042775406</v>
+        <v>26.20995322044084</v>
       </c>
       <c r="P9" t="n">
-        <v>180.8754427390791</v>
+        <v>181.8257256349458</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.105099446008537</v>
+        <v>1.004385964912281</v>
       </c>
       <c r="R9" t="n">
-        <v>74.46884933248569</v>
+        <v>68.38324238218782</v>
       </c>
       <c r="S9" t="n">
-        <v>7590431.386795023</v>
+        <v>2025701.885287557</v>
       </c>
       <c r="T9" t="n">
-        <v>76.58514213059667</v>
+        <v>72.72207497202659</v>
       </c>
       <c r="U9" t="n">
-        <v>25.13281690693971</v>
+        <v>26.25620620663493</v>
       </c>
       <c r="V9" t="n">
-        <v>179.9695843062071</v>
+        <v>178.6930502086418</v>
       </c>
       <c r="W9" t="n">
-        <v>2.832384111989375</v>
+        <v>1.13134209914463</v>
       </c>
       <c r="X9" t="n">
-        <v>82.99050600147092</v>
+        <v>73.17096691099989</v>
       </c>
       <c r="Y9" t="n">
-        <v>63210719.4178466</v>
+        <v>6018265.635898629</v>
       </c>
       <c r="Z9" t="n">
-        <v>87.23376773486423</v>
+        <v>75.4571280852678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.9074074074074</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="D10" t="n">
-        <v>180.0069444444445</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="E10" t="n">
-        <v>1.189814814814815</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>70.3912037037037</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="G10" t="n">
-        <v>2919155.092592593</v>
+        <v>4062500</v>
       </c>
       <c r="H10" t="n">
-        <v>75.54398148148148</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="I10" t="n">
-        <v>26.91666666666666</v>
+        <v>27.86631944444444</v>
       </c>
       <c r="J10" t="n">
-        <v>182.8777777777778</v>
+        <v>181.9479166666667</v>
       </c>
       <c r="K10" t="n">
-        <v>1.122222222222222</v>
+        <v>1.887152777777778</v>
       </c>
       <c r="L10" t="n">
-        <v>71.95833333333334</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="M10" t="n">
-        <v>3914166.666666667</v>
+        <v>11931944.44444444</v>
       </c>
       <c r="N10" t="n">
-        <v>75.25833333333334</v>
+        <v>78.83159722222223</v>
       </c>
       <c r="O10" t="n">
-        <v>25.91150027124292</v>
+        <v>23.60128285139727</v>
       </c>
       <c r="P10" t="n">
-        <v>180.617196583373</v>
+        <v>180.8280609296628</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.179574891339597</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>69.96502282439782</v>
+        <v>70.67347007175383</v>
       </c>
       <c r="S10" t="n">
-        <v>2379828.495306436</v>
+        <v>3797718.542898749</v>
       </c>
       <c r="T10" t="n">
-        <v>74.48039418370301</v>
+        <v>76.33266895829824</v>
       </c>
       <c r="U10" t="n">
-        <v>27.23790339052287</v>
+        <v>27.65425976800977</v>
       </c>
       <c r="V10" t="n">
-        <v>179.7714282347554</v>
+        <v>183.4720833333333</v>
       </c>
       <c r="W10" t="n">
-        <v>1.090361216602026</v>
+        <v>1.954102564102564</v>
       </c>
       <c r="X10" t="n">
-        <v>71.40358461493572</v>
+        <v>75.75265720390721</v>
       </c>
       <c r="Y10" t="n">
-        <v>2888474.881939956</v>
+        <v>10349814.71306472</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.70217204670328</v>
+        <v>79.18877594627595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.69166666666667</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="D11" t="n">
-        <v>185.6166666666667</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>1.541666666666667</v>
+        <v>2.429166666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>75.84166666666667</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="G11" t="n">
-        <v>9787222.222222222</v>
+        <v>33006250</v>
       </c>
       <c r="H11" t="n">
-        <v>78.84166666666667</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="I11" t="n">
-        <v>28.59876543209877</v>
+        <v>25.1225</v>
       </c>
       <c r="J11" t="n">
-        <v>179.9027777777778</v>
+        <v>182.185</v>
       </c>
       <c r="K11" t="n">
-        <v>2.439814814814815</v>
+        <v>1.345</v>
       </c>
       <c r="L11" t="n">
-        <v>82.20833333333333</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>33334104.9382716</v>
+        <v>24073250</v>
       </c>
       <c r="N11" t="n">
-        <v>83.73456790123457</v>
+        <v>82.5175</v>
       </c>
       <c r="O11" t="n">
-        <v>27.69999649859944</v>
+        <v>27.0506199321834</v>
       </c>
       <c r="P11" t="n">
-        <v>183.2354549977886</v>
+        <v>180.7196935967369</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.644802078726227</v>
+        <v>1.932325421396629</v>
       </c>
       <c r="R11" t="n">
-        <v>76.30585323603125</v>
+        <v>78.81242714629711</v>
       </c>
       <c r="S11" t="n">
-        <v>9400003.515221879</v>
+        <v>20477679.66484839</v>
       </c>
       <c r="T11" t="n">
-        <v>79.02398164528969</v>
+        <v>81.66069094304387</v>
       </c>
       <c r="U11" t="n">
-        <v>27.16231583861615</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="V11" t="n">
-        <v>180.7869450587253</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="W11" t="n">
-        <v>2.008348813209494</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="X11" t="n">
-        <v>78.72997100594623</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="Y11" t="n">
-        <v>20172007.15022851</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="Z11" t="n">
-        <v>81.55250380854096</v>
+        <v>80.79895227198431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>27.07407407407407</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="D12" t="n">
-        <v>182.1604938271605</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.41358024691358</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>75.2037037037037</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="G12" t="n">
-        <v>8313580.246913578</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="H12" t="n">
-        <v>78.30123456790122</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="I12" t="n">
-        <v>22.925</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="J12" t="n">
-        <v>181.5819444444444</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="K12" t="n">
-        <v>1.134722222222222</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="L12" t="n">
-        <v>71.63333333333333</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="M12" t="n">
-        <v>9446666.666666666</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="N12" t="n">
-        <v>77.25277777777778</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="O12" t="n">
-        <v>25.47484848484849</v>
+        <v>27.46666316526611</v>
       </c>
       <c r="P12" t="n">
-        <v>180.1052741702742</v>
+        <v>182.7437883311219</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.162835497835498</v>
+        <v>1.619802078726227</v>
       </c>
       <c r="R12" t="n">
-        <v>73.58965367965368</v>
+        <v>76.36418656936459</v>
       </c>
       <c r="S12" t="n">
-        <v>6629696.96969697</v>
+        <v>9585836.848555211</v>
       </c>
       <c r="T12" t="n">
-        <v>76.97379509379509</v>
+        <v>79.15731497862302</v>
       </c>
       <c r="U12" t="n">
-        <v>23.76410067869398</v>
+        <v>25.42484848484849</v>
       </c>
       <c r="V12" t="n">
-        <v>180.3781718759709</v>
+        <v>180.1719408369408</v>
       </c>
       <c r="W12" t="n">
-        <v>1.064628099173554</v>
+        <v>1.190613275613276</v>
       </c>
       <c r="X12" t="n">
-        <v>70.95124395009562</v>
+        <v>73.70076479076479</v>
       </c>
       <c r="Y12" t="n">
-        <v>5228807.22812541</v>
+        <v>7235113.636363636</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.45144493465068</v>
+        <v>77.20712842712842</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>28.57333333333333</v>
+        <v>27.74242424242425</v>
       </c>
       <c r="D13" t="n">
-        <v>184.7841666666667</v>
+        <v>183.4183654729109</v>
       </c>
       <c r="E13" t="n">
-        <v>2.079444444444444</v>
+        <v>1.281542699724518</v>
       </c>
       <c r="F13" t="n">
-        <v>78.08166666666666</v>
+        <v>75.81662075298438</v>
       </c>
       <c r="G13" t="n">
-        <v>14353388.88888889</v>
+        <v>9759742.883379247</v>
       </c>
       <c r="H13" t="n">
-        <v>80.13083333333334</v>
+        <v>77.65858585858585</v>
       </c>
       <c r="I13" t="n">
-        <v>26.69166666666667</v>
+        <v>28.06222222222222</v>
       </c>
       <c r="J13" t="n">
-        <v>185.6166666666667</v>
+        <v>185.0286111111111</v>
       </c>
       <c r="K13" t="n">
-        <v>1.541666666666667</v>
+        <v>1.990555555555555</v>
       </c>
       <c r="L13" t="n">
-        <v>75.84166666666667</v>
+        <v>77.65944444444445</v>
       </c>
       <c r="M13" t="n">
-        <v>9787222.222222222</v>
+        <v>13911166.66666667</v>
       </c>
       <c r="N13" t="n">
-        <v>78.84166666666667</v>
+        <v>80.0975</v>
       </c>
       <c r="O13" t="n">
-        <v>25.37854479549257</v>
+        <v>27.13480060609247</v>
       </c>
       <c r="P13" t="n">
-        <v>183.5299294912473</v>
+        <v>181.1055427825763</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.629558273347478</v>
+        <v>1.101619672193835</v>
       </c>
       <c r="R13" t="n">
-        <v>75.69042831930636</v>
+        <v>74.44492588750963</v>
       </c>
       <c r="S13" t="n">
-        <v>11843066.30707203</v>
+        <v>7526368.750866359</v>
       </c>
       <c r="T13" t="n">
-        <v>80.09128673132106</v>
+        <v>76.6142852362948</v>
       </c>
       <c r="U13" t="n">
-        <v>27.69999649859944</v>
+        <v>25.56743368438146</v>
       </c>
       <c r="V13" t="n">
-        <v>183.2354549977886</v>
+        <v>182.996596157914</v>
       </c>
       <c r="W13" t="n">
-        <v>1.644802078726227</v>
+        <v>1.640669384458589</v>
       </c>
       <c r="X13" t="n">
-        <v>76.30585323603125</v>
+        <v>75.67931720819526</v>
       </c>
       <c r="Y13" t="n">
-        <v>9400003.515221879</v>
+        <v>11720844.0848498</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.02398164528969</v>
+        <v>80.21350895354327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>27.41666666666667</v>
+        <v>28.73055555555555</v>
       </c>
       <c r="D14" t="n">
-        <v>183.4166666666667</v>
+        <v>179.5638888888889</v>
       </c>
       <c r="E14" t="n">
-        <v>1.166666666666667</v>
+        <v>1.283333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>75.25</v>
+        <v>75.32083333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>10925000</v>
+        <v>6703055.555555555</v>
       </c>
       <c r="H14" t="n">
-        <v>77.83333333333333</v>
+        <v>76.56527777777778</v>
       </c>
       <c r="I14" t="n">
-        <v>27.74545454545455</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="J14" t="n">
-        <v>183.3537190082644</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="K14" t="n">
-        <v>1.269421487603306</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="L14" t="n">
-        <v>75.69338842975206</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="M14" t="n">
-        <v>9326611.570247935</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="N14" t="n">
-        <v>77.49090909090908</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="O14" t="n">
-        <v>26.13074255990923</v>
+        <v>28.85886800334168</v>
       </c>
       <c r="P14" t="n">
-        <v>181.0787205078872</v>
+        <v>180.164530075188</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.057850328683662</v>
+        <v>1.34984440267335</v>
       </c>
       <c r="R14" t="n">
-        <v>73.15174223924224</v>
+        <v>74.55217627401836</v>
       </c>
       <c r="S14" t="n">
-        <v>8064906.255010421</v>
+        <v>5359476.921470342</v>
       </c>
       <c r="T14" t="n">
-        <v>76.91481527731528</v>
+        <v>75.46285505430242</v>
       </c>
       <c r="U14" t="n">
-        <v>27.29139042775406</v>
+        <v>23.21304510816878</v>
       </c>
       <c r="V14" t="n">
-        <v>180.8754427390791</v>
+        <v>180.7381363745138</v>
       </c>
       <c r="W14" t="n">
-        <v>1.105099446008537</v>
+        <v>2.223463612093475</v>
       </c>
       <c r="X14" t="n">
-        <v>74.46884933248569</v>
+        <v>78.53135254143265</v>
       </c>
       <c r="Y14" t="n">
-        <v>7590431.386795023</v>
+        <v>38380836.30838265</v>
       </c>
       <c r="Z14" t="n">
-        <v>76.58514213059667</v>
+        <v>84.88019462018217</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.87361111111111</v>
+        <v>25.33383838383838</v>
       </c>
       <c r="D15" t="n">
-        <v>181.775</v>
+        <v>183.270202020202</v>
       </c>
       <c r="E15" t="n">
-        <v>2.715277777777778</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="F15" t="n">
-        <v>81.15000000000001</v>
+        <v>78.66742424242423</v>
       </c>
       <c r="G15" t="n">
-        <v>43920694.44444444</v>
+        <v>22654797.97979798</v>
       </c>
       <c r="H15" t="n">
-        <v>85.49027777777778</v>
+        <v>81.9729797979798</v>
       </c>
       <c r="I15" t="n">
-        <v>25.20631313131313</v>
+        <v>22.65</v>
       </c>
       <c r="J15" t="n">
-        <v>183.1111111111111</v>
+        <v>181.5194444444444</v>
       </c>
       <c r="K15" t="n">
-        <v>1.478030303030303</v>
+        <v>1.122222222222222</v>
       </c>
       <c r="L15" t="n">
-        <v>78.86186868686868</v>
+        <v>71.55833333333332</v>
       </c>
       <c r="M15" t="n">
-        <v>23356818.18181818</v>
+        <v>9487916.666666666</v>
       </c>
       <c r="N15" t="n">
-        <v>82.16363636363636</v>
+        <v>77.56527777777778</v>
       </c>
       <c r="O15" t="n">
-        <v>23.46750939388307</v>
+        <v>25.2314288143156</v>
       </c>
       <c r="P15" t="n">
-        <v>180.6559935173709</v>
+        <v>181.6767130792783</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.183285040664904</v>
+        <v>1.372269467765925</v>
       </c>
       <c r="R15" t="n">
-        <v>78.51349539857549</v>
+        <v>75.65688228200862</v>
       </c>
       <c r="S15" t="n">
-        <v>36364898.80838265</v>
+        <v>13939784.1428305</v>
       </c>
       <c r="T15" t="n">
-        <v>84.76769462018217</v>
+        <v>80.02033539440323</v>
       </c>
       <c r="U15" t="n">
-        <v>25.33190728321512</v>
+        <v>23.81081785041115</v>
       </c>
       <c r="V15" t="n">
-        <v>181.6462106869338</v>
+        <v>180.1849900577891</v>
       </c>
       <c r="W15" t="n">
-        <v>1.340570903172624</v>
+        <v>1.070309917355372</v>
       </c>
       <c r="X15" t="n">
-        <v>75.61980094229571</v>
+        <v>70.76879445514614</v>
       </c>
       <c r="Y15" t="n">
-        <v>13677224.33421806</v>
+        <v>5187711.899842582</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.89114879153243</v>
+        <v>76.25636917707492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>26.91666666666666</v>
+        <v>25.76190476190476</v>
       </c>
       <c r="D16" t="n">
-        <v>182.8777777777778</v>
+        <v>179.8472222222222</v>
       </c>
       <c r="E16" t="n">
-        <v>1.122222222222222</v>
+        <v>1.162698412698413</v>
       </c>
       <c r="F16" t="n">
-        <v>71.95833333333334</v>
+        <v>70.54166666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>3914166.666666667</v>
+        <v>3019593.253968254</v>
       </c>
       <c r="H16" t="n">
-        <v>75.25833333333334</v>
-      </c>
-      <c r="I16" t="n">
-        <v>25.84343434343434</v>
-      </c>
-      <c r="J16" t="n">
-        <v>181.5691919191919</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.698686868686869</v>
-      </c>
-      <c r="L16" t="n">
-        <v>79.43323232323232</v>
-      </c>
-      <c r="M16" t="n">
-        <v>25763181.81818182</v>
-      </c>
-      <c r="N16" t="n">
-        <v>82.44686868686868</v>
-      </c>
+        <v>75.54563492063492</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>27.23790339052287</v>
+        <v>25.69795860457625</v>
       </c>
       <c r="P16" t="n">
-        <v>179.7714282347554</v>
+        <v>180.4825239643254</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.090361216602026</v>
+        <v>1.160973700863407</v>
       </c>
       <c r="R16" t="n">
-        <v>71.40358461493572</v>
+        <v>69.87127282439782</v>
       </c>
       <c r="S16" t="n">
-        <v>2888474.881939956</v>
+        <v>2449713.167925484</v>
       </c>
       <c r="T16" t="n">
-        <v>73.70217204670328</v>
+        <v>74.57414418370301</v>
       </c>
       <c r="U16" t="n">
-        <v>24.39584619486794</v>
+        <v>26.20995322044084</v>
       </c>
       <c r="V16" t="n">
-        <v>180.8557916117699</v>
+        <v>181.8257256349458</v>
       </c>
       <c r="W16" t="n">
-        <v>1.646155342242299</v>
+        <v>1.004385964912281</v>
       </c>
       <c r="X16" t="n">
-        <v>75.20563256791517</v>
+        <v>68.38324238218782</v>
       </c>
       <c r="Y16" t="n">
-        <v>15812387.8419286</v>
+        <v>2025701.885287557</v>
       </c>
       <c r="Z16" t="n">
-        <v>80.07366318464145</v>
+        <v>72.72207497202659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.28993055555555</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="D17" t="n">
-        <v>183.5694444444444</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>1.321180555555555</v>
+        <v>2.429166666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>76.14409722222223</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="G17" t="n">
-        <v>12212456.59722222</v>
+        <v>33006250</v>
       </c>
       <c r="H17" t="n">
-        <v>79.30381944444444</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="I17" t="n">
-        <v>28.70694444444445</v>
+        <v>26.8</v>
       </c>
       <c r="J17" t="n">
-        <v>179.6513888888889</v>
+        <v>183.0083333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>1.268055555555555</v>
+        <v>1.097222222222222</v>
       </c>
       <c r="L17" t="n">
-        <v>75.35277777777779</v>
+        <v>71.93055555555556</v>
       </c>
       <c r="M17" t="n">
-        <v>6780972.222222222</v>
+        <v>3944166.666666667</v>
       </c>
       <c r="N17" t="n">
-        <v>76.55694444444445</v>
+        <v>75.34722222222223</v>
       </c>
       <c r="O17" t="n">
-        <v>24.67694444444444</v>
+        <v>27.0506199321834</v>
       </c>
       <c r="P17" t="n">
-        <v>184.7762301587302</v>
+        <v>180.7196935967369</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.096865079365079</v>
+        <v>1.932325421396629</v>
       </c>
       <c r="R17" t="n">
-        <v>72.03696428571429</v>
+        <v>78.81242714629711</v>
       </c>
       <c r="S17" t="n">
-        <v>5435271.329365079</v>
+        <v>20477679.66484839</v>
       </c>
       <c r="T17" t="n">
-        <v>77.33422619047619</v>
+        <v>81.66069094304387</v>
       </c>
       <c r="U17" t="n">
-        <v>29.1236299081036</v>
+        <v>27.06555490567439</v>
       </c>
       <c r="V17" t="n">
-        <v>180.5778634085213</v>
+        <v>179.5725645983918</v>
       </c>
       <c r="W17" t="n">
-        <v>1.393653926482874</v>
+        <v>1.079944549935359</v>
       </c>
       <c r="X17" t="n">
-        <v>74.63693817878028</v>
+        <v>71.34866037251147</v>
       </c>
       <c r="Y17" t="n">
-        <v>5295762.635756057</v>
+        <v>2953721.094061168</v>
       </c>
       <c r="Z17" t="n">
-        <v>75.45333124477861</v>
+        <v>73.87925538003662</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.50299873737374</v>
+        <v>25.77777777777778</v>
       </c>
       <c r="D18" t="n">
-        <v>181.7230113636363</v>
+        <v>181.6055555555556</v>
       </c>
       <c r="E18" t="n">
-        <v>2.787689393939394</v>
+        <v>1.705757575757576</v>
       </c>
       <c r="F18" t="n">
-        <v>83.56650883838384</v>
+        <v>79.09080808080807</v>
       </c>
       <c r="G18" t="n">
-        <v>63154198.23232324</v>
+        <v>24896010.1010101</v>
       </c>
       <c r="H18" t="n">
-        <v>87.18503787878788</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>25.9074074074074</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="J18" t="n">
-        <v>180.0069444444445</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="K18" t="n">
-        <v>1.189814814814815</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>70.3912037037037</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="M18" t="n">
-        <v>2919155.092592593</v>
+        <v>4062500</v>
       </c>
       <c r="N18" t="n">
-        <v>75.54398148148148</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="O18" t="n">
-        <v>25.13281690693971</v>
+        <v>24.33056841709016</v>
       </c>
       <c r="P18" t="n">
-        <v>179.9695843062071</v>
+        <v>180.5030138339921</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.832384111989375</v>
+        <v>1.639210897797855</v>
       </c>
       <c r="R18" t="n">
-        <v>82.99050600147092</v>
+        <v>75.37785479013739</v>
       </c>
       <c r="S18" t="n">
-        <v>63210719.4178466</v>
+        <v>16504748.95303971</v>
       </c>
       <c r="T18" t="n">
-        <v>87.23376773486423</v>
+        <v>80.29241318464145</v>
       </c>
       <c r="U18" t="n">
-        <v>25.91150027124292</v>
+        <v>23.60128285139727</v>
       </c>
       <c r="V18" t="n">
-        <v>180.617196583373</v>
+        <v>180.8280609296628</v>
       </c>
       <c r="W18" t="n">
-        <v>1.179574891339597</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>69.96502282439782</v>
+        <v>70.67347007175383</v>
       </c>
       <c r="Y18" t="n">
-        <v>2379828.495306436</v>
+        <v>3797718.542898749</v>
       </c>
       <c r="Z18" t="n">
-        <v>74.48039418370301</v>
+        <v>76.33266895829824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="D19" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="F19" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="H19" t="n">
+        <v>82.5175</v>
+      </c>
       <c r="I19" t="n">
-        <v>24.91666666666667</v>
+        <v>26.8125</v>
       </c>
       <c r="J19" t="n">
-        <v>179.6219135802469</v>
+        <v>182.4375</v>
       </c>
       <c r="K19" t="n">
-        <v>1.027777777777778</v>
+        <v>1.1875</v>
       </c>
       <c r="L19" t="n">
-        <v>74.98456790123457</v>
+        <v>74.4375</v>
       </c>
       <c r="M19" t="n">
-        <v>10353395.0617284</v>
+        <v>10537500</v>
       </c>
       <c r="N19" t="n">
-        <v>78.64351851851853</v>
+        <v>77.875</v>
       </c>
       <c r="O19" t="n">
-        <v>26.18199269412505</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="P19" t="n">
-        <v>181.7001773893318</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="R19" t="n">
-        <v>67.97260641727554</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="S19" t="n">
-        <v>1721028.091427908</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="T19" t="n">
-        <v>72.42437760360555</v>
+        <v>80.79895227198431</v>
       </c>
       <c r="U19" t="n">
-        <v>26.42893347936221</v>
+        <v>26.0051683039183</v>
       </c>
       <c r="V19" t="n">
-        <v>178.9630502086418</v>
+        <v>180.7583484570985</v>
       </c>
       <c r="W19" t="n">
-        <v>1.132251190053721</v>
+        <v>1.052065295815296</v>
       </c>
       <c r="X19" t="n">
-        <v>73.06551236554535</v>
+        <v>73.06781801531801</v>
       </c>
       <c r="Y19" t="n">
-        <v>5814538.363171356</v>
+        <v>8045446.87950938</v>
       </c>
       <c r="Z19" t="n">
-        <v>75.27621899435871</v>
+        <v>77.04208374958375</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>23.64814814814815</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="D20" t="n">
-        <v>182.0972222222223</v>
+        <v>179.671875</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.03125</v>
       </c>
       <c r="F20" t="n">
-        <v>71.25462962962963</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="G20" t="n">
-        <v>4062500</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="H20" t="n">
-        <v>77.19907407407408</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="I20" t="n">
-        <v>27.78395061728395</v>
+        <v>25.52118055555555</v>
       </c>
       <c r="J20" t="n">
-        <v>182.037037037037</v>
+        <v>182.0582386363636</v>
       </c>
       <c r="K20" t="n">
-        <v>1.871913580246914</v>
+        <v>2.859280303030303</v>
       </c>
       <c r="L20" t="n">
-        <v>76.6141975308642</v>
+        <v>83.77219065656566</v>
       </c>
       <c r="M20" t="n">
-        <v>12136728.39506173</v>
+        <v>65004766.41414142</v>
       </c>
       <c r="N20" t="n">
-        <v>78.90586419753087</v>
+        <v>87.31799242424242</v>
       </c>
       <c r="O20" t="n">
-        <v>23.53052261747914</v>
+        <v>26.25620620663493</v>
       </c>
       <c r="P20" t="n">
-        <v>180.7263065436979</v>
+        <v>178.6930502086418</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>1.13134209914463</v>
       </c>
       <c r="R20" t="n">
-        <v>70.54598469163686</v>
+        <v>73.17096691099989</v>
       </c>
       <c r="S20" t="n">
-        <v>3713771.174477696</v>
+        <v>6018265.635898629</v>
       </c>
       <c r="T20" t="n">
-        <v>76.28237656063743</v>
+        <v>75.4571280852678</v>
       </c>
       <c r="U20" t="n">
-        <v>28.1894246031746</v>
+        <v>25.07216679519311</v>
       </c>
       <c r="V20" t="n">
-        <v>183.5720833333333</v>
+        <v>179.6831521913759</v>
       </c>
       <c r="W20" t="n">
-        <v>2.023333333333333</v>
+        <v>2.754408858685175</v>
       </c>
       <c r="X20" t="n">
-        <v>75.9471626984127</v>
+        <v>82.48092908553436</v>
       </c>
       <c r="Y20" t="n">
-        <v>10458496.03174603</v>
+        <v>60388463.26553564</v>
       </c>
       <c r="Z20" t="n">
-        <v>79.1536111111111</v>
+        <v>86.84723306664095</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>25.20631313131313</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="D21" t="n">
-        <v>183.1111111111111</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="E21" t="n">
-        <v>1.478030303030303</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>78.86186868686868</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="G21" t="n">
-        <v>23356818.18181818</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="H21" t="n">
-        <v>82.16363636363636</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="I21" t="n">
-        <v>25.87361111111111</v>
+        <v>25.76190476190476</v>
       </c>
       <c r="J21" t="n">
-        <v>181.775</v>
+        <v>179.8472222222222</v>
       </c>
       <c r="K21" t="n">
-        <v>2.715277777777778</v>
+        <v>1.162698412698413</v>
       </c>
       <c r="L21" t="n">
-        <v>81.15000000000001</v>
+        <v>70.54166666666666</v>
       </c>
       <c r="M21" t="n">
-        <v>43920694.44444444</v>
+        <v>3019593.253968254</v>
       </c>
       <c r="N21" t="n">
-        <v>85.49027777777778</v>
+        <v>75.54563492063492</v>
       </c>
       <c r="O21" t="n">
-        <v>25.33190728321512</v>
+        <v>23.21304510816878</v>
       </c>
       <c r="P21" t="n">
-        <v>181.6462106869338</v>
+        <v>180.7381363745138</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.340570903172624</v>
+        <v>2.223463612093475</v>
       </c>
       <c r="R21" t="n">
-        <v>75.61980094229571</v>
+        <v>78.53135254143265</v>
       </c>
       <c r="S21" t="n">
-        <v>13677224.33421806</v>
+        <v>38380836.30838265</v>
       </c>
       <c r="T21" t="n">
-        <v>79.89114879153243</v>
+        <v>84.88019462018217</v>
       </c>
       <c r="U21" t="n">
-        <v>23.46750939388307</v>
+        <v>25.69795860457625</v>
       </c>
       <c r="V21" t="n">
-        <v>180.6559935173709</v>
+        <v>180.4825239643254</v>
       </c>
       <c r="W21" t="n">
-        <v>2.183285040664904</v>
+        <v>1.160973700863407</v>
       </c>
       <c r="X21" t="n">
-        <v>78.51349539857549</v>
+        <v>69.87127282439782</v>
       </c>
       <c r="Y21" t="n">
-        <v>36364898.80838265</v>
+        <v>2449713.167925484</v>
       </c>
       <c r="Z21" t="n">
-        <v>84.76769462018217</v>
+        <v>74.57414418370301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.33383838383838</v>
+      </c>
+      <c r="D22" t="n">
+        <v>183.270202020202</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="F22" t="n">
+        <v>78.66742424242423</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22654797.97979798</v>
+      </c>
+      <c r="H22" t="n">
+        <v>81.9729797979798</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28.56111111111111</v>
+      </c>
+      <c r="J22" t="n">
+        <v>180.1458333333333</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.429166666666667</v>
+      </c>
+      <c r="L22" t="n">
+        <v>82.12083333333332</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33006250</v>
+      </c>
+      <c r="N22" t="n">
+        <v>83.69444444444444</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25.2314288143156</v>
+      </c>
+      <c r="P22" t="n">
+        <v>181.6767130792783</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.372269467765925</v>
+      </c>
+      <c r="R22" t="n">
+        <v>75.65688228200862</v>
+      </c>
+      <c r="S22" t="n">
+        <v>13939784.1428305</v>
+      </c>
+      <c r="T22" t="n">
+        <v>80.02033539440323</v>
+      </c>
+      <c r="U22" t="n">
+        <v>27.0506199321834</v>
+      </c>
+      <c r="V22" t="n">
+        <v>180.7196935967369</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.932325421396629</v>
+      </c>
+      <c r="X22" t="n">
+        <v>78.81242714629711</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>20477679.66484839</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>81.66069094304387</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>183.0083333333334</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.097222222222222</v>
+      </c>
+      <c r="F23" t="n">
+        <v>71.93055555555556</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3944166.666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.34722222222223</v>
+      </c>
+      <c r="I23" t="n">
+        <v>28.73055555555555</v>
+      </c>
+      <c r="J23" t="n">
+        <v>179.5638888888889</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="L23" t="n">
+        <v>75.32083333333334</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6703055.555555555</v>
+      </c>
+      <c r="N23" t="n">
+        <v>76.56527777777778</v>
+      </c>
+      <c r="O23" t="n">
+        <v>27.06555490567439</v>
+      </c>
+      <c r="P23" t="n">
+        <v>179.5725645983918</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.079944549935359</v>
+      </c>
+      <c r="R23" t="n">
+        <v>71.34866037251147</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2953721.094061168</v>
+      </c>
+      <c r="T23" t="n">
+        <v>73.87925538003662</v>
+      </c>
+      <c r="U23" t="n">
+        <v>28.85886800334168</v>
+      </c>
+      <c r="V23" t="n">
+        <v>180.164530075188</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.34984440267335</v>
+      </c>
+      <c r="X23" t="n">
+        <v>74.55217627401836</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5359476.921470342</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>75.46285505430242</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>27.74242424242425</v>
+      </c>
+      <c r="J24" t="n">
+        <v>183.4183654729109</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.281542699724518</v>
+      </c>
+      <c r="L24" t="n">
+        <v>75.81662075298438</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9759742.883379247</v>
+      </c>
+      <c r="N24" t="n">
+        <v>77.65858585858585</v>
+      </c>
+      <c r="O24" t="n">
+        <v>26.20995322044084</v>
+      </c>
+      <c r="P24" t="n">
+        <v>181.8257256349458</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.004385964912281</v>
+      </c>
+      <c r="R24" t="n">
+        <v>68.38324238218782</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2025701.885287557</v>
+      </c>
+      <c r="T24" t="n">
+        <v>72.72207497202659</v>
+      </c>
+      <c r="U24" t="n">
+        <v>27.13480060609247</v>
+      </c>
+      <c r="V24" t="n">
+        <v>181.1055427825763</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.101619672193835</v>
+      </c>
+      <c r="X24" t="n">
+        <v>74.44492588750963</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>7526368.750866359</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>76.6142852362948</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="D25" t="n">
+        <v>181.5194444444444</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.122222222222222</v>
+      </c>
+      <c r="F25" t="n">
+        <v>71.55833333333332</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9487916.666666666</v>
+      </c>
+      <c r="H25" t="n">
+        <v>77.56527777777778</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="J25" t="n">
+        <v>185.5520833333334</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="L25" t="n">
+        <v>76.02083333333334</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10193402.77777778</v>
+      </c>
+      <c r="N25" t="n">
+        <v>79.05208333333334</v>
+      </c>
+      <c r="O25" t="n">
+        <v>23.81081785041115</v>
+      </c>
+      <c r="P25" t="n">
+        <v>180.1849900577891</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.070309917355372</v>
+      </c>
+      <c r="R25" t="n">
+        <v>70.76879445514614</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5187711.899842582</v>
+      </c>
+      <c r="T25" t="n">
+        <v>76.25636917707492</v>
+      </c>
+      <c r="U25" t="n">
+        <v>27.46666316526611</v>
+      </c>
+      <c r="V25" t="n">
+        <v>182.7437883311219</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.619802078726227</v>
+      </c>
+      <c r="X25" t="n">
+        <v>76.36418656936459</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9585836.848555211</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>79.15731497862302</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="D26" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="H26" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="I26" t="n">
+        <v>24.97569444444444</v>
+      </c>
+      <c r="J26" t="n">
+        <v>179.671875</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.03125</v>
+      </c>
+      <c r="L26" t="n">
+        <v>74.95486111111111</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10317013.88888889</v>
+      </c>
+      <c r="N26" t="n">
+        <v>78.54340277777777</v>
+      </c>
+      <c r="O26" t="n">
+        <v>23.60128285139727</v>
+      </c>
+      <c r="P26" t="n">
+        <v>180.8280609296628</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>70.67347007175383</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3797718.542898749</v>
+      </c>
+      <c r="T26" t="n">
+        <v>76.33266895829824</v>
+      </c>
+      <c r="U26" t="n">
+        <v>26.25620620663493</v>
+      </c>
+      <c r="V26" t="n">
+        <v>178.6930502086418</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.13134209914463</v>
+      </c>
+      <c r="X26" t="n">
+        <v>73.17096691099989</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6018265.635898629</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>75.4571280852678</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="D27" t="n">
+        <v>182.4375</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10537500</v>
+      </c>
+      <c r="H27" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>27.00925925925926</v>
+      </c>
+      <c r="J27" t="n">
+        <v>181.9737654320987</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="L27" t="n">
+        <v>75.12191358024693</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8219135.802469134</v>
+      </c>
+      <c r="N27" t="n">
+        <v>78.20555555555556</v>
+      </c>
+      <c r="O27" t="n">
+        <v>26.0051683039183</v>
+      </c>
+      <c r="P27" t="n">
+        <v>180.7583484570985</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.052065295815296</v>
+      </c>
+      <c r="R27" t="n">
+        <v>73.06781801531801</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8045446.87950938</v>
+      </c>
+      <c r="T27" t="n">
+        <v>77.04208374958375</v>
+      </c>
+      <c r="U27" t="n">
+        <v>25.42484848484849</v>
+      </c>
+      <c r="V27" t="n">
+        <v>180.1719408369408</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.190613275613276</v>
+      </c>
+      <c r="X27" t="n">
+        <v>73.70076479076479</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>7235113.636363636</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>77.20712842712842</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>28.06222222222222</v>
+      </c>
+      <c r="D28" t="n">
+        <v>185.0286111111111</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.990555555555555</v>
+      </c>
+      <c r="F28" t="n">
+        <v>77.65944444444445</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13911166.66666667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>80.0975</v>
+      </c>
+      <c r="I28" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="J28" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L28" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="N28" t="n">
+        <v>82.5175</v>
+      </c>
+      <c r="O28" t="n">
+        <v>25.56743368438146</v>
+      </c>
+      <c r="P28" t="n">
+        <v>182.996596157914</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.640669384458589</v>
+      </c>
+      <c r="R28" t="n">
+        <v>75.67931720819526</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11720844.0848498</v>
+      </c>
+      <c r="T28" t="n">
+        <v>80.21350895354327</v>
+      </c>
+      <c r="U28" t="n">
+        <v>24.0748204751008</v>
+      </c>
+      <c r="V28" t="n">
+        <v>179.0032096545712</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.136246730957829</v>
+      </c>
+      <c r="X28" t="n">
+        <v>74.80828783916313</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14677284.62460499</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>80.79895227198431</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>26.34413580246913</v>
+      </c>
+      <c r="D29" t="n">
+        <v>183.1604938271605</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.322530864197531</v>
+      </c>
+      <c r="F29" t="n">
+        <v>75.97993827160494</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11894714.50617284</v>
+      </c>
+      <c r="H29" t="n">
+        <v>79.08487654320987</v>
+      </c>
+      <c r="I29" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="J29" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="L29" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="M29" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="N29" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24.49551587301588</v>
+      </c>
+      <c r="P29" t="n">
+        <v>184.1648015873016</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.096865079365079</v>
+      </c>
+      <c r="R29" t="n">
+        <v>71.97553571428571</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5478414.186507936</v>
+      </c>
+      <c r="T29" t="n">
+        <v>77.42136904761905</v>
+      </c>
+      <c r="U29" t="n">
+        <v>24.33056841709016</v>
+      </c>
+      <c r="V29" t="n">
+        <v>180.5030138339921</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.639210897797855</v>
+      </c>
+      <c r="X29" t="n">
+        <v>75.37785479013739</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16504748.95303971</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>80.29241318464145</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D30" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F30" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G30" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H30" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I30" t="n">
+        <v>27.86631944444444</v>
+      </c>
+      <c r="J30" t="n">
+        <v>181.9479166666667</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.887152777777778</v>
+      </c>
+      <c r="L30" t="n">
+        <v>76.58159722222223</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11931944.44444444</v>
+      </c>
+      <c r="N30" t="n">
+        <v>78.83159722222223</v>
+      </c>
+      <c r="O30" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="P30" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="R30" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="S30" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="T30" t="n">
+        <v>86.84723306664095</v>
+      </c>
+      <c r="U30" t="n">
+        <v>27.65425976800977</v>
+      </c>
+      <c r="V30" t="n">
+        <v>183.4720833333333</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.954102564102564</v>
+      </c>
+      <c r="X30" t="n">
+        <v>75.75265720390721</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10349814.71306472</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>79.18877594627595</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>25.33383838383838</v>
+      </c>
+      <c r="D31" t="n">
+        <v>183.270202020202</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="F31" t="n">
+        <v>78.66742424242423</v>
+      </c>
+      <c r="G31" t="n">
+        <v>22654797.97979798</v>
+      </c>
+      <c r="H31" t="n">
+        <v>81.9729797979798</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.99537037037037</v>
+      </c>
+      <c r="J31" t="n">
+        <v>181.7623456790124</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="L31" t="n">
+        <v>81.29012345679013</v>
+      </c>
+      <c r="M31" t="n">
+        <v>44161265.43209876</v>
+      </c>
+      <c r="N31" t="n">
+        <v>85.47067901234567</v>
+      </c>
+      <c r="O31" t="n">
+        <v>25.2314288143156</v>
+      </c>
+      <c r="P31" t="n">
+        <v>181.6767130792783</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.372269467765925</v>
+      </c>
+      <c r="R31" t="n">
+        <v>75.65688228200862</v>
+      </c>
+      <c r="S31" t="n">
+        <v>13939784.1428305</v>
+      </c>
+      <c r="T31" t="n">
+        <v>80.02033539440323</v>
+      </c>
+      <c r="U31" t="n">
+        <v>23.21304510816878</v>
+      </c>
+      <c r="V31" t="n">
+        <v>180.7381363745138</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.223463612093475</v>
+      </c>
+      <c r="X31" t="n">
+        <v>78.53135254143265</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>38380836.30838265</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>84.88019462018217</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>25.50299873737374</v>
-      </c>
-      <c r="D22" t="n">
-        <v>181.7230113636363</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.787689393939394</v>
-      </c>
-      <c r="F22" t="n">
-        <v>83.56650883838384</v>
-      </c>
-      <c r="G22" t="n">
-        <v>63154198.23232324</v>
-      </c>
-      <c r="H22" t="n">
-        <v>87.18503787878788</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27.74545454545455</v>
-      </c>
-      <c r="J22" t="n">
-        <v>183.3537190082644</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.269421487603306</v>
-      </c>
-      <c r="L22" t="n">
-        <v>75.69338842975206</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9326611.570247935</v>
-      </c>
-      <c r="N22" t="n">
-        <v>77.49090909090908</v>
-      </c>
-      <c r="O22" t="n">
-        <v>25.13281690693971</v>
-      </c>
-      <c r="P22" t="n">
-        <v>179.9695843062071</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.832384111989375</v>
-      </c>
-      <c r="R22" t="n">
-        <v>82.99050600147092</v>
-      </c>
-      <c r="S22" t="n">
-        <v>63210719.4178466</v>
-      </c>
-      <c r="T22" t="n">
-        <v>87.23376773486423</v>
-      </c>
-      <c r="U22" t="n">
-        <v>27.29139042775406</v>
-      </c>
-      <c r="V22" t="n">
-        <v>180.8754427390791</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.105099446008537</v>
-      </c>
-      <c r="X22" t="n">
-        <v>74.46884933248569</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>7590431.386795023</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>76.58514213059667</v>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D32" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F32" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G32" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H32" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I32" t="n">
+        <v>27.74242424242425</v>
+      </c>
+      <c r="J32" t="n">
+        <v>183.4183654729109</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.281542699724518</v>
+      </c>
+      <c r="L32" t="n">
+        <v>75.81662075298438</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9759742.883379247</v>
+      </c>
+      <c r="N32" t="n">
+        <v>77.65858585858585</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="P32" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="R32" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="S32" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="T32" t="n">
+        <v>86.84723306664095</v>
+      </c>
+      <c r="U32" t="n">
+        <v>27.13480060609247</v>
+      </c>
+      <c r="V32" t="n">
+        <v>181.1055427825763</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.101619672193835</v>
+      </c>
+      <c r="X32" t="n">
+        <v>74.44492588750963</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7526368.750866359</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>76.6142852362948</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,22 +929,22 @@
         <v>82.26000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>27.06555490567439</v>
+        <v>26.97468713748125</v>
       </c>
       <c r="P6" t="n">
-        <v>179.5725645983918</v>
+        <v>179.3821641430465</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.079944549935359</v>
+        <v>1.075750377073907</v>
       </c>
       <c r="R6" t="n">
-        <v>71.34866037251147</v>
+        <v>71.31476154020271</v>
       </c>
       <c r="S6" t="n">
-        <v>2953721.094061168</v>
+        <v>2982064.405093817</v>
       </c>
       <c r="T6" t="n">
-        <v>73.87925538003662</v>
+        <v>73.94739621489622</v>
       </c>
       <c r="U6" t="n">
         <v>24.33056841709016</v>
@@ -1163,22 +1163,22 @@
         <v>78.54340277777777</v>
       </c>
       <c r="O9" t="n">
-        <v>26.20995322044084</v>
+        <v>26.2795449273496</v>
       </c>
       <c r="P9" t="n">
-        <v>181.8257256349458</v>
+        <v>181.9058421068096</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.004385964912281</v>
+        <v>1.004784688995215</v>
       </c>
       <c r="R9" t="n">
-        <v>68.38324238218782</v>
+        <v>68.43323411390188</v>
       </c>
       <c r="S9" t="n">
-        <v>2025701.885287557</v>
+        <v>2056194.985970264</v>
       </c>
       <c r="T9" t="n">
-        <v>72.72207497202659</v>
+        <v>72.81802118160478</v>
       </c>
       <c r="U9" t="n">
         <v>26.25620620663493</v>
@@ -1297,7 +1297,7 @@
         <v>180.1458333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>2.429166666666667</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="F11" t="n">
         <v>82.12083333333332</v>
@@ -1743,22 +1743,22 @@
         <v>74.57414418370301</v>
       </c>
       <c r="U16" t="n">
-        <v>26.20995322044084</v>
+        <v>26.2795449273496</v>
       </c>
       <c r="V16" t="n">
-        <v>181.8257256349458</v>
+        <v>181.9058421068096</v>
       </c>
       <c r="W16" t="n">
-        <v>1.004385964912281</v>
+        <v>1.004784688995215</v>
       </c>
       <c r="X16" t="n">
-        <v>68.38324238218782</v>
+        <v>68.43323411390188</v>
       </c>
       <c r="Y16" t="n">
-        <v>2025701.885287557</v>
+        <v>2056194.985970264</v>
       </c>
       <c r="Z16" t="n">
-        <v>72.72207497202659</v>
+        <v>72.81802118160478</v>
       </c>
     </row>
     <row r="17">
@@ -1777,7 +1777,7 @@
         <v>180.1458333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>2.429166666666667</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="F17" t="n">
         <v>82.12083333333332</v>
@@ -1825,22 +1825,22 @@
         <v>81.66069094304387</v>
       </c>
       <c r="U17" t="n">
-        <v>27.06555490567439</v>
+        <v>26.97468713748125</v>
       </c>
       <c r="V17" t="n">
-        <v>179.5725645983918</v>
+        <v>179.3821641430465</v>
       </c>
       <c r="W17" t="n">
-        <v>1.079944549935359</v>
+        <v>1.075750377073907</v>
       </c>
       <c r="X17" t="n">
-        <v>71.34866037251147</v>
+        <v>71.31476154020271</v>
       </c>
       <c r="Y17" t="n">
-        <v>2953721.094061168</v>
+        <v>2982064.405093817</v>
       </c>
       <c r="Z17" t="n">
-        <v>73.87925538003662</v>
+        <v>73.94739621489622</v>
       </c>
     </row>
     <row r="18">
@@ -2205,7 +2205,7 @@
         <v>180.1458333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>2.429166666666667</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="L22" t="n">
         <v>82.12083333333332</v>
@@ -2299,22 +2299,22 @@
         <v>76.56527777777778</v>
       </c>
       <c r="O23" t="n">
-        <v>27.06555490567439</v>
+        <v>26.97468713748125</v>
       </c>
       <c r="P23" t="n">
-        <v>179.5725645983918</v>
+        <v>179.3821641430465</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.079944549935359</v>
+        <v>1.075750377073907</v>
       </c>
       <c r="R23" t="n">
-        <v>71.34866037251147</v>
+        <v>71.31476154020271</v>
       </c>
       <c r="S23" t="n">
-        <v>2953721.094061168</v>
+        <v>2982064.405093817</v>
       </c>
       <c r="T23" t="n">
-        <v>73.87925538003662</v>
+        <v>73.94739621489622</v>
       </c>
       <c r="U23" t="n">
         <v>28.85886800334168</v>
@@ -2369,22 +2369,22 @@
         <v>77.65858585858585</v>
       </c>
       <c r="O24" t="n">
-        <v>26.20995322044084</v>
+        <v>26.2795449273496</v>
       </c>
       <c r="P24" t="n">
-        <v>181.8257256349458</v>
+        <v>181.9058421068096</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.004385964912281</v>
+        <v>1.004784688995215</v>
       </c>
       <c r="R24" t="n">
-        <v>68.38324238218782</v>
+        <v>68.43323411390188</v>
       </c>
       <c r="S24" t="n">
-        <v>2025701.885287557</v>
+        <v>2056194.985970264</v>
       </c>
       <c r="T24" t="n">
-        <v>72.72207497202659</v>
+        <v>72.81802118160478</v>
       </c>
       <c r="U24" t="n">
         <v>27.13480060609247</v>
@@ -2895,170 +2895,6 @@
       </c>
       <c r="Z30" t="n">
         <v>79.18877594627595</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>25.33383838383838</v>
-      </c>
-      <c r="D31" t="n">
-        <v>183.270202020202</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.452777777777778</v>
-      </c>
-      <c r="F31" t="n">
-        <v>78.66742424242423</v>
-      </c>
-      <c r="G31" t="n">
-        <v>22654797.97979798</v>
-      </c>
-      <c r="H31" t="n">
-        <v>81.9729797979798</v>
-      </c>
-      <c r="I31" t="n">
-        <v>25.99537037037037</v>
-      </c>
-      <c r="J31" t="n">
-        <v>181.7623456790124</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.708333333333333</v>
-      </c>
-      <c r="L31" t="n">
-        <v>81.29012345679013</v>
-      </c>
-      <c r="M31" t="n">
-        <v>44161265.43209876</v>
-      </c>
-      <c r="N31" t="n">
-        <v>85.47067901234567</v>
-      </c>
-      <c r="O31" t="n">
-        <v>25.2314288143156</v>
-      </c>
-      <c r="P31" t="n">
-        <v>181.6767130792783</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.372269467765925</v>
-      </c>
-      <c r="R31" t="n">
-        <v>75.65688228200862</v>
-      </c>
-      <c r="S31" t="n">
-        <v>13939784.1428305</v>
-      </c>
-      <c r="T31" t="n">
-        <v>80.02033539440323</v>
-      </c>
-      <c r="U31" t="n">
-        <v>23.21304510816878</v>
-      </c>
-      <c r="V31" t="n">
-        <v>180.7381363745138</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.223463612093475</v>
-      </c>
-      <c r="X31" t="n">
-        <v>78.53135254143265</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>38380836.30838265</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>84.88019462018217</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>25.52118055555555</v>
-      </c>
-      <c r="D32" t="n">
-        <v>182.0582386363636</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.859280303030303</v>
-      </c>
-      <c r="F32" t="n">
-        <v>83.77219065656566</v>
-      </c>
-      <c r="G32" t="n">
-        <v>65004766.41414142</v>
-      </c>
-      <c r="H32" t="n">
-        <v>87.31799242424242</v>
-      </c>
-      <c r="I32" t="n">
-        <v>27.74242424242425</v>
-      </c>
-      <c r="J32" t="n">
-        <v>183.4183654729109</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.281542699724518</v>
-      </c>
-      <c r="L32" t="n">
-        <v>75.81662075298438</v>
-      </c>
-      <c r="M32" t="n">
-        <v>9759742.883379247</v>
-      </c>
-      <c r="N32" t="n">
-        <v>77.65858585858585</v>
-      </c>
-      <c r="O32" t="n">
-        <v>25.07216679519311</v>
-      </c>
-      <c r="P32" t="n">
-        <v>179.6831521913759</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.754408858685175</v>
-      </c>
-      <c r="R32" t="n">
-        <v>82.48092908553436</v>
-      </c>
-      <c r="S32" t="n">
-        <v>60388463.26553564</v>
-      </c>
-      <c r="T32" t="n">
-        <v>86.84723306664095</v>
-      </c>
-      <c r="U32" t="n">
-        <v>27.13480060609247</v>
-      </c>
-      <c r="V32" t="n">
-        <v>181.1055427825763</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.101619672193835</v>
-      </c>
-      <c r="X32" t="n">
-        <v>74.44492588750963</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>7526368.750866359</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>76.6142852362948</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,329 +558,1851 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.8125</v>
+        <v>25.52118055555555</v>
       </c>
       <c r="D2" t="n">
-        <v>182.4375</v>
+        <v>182.0582386363636</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1875</v>
+        <v>2.859280303030303</v>
       </c>
       <c r="F2" t="n">
-        <v>74.4375</v>
+        <v>83.77219065656566</v>
       </c>
       <c r="G2" t="n">
-        <v>10537500</v>
+        <v>65004766.41414142</v>
       </c>
       <c r="H2" t="n">
-        <v>77.875</v>
+        <v>87.31799242424242</v>
       </c>
       <c r="I2" t="n">
-        <v>27.74242424242425</v>
+        <v>25.55555555555555</v>
       </c>
       <c r="J2" t="n">
-        <v>183.4183654729109</v>
+        <v>179.863425925926</v>
       </c>
       <c r="K2" t="n">
-        <v>1.281542699724518</v>
+        <v>1.148148148148148</v>
       </c>
       <c r="L2" t="n">
-        <v>75.81662075298438</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="M2" t="n">
-        <v>9759742.883379247</v>
+        <v>3008796.296296296</v>
       </c>
       <c r="N2" t="n">
-        <v>77.65858585858585</v>
+        <v>75.57407407407408</v>
       </c>
       <c r="O2" t="n">
-        <v>26.0051683039183</v>
+        <v>25.07216679519311</v>
       </c>
       <c r="P2" t="n">
-        <v>180.7583484570985</v>
+        <v>179.6831521913759</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.052065295815296</v>
+        <v>2.754408858685175</v>
       </c>
       <c r="R2" t="n">
-        <v>73.06781801531801</v>
+        <v>82.48092908553436</v>
       </c>
       <c r="S2" t="n">
-        <v>8045446.87950938</v>
+        <v>60388463.26553564</v>
       </c>
       <c r="T2" t="n">
-        <v>77.04208374958375</v>
+        <v>86.84723306664095</v>
       </c>
       <c r="U2" t="n">
-        <v>27.13480060609247</v>
+        <v>25.63553526093633</v>
       </c>
       <c r="V2" t="n">
-        <v>181.1055427825763</v>
+        <v>180.386529639404</v>
       </c>
       <c r="W2" t="n">
-        <v>1.101619672193835</v>
+        <v>1.161621659683157</v>
       </c>
       <c r="X2" t="n">
-        <v>74.44492588750963</v>
+        <v>69.86656336088154</v>
       </c>
       <c r="Y2" t="n">
-        <v>7526368.750866359</v>
+        <v>2497064.714659968</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.6142852362948</v>
+        <v>74.70326218641726</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>25.99537037037037</v>
-      </c>
-      <c r="D3" t="n">
-        <v>181.7623456790124</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.708333333333333</v>
-      </c>
-      <c r="F3" t="n">
-        <v>81.29012345679013</v>
-      </c>
-      <c r="G3" t="n">
-        <v>44161265.43209876</v>
-      </c>
-      <c r="H3" t="n">
-        <v>85.47067901234567</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>25.33383838383838</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="J3" t="n">
-        <v>183.270202020202</v>
+        <v>179.671875</v>
       </c>
       <c r="K3" t="n">
-        <v>1.452777777777778</v>
+        <v>1.03125</v>
       </c>
       <c r="L3" t="n">
-        <v>78.66742424242423</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>22654797.97979798</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="N3" t="n">
-        <v>81.9729797979798</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="O3" t="n">
-        <v>23.21304510816878</v>
+        <v>26.2795449273496</v>
       </c>
       <c r="P3" t="n">
-        <v>180.7381363745138</v>
+        <v>181.9058421068096</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.223463612093475</v>
+        <v>1.004784688995215</v>
       </c>
       <c r="R3" t="n">
-        <v>78.53135254143265</v>
+        <v>68.43323411390188</v>
       </c>
       <c r="S3" t="n">
-        <v>38380836.30838265</v>
+        <v>2056194.985970264</v>
       </c>
       <c r="T3" t="n">
-        <v>84.88019462018217</v>
+        <v>72.81802118160478</v>
       </c>
       <c r="U3" t="n">
-        <v>25.2314288143156</v>
+        <v>26.25620620663493</v>
       </c>
       <c r="V3" t="n">
-        <v>181.6767130792783</v>
+        <v>178.6930502086418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.372269467765925</v>
+        <v>1.13134209914463</v>
       </c>
       <c r="X3" t="n">
-        <v>75.65688228200862</v>
+        <v>73.17096691099989</v>
       </c>
       <c r="Y3" t="n">
-        <v>13939784.1428305</v>
+        <v>6018265.635898629</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.02033539440323</v>
+        <v>75.4571280852678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.8</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="D4" t="n">
-        <v>183.0083333333334</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="E4" t="n">
-        <v>1.097222222222222</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>71.93055555555556</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="G4" t="n">
-        <v>3944166.666666667</v>
+        <v>4062500</v>
       </c>
       <c r="H4" t="n">
-        <v>75.34722222222223</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="I4" t="n">
-        <v>25.77777777777778</v>
+        <v>27.86631944444444</v>
       </c>
       <c r="J4" t="n">
-        <v>181.6055555555556</v>
+        <v>181.9479166666667</v>
       </c>
       <c r="K4" t="n">
-        <v>1.705757575757576</v>
+        <v>1.887152777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>79.09080808080807</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="M4" t="n">
-        <v>24896010.1010101</v>
+        <v>11931944.44444444</v>
       </c>
       <c r="N4" t="n">
-        <v>82.26000000000001</v>
+        <v>78.83159722222223</v>
       </c>
       <c r="O4" t="n">
-        <v>26.97468713748125</v>
+        <v>23.60128285139727</v>
       </c>
       <c r="P4" t="n">
-        <v>179.3821641430465</v>
+        <v>180.8280609296628</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.075750377073907</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>71.31476154020271</v>
+        <v>70.67347007175383</v>
       </c>
       <c r="S4" t="n">
-        <v>2982064.405093817</v>
+        <v>3797718.542898749</v>
       </c>
       <c r="T4" t="n">
-        <v>73.94739621489622</v>
+        <v>76.33266895829824</v>
       </c>
       <c r="U4" t="n">
-        <v>24.33056841709016</v>
+        <v>27.65425976800977</v>
       </c>
       <c r="V4" t="n">
-        <v>180.5030138339921</v>
+        <v>183.4720833333333</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639210897797855</v>
+        <v>1.954102564102564</v>
       </c>
       <c r="X4" t="n">
-        <v>75.37785479013739</v>
+        <v>75.75265720390721</v>
       </c>
       <c r="Y4" t="n">
-        <v>16504748.95303971</v>
+        <v>10349814.71306472</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.29241318464145</v>
+        <v>79.18877594627595</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>28.56111111111111</v>
+      </c>
+      <c r="D5" t="n">
+        <v>180.1458333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.429166666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82.12083333333332</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33006250</v>
+      </c>
+      <c r="H5" t="n">
+        <v>83.69444444444444</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="J5" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L5" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="N5" t="n">
+        <v>82.5175</v>
+      </c>
+      <c r="O5" t="n">
+        <v>27.0506199321834</v>
+      </c>
+      <c r="P5" t="n">
+        <v>180.7196935967369</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.932325421396629</v>
+      </c>
+      <c r="R5" t="n">
+        <v>78.81242714629711</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20477679.66484839</v>
+      </c>
+      <c r="T5" t="n">
+        <v>81.66069094304387</v>
+      </c>
+      <c r="U5" t="n">
+        <v>24.0748204751008</v>
+      </c>
+      <c r="V5" t="n">
+        <v>179.0032096545712</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.136246730957829</v>
+      </c>
+      <c r="X5" t="n">
+        <v>74.80828783916313</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14677284.62460499</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>80.79895227198431</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="D6" t="n">
+        <v>185.5520833333334</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>76.02083333333334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10193402.77777778</v>
+      </c>
+      <c r="H6" t="n">
+        <v>79.05208333333334</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27.00925925925926</v>
+      </c>
+      <c r="J6" t="n">
+        <v>181.9737654320987</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75.12191358024693</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8219135.802469134</v>
+      </c>
+      <c r="N6" t="n">
+        <v>78.20555555555556</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27.58333015024192</v>
+      </c>
+      <c r="P6" t="n">
+        <v>182.7216257555654</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.654365526114752</v>
+      </c>
+      <c r="R6" t="n">
+        <v>76.42956354790721</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9668185.013838071</v>
+      </c>
+      <c r="T6" t="n">
+        <v>79.19604391996032</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.55895316804408</v>
+      </c>
+      <c r="V6" t="n">
+        <v>180.1654007608553</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.218739341466614</v>
+      </c>
+      <c r="X6" t="n">
+        <v>73.75978617342254</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7529535.123966943</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>77.2428440246622</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.73611111111111</v>
+      </c>
+      <c r="D7" t="n">
+        <v>183.5594276094276</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.285858585858586</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75.87819865319865</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9983468.013468012</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.72407407407407</v>
+      </c>
+      <c r="I7" t="n">
+        <v>27.75353535353536</v>
+      </c>
+      <c r="J7" t="n">
+        <v>185.1169191919192</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.940909090909091</v>
+      </c>
+      <c r="L7" t="n">
+        <v>77.41767676767677</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13708131.31313132</v>
+      </c>
+      <c r="N7" t="n">
+        <v>80.08863636363637</v>
+      </c>
+      <c r="O7" t="n">
+        <v>27.132339152076</v>
+      </c>
+      <c r="P7" t="n">
+        <v>181.1581510594669</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.097537331089963</v>
+      </c>
+      <c r="R7" t="n">
+        <v>74.36837504600663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7397022.232153811</v>
+      </c>
+      <c r="T7" t="n">
+        <v>76.53239304555093</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.7703942585286</v>
+      </c>
+      <c r="V7" t="n">
+        <v>182.821148022346</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.655153985871445</v>
+      </c>
+      <c r="X7" t="n">
+        <v>75.80543988623812</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11820161.2892574</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>80.21834147291811</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28.73055555555555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>179.5638888888889</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75.32083333333334</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6703055.555555555</v>
+      </c>
+      <c r="H8" t="n">
+        <v>76.56527777777778</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25.99537037037037</v>
+      </c>
+      <c r="J8" t="n">
+        <v>181.7623456790124</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="L8" t="n">
+        <v>81.29012345679013</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44161265.43209876</v>
+      </c>
+      <c r="N8" t="n">
+        <v>85.47067901234567</v>
+      </c>
+      <c r="O8" t="n">
+        <v>28.85886800334168</v>
+      </c>
+      <c r="P8" t="n">
+        <v>180.164530075188</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.34984440267335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>74.55217627401836</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5359476.921470342</v>
+      </c>
+      <c r="T8" t="n">
+        <v>75.46285505430242</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22.94822282560798</v>
+      </c>
+      <c r="V8" t="n">
+        <v>180.8801239768307</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.130421465539523</v>
+      </c>
+      <c r="X8" t="n">
+        <v>77.51941140130239</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>35599396.64398423</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>84.24563147289287</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.31527777777778</v>
+      </c>
+      <c r="D9" t="n">
+        <v>183.3217592592593</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.442824074074074</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78.59328703703703</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22660416.66666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>81.97523148148149</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.60227272727273</v>
+      </c>
+      <c r="J9" t="n">
+        <v>181.5858585858586</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.133838383838384</v>
+      </c>
+      <c r="L9" t="n">
+        <v>71.59848484848484</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9680151.515151514</v>
+      </c>
+      <c r="N9" t="n">
+        <v>77.65025252525253</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25.15153701918324</v>
+      </c>
+      <c r="P9" t="n">
+        <v>181.7983506257021</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.367762163633916</v>
+      </c>
+      <c r="R9" t="n">
+        <v>75.51880875850792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13750483.94910977</v>
+      </c>
+      <c r="T9" t="n">
+        <v>80.01106502062721</v>
+      </c>
+      <c r="U9" t="n">
+        <v>23.90011244130826</v>
+      </c>
+      <c r="V9" t="n">
+        <v>180.0666330431694</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.069352718360071</v>
+      </c>
+      <c r="X9" t="n">
+        <v>70.76355177996238</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5258564.339561583</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>76.23010311820103</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25.55555555555555</v>
+      </c>
+      <c r="D10" t="n">
+        <v>179.863425925926</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.148148148148148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3008796.296296296</v>
+      </c>
+      <c r="H10" t="n">
+        <v>75.57407407407408</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>25.63553526093633</v>
+      </c>
+      <c r="P10" t="n">
+        <v>180.386529639404</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.161621659683157</v>
+      </c>
+      <c r="R10" t="n">
+        <v>69.86656336088154</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2497064.714659968</v>
+      </c>
+      <c r="T10" t="n">
+        <v>74.70326218641726</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26.2795449273496</v>
+      </c>
+      <c r="V10" t="n">
+        <v>181.9058421068096</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.004784688995215</v>
+      </c>
+      <c r="X10" t="n">
+        <v>68.43323411390188</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2056194.985970264</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>72.81802118160478</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28.56111111111111</v>
+      </c>
+      <c r="D11" t="n">
+        <v>180.1458333333333</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.429166666666666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>82.12083333333332</v>
+      </c>
+      <c r="G11" t="n">
+        <v>33006250</v>
+      </c>
+      <c r="H11" t="n">
+        <v>83.69444444444444</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>183.0083333333334</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.097222222222222</v>
+      </c>
+      <c r="L11" t="n">
+        <v>71.93055555555556</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3944166.666666667</v>
+      </c>
+      <c r="N11" t="n">
+        <v>75.34722222222223</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27.0506199321834</v>
+      </c>
+      <c r="P11" t="n">
+        <v>180.7196935967369</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.932325421396629</v>
+      </c>
+      <c r="R11" t="n">
+        <v>78.81242714629711</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20477679.66484839</v>
+      </c>
+      <c r="T11" t="n">
+        <v>81.66069094304387</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.97468713748125</v>
+      </c>
+      <c r="V11" t="n">
+        <v>179.3821641430465</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.075750377073907</v>
+      </c>
+      <c r="X11" t="n">
+        <v>71.31476154020271</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2982064.405093817</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>73.94739621489622</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="D12" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="F12" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="H12" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="J12" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="N12" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="O12" t="n">
+        <v>24.33056841709016</v>
+      </c>
+      <c r="P12" t="n">
+        <v>180.5030138339921</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.639210897797855</v>
+      </c>
+      <c r="R12" t="n">
+        <v>75.37785479013739</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16504748.95303971</v>
+      </c>
+      <c r="T12" t="n">
+        <v>80.29241318464145</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.60128285139727</v>
+      </c>
+      <c r="V12" t="n">
+        <v>180.8280609296628</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>70.67347007175383</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3797718.542898749</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>76.33266895829824</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="D13" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="F13" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="H13" t="n">
+        <v>82.5175</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="J13" t="n">
+        <v>182.4375</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="L13" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10537500</v>
+      </c>
+      <c r="N13" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24.0748204751008</v>
+      </c>
+      <c r="P13" t="n">
+        <v>179.0032096545712</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.136246730957829</v>
+      </c>
+      <c r="R13" t="n">
+        <v>74.80828783916313</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14677284.62460499</v>
+      </c>
+      <c r="T13" t="n">
+        <v>80.79895227198431</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.85128936719846</v>
+      </c>
+      <c r="V13" t="n">
+        <v>180.6609985973622</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.053013905286633</v>
+      </c>
+      <c r="X13" t="n">
+        <v>72.85710728665275</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7892025.572281255</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.0212124996216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.97569444444444</v>
+      </c>
+      <c r="D14" t="n">
+        <v>179.671875</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.03125</v>
+      </c>
+      <c r="F14" t="n">
+        <v>74.95486111111111</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10317013.88888889</v>
+      </c>
+      <c r="H14" t="n">
+        <v>78.54340277777777</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="J14" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="L14" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="M14" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="N14" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26.25620620663493</v>
+      </c>
+      <c r="P14" t="n">
+        <v>178.6930502086418</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.13134209914463</v>
+      </c>
+      <c r="R14" t="n">
+        <v>73.17096691099989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6018265.635898629</v>
+      </c>
+      <c r="T14" t="n">
+        <v>75.4571280852678</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="V14" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="X14" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>86.84723306664095</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.99537037037037</v>
+      </c>
+      <c r="D15" t="n">
+        <v>181.7623456790124</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81.29012345679013</v>
+      </c>
+      <c r="G15" t="n">
+        <v>44161265.43209876</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85.47067901234567</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.55555555555555</v>
+      </c>
+      <c r="J15" t="n">
+        <v>179.863425925926</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.148148148148148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3008796.296296296</v>
+      </c>
+      <c r="N15" t="n">
+        <v>75.57407407407408</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22.94822282560798</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180.8801239768307</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.130421465539523</v>
+      </c>
+      <c r="R15" t="n">
+        <v>77.51941140130239</v>
+      </c>
+      <c r="S15" t="n">
+        <v>35599396.64398423</v>
+      </c>
+      <c r="T15" t="n">
+        <v>84.24563147289287</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.63553526093633</v>
+      </c>
+      <c r="V15" t="n">
+        <v>180.386529639404</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.161621659683157</v>
+      </c>
+      <c r="X15" t="n">
+        <v>69.86656336088154</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2497064.714659968</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>74.70326218641726</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.31527777777778</v>
+      </c>
+      <c r="D16" t="n">
+        <v>183.3217592592593</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.442824074074074</v>
+      </c>
+      <c r="F16" t="n">
+        <v>78.59328703703703</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22660416.66666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>81.97523148148149</v>
+      </c>
+      <c r="I16" t="n">
+        <v>28.56111111111111</v>
+      </c>
+      <c r="J16" t="n">
+        <v>180.1458333333333</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.429166666666666</v>
+      </c>
+      <c r="L16" t="n">
+        <v>82.12083333333332</v>
+      </c>
+      <c r="M16" t="n">
+        <v>33006250</v>
+      </c>
+      <c r="N16" t="n">
+        <v>83.69444444444444</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25.15153701918324</v>
+      </c>
+      <c r="P16" t="n">
+        <v>181.7983506257021</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.367762163633916</v>
+      </c>
+      <c r="R16" t="n">
+        <v>75.51880875850792</v>
+      </c>
+      <c r="S16" t="n">
+        <v>13750483.94910977</v>
+      </c>
+      <c r="T16" t="n">
+        <v>80.01106502062721</v>
+      </c>
+      <c r="U16" t="n">
+        <v>27.0506199321834</v>
+      </c>
+      <c r="V16" t="n">
+        <v>180.7196935967369</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.932325421396629</v>
+      </c>
+      <c r="X16" t="n">
+        <v>78.81242714629711</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20477679.66484839</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>81.66069094304387</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183.0083333333334</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.097222222222222</v>
+      </c>
+      <c r="F17" t="n">
+        <v>71.93055555555556</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3944166.666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>75.34722222222223</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28.73055555555555</v>
+      </c>
+      <c r="J17" t="n">
+        <v>179.5638888888889</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="L17" t="n">
+        <v>75.32083333333334</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6703055.555555555</v>
+      </c>
+      <c r="N17" t="n">
+        <v>76.56527777777778</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26.97468713748125</v>
+      </c>
+      <c r="P17" t="n">
+        <v>179.3821641430465</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.075750377073907</v>
+      </c>
+      <c r="R17" t="n">
+        <v>71.31476154020271</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2982064.405093817</v>
+      </c>
+      <c r="T17" t="n">
+        <v>73.94739621489622</v>
+      </c>
+      <c r="U17" t="n">
+        <v>28.85886800334168</v>
+      </c>
+      <c r="V17" t="n">
+        <v>180.164530075188</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.34984440267335</v>
+      </c>
+      <c r="X17" t="n">
+        <v>74.55217627401836</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5359476.921470342</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>75.46285505430242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>27.73611111111111</v>
+      </c>
+      <c r="J18" t="n">
+        <v>183.5594276094276</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.285858585858586</v>
+      </c>
+      <c r="L18" t="n">
+        <v>75.87819865319865</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9983468.013468012</v>
+      </c>
+      <c r="N18" t="n">
+        <v>77.72407407407407</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26.2795449273496</v>
+      </c>
+      <c r="P18" t="n">
+        <v>181.9058421068096</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.004784688995215</v>
+      </c>
+      <c r="R18" t="n">
+        <v>68.43323411390188</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2056194.985970264</v>
+      </c>
+      <c r="T18" t="n">
+        <v>72.81802118160478</v>
+      </c>
+      <c r="U18" t="n">
+        <v>27.132339152076</v>
+      </c>
+      <c r="V18" t="n">
+        <v>181.1581510594669</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.097537331089963</v>
+      </c>
+      <c r="X18" t="n">
+        <v>74.36837504600663</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7397022.232153811</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>76.53239304555093</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>22.60227272727273</v>
+      </c>
+      <c r="D19" t="n">
+        <v>181.5858585858586</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.133838383838384</v>
+      </c>
+      <c r="F19" t="n">
+        <v>71.59848484848484</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9680151.515151514</v>
+      </c>
+      <c r="H19" t="n">
+        <v>77.65025252525253</v>
+      </c>
+      <c r="I19" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="J19" t="n">
+        <v>185.5520833333334</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="L19" t="n">
+        <v>76.02083333333334</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10193402.77777778</v>
+      </c>
+      <c r="N19" t="n">
+        <v>79.05208333333334</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23.90011244130826</v>
+      </c>
+      <c r="P19" t="n">
+        <v>180.0666330431694</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.069352718360071</v>
+      </c>
+      <c r="R19" t="n">
+        <v>70.76355177996238</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5258564.339561583</v>
+      </c>
+      <c r="T19" t="n">
+        <v>76.23010311820103</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.58333015024192</v>
+      </c>
+      <c r="V19" t="n">
+        <v>182.7216257555654</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.654365526114752</v>
+      </c>
+      <c r="X19" t="n">
+        <v>76.42956354790721</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9668185.013838071</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>79.19604391996032</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.64814814814815</v>
+      </c>
+      <c r="D20" t="n">
+        <v>182.0972222222223</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71.25462962962963</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4062500</v>
+      </c>
+      <c r="H20" t="n">
+        <v>77.19907407407408</v>
+      </c>
+      <c r="I20" t="n">
+        <v>24.97569444444444</v>
+      </c>
+      <c r="J20" t="n">
+        <v>179.671875</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.03125</v>
+      </c>
+      <c r="L20" t="n">
+        <v>74.95486111111111</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10317013.88888889</v>
+      </c>
+      <c r="N20" t="n">
+        <v>78.54340277777777</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23.60128285139727</v>
+      </c>
+      <c r="P20" t="n">
+        <v>180.8280609296628</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>70.67347007175383</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3797718.542898749</v>
+      </c>
+      <c r="T20" t="n">
+        <v>76.33266895829824</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.25620620663493</v>
+      </c>
+      <c r="V20" t="n">
+        <v>178.6930502086418</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13134209914463</v>
+      </c>
+      <c r="X20" t="n">
+        <v>73.17096691099989</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6018265.635898629</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>75.4571280852678</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="D21" t="n">
+        <v>182.4375</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10537500</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>27.00925925925926</v>
+      </c>
+      <c r="J21" t="n">
+        <v>181.9737654320987</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="L21" t="n">
+        <v>75.12191358024693</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8219135.802469134</v>
+      </c>
+      <c r="N21" t="n">
+        <v>78.20555555555556</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25.85128936719846</v>
+      </c>
+      <c r="P21" t="n">
+        <v>180.6609985973622</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.053013905286633</v>
+      </c>
+      <c r="R21" t="n">
+        <v>72.85710728665275</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7892025.572281255</v>
+      </c>
+      <c r="T21" t="n">
+        <v>77.0212124996216</v>
+      </c>
+      <c r="U21" t="n">
+        <v>25.55895316804408</v>
+      </c>
+      <c r="V21" t="n">
+        <v>180.1654007608553</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.218739341466614</v>
+      </c>
+      <c r="X21" t="n">
+        <v>73.75978617342254</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7529535.123966943</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>77.2428440246622</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27.75353535353536</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185.1169191919192</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.940909090909091</v>
+      </c>
+      <c r="F22" t="n">
+        <v>77.41767676767677</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13708131.31313132</v>
+      </c>
+      <c r="H22" t="n">
+        <v>80.08863636363637</v>
+      </c>
+      <c r="I22" t="n">
+        <v>25.1225</v>
+      </c>
+      <c r="J22" t="n">
+        <v>182.185</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L22" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24073250</v>
+      </c>
+      <c r="N22" t="n">
+        <v>82.5175</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25.7703942585286</v>
+      </c>
+      <c r="P22" t="n">
+        <v>182.821148022346</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.655153985871445</v>
+      </c>
+      <c r="R22" t="n">
+        <v>75.80543988623812</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11820161.2892574</v>
+      </c>
+      <c r="T22" t="n">
+        <v>80.21834147291811</v>
+      </c>
+      <c r="U22" t="n">
+        <v>24.0748204751008</v>
+      </c>
+      <c r="V22" t="n">
+        <v>179.0032096545712</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.136246730957829</v>
+      </c>
+      <c r="X22" t="n">
+        <v>74.80828783916313</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>14677284.62460499</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>80.79895227198431</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
         <v>26.34413580246913</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D23" t="n">
         <v>183.1604938271605</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E23" t="n">
         <v>1.322530864197531</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F23" t="n">
         <v>75.97993827160494</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G23" t="n">
         <v>11894714.50617284</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H23" t="n">
         <v>79.08487654320987</v>
       </c>
-      <c r="I5" t="n">
-        <v>28.73055555555555</v>
-      </c>
-      <c r="J5" t="n">
-        <v>179.5638888888889</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.283333333333333</v>
-      </c>
-      <c r="L5" t="n">
-        <v>75.32083333333334</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6703055.555555555</v>
-      </c>
-      <c r="N5" t="n">
-        <v>76.56527777777778</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="I23" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="J23" t="n">
+        <v>181.6055555555556</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.705757575757576</v>
+      </c>
+      <c r="L23" t="n">
+        <v>79.09080808080807</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24896010.1010101</v>
+      </c>
+      <c r="N23" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="O23" t="n">
         <v>24.49551587301588</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P23" t="n">
         <v>184.1648015873016</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q23" t="n">
         <v>1.096865079365079</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R23" t="n">
         <v>71.97553571428571</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S23" t="n">
         <v>5478414.186507936</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T23" t="n">
         <v>77.42136904761905</v>
       </c>
-      <c r="U5" t="n">
-        <v>28.85886800334168</v>
-      </c>
-      <c r="V5" t="n">
-        <v>180.164530075188</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.34984440267335</v>
-      </c>
-      <c r="X5" t="n">
-        <v>74.55217627401836</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5359476.921470342</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>75.46285505430242</v>
+      <c r="U23" t="n">
+        <v>24.33056841709016</v>
+      </c>
+      <c r="V23" t="n">
+        <v>180.5030138339921</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.639210897797855</v>
+      </c>
+      <c r="X23" t="n">
+        <v>75.37785479013739</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16504748.95303971</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>80.29241318464145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.52118055555555</v>
+      </c>
+      <c r="D24" t="n">
+        <v>182.0582386363636</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.859280303030303</v>
+      </c>
+      <c r="F24" t="n">
+        <v>83.77219065656566</v>
+      </c>
+      <c r="G24" t="n">
+        <v>65004766.41414142</v>
+      </c>
+      <c r="H24" t="n">
+        <v>87.31799242424242</v>
+      </c>
+      <c r="I24" t="n">
+        <v>27.86631944444444</v>
+      </c>
+      <c r="J24" t="n">
+        <v>181.9479166666667</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.887152777777778</v>
+      </c>
+      <c r="L24" t="n">
+        <v>76.58159722222223</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11931944.44444444</v>
+      </c>
+      <c r="N24" t="n">
+        <v>78.83159722222223</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25.07216679519311</v>
+      </c>
+      <c r="P24" t="n">
+        <v>179.6831521913759</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.754408858685175</v>
+      </c>
+      <c r="R24" t="n">
+        <v>82.48092908553436</v>
+      </c>
+      <c r="S24" t="n">
+        <v>60388463.26553564</v>
+      </c>
+      <c r="T24" t="n">
+        <v>86.84723306664095</v>
+      </c>
+      <c r="U24" t="n">
+        <v>27.65425976800977</v>
+      </c>
+      <c r="V24" t="n">
+        <v>183.4720833333333</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.954102564102564</v>
+      </c>
+      <c r="X24" t="n">
+        <v>75.75265720390721</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10349814.71306472</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>79.18877594627595</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1851 +558,1535 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.52118055555555</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="D2" t="n">
-        <v>182.0582386363636</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="E2" t="n">
-        <v>2.859280303030303</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>83.77219065656566</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>65004766.41414142</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="H2" t="n">
-        <v>87.31799242424242</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="I2" t="n">
-        <v>25.55555555555555</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="J2" t="n">
-        <v>179.863425925926</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="K2" t="n">
-        <v>1.148148148148148</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="L2" t="n">
-        <v>70.44444444444444</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="M2" t="n">
-        <v>3008796.296296296</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="N2" t="n">
-        <v>75.57407407407408</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="O2" t="n">
-        <v>25.07216679519311</v>
+        <v>27.58333015024192</v>
       </c>
       <c r="P2" t="n">
-        <v>179.6831521913759</v>
+        <v>182.7216257555654</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.754408858685175</v>
+        <v>1.654365526114752</v>
       </c>
       <c r="R2" t="n">
-        <v>82.48092908553436</v>
+        <v>76.42956354790721</v>
       </c>
       <c r="S2" t="n">
-        <v>60388463.26553564</v>
+        <v>9668185.013838071</v>
       </c>
       <c r="T2" t="n">
-        <v>86.84723306664095</v>
+        <v>79.19604391996032</v>
       </c>
       <c r="U2" t="n">
-        <v>25.63553526093633</v>
+        <v>25.55895316804408</v>
       </c>
       <c r="V2" t="n">
-        <v>180.386529639404</v>
+        <v>180.1654007608553</v>
       </c>
       <c r="W2" t="n">
-        <v>1.161621659683157</v>
+        <v>1.218739341466614</v>
       </c>
       <c r="X2" t="n">
-        <v>69.86656336088154</v>
+        <v>73.75978617342254</v>
       </c>
       <c r="Y2" t="n">
-        <v>2497064.714659968</v>
+        <v>7529535.123966943</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.70326218641726</v>
+        <v>77.2428440246622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>27.73611111111111</v>
+      </c>
+      <c r="D3" t="n">
+        <v>183.5594276094276</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.285858585858586</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75.87819865319865</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9983468.013468012</v>
+      </c>
+      <c r="H3" t="n">
+        <v>77.72407407407407</v>
+      </c>
       <c r="I3" t="n">
-        <v>24.97569444444444</v>
+        <v>27.75353535353536</v>
       </c>
       <c r="J3" t="n">
-        <v>179.671875</v>
+        <v>185.1169191919192</v>
       </c>
       <c r="K3" t="n">
-        <v>1.03125</v>
+        <v>1.940909090909091</v>
       </c>
       <c r="L3" t="n">
-        <v>74.95486111111111</v>
+        <v>77.41767676767677</v>
       </c>
       <c r="M3" t="n">
-        <v>10317013.88888889</v>
+        <v>13708131.31313132</v>
       </c>
       <c r="N3" t="n">
-        <v>78.54340277777777</v>
+        <v>80.08863636363637</v>
       </c>
       <c r="O3" t="n">
-        <v>26.2795449273496</v>
+        <v>27.132339152076</v>
       </c>
       <c r="P3" t="n">
-        <v>181.9058421068096</v>
+        <v>181.1581510594669</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.004784688995215</v>
+        <v>1.097537331089963</v>
       </c>
       <c r="R3" t="n">
-        <v>68.43323411390188</v>
+        <v>74.36837504600663</v>
       </c>
       <c r="S3" t="n">
-        <v>2056194.985970264</v>
+        <v>7397022.232153811</v>
       </c>
       <c r="T3" t="n">
-        <v>72.81802118160478</v>
+        <v>76.53239304555093</v>
       </c>
       <c r="U3" t="n">
-        <v>26.25620620663493</v>
+        <v>25.7703942585286</v>
       </c>
       <c r="V3" t="n">
-        <v>178.6930502086418</v>
+        <v>182.821148022346</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13134209914463</v>
+        <v>1.655153985871445</v>
       </c>
       <c r="X3" t="n">
-        <v>73.17096691099989</v>
+        <v>75.80543988623812</v>
       </c>
       <c r="Y3" t="n">
-        <v>6018265.635898629</v>
+        <v>11820161.2892574</v>
       </c>
       <c r="Z3" t="n">
-        <v>75.4571280852678</v>
+        <v>80.21834147291811</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>23.64814814814815</v>
+        <v>28.82575757575758</v>
       </c>
       <c r="D4" t="n">
-        <v>182.0972222222223</v>
+        <v>179.5025252525253</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.297979797979798</v>
       </c>
       <c r="F4" t="n">
-        <v>71.25462962962963</v>
+        <v>75.36237373737373</v>
       </c>
       <c r="G4" t="n">
-        <v>4062500</v>
+        <v>6719949.494949495</v>
       </c>
       <c r="H4" t="n">
-        <v>77.19907407407408</v>
+        <v>76.56439393939394</v>
       </c>
       <c r="I4" t="n">
-        <v>27.86631944444444</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="J4" t="n">
-        <v>181.9479166666667</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="K4" t="n">
-        <v>1.887152777777778</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>76.58159722222223</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="M4" t="n">
-        <v>11931944.44444444</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="N4" t="n">
-        <v>78.83159722222223</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="O4" t="n">
-        <v>23.60128285139727</v>
+        <v>28.79897091212881</v>
       </c>
       <c r="P4" t="n">
-        <v>180.8280609296628</v>
+        <v>179.79502734108</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>1.345313093339409</v>
       </c>
       <c r="R4" t="n">
-        <v>70.67347007175383</v>
+        <v>74.6110693400167</v>
       </c>
       <c r="S4" t="n">
-        <v>3797718.542898749</v>
+        <v>5484069.928609402</v>
       </c>
       <c r="T4" t="n">
-        <v>76.33266895829824</v>
+        <v>75.5116864130022</v>
       </c>
       <c r="U4" t="n">
-        <v>27.65425976800977</v>
+        <v>22.94822282560798</v>
       </c>
       <c r="V4" t="n">
-        <v>183.4720833333333</v>
+        <v>180.8801239768307</v>
       </c>
       <c r="W4" t="n">
-        <v>1.954102564102564</v>
+        <v>2.130421465539523</v>
       </c>
       <c r="X4" t="n">
-        <v>75.75265720390721</v>
+        <v>77.51941140130239</v>
       </c>
       <c r="Y4" t="n">
-        <v>10349814.71306472</v>
+        <v>35599396.64398423</v>
       </c>
       <c r="Z4" t="n">
-        <v>79.18877594627595</v>
+        <v>84.24563147289287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>28.56111111111111</v>
+        <v>25.31527777777778</v>
       </c>
       <c r="D5" t="n">
-        <v>180.1458333333333</v>
+        <v>183.3217592592593</v>
       </c>
       <c r="E5" t="n">
-        <v>2.429166666666666</v>
+        <v>1.442824074074074</v>
       </c>
       <c r="F5" t="n">
-        <v>82.12083333333332</v>
+        <v>78.59328703703703</v>
       </c>
       <c r="G5" t="n">
-        <v>33006250</v>
+        <v>22660416.66666667</v>
       </c>
       <c r="H5" t="n">
-        <v>83.69444444444444</v>
+        <v>81.97523148148149</v>
       </c>
       <c r="I5" t="n">
-        <v>25.1225</v>
+        <v>22.60227272727273</v>
       </c>
       <c r="J5" t="n">
-        <v>182.185</v>
+        <v>181.5858585858586</v>
       </c>
       <c r="K5" t="n">
-        <v>1.345</v>
+        <v>1.133838383838384</v>
       </c>
       <c r="L5" t="n">
-        <v>78.38499999999999</v>
+        <v>71.59848484848484</v>
       </c>
       <c r="M5" t="n">
-        <v>24073250</v>
+        <v>9680151.515151514</v>
       </c>
       <c r="N5" t="n">
-        <v>82.5175</v>
+        <v>77.65025252525253</v>
       </c>
       <c r="O5" t="n">
-        <v>27.0506199321834</v>
+        <v>25.15153701918324</v>
       </c>
       <c r="P5" t="n">
-        <v>180.7196935967369</v>
+        <v>181.7983506257021</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.932325421396629</v>
+        <v>1.367762163633916</v>
       </c>
       <c r="R5" t="n">
-        <v>78.81242714629711</v>
+        <v>75.51880875850792</v>
       </c>
       <c r="S5" t="n">
-        <v>20477679.66484839</v>
+        <v>13750483.94910977</v>
       </c>
       <c r="T5" t="n">
-        <v>81.66069094304387</v>
+        <v>80.01106502062721</v>
       </c>
       <c r="U5" t="n">
-        <v>24.0748204751008</v>
+        <v>23.90011244130826</v>
       </c>
       <c r="V5" t="n">
-        <v>179.0032096545712</v>
+        <v>180.0666330431694</v>
       </c>
       <c r="W5" t="n">
-        <v>1.136246730957829</v>
+        <v>1.069352718360071</v>
       </c>
       <c r="X5" t="n">
-        <v>74.80828783916313</v>
+        <v>70.76355177996238</v>
       </c>
       <c r="Y5" t="n">
-        <v>14677284.62460499</v>
+        <v>5258564.339561583</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.79895227198431</v>
+        <v>76.23010311820103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.83333333333334</v>
+        <v>25.5297619047619</v>
       </c>
       <c r="D6" t="n">
-        <v>185.5520833333334</v>
+        <v>179.9722222222222</v>
       </c>
       <c r="E6" t="n">
-        <v>1.583333333333333</v>
+        <v>1.14484126984127</v>
       </c>
       <c r="F6" t="n">
-        <v>76.02083333333334</v>
+        <v>70.61309523809523</v>
       </c>
       <c r="G6" t="n">
-        <v>10193402.77777778</v>
+        <v>3220039.682539682</v>
       </c>
       <c r="H6" t="n">
-        <v>79.05208333333334</v>
-      </c>
-      <c r="I6" t="n">
-        <v>27.00925925925926</v>
-      </c>
-      <c r="J6" t="n">
-        <v>181.9737654320987</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.407407407407407</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75.12191358024693</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8219135.802469134</v>
-      </c>
-      <c r="N6" t="n">
-        <v>78.20555555555556</v>
-      </c>
+        <v>75.67063492063492</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>27.58333015024192</v>
+        <v>25.6242406558583</v>
       </c>
       <c r="P6" t="n">
-        <v>182.7216257555654</v>
+        <v>180.2339484657499</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.654365526114752</v>
+        <v>1.152782817672524</v>
       </c>
       <c r="R6" t="n">
-        <v>76.42956354790721</v>
+        <v>69.95175715488216</v>
       </c>
       <c r="S6" t="n">
-        <v>9668185.013838071</v>
+        <v>2543026.91436423</v>
       </c>
       <c r="T6" t="n">
-        <v>79.19604391996032</v>
+        <v>74.68169404125287</v>
       </c>
       <c r="U6" t="n">
-        <v>25.55895316804408</v>
+        <v>26.1729161834038</v>
       </c>
       <c r="V6" t="n">
-        <v>180.1654007608553</v>
+        <v>181.8136885979088</v>
       </c>
       <c r="W6" t="n">
-        <v>1.218739341466614</v>
+        <v>1.008552631578947</v>
       </c>
       <c r="X6" t="n">
-        <v>73.75978617342254</v>
+        <v>68.60963127107671</v>
       </c>
       <c r="Y6" t="n">
-        <v>7529535.123966943</v>
+        <v>2290782.903806075</v>
       </c>
       <c r="Z6" t="n">
-        <v>77.2428440246622</v>
+        <v>72.97901941647105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>27.73611111111111</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="D7" t="n">
-        <v>183.5594276094276</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.285858585858586</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="F7" t="n">
-        <v>75.87819865319865</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="G7" t="n">
-        <v>9983468.013468012</v>
+        <v>33006250</v>
       </c>
       <c r="H7" t="n">
-        <v>77.72407407407407</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="I7" t="n">
-        <v>27.75353535353536</v>
+        <v>26.8</v>
       </c>
       <c r="J7" t="n">
-        <v>185.1169191919192</v>
+        <v>183.0083333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>1.940909090909091</v>
+        <v>1.097222222222222</v>
       </c>
       <c r="L7" t="n">
-        <v>77.41767676767677</v>
+        <v>71.93055555555556</v>
       </c>
       <c r="M7" t="n">
-        <v>13708131.31313132</v>
+        <v>3944166.666666667</v>
       </c>
       <c r="N7" t="n">
-        <v>80.08863636363637</v>
+        <v>75.34722222222223</v>
       </c>
       <c r="O7" t="n">
-        <v>27.132339152076</v>
+        <v>27.0506199321834</v>
       </c>
       <c r="P7" t="n">
-        <v>181.1581510594669</v>
+        <v>180.7196935967369</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.097537331089963</v>
+        <v>1.932325421396629</v>
       </c>
       <c r="R7" t="n">
-        <v>74.36837504600663</v>
+        <v>78.81242714629711</v>
       </c>
       <c r="S7" t="n">
-        <v>7397022.232153811</v>
+        <v>20477679.66484839</v>
       </c>
       <c r="T7" t="n">
-        <v>76.53239304555093</v>
+        <v>81.66069094304387</v>
       </c>
       <c r="U7" t="n">
-        <v>25.7703942585286</v>
+        <v>26.92479860315338</v>
       </c>
       <c r="V7" t="n">
-        <v>182.821148022346</v>
+        <v>179.3325435899884</v>
       </c>
       <c r="W7" t="n">
-        <v>1.655153985871445</v>
+        <v>1.071015978506787</v>
       </c>
       <c r="X7" t="n">
-        <v>75.80543988623812</v>
+        <v>71.25097129688123</v>
       </c>
       <c r="Y7" t="n">
-        <v>11820161.2892574</v>
+        <v>2943847.144481336</v>
       </c>
       <c r="Z7" t="n">
-        <v>80.21834147291811</v>
+        <v>73.95436042205344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>28.73055555555555</v>
+        <v>25.85479797979798</v>
       </c>
       <c r="D8" t="n">
-        <v>179.5638888888889</v>
+        <v>181.6527777777778</v>
       </c>
       <c r="E8" t="n">
-        <v>1.283333333333333</v>
+        <v>1.709779614325069</v>
       </c>
       <c r="F8" t="n">
-        <v>75.32083333333334</v>
+        <v>79.09391643709824</v>
       </c>
       <c r="G8" t="n">
-        <v>6703055.555555555</v>
+        <v>24725918.27364555</v>
       </c>
       <c r="H8" t="n">
-        <v>76.56527777777778</v>
+        <v>82.19090909090909</v>
       </c>
       <c r="I8" t="n">
-        <v>25.99537037037037</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="J8" t="n">
-        <v>181.7623456790124</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="K8" t="n">
-        <v>2.708333333333333</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>81.29012345679013</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="M8" t="n">
-        <v>44161265.43209876</v>
+        <v>4062500</v>
       </c>
       <c r="N8" t="n">
-        <v>85.47067901234567</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="O8" t="n">
-        <v>28.85886800334168</v>
+        <v>24.24142583371832</v>
       </c>
       <c r="P8" t="n">
-        <v>180.164530075188</v>
+        <v>180.4800125763564</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.34984440267335</v>
+        <v>1.644737179816231</v>
       </c>
       <c r="R8" t="n">
-        <v>74.55217627401836</v>
+        <v>75.16623162739764</v>
       </c>
       <c r="S8" t="n">
-        <v>5359476.921470342</v>
+        <v>16413862.68458156</v>
       </c>
       <c r="T8" t="n">
-        <v>75.46285505430242</v>
+        <v>80.23855744058314</v>
       </c>
       <c r="U8" t="n">
-        <v>22.94822282560798</v>
+        <v>23.59510562248236</v>
       </c>
       <c r="V8" t="n">
-        <v>180.8801239768307</v>
+        <v>180.564903875451</v>
       </c>
       <c r="W8" t="n">
-        <v>2.130421465539523</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>77.51941140130239</v>
+        <v>70.74557885310955</v>
       </c>
       <c r="Y8" t="n">
-        <v>35599396.64398423</v>
+        <v>3790047.160210984</v>
       </c>
       <c r="Z8" t="n">
-        <v>84.24563147289287</v>
+        <v>76.35091117421052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.31527777777778</v>
+        <v>25.1225</v>
       </c>
       <c r="D9" t="n">
-        <v>183.3217592592593</v>
+        <v>182.185</v>
       </c>
       <c r="E9" t="n">
-        <v>1.442824074074074</v>
+        <v>1.345</v>
       </c>
       <c r="F9" t="n">
-        <v>78.59328703703703</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>22660416.66666667</v>
+        <v>24073250</v>
       </c>
       <c r="H9" t="n">
-        <v>81.97523148148149</v>
+        <v>82.5175</v>
       </c>
       <c r="I9" t="n">
-        <v>22.60227272727273</v>
+        <v>26.8125</v>
       </c>
       <c r="J9" t="n">
-        <v>181.5858585858586</v>
+        <v>182.4375</v>
       </c>
       <c r="K9" t="n">
-        <v>1.133838383838384</v>
+        <v>1.1875</v>
       </c>
       <c r="L9" t="n">
-        <v>71.59848484848484</v>
+        <v>74.4375</v>
       </c>
       <c r="M9" t="n">
-        <v>9680151.515151514</v>
+        <v>10537500</v>
       </c>
       <c r="N9" t="n">
-        <v>77.65025252525253</v>
+        <v>77.875</v>
       </c>
       <c r="O9" t="n">
-        <v>25.15153701918324</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="P9" t="n">
-        <v>181.7983506257021</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.367762163633916</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="R9" t="n">
-        <v>75.51880875850792</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="S9" t="n">
-        <v>13750483.94910977</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="T9" t="n">
-        <v>80.01106502062721</v>
+        <v>80.79895227198431</v>
       </c>
       <c r="U9" t="n">
-        <v>23.90011244130826</v>
+        <v>25.85128936719846</v>
       </c>
       <c r="V9" t="n">
-        <v>180.0666330431694</v>
+        <v>180.6609985973622</v>
       </c>
       <c r="W9" t="n">
-        <v>1.069352718360071</v>
+        <v>1.053013905286633</v>
       </c>
       <c r="X9" t="n">
-        <v>70.76355177996238</v>
+        <v>72.85710728665275</v>
       </c>
       <c r="Y9" t="n">
-        <v>5258564.339561583</v>
+        <v>7892025.572281255</v>
       </c>
       <c r="Z9" t="n">
-        <v>76.23010311820103</v>
+        <v>77.0212124996216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.55555555555555</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="D10" t="n">
-        <v>179.863425925926</v>
+        <v>179.671875</v>
       </c>
       <c r="E10" t="n">
-        <v>1.148148148148148</v>
+        <v>1.03125</v>
       </c>
       <c r="F10" t="n">
-        <v>70.44444444444444</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="G10" t="n">
-        <v>3008796.296296296</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="H10" t="n">
-        <v>75.57407407407408</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>78.54340277777777</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.47561728395062</v>
+      </c>
+      <c r="J10" t="n">
+        <v>182.1258417508417</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.899607182940516</v>
+      </c>
+      <c r="L10" t="n">
+        <v>83.94565095398428</v>
+      </c>
+      <c r="M10" t="n">
+        <v>66109175.08417508</v>
+      </c>
+      <c r="N10" t="n">
+        <v>87.50488215488215</v>
+      </c>
       <c r="O10" t="n">
-        <v>25.63553526093633</v>
+        <v>26.1549926553824</v>
       </c>
       <c r="P10" t="n">
-        <v>180.386529639404</v>
+        <v>178.4871885013627</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.161621659683157</v>
+        <v>1.132388921300313</v>
       </c>
       <c r="R10" t="n">
-        <v>69.86656336088154</v>
+        <v>73.26581407493497</v>
       </c>
       <c r="S10" t="n">
-        <v>2497064.714659968</v>
+        <v>6189981.746920832</v>
       </c>
       <c r="T10" t="n">
-        <v>74.70326218641726</v>
+        <v>75.63635020738633</v>
       </c>
       <c r="U10" t="n">
-        <v>26.2795449273496</v>
+        <v>25.15651526835737</v>
       </c>
       <c r="V10" t="n">
-        <v>181.9058421068096</v>
+        <v>179.2574110830689</v>
       </c>
       <c r="W10" t="n">
-        <v>1.004784688995215</v>
+        <v>2.708553507895614</v>
       </c>
       <c r="X10" t="n">
-        <v>68.43323411390188</v>
+        <v>82.26296583533426</v>
       </c>
       <c r="Y10" t="n">
-        <v>2056194.985970264</v>
+        <v>58603716.60503239</v>
       </c>
       <c r="Z10" t="n">
-        <v>72.81802118160478</v>
+        <v>86.62627248482512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>28.56111111111111</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="D11" t="n">
-        <v>180.1458333333333</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="E11" t="n">
-        <v>2.429166666666666</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>82.12083333333332</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="G11" t="n">
-        <v>33006250</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="H11" t="n">
-        <v>83.69444444444444</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="I11" t="n">
-        <v>26.8</v>
+        <v>25.5297619047619</v>
       </c>
       <c r="J11" t="n">
-        <v>183.0083333333334</v>
+        <v>179.9722222222222</v>
       </c>
       <c r="K11" t="n">
-        <v>1.097222222222222</v>
+        <v>1.14484126984127</v>
       </c>
       <c r="L11" t="n">
-        <v>71.93055555555556</v>
+        <v>70.61309523809523</v>
       </c>
       <c r="M11" t="n">
-        <v>3944166.666666667</v>
+        <v>3220039.682539682</v>
       </c>
       <c r="N11" t="n">
-        <v>75.34722222222223</v>
+        <v>75.67063492063492</v>
       </c>
       <c r="O11" t="n">
-        <v>27.0506199321834</v>
+        <v>22.94822282560798</v>
       </c>
       <c r="P11" t="n">
-        <v>180.7196935967369</v>
+        <v>180.8801239768307</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.932325421396629</v>
+        <v>2.130421465539523</v>
       </c>
       <c r="R11" t="n">
-        <v>78.81242714629711</v>
+        <v>77.51941140130239</v>
       </c>
       <c r="S11" t="n">
-        <v>20477679.66484839</v>
+        <v>35599396.64398423</v>
       </c>
       <c r="T11" t="n">
-        <v>81.66069094304387</v>
+        <v>84.24563147289287</v>
       </c>
       <c r="U11" t="n">
-        <v>26.97468713748125</v>
+        <v>25.6242406558583</v>
       </c>
       <c r="V11" t="n">
-        <v>179.3821641430465</v>
+        <v>180.2339484657499</v>
       </c>
       <c r="W11" t="n">
-        <v>1.075750377073907</v>
+        <v>1.152782817672524</v>
       </c>
       <c r="X11" t="n">
-        <v>71.31476154020271</v>
+        <v>69.95175715488216</v>
       </c>
       <c r="Y11" t="n">
-        <v>2982064.405093817</v>
+        <v>2543026.91436423</v>
       </c>
       <c r="Z11" t="n">
-        <v>73.94739621489622</v>
+        <v>74.68169404125287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.77777777777778</v>
+        <v>25.31527777777778</v>
       </c>
       <c r="D12" t="n">
-        <v>181.6055555555556</v>
+        <v>183.3217592592593</v>
       </c>
       <c r="E12" t="n">
-        <v>1.705757575757576</v>
+        <v>1.442824074074074</v>
       </c>
       <c r="F12" t="n">
-        <v>79.09080808080807</v>
+        <v>78.59328703703703</v>
       </c>
       <c r="G12" t="n">
-        <v>24896010.1010101</v>
+        <v>22660416.66666667</v>
       </c>
       <c r="H12" t="n">
-        <v>82.26000000000001</v>
+        <v>81.97523148148149</v>
       </c>
       <c r="I12" t="n">
-        <v>23.64814814814815</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="J12" t="n">
-        <v>182.0972222222223</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="L12" t="n">
-        <v>71.25462962962963</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="M12" t="n">
-        <v>4062500</v>
+        <v>33006250</v>
       </c>
       <c r="N12" t="n">
-        <v>77.19907407407408</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="O12" t="n">
-        <v>24.33056841709016</v>
+        <v>25.15153701918324</v>
       </c>
       <c r="P12" t="n">
-        <v>180.5030138339921</v>
+        <v>181.7983506257021</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.639210897797855</v>
+        <v>1.367762163633916</v>
       </c>
       <c r="R12" t="n">
-        <v>75.37785479013739</v>
+        <v>75.51880875850792</v>
       </c>
       <c r="S12" t="n">
-        <v>16504748.95303971</v>
+        <v>13750483.94910977</v>
       </c>
       <c r="T12" t="n">
-        <v>80.29241318464145</v>
+        <v>80.01106502062721</v>
       </c>
       <c r="U12" t="n">
-        <v>23.60128285139727</v>
+        <v>27.0506199321834</v>
       </c>
       <c r="V12" t="n">
-        <v>180.8280609296628</v>
+        <v>180.7196935967369</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.932325421396629</v>
       </c>
       <c r="X12" t="n">
-        <v>70.67347007175383</v>
+        <v>78.81242714629711</v>
       </c>
       <c r="Y12" t="n">
-        <v>3797718.542898749</v>
+        <v>20477679.66484839</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.33266895829824</v>
+        <v>81.66069094304387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>25.1225</v>
+        <v>26.8</v>
       </c>
       <c r="D13" t="n">
-        <v>182.185</v>
+        <v>183.0083333333334</v>
       </c>
       <c r="E13" t="n">
-        <v>1.345</v>
+        <v>1.097222222222222</v>
       </c>
       <c r="F13" t="n">
-        <v>78.38499999999999</v>
+        <v>71.93055555555556</v>
       </c>
       <c r="G13" t="n">
-        <v>24073250</v>
+        <v>3944166.666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>82.5175</v>
+        <v>75.34722222222223</v>
       </c>
       <c r="I13" t="n">
-        <v>26.8125</v>
+        <v>28.82575757575758</v>
       </c>
       <c r="J13" t="n">
-        <v>182.4375</v>
+        <v>179.5025252525253</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1875</v>
+        <v>1.297979797979798</v>
       </c>
       <c r="L13" t="n">
-        <v>74.4375</v>
+        <v>75.36237373737373</v>
       </c>
       <c r="M13" t="n">
-        <v>10537500</v>
+        <v>6719949.494949495</v>
       </c>
       <c r="N13" t="n">
-        <v>77.875</v>
+        <v>76.56439393939394</v>
       </c>
       <c r="O13" t="n">
-        <v>24.0748204751008</v>
+        <v>26.92479860315338</v>
       </c>
       <c r="P13" t="n">
-        <v>179.0032096545712</v>
+        <v>179.3325435899884</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.136246730957829</v>
+        <v>1.071015978506787</v>
       </c>
       <c r="R13" t="n">
-        <v>74.80828783916313</v>
+        <v>71.25097129688123</v>
       </c>
       <c r="S13" t="n">
-        <v>14677284.62460499</v>
+        <v>2943847.144481336</v>
       </c>
       <c r="T13" t="n">
-        <v>80.79895227198431</v>
+        <v>73.95436042205344</v>
       </c>
       <c r="U13" t="n">
-        <v>25.85128936719846</v>
+        <v>28.79897091212881</v>
       </c>
       <c r="V13" t="n">
-        <v>180.6609985973622</v>
+        <v>179.79502734108</v>
       </c>
       <c r="W13" t="n">
-        <v>1.053013905286633</v>
+        <v>1.345313093339409</v>
       </c>
       <c r="X13" t="n">
-        <v>72.85710728665275</v>
+        <v>74.6110693400167</v>
       </c>
       <c r="Y13" t="n">
-        <v>7892025.572281255</v>
+        <v>5484069.928609402</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.0212124996216</v>
+        <v>75.5116864130022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>24.97569444444444</v>
-      </c>
-      <c r="D14" t="n">
-        <v>179.671875</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.03125</v>
-      </c>
-      <c r="F14" t="n">
-        <v>74.95486111111111</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10317013.88888889</v>
-      </c>
-      <c r="H14" t="n">
-        <v>78.54340277777777</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>25.52118055555555</v>
+        <v>27.73611111111111</v>
       </c>
       <c r="J14" t="n">
-        <v>182.0582386363636</v>
+        <v>183.5594276094276</v>
       </c>
       <c r="K14" t="n">
-        <v>2.859280303030303</v>
+        <v>1.285858585858586</v>
       </c>
       <c r="L14" t="n">
-        <v>83.77219065656566</v>
+        <v>75.87819865319865</v>
       </c>
       <c r="M14" t="n">
-        <v>65004766.41414142</v>
+        <v>9983468.013468012</v>
       </c>
       <c r="N14" t="n">
-        <v>87.31799242424242</v>
+        <v>77.72407407407407</v>
       </c>
       <c r="O14" t="n">
-        <v>26.25620620663493</v>
+        <v>26.1729161834038</v>
       </c>
       <c r="P14" t="n">
-        <v>178.6930502086418</v>
+        <v>181.8136885979088</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.13134209914463</v>
+        <v>1.008552631578947</v>
       </c>
       <c r="R14" t="n">
-        <v>73.17096691099989</v>
+        <v>68.60963127107671</v>
       </c>
       <c r="S14" t="n">
-        <v>6018265.635898629</v>
+        <v>2290782.903806075</v>
       </c>
       <c r="T14" t="n">
-        <v>75.4571280852678</v>
+        <v>72.97901941647105</v>
       </c>
       <c r="U14" t="n">
-        <v>25.07216679519311</v>
+        <v>27.132339152076</v>
       </c>
       <c r="V14" t="n">
-        <v>179.6831521913759</v>
+        <v>181.1581510594669</v>
       </c>
       <c r="W14" t="n">
-        <v>2.754408858685175</v>
+        <v>1.097537331089963</v>
       </c>
       <c r="X14" t="n">
-        <v>82.48092908553436</v>
+        <v>74.36837504600663</v>
       </c>
       <c r="Y14" t="n">
-        <v>60388463.26553564</v>
+        <v>7397022.232153811</v>
       </c>
       <c r="Z14" t="n">
-        <v>86.84723306664095</v>
+        <v>76.53239304555093</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25.99537037037037</v>
+        <v>22.60227272727273</v>
       </c>
       <c r="D15" t="n">
-        <v>181.7623456790124</v>
+        <v>181.5858585858586</v>
       </c>
       <c r="E15" t="n">
-        <v>2.708333333333333</v>
+        <v>1.133838383838384</v>
       </c>
       <c r="F15" t="n">
-        <v>81.29012345679013</v>
+        <v>71.59848484848484</v>
       </c>
       <c r="G15" t="n">
-        <v>44161265.43209876</v>
+        <v>9680151.515151514</v>
       </c>
       <c r="H15" t="n">
-        <v>85.47067901234567</v>
+        <v>77.65025252525253</v>
       </c>
       <c r="I15" t="n">
-        <v>25.55555555555555</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="J15" t="n">
-        <v>179.863425925926</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="K15" t="n">
-        <v>1.148148148148148</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>70.44444444444444</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="M15" t="n">
-        <v>3008796.296296296</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="N15" t="n">
-        <v>75.57407407407408</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="O15" t="n">
-        <v>22.94822282560798</v>
+        <v>23.90011244130826</v>
       </c>
       <c r="P15" t="n">
-        <v>180.8801239768307</v>
+        <v>180.0666330431694</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.130421465539523</v>
+        <v>1.069352718360071</v>
       </c>
       <c r="R15" t="n">
-        <v>77.51941140130239</v>
+        <v>70.76355177996238</v>
       </c>
       <c r="S15" t="n">
-        <v>35599396.64398423</v>
+        <v>5258564.339561583</v>
       </c>
       <c r="T15" t="n">
-        <v>84.24563147289287</v>
+        <v>76.23010311820103</v>
       </c>
       <c r="U15" t="n">
-        <v>25.63553526093633</v>
+        <v>27.58333015024192</v>
       </c>
       <c r="V15" t="n">
-        <v>180.386529639404</v>
+        <v>182.7216257555654</v>
       </c>
       <c r="W15" t="n">
-        <v>1.161621659683157</v>
+        <v>1.654365526114752</v>
       </c>
       <c r="X15" t="n">
-        <v>69.86656336088154</v>
+        <v>76.42956354790721</v>
       </c>
       <c r="Y15" t="n">
-        <v>2497064.714659968</v>
+        <v>9668185.013838071</v>
       </c>
       <c r="Z15" t="n">
-        <v>74.70326218641726</v>
+        <v>79.19604391996032</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>25.31527777777778</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="D16" t="n">
-        <v>183.3217592592593</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="E16" t="n">
-        <v>1.442824074074074</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>78.59328703703703</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="G16" t="n">
-        <v>22660416.66666667</v>
+        <v>4062500</v>
       </c>
       <c r="H16" t="n">
-        <v>81.97523148148149</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="I16" t="n">
-        <v>28.56111111111111</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="J16" t="n">
-        <v>180.1458333333333</v>
+        <v>179.671875</v>
       </c>
       <c r="K16" t="n">
-        <v>2.429166666666666</v>
+        <v>1.03125</v>
       </c>
       <c r="L16" t="n">
-        <v>82.12083333333332</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="M16" t="n">
-        <v>33006250</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="N16" t="n">
-        <v>83.69444444444444</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="O16" t="n">
-        <v>25.15153701918324</v>
+        <v>23.59510562248236</v>
       </c>
       <c r="P16" t="n">
-        <v>181.7983506257021</v>
+        <v>180.564903875451</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.367762163633916</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>75.51880875850792</v>
+        <v>70.74557885310955</v>
       </c>
       <c r="S16" t="n">
-        <v>13750483.94910977</v>
+        <v>3790047.160210984</v>
       </c>
       <c r="T16" t="n">
-        <v>80.01106502062721</v>
+        <v>76.35091117421052</v>
       </c>
       <c r="U16" t="n">
-        <v>27.0506199321834</v>
+        <v>26.1549926553824</v>
       </c>
       <c r="V16" t="n">
-        <v>180.7196935967369</v>
+        <v>178.4871885013627</v>
       </c>
       <c r="W16" t="n">
-        <v>1.932325421396629</v>
+        <v>1.132388921300313</v>
       </c>
       <c r="X16" t="n">
-        <v>78.81242714629711</v>
+        <v>73.26581407493497</v>
       </c>
       <c r="Y16" t="n">
-        <v>20477679.66484839</v>
+        <v>6189981.746920832</v>
       </c>
       <c r="Z16" t="n">
-        <v>81.66069094304387</v>
+        <v>75.63635020738633</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.8</v>
+        <v>26.8125</v>
       </c>
       <c r="D17" t="n">
-        <v>183.0083333333334</v>
+        <v>182.4375</v>
       </c>
       <c r="E17" t="n">
-        <v>1.097222222222222</v>
+        <v>1.1875</v>
       </c>
       <c r="F17" t="n">
-        <v>71.93055555555556</v>
+        <v>74.4375</v>
       </c>
       <c r="G17" t="n">
-        <v>3944166.666666667</v>
+        <v>10537500</v>
       </c>
       <c r="H17" t="n">
-        <v>75.34722222222223</v>
+        <v>77.875</v>
       </c>
       <c r="I17" t="n">
-        <v>28.73055555555555</v>
+        <v>27.00925925925926</v>
       </c>
       <c r="J17" t="n">
-        <v>179.5638888888889</v>
+        <v>181.9737654320987</v>
       </c>
       <c r="K17" t="n">
-        <v>1.283333333333333</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="L17" t="n">
-        <v>75.32083333333334</v>
+        <v>75.12191358024693</v>
       </c>
       <c r="M17" t="n">
-        <v>6703055.555555555</v>
+        <v>8219135.802469134</v>
       </c>
       <c r="N17" t="n">
-        <v>76.56527777777778</v>
+        <v>78.20555555555556</v>
       </c>
       <c r="O17" t="n">
-        <v>26.97468713748125</v>
+        <v>25.85128936719846</v>
       </c>
       <c r="P17" t="n">
-        <v>179.3821641430465</v>
+        <v>180.6609985973622</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.075750377073907</v>
+        <v>1.053013905286633</v>
       </c>
       <c r="R17" t="n">
-        <v>71.31476154020271</v>
+        <v>72.85710728665275</v>
       </c>
       <c r="S17" t="n">
-        <v>2982064.405093817</v>
+        <v>7892025.572281255</v>
       </c>
       <c r="T17" t="n">
-        <v>73.94739621489622</v>
+        <v>77.0212124996216</v>
       </c>
       <c r="U17" t="n">
-        <v>28.85886800334168</v>
+        <v>25.55895316804408</v>
       </c>
       <c r="V17" t="n">
-        <v>180.164530075188</v>
+        <v>180.1654007608553</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34984440267335</v>
+        <v>1.218739341466614</v>
       </c>
       <c r="X17" t="n">
-        <v>74.55217627401836</v>
+        <v>73.75978617342254</v>
       </c>
       <c r="Y17" t="n">
-        <v>5359476.921470342</v>
+        <v>7529535.123966943</v>
       </c>
       <c r="Z17" t="n">
-        <v>75.46285505430242</v>
+        <v>77.2428440246622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>27.75353535353536</v>
+      </c>
+      <c r="D18" t="n">
+        <v>185.1169191919192</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.940909090909091</v>
+      </c>
+      <c r="F18" t="n">
+        <v>77.41767676767677</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13708131.31313132</v>
+      </c>
+      <c r="H18" t="n">
+        <v>80.08863636363637</v>
+      </c>
       <c r="I18" t="n">
-        <v>27.73611111111111</v>
+        <v>25.1225</v>
       </c>
       <c r="J18" t="n">
-        <v>183.5594276094276</v>
+        <v>182.185</v>
       </c>
       <c r="K18" t="n">
-        <v>1.285858585858586</v>
+        <v>1.345</v>
       </c>
       <c r="L18" t="n">
-        <v>75.87819865319865</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>9983468.013468012</v>
+        <v>24073250</v>
       </c>
       <c r="N18" t="n">
-        <v>77.72407407407407</v>
+        <v>82.5175</v>
       </c>
       <c r="O18" t="n">
-        <v>26.2795449273496</v>
+        <v>25.7703942585286</v>
       </c>
       <c r="P18" t="n">
-        <v>181.9058421068096</v>
+        <v>182.821148022346</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.004784688995215</v>
+        <v>1.655153985871445</v>
       </c>
       <c r="R18" t="n">
-        <v>68.43323411390188</v>
+        <v>75.80543988623812</v>
       </c>
       <c r="S18" t="n">
-        <v>2056194.985970264</v>
+        <v>11820161.2892574</v>
       </c>
       <c r="T18" t="n">
-        <v>72.81802118160478</v>
+        <v>80.21834147291811</v>
       </c>
       <c r="U18" t="n">
-        <v>27.132339152076</v>
+        <v>24.0748204751008</v>
       </c>
       <c r="V18" t="n">
-        <v>181.1581510594669</v>
+        <v>179.0032096545712</v>
       </c>
       <c r="W18" t="n">
-        <v>1.097537331089963</v>
+        <v>1.136246730957829</v>
       </c>
       <c r="X18" t="n">
-        <v>74.36837504600663</v>
+        <v>74.80828783916313</v>
       </c>
       <c r="Y18" t="n">
-        <v>7397022.232153811</v>
+        <v>14677284.62460499</v>
       </c>
       <c r="Z18" t="n">
-        <v>76.53239304555093</v>
+        <v>80.79895227198431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>22.60227272727273</v>
+        <v>26.36527777777778</v>
       </c>
       <c r="D19" t="n">
-        <v>181.5858585858586</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="E19" t="n">
-        <v>1.133838383838384</v>
+        <v>1.323611111111111</v>
       </c>
       <c r="F19" t="n">
-        <v>71.59848484848484</v>
+        <v>75.78194444444445</v>
       </c>
       <c r="G19" t="n">
-        <v>9680151.515151514</v>
+        <v>11501631.94444444</v>
       </c>
       <c r="H19" t="n">
-        <v>77.65025252525253</v>
+        <v>78.8763888888889</v>
       </c>
       <c r="I19" t="n">
-        <v>26.83333333333334</v>
+        <v>25.85479797979798</v>
       </c>
       <c r="J19" t="n">
-        <v>185.5520833333334</v>
+        <v>181.6527777777778</v>
       </c>
       <c r="K19" t="n">
-        <v>1.583333333333333</v>
+        <v>1.709779614325069</v>
       </c>
       <c r="L19" t="n">
-        <v>76.02083333333334</v>
+        <v>79.09391643709824</v>
       </c>
       <c r="M19" t="n">
-        <v>10193402.77777778</v>
+        <v>24725918.27364555</v>
       </c>
       <c r="N19" t="n">
-        <v>79.05208333333334</v>
+        <v>82.19090909090909</v>
       </c>
       <c r="O19" t="n">
-        <v>23.90011244130826</v>
+        <v>24.43531746031746</v>
       </c>
       <c r="P19" t="n">
-        <v>180.0666330431694</v>
+        <v>183.7104256854257</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.069352718360071</v>
+        <v>1.088059163059163</v>
       </c>
       <c r="R19" t="n">
-        <v>70.76355177996238</v>
+        <v>71.94745670995671</v>
       </c>
       <c r="S19" t="n">
-        <v>5258564.339561583</v>
+        <v>5596096.23015873</v>
       </c>
       <c r="T19" t="n">
-        <v>76.23010311820103</v>
+        <v>77.42094155844156</v>
       </c>
       <c r="U19" t="n">
-        <v>27.58333015024192</v>
+        <v>24.24142583371832</v>
       </c>
       <c r="V19" t="n">
-        <v>182.7216257555654</v>
+        <v>180.4800125763564</v>
       </c>
       <c r="W19" t="n">
-        <v>1.654365526114752</v>
+        <v>1.644737179816231</v>
       </c>
       <c r="X19" t="n">
-        <v>76.42956354790721</v>
+        <v>75.16623162739764</v>
       </c>
       <c r="Y19" t="n">
-        <v>9668185.013838071</v>
+        <v>16413862.68458156</v>
       </c>
       <c r="Z19" t="n">
-        <v>79.19604391996032</v>
+        <v>80.23855744058314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>23.64814814814815</v>
+        <v>25.47561728395062</v>
       </c>
       <c r="D20" t="n">
-        <v>182.0972222222223</v>
+        <v>182.1258417508417</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2.899607182940516</v>
       </c>
       <c r="F20" t="n">
-        <v>71.25462962962963</v>
+        <v>83.94565095398428</v>
       </c>
       <c r="G20" t="n">
-        <v>4062500</v>
+        <v>66109175.08417508</v>
       </c>
       <c r="H20" t="n">
-        <v>77.19907407407408</v>
+        <v>87.50488215488215</v>
       </c>
       <c r="I20" t="n">
-        <v>24.97569444444444</v>
+        <v>27.86631944444444</v>
       </c>
       <c r="J20" t="n">
-        <v>179.671875</v>
+        <v>181.9479166666667</v>
       </c>
       <c r="K20" t="n">
-        <v>1.03125</v>
+        <v>1.887152777777778</v>
       </c>
       <c r="L20" t="n">
-        <v>74.95486111111111</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="M20" t="n">
-        <v>10317013.88888889</v>
+        <v>11931944.44444444</v>
       </c>
       <c r="N20" t="n">
-        <v>78.54340277777777</v>
+        <v>78.83159722222223</v>
       </c>
       <c r="O20" t="n">
-        <v>23.60128285139727</v>
+        <v>25.15651526835737</v>
       </c>
       <c r="P20" t="n">
-        <v>180.8280609296628</v>
+        <v>179.2574110830689</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2.708553507895614</v>
       </c>
       <c r="R20" t="n">
-        <v>70.67347007175383</v>
+        <v>82.26296583533426</v>
       </c>
       <c r="S20" t="n">
-        <v>3797718.542898749</v>
+        <v>58603716.60503239</v>
       </c>
       <c r="T20" t="n">
-        <v>76.33266895829824</v>
+        <v>86.62627248482512</v>
       </c>
       <c r="U20" t="n">
-        <v>26.25620620663493</v>
+        <v>27.30906732156733</v>
       </c>
       <c r="V20" t="n">
-        <v>178.6930502086418</v>
+        <v>183.3382575757576</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13134209914463</v>
+        <v>1.932301032301032</v>
       </c>
       <c r="X20" t="n">
-        <v>73.17096691099989</v>
+        <v>75.55436369186368</v>
       </c>
       <c r="Y20" t="n">
-        <v>6018265.635898629</v>
+        <v>10001130.25863026</v>
       </c>
       <c r="Z20" t="n">
-        <v>75.4571280852678</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>26.8125</v>
-      </c>
-      <c r="D21" t="n">
-        <v>182.4375</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.1875</v>
-      </c>
-      <c r="F21" t="n">
-        <v>74.4375</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10537500</v>
-      </c>
-      <c r="H21" t="n">
-        <v>77.875</v>
-      </c>
-      <c r="I21" t="n">
-        <v>27.00925925925926</v>
-      </c>
-      <c r="J21" t="n">
-        <v>181.9737654320987</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.407407407407407</v>
-      </c>
-      <c r="L21" t="n">
-        <v>75.12191358024693</v>
-      </c>
-      <c r="M21" t="n">
-        <v>8219135.802469134</v>
-      </c>
-      <c r="N21" t="n">
-        <v>78.20555555555556</v>
-      </c>
-      <c r="O21" t="n">
-        <v>25.85128936719846</v>
-      </c>
-      <c r="P21" t="n">
-        <v>180.6609985973622</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.053013905286633</v>
-      </c>
-      <c r="R21" t="n">
-        <v>72.85710728665275</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7892025.572281255</v>
-      </c>
-      <c r="T21" t="n">
-        <v>77.0212124996216</v>
-      </c>
-      <c r="U21" t="n">
-        <v>25.55895316804408</v>
-      </c>
-      <c r="V21" t="n">
-        <v>180.1654007608553</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.218739341466614</v>
-      </c>
-      <c r="X21" t="n">
-        <v>73.75978617342254</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>7529535.123966943</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>77.2428440246622</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>27.75353535353536</v>
-      </c>
-      <c r="D22" t="n">
-        <v>185.1169191919192</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.940909090909091</v>
-      </c>
-      <c r="F22" t="n">
-        <v>77.41767676767677</v>
-      </c>
-      <c r="G22" t="n">
-        <v>13708131.31313132</v>
-      </c>
-      <c r="H22" t="n">
-        <v>80.08863636363637</v>
-      </c>
-      <c r="I22" t="n">
-        <v>25.1225</v>
-      </c>
-      <c r="J22" t="n">
-        <v>182.185</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.345</v>
-      </c>
-      <c r="L22" t="n">
-        <v>78.38499999999999</v>
-      </c>
-      <c r="M22" t="n">
-        <v>24073250</v>
-      </c>
-      <c r="N22" t="n">
-        <v>82.5175</v>
-      </c>
-      <c r="O22" t="n">
-        <v>25.7703942585286</v>
-      </c>
-      <c r="P22" t="n">
-        <v>182.821148022346</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.655153985871445</v>
-      </c>
-      <c r="R22" t="n">
-        <v>75.80543988623812</v>
-      </c>
-      <c r="S22" t="n">
-        <v>11820161.2892574</v>
-      </c>
-      <c r="T22" t="n">
-        <v>80.21834147291811</v>
-      </c>
-      <c r="U22" t="n">
-        <v>24.0748204751008</v>
-      </c>
-      <c r="V22" t="n">
-        <v>179.0032096545712</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.136246730957829</v>
-      </c>
-      <c r="X22" t="n">
-        <v>74.80828783916313</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>14677284.62460499</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>80.79895227198431</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>26.34413580246913</v>
-      </c>
-      <c r="D23" t="n">
-        <v>183.1604938271605</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.322530864197531</v>
-      </c>
-      <c r="F23" t="n">
-        <v>75.97993827160494</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11894714.50617284</v>
-      </c>
-      <c r="H23" t="n">
-        <v>79.08487654320987</v>
-      </c>
-      <c r="I23" t="n">
-        <v>25.77777777777778</v>
-      </c>
-      <c r="J23" t="n">
-        <v>181.6055555555556</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.705757575757576</v>
-      </c>
-      <c r="L23" t="n">
-        <v>79.09080808080807</v>
-      </c>
-      <c r="M23" t="n">
-        <v>24896010.1010101</v>
-      </c>
-      <c r="N23" t="n">
-        <v>82.26000000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>24.49551587301588</v>
-      </c>
-      <c r="P23" t="n">
-        <v>184.1648015873016</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.096865079365079</v>
-      </c>
-      <c r="R23" t="n">
-        <v>71.97553571428571</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5478414.186507936</v>
-      </c>
-      <c r="T23" t="n">
-        <v>77.42136904761905</v>
-      </c>
-      <c r="U23" t="n">
-        <v>24.33056841709016</v>
-      </c>
-      <c r="V23" t="n">
-        <v>180.5030138339921</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.639210897797855</v>
-      </c>
-      <c r="X23" t="n">
-        <v>75.37785479013739</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>16504748.95303971</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>80.29241318464145</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>25.52118055555555</v>
-      </c>
-      <c r="D24" t="n">
-        <v>182.0582386363636</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.859280303030303</v>
-      </c>
-      <c r="F24" t="n">
-        <v>83.77219065656566</v>
-      </c>
-      <c r="G24" t="n">
-        <v>65004766.41414142</v>
-      </c>
-      <c r="H24" t="n">
-        <v>87.31799242424242</v>
-      </c>
-      <c r="I24" t="n">
-        <v>27.86631944444444</v>
-      </c>
-      <c r="J24" t="n">
-        <v>181.9479166666667</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.887152777777778</v>
-      </c>
-      <c r="L24" t="n">
-        <v>76.58159722222223</v>
-      </c>
-      <c r="M24" t="n">
-        <v>11931944.44444444</v>
-      </c>
-      <c r="N24" t="n">
-        <v>78.83159722222223</v>
-      </c>
-      <c r="O24" t="n">
-        <v>25.07216679519311</v>
-      </c>
-      <c r="P24" t="n">
-        <v>179.6831521913759</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.754408858685175</v>
-      </c>
-      <c r="R24" t="n">
-        <v>82.48092908553436</v>
-      </c>
-      <c r="S24" t="n">
-        <v>60388463.26553564</v>
-      </c>
-      <c r="T24" t="n">
-        <v>86.84723306664095</v>
-      </c>
-      <c r="U24" t="n">
-        <v>27.65425976800977</v>
-      </c>
-      <c r="V24" t="n">
-        <v>183.4720833333333</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.954102564102564</v>
-      </c>
-      <c r="X24" t="n">
-        <v>75.75265720390721</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10349814.71306472</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>79.18877594627595</v>
+        <v>79.24953657453658</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1534 +558,1288 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.83333333333334</v>
+        <v>25.31527777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>185.5520833333334</v>
+        <v>183.3217592592593</v>
       </c>
       <c r="E2" t="n">
-        <v>1.583333333333333</v>
+        <v>1.442824074074074</v>
       </c>
       <c r="F2" t="n">
-        <v>76.02083333333334</v>
+        <v>78.59328703703703</v>
       </c>
       <c r="G2" t="n">
-        <v>10193402.77777778</v>
+        <v>22660416.66666667</v>
       </c>
       <c r="H2" t="n">
-        <v>79.05208333333334</v>
+        <v>81.97523148148149</v>
       </c>
       <c r="I2" t="n">
-        <v>27.00925925925926</v>
+        <v>22.51805555555556</v>
       </c>
       <c r="J2" t="n">
-        <v>181.9737654320987</v>
+        <v>181.4222222222222</v>
       </c>
       <c r="K2" t="n">
-        <v>1.407407407407407</v>
+        <v>1.136111111111111</v>
       </c>
       <c r="L2" t="n">
-        <v>75.12191358024693</v>
+        <v>71.35833333333332</v>
       </c>
       <c r="M2" t="n">
-        <v>8219135.802469134</v>
+        <v>9669277.777777778</v>
       </c>
       <c r="N2" t="n">
-        <v>78.20555555555556</v>
+        <v>77.49305555555556</v>
       </c>
       <c r="O2" t="n">
-        <v>27.58333015024192</v>
+        <v>25.15153701918324</v>
       </c>
       <c r="P2" t="n">
-        <v>182.7216257555654</v>
+        <v>181.7983506257021</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.654365526114752</v>
+        <v>1.367762163633916</v>
       </c>
       <c r="R2" t="n">
-        <v>76.42956354790721</v>
+        <v>75.51880875850792</v>
       </c>
       <c r="S2" t="n">
-        <v>9668185.013838071</v>
+        <v>13750483.94910977</v>
       </c>
       <c r="T2" t="n">
-        <v>79.19604391996032</v>
+        <v>80.01106502062721</v>
       </c>
       <c r="U2" t="n">
-        <v>25.55895316804408</v>
+        <v>23.99059885372157</v>
       </c>
       <c r="V2" t="n">
-        <v>180.1654007608553</v>
+        <v>180.0597035795615</v>
       </c>
       <c r="W2" t="n">
-        <v>1.218739341466614</v>
+        <v>1.07565751093826</v>
       </c>
       <c r="X2" t="n">
-        <v>73.75978617342254</v>
+        <v>71.049415794591</v>
       </c>
       <c r="Y2" t="n">
-        <v>7529535.123966943</v>
+        <v>5473260.664803111</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.2428440246622</v>
+        <v>76.44149777396821</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27.73611111111111</v>
+        <v>25.39583333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>183.5594276094276</v>
+        <v>179.7638888888889</v>
       </c>
       <c r="E3" t="n">
-        <v>1.285858585858586</v>
+        <v>1.131944444444444</v>
       </c>
       <c r="F3" t="n">
-        <v>75.87819865319865</v>
+        <v>70.65972222222221</v>
       </c>
       <c r="G3" t="n">
-        <v>9983468.013468012</v>
+        <v>3273842.592592593</v>
       </c>
       <c r="H3" t="n">
-        <v>77.72407407407407</v>
-      </c>
-      <c r="I3" t="n">
-        <v>27.75353535353536</v>
-      </c>
-      <c r="J3" t="n">
-        <v>185.1169191919192</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.940909090909091</v>
-      </c>
-      <c r="L3" t="n">
-        <v>77.41767676767677</v>
-      </c>
-      <c r="M3" t="n">
-        <v>13708131.31313132</v>
-      </c>
-      <c r="N3" t="n">
-        <v>80.08863636363637</v>
-      </c>
+        <v>75.67129629629629</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>27.132339152076</v>
+        <v>25.63553526093633</v>
       </c>
       <c r="P3" t="n">
-        <v>181.1581510594669</v>
+        <v>180.0669048197791</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.097537331089963</v>
+        <v>1.153685151746649</v>
       </c>
       <c r="R3" t="n">
-        <v>74.36837504600663</v>
+        <v>69.85646235078053</v>
       </c>
       <c r="S3" t="n">
-        <v>7397022.232153811</v>
+        <v>2491905.984501238</v>
       </c>
       <c r="T3" t="n">
-        <v>76.53239304555093</v>
+        <v>74.61379609695118</v>
       </c>
       <c r="U3" t="n">
-        <v>25.7703942585286</v>
+        <v>26.31697808242981</v>
       </c>
       <c r="V3" t="n">
-        <v>182.821148022346</v>
+        <v>181.8983554757936</v>
       </c>
       <c r="W3" t="n">
-        <v>1.655153985871445</v>
+        <v>1.00933014354067</v>
       </c>
       <c r="X3" t="n">
-        <v>75.80543988623812</v>
+        <v>68.72922341871471</v>
       </c>
       <c r="Y3" t="n">
-        <v>11820161.2892574</v>
+        <v>2330586.697200211</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.21834147291811</v>
+        <v>72.94502652919836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>28.82575757575758</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5025252525253</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.297979797979798</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>75.36237373737373</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="G4" t="n">
-        <v>6719949.494949495</v>
+        <v>33006250</v>
       </c>
       <c r="H4" t="n">
-        <v>76.56439393939394</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="I4" t="n">
-        <v>25.99537037037037</v>
+        <v>26.71875</v>
       </c>
       <c r="J4" t="n">
-        <v>181.7623456790124</v>
+        <v>182.8541666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>2.708333333333333</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>81.29012345679013</v>
+        <v>71.91319444444444</v>
       </c>
       <c r="M4" t="n">
-        <v>44161265.43209876</v>
+        <v>4064583.333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>85.47067901234567</v>
+        <v>75.46527777777779</v>
       </c>
       <c r="O4" t="n">
-        <v>28.79897091212881</v>
+        <v>26.98036155451016</v>
       </c>
       <c r="P4" t="n">
-        <v>179.79502734108</v>
+        <v>180.7249739768316</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.345313093339409</v>
+        <v>1.908174625512087</v>
       </c>
       <c r="R4" t="n">
-        <v>74.6110693400167</v>
+        <v>78.7587721531994</v>
       </c>
       <c r="S4" t="n">
-        <v>5484069.928609402</v>
+        <v>20598900.70541774</v>
       </c>
       <c r="T4" t="n">
-        <v>75.5116864130022</v>
+        <v>81.63093116034293</v>
       </c>
       <c r="U4" t="n">
-        <v>22.94822282560798</v>
+        <v>26.79670825362001</v>
       </c>
       <c r="V4" t="n">
-        <v>180.8801239768307</v>
+        <v>179.3649695729108</v>
       </c>
       <c r="W4" t="n">
-        <v>2.130421465539523</v>
+        <v>1.060365761689291</v>
       </c>
       <c r="X4" t="n">
-        <v>77.51941140130239</v>
+        <v>71.12411297308357</v>
       </c>
       <c r="Y4" t="n">
-        <v>35599396.64398423</v>
+        <v>2849847.210523681</v>
       </c>
       <c r="Z4" t="n">
-        <v>84.24563147289287</v>
+        <v>73.94618957839545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.31527777777778</v>
+        <v>25.85479797979798</v>
       </c>
       <c r="D5" t="n">
-        <v>183.3217592592593</v>
+        <v>181.6527777777778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.442824074074074</v>
+        <v>1.709779614325069</v>
       </c>
       <c r="F5" t="n">
-        <v>78.59328703703703</v>
+        <v>79.09391643709824</v>
       </c>
       <c r="G5" t="n">
-        <v>22660416.66666667</v>
+        <v>24725918.27364555</v>
       </c>
       <c r="H5" t="n">
-        <v>81.97523148148149</v>
+        <v>82.19090909090909</v>
       </c>
       <c r="I5" t="n">
-        <v>22.60227272727273</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="J5" t="n">
-        <v>181.5858585858586</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="K5" t="n">
-        <v>1.133838383838384</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>71.59848484848484</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="M5" t="n">
-        <v>9680151.515151514</v>
+        <v>4062500</v>
       </c>
       <c r="N5" t="n">
-        <v>77.65025252525253</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="O5" t="n">
-        <v>25.15153701918324</v>
+        <v>24.24142583371832</v>
       </c>
       <c r="P5" t="n">
-        <v>181.7983506257021</v>
+        <v>180.4800125763564</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.367762163633916</v>
+        <v>1.644737179816231</v>
       </c>
       <c r="R5" t="n">
-        <v>75.51880875850792</v>
+        <v>75.16623162739764</v>
       </c>
       <c r="S5" t="n">
-        <v>13750483.94910977</v>
+        <v>16413862.68458156</v>
       </c>
       <c r="T5" t="n">
-        <v>80.01106502062721</v>
+        <v>80.23855744058314</v>
       </c>
       <c r="U5" t="n">
-        <v>23.90011244130826</v>
+        <v>23.59510562248236</v>
       </c>
       <c r="V5" t="n">
-        <v>180.0666330431694</v>
+        <v>180.564903875451</v>
       </c>
       <c r="W5" t="n">
-        <v>1.069352718360071</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>70.76355177996238</v>
+        <v>70.74557885310955</v>
       </c>
       <c r="Y5" t="n">
-        <v>5258564.339561583</v>
+        <v>3790047.160210984</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.23010311820103</v>
+        <v>76.35091117421052</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.5297619047619</v>
+        <v>25.1</v>
       </c>
       <c r="D6" t="n">
-        <v>179.9722222222222</v>
+        <v>182.3613636363636</v>
       </c>
       <c r="E6" t="n">
-        <v>1.14484126984127</v>
+        <v>1.347727272727273</v>
       </c>
       <c r="F6" t="n">
-        <v>70.61309523809523</v>
+        <v>78.36136363636363</v>
       </c>
       <c r="G6" t="n">
-        <v>3220039.682539682</v>
+        <v>23902954.54545455</v>
       </c>
       <c r="H6" t="n">
-        <v>75.67063492063492</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>82.50454545454545</v>
+      </c>
+      <c r="I6" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="J6" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>78</v>
+      </c>
       <c r="O6" t="n">
-        <v>25.6242406558583</v>
+        <v>24.04703959274898</v>
       </c>
       <c r="P6" t="n">
-        <v>180.2339484657499</v>
+        <v>178.939980804855</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.152782817672524</v>
+        <v>1.137846678493132</v>
       </c>
       <c r="R6" t="n">
-        <v>69.95175715488216</v>
+        <v>74.53200992371472</v>
       </c>
       <c r="S6" t="n">
-        <v>2543026.91436423</v>
+        <v>14114314.69369685</v>
       </c>
       <c r="T6" t="n">
-        <v>74.68169404125287</v>
+        <v>80.67736919830742</v>
       </c>
       <c r="U6" t="n">
-        <v>26.1729161834038</v>
+        <v>25.70784687534688</v>
       </c>
       <c r="V6" t="n">
-        <v>181.8136885979088</v>
+        <v>180.8413841713842</v>
       </c>
       <c r="W6" t="n">
-        <v>1.008552631578947</v>
+        <v>1.044029581529581</v>
       </c>
       <c r="X6" t="n">
-        <v>68.60963127107671</v>
+        <v>72.58567515817515</v>
       </c>
       <c r="Y6" t="n">
-        <v>2290782.903806075</v>
+        <v>7703370.986652237</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.97901941647105</v>
+        <v>76.89476232101234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>28.56111111111111</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="D7" t="n">
-        <v>180.1458333333333</v>
+        <v>179.671875</v>
       </c>
       <c r="E7" t="n">
-        <v>2.429166666666666</v>
+        <v>1.03125</v>
       </c>
       <c r="F7" t="n">
-        <v>82.12083333333332</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="G7" t="n">
-        <v>33006250</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="H7" t="n">
-        <v>83.69444444444444</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="I7" t="n">
-        <v>26.8</v>
+        <v>25.47561728395062</v>
       </c>
       <c r="J7" t="n">
-        <v>183.0083333333334</v>
+        <v>182.1258417508417</v>
       </c>
       <c r="K7" t="n">
-        <v>1.097222222222222</v>
+        <v>2.899607182940516</v>
       </c>
       <c r="L7" t="n">
-        <v>71.93055555555556</v>
+        <v>83.94565095398428</v>
       </c>
       <c r="M7" t="n">
-        <v>3944166.666666667</v>
+        <v>66109175.08417508</v>
       </c>
       <c r="N7" t="n">
-        <v>75.34722222222223</v>
+        <v>87.50488215488215</v>
       </c>
       <c r="O7" t="n">
-        <v>27.0506199321834</v>
+        <v>26.1549926553824</v>
       </c>
       <c r="P7" t="n">
-        <v>180.7196935967369</v>
+        <v>178.4871885013627</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.932325421396629</v>
+        <v>1.132388921300313</v>
       </c>
       <c r="R7" t="n">
-        <v>78.81242714629711</v>
+        <v>73.26581407493497</v>
       </c>
       <c r="S7" t="n">
-        <v>20477679.66484839</v>
+        <v>6189981.746920832</v>
       </c>
       <c r="T7" t="n">
-        <v>81.66069094304387</v>
+        <v>75.63635020738633</v>
       </c>
       <c r="U7" t="n">
-        <v>26.92479860315338</v>
+        <v>25.15651526835737</v>
       </c>
       <c r="V7" t="n">
-        <v>179.3325435899884</v>
+        <v>179.2574110830689</v>
       </c>
       <c r="W7" t="n">
-        <v>1.071015978506787</v>
+        <v>2.708553507895614</v>
       </c>
       <c r="X7" t="n">
-        <v>71.25097129688123</v>
+        <v>82.26296583533426</v>
       </c>
       <c r="Y7" t="n">
-        <v>2943847.144481336</v>
+        <v>58603716.60503239</v>
       </c>
       <c r="Z7" t="n">
-        <v>73.95436042205344</v>
+        <v>86.62627248482512</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.85479797979798</v>
+        <v>25.99537037037037</v>
       </c>
       <c r="D8" t="n">
-        <v>181.6527777777778</v>
+        <v>181.7623456790124</v>
       </c>
       <c r="E8" t="n">
-        <v>1.709779614325069</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>79.09391643709824</v>
+        <v>81.29012345679013</v>
       </c>
       <c r="G8" t="n">
-        <v>24725918.27364555</v>
+        <v>44161265.43209876</v>
       </c>
       <c r="H8" t="n">
-        <v>82.19090909090909</v>
+        <v>85.47067901234567</v>
       </c>
       <c r="I8" t="n">
-        <v>23.64814814814815</v>
+        <v>25.39583333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>182.0972222222223</v>
+        <v>179.7638888888889</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.131944444444444</v>
       </c>
       <c r="L8" t="n">
-        <v>71.25462962962963</v>
+        <v>70.65972222222221</v>
       </c>
       <c r="M8" t="n">
-        <v>4062500</v>
+        <v>3273842.592592593</v>
       </c>
       <c r="N8" t="n">
-        <v>77.19907407407408</v>
+        <v>75.67129629629629</v>
       </c>
       <c r="O8" t="n">
-        <v>24.24142583371832</v>
+        <v>22.94822282560798</v>
       </c>
       <c r="P8" t="n">
-        <v>180.4800125763564</v>
+        <v>180.8801239768307</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.644737179816231</v>
+        <v>2.130421465539523</v>
       </c>
       <c r="R8" t="n">
-        <v>75.16623162739764</v>
+        <v>77.51941140130239</v>
       </c>
       <c r="S8" t="n">
-        <v>16413862.68458156</v>
+        <v>35599396.64398423</v>
       </c>
       <c r="T8" t="n">
-        <v>80.23855744058314</v>
+        <v>84.24563147289287</v>
       </c>
       <c r="U8" t="n">
-        <v>23.59510562248236</v>
+        <v>25.63553526093633</v>
       </c>
       <c r="V8" t="n">
-        <v>180.564903875451</v>
+        <v>180.0669048197791</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.153685151746649</v>
       </c>
       <c r="X8" t="n">
-        <v>70.74557885310955</v>
+        <v>69.85646235078053</v>
       </c>
       <c r="Y8" t="n">
-        <v>3790047.160210984</v>
+        <v>2491905.984501238</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.35091117421052</v>
+        <v>74.61379609695118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.1225</v>
+        <v>25.31527777777778</v>
       </c>
       <c r="D9" t="n">
-        <v>182.185</v>
+        <v>183.3217592592593</v>
       </c>
       <c r="E9" t="n">
-        <v>1.345</v>
+        <v>1.442824074074074</v>
       </c>
       <c r="F9" t="n">
-        <v>78.38499999999999</v>
+        <v>78.59328703703703</v>
       </c>
       <c r="G9" t="n">
-        <v>24073250</v>
+        <v>22660416.66666667</v>
       </c>
       <c r="H9" t="n">
-        <v>82.5175</v>
+        <v>81.97523148148149</v>
       </c>
       <c r="I9" t="n">
-        <v>26.8125</v>
+        <v>28.56111111111111</v>
       </c>
       <c r="J9" t="n">
-        <v>182.4375</v>
+        <v>180.1458333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1875</v>
+        <v>2.429166666666666</v>
       </c>
       <c r="L9" t="n">
-        <v>74.4375</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="M9" t="n">
-        <v>10537500</v>
+        <v>33006250</v>
       </c>
       <c r="N9" t="n">
-        <v>77.875</v>
+        <v>83.69444444444444</v>
       </c>
       <c r="O9" t="n">
-        <v>24.0748204751008</v>
+        <v>25.15153701918324</v>
       </c>
       <c r="P9" t="n">
-        <v>179.0032096545712</v>
+        <v>181.7983506257021</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.136246730957829</v>
+        <v>1.367762163633916</v>
       </c>
       <c r="R9" t="n">
-        <v>74.80828783916313</v>
+        <v>75.51880875850792</v>
       </c>
       <c r="S9" t="n">
-        <v>14677284.62460499</v>
+        <v>13750483.94910977</v>
       </c>
       <c r="T9" t="n">
-        <v>80.79895227198431</v>
+        <v>80.01106502062721</v>
       </c>
       <c r="U9" t="n">
-        <v>25.85128936719846</v>
+        <v>26.98036155451016</v>
       </c>
       <c r="V9" t="n">
-        <v>180.6609985973622</v>
+        <v>180.7249739768316</v>
       </c>
       <c r="W9" t="n">
-        <v>1.053013905286633</v>
+        <v>1.908174625512087</v>
       </c>
       <c r="X9" t="n">
-        <v>72.85710728665275</v>
+        <v>78.7587721531994</v>
       </c>
       <c r="Y9" t="n">
-        <v>7892025.572281255</v>
+        <v>20598900.70541774</v>
       </c>
       <c r="Z9" t="n">
-        <v>77.0212124996216</v>
+        <v>81.63093116034293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.97569444444444</v>
+        <v>26.71875</v>
       </c>
       <c r="D10" t="n">
-        <v>179.671875</v>
+        <v>182.8541666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>1.03125</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>74.95486111111111</v>
+        <v>71.91319444444444</v>
       </c>
       <c r="G10" t="n">
-        <v>10317013.88888889</v>
+        <v>4064583.333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>78.54340277777777</v>
+        <v>75.46527777777779</v>
       </c>
       <c r="I10" t="n">
-        <v>25.47561728395062</v>
+        <v>28.82575757575758</v>
       </c>
       <c r="J10" t="n">
-        <v>182.1258417508417</v>
+        <v>179.5025252525253</v>
       </c>
       <c r="K10" t="n">
-        <v>2.899607182940516</v>
+        <v>1.297979797979798</v>
       </c>
       <c r="L10" t="n">
-        <v>83.94565095398428</v>
+        <v>75.36237373737373</v>
       </c>
       <c r="M10" t="n">
-        <v>66109175.08417508</v>
+        <v>6719949.494949495</v>
       </c>
       <c r="N10" t="n">
-        <v>87.50488215488215</v>
+        <v>76.56439393939394</v>
       </c>
       <c r="O10" t="n">
-        <v>26.1549926553824</v>
+        <v>26.79670825362001</v>
       </c>
       <c r="P10" t="n">
-        <v>178.4871885013627</v>
+        <v>179.3649695729108</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.132388921300313</v>
+        <v>1.060365761689291</v>
       </c>
       <c r="R10" t="n">
-        <v>73.26581407493497</v>
+        <v>71.12411297308357</v>
       </c>
       <c r="S10" t="n">
-        <v>6189981.746920832</v>
+        <v>2849847.210523681</v>
       </c>
       <c r="T10" t="n">
-        <v>75.63635020738633</v>
+        <v>73.94618957839545</v>
       </c>
       <c r="U10" t="n">
-        <v>25.15651526835737</v>
+        <v>28.79897091212881</v>
       </c>
       <c r="V10" t="n">
-        <v>179.2574110830689</v>
+        <v>179.79502734108</v>
       </c>
       <c r="W10" t="n">
-        <v>2.708553507895614</v>
+        <v>1.345313093339409</v>
       </c>
       <c r="X10" t="n">
-        <v>82.26296583533426</v>
+        <v>74.6110693400167</v>
       </c>
       <c r="Y10" t="n">
-        <v>58603716.60503239</v>
+        <v>5484069.928609402</v>
       </c>
       <c r="Z10" t="n">
-        <v>86.62627248482512</v>
+        <v>75.5116864130022</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
-        <v>25.99537037037037</v>
-      </c>
-      <c r="D11" t="n">
-        <v>181.7623456790124</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.708333333333333</v>
-      </c>
-      <c r="F11" t="n">
-        <v>81.29012345679013</v>
-      </c>
-      <c r="G11" t="n">
-        <v>44161265.43209876</v>
-      </c>
-      <c r="H11" t="n">
-        <v>85.47067901234567</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>25.5297619047619</v>
+        <v>27.6459595959596</v>
       </c>
       <c r="J11" t="n">
-        <v>179.9722222222222</v>
+        <v>183.5162457912458</v>
       </c>
       <c r="K11" t="n">
-        <v>1.14484126984127</v>
+        <v>1.295707070707071</v>
       </c>
       <c r="L11" t="n">
-        <v>70.61309523809523</v>
+        <v>75.9736531986532</v>
       </c>
       <c r="M11" t="n">
-        <v>3220039.682539682</v>
+        <v>10256649.83164983</v>
       </c>
       <c r="N11" t="n">
-        <v>75.67063492063492</v>
+        <v>77.84074074074074</v>
       </c>
       <c r="O11" t="n">
-        <v>22.94822282560798</v>
+        <v>26.31697808242981</v>
       </c>
       <c r="P11" t="n">
-        <v>180.8801239768307</v>
+        <v>181.8983554757936</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.130421465539523</v>
+        <v>1.00933014354067</v>
       </c>
       <c r="R11" t="n">
-        <v>77.51941140130239</v>
+        <v>68.72922341871471</v>
       </c>
       <c r="S11" t="n">
-        <v>35599396.64398423</v>
+        <v>2330586.697200211</v>
       </c>
       <c r="T11" t="n">
-        <v>84.24563147289287</v>
+        <v>72.94502652919836</v>
       </c>
       <c r="U11" t="n">
-        <v>25.6242406558583</v>
+        <v>27.20266343563557</v>
       </c>
       <c r="V11" t="n">
-        <v>180.2339484657499</v>
+        <v>181.4422762480038</v>
       </c>
       <c r="W11" t="n">
-        <v>1.152782817672524</v>
+        <v>1.104136124453462</v>
       </c>
       <c r="X11" t="n">
-        <v>69.95175715488216</v>
+        <v>74.34386524208504</v>
       </c>
       <c r="Y11" t="n">
-        <v>2543026.91436423</v>
+        <v>7478769.969710372</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.68169404125287</v>
+        <v>76.48865247239861</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.31527777777778</v>
+        <v>22.51805555555556</v>
       </c>
       <c r="D12" t="n">
-        <v>183.3217592592593</v>
+        <v>181.4222222222222</v>
       </c>
       <c r="E12" t="n">
-        <v>1.442824074074074</v>
+        <v>1.136111111111111</v>
       </c>
       <c r="F12" t="n">
-        <v>78.59328703703703</v>
+        <v>71.35833333333332</v>
       </c>
       <c r="G12" t="n">
-        <v>22660416.66666667</v>
+        <v>9669277.777777778</v>
       </c>
       <c r="H12" t="n">
-        <v>81.97523148148149</v>
+        <v>77.49305555555556</v>
       </c>
       <c r="I12" t="n">
-        <v>28.56111111111111</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="J12" t="n">
-        <v>180.1458333333333</v>
+        <v>185.5520833333334</v>
       </c>
       <c r="K12" t="n">
-        <v>2.429166666666666</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>82.12083333333332</v>
+        <v>76.02083333333334</v>
       </c>
       <c r="M12" t="n">
-        <v>33006250</v>
+        <v>10193402.77777778</v>
       </c>
       <c r="N12" t="n">
-        <v>83.69444444444444</v>
+        <v>79.05208333333334</v>
       </c>
       <c r="O12" t="n">
-        <v>25.15153701918324</v>
+        <v>23.99059885372157</v>
       </c>
       <c r="P12" t="n">
-        <v>181.7983506257021</v>
+        <v>180.0597035795615</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.367762163633916</v>
+        <v>1.07565751093826</v>
       </c>
       <c r="R12" t="n">
-        <v>75.51880875850792</v>
+        <v>71.049415794591</v>
       </c>
       <c r="S12" t="n">
-        <v>13750483.94910977</v>
+        <v>5473260.664803111</v>
       </c>
       <c r="T12" t="n">
-        <v>80.01106502062721</v>
+        <v>76.44149777396821</v>
       </c>
       <c r="U12" t="n">
-        <v>27.0506199321834</v>
+        <v>27.45138597105509</v>
       </c>
       <c r="V12" t="n">
-        <v>180.7196935967369</v>
+        <v>182.4531569426016</v>
       </c>
       <c r="W12" t="n">
-        <v>1.932325421396629</v>
+        <v>1.662335065605189</v>
       </c>
       <c r="X12" t="n">
-        <v>78.81242714629711</v>
+        <v>76.41459991891493</v>
       </c>
       <c r="Y12" t="n">
-        <v>20477679.66484839</v>
+        <v>9987502.929351566</v>
       </c>
       <c r="Z12" t="n">
-        <v>81.66069094304387</v>
+        <v>79.25262359329696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.8</v>
+        <v>23.64814814814815</v>
       </c>
       <c r="D13" t="n">
-        <v>183.0083333333334</v>
+        <v>182.0972222222223</v>
       </c>
       <c r="E13" t="n">
-        <v>1.097222222222222</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>71.93055555555556</v>
+        <v>71.25462962962963</v>
       </c>
       <c r="G13" t="n">
-        <v>3944166.666666667</v>
+        <v>4062500</v>
       </c>
       <c r="H13" t="n">
-        <v>75.34722222222223</v>
+        <v>77.19907407407408</v>
       </c>
       <c r="I13" t="n">
-        <v>28.82575757575758</v>
+        <v>24.97569444444444</v>
       </c>
       <c r="J13" t="n">
-        <v>179.5025252525253</v>
+        <v>179.671875</v>
       </c>
       <c r="K13" t="n">
-        <v>1.297979797979798</v>
+        <v>1.03125</v>
       </c>
       <c r="L13" t="n">
-        <v>75.36237373737373</v>
+        <v>74.95486111111111</v>
       </c>
       <c r="M13" t="n">
-        <v>6719949.494949495</v>
+        <v>10317013.88888889</v>
       </c>
       <c r="N13" t="n">
-        <v>76.56439393939394</v>
+        <v>78.54340277777777</v>
       </c>
       <c r="O13" t="n">
-        <v>26.92479860315338</v>
+        <v>23.59510562248236</v>
       </c>
       <c r="P13" t="n">
-        <v>179.3325435899884</v>
+        <v>180.564903875451</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.071015978506787</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>71.25097129688123</v>
+        <v>70.74557885310955</v>
       </c>
       <c r="S13" t="n">
-        <v>2943847.144481336</v>
+        <v>3790047.160210984</v>
       </c>
       <c r="T13" t="n">
-        <v>73.95436042205344</v>
+        <v>76.35091117421052</v>
       </c>
       <c r="U13" t="n">
-        <v>28.79897091212881</v>
+        <v>26.1549926553824</v>
       </c>
       <c r="V13" t="n">
-        <v>179.79502734108</v>
+        <v>178.4871885013627</v>
       </c>
       <c r="W13" t="n">
-        <v>1.345313093339409</v>
+        <v>1.132388921300313</v>
       </c>
       <c r="X13" t="n">
-        <v>74.6110693400167</v>
+        <v>73.26581407493497</v>
       </c>
       <c r="Y13" t="n">
-        <v>5484069.928609402</v>
+        <v>6189981.746920832</v>
       </c>
       <c r="Z13" t="n">
-        <v>75.5116864130022</v>
+        <v>75.63635020738633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="D14" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>78</v>
+      </c>
       <c r="I14" t="n">
-        <v>27.73611111111111</v>
+        <v>26.93055555555555</v>
       </c>
       <c r="J14" t="n">
-        <v>183.5594276094276</v>
+        <v>181.8541666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>1.285858585858586</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="n">
-        <v>75.87819865319865</v>
+        <v>74.89861111111111</v>
       </c>
       <c r="M14" t="n">
-        <v>9983468.013468012</v>
+        <v>8176111.11111111</v>
       </c>
       <c r="N14" t="n">
-        <v>77.72407407407407</v>
+        <v>77.97388888888889</v>
       </c>
       <c r="O14" t="n">
-        <v>26.1729161834038</v>
+        <v>25.70784687534688</v>
       </c>
       <c r="P14" t="n">
-        <v>181.8136885979088</v>
+        <v>180.8413841713842</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.008552631578947</v>
+        <v>1.044029581529581</v>
       </c>
       <c r="R14" t="n">
-        <v>68.60963127107671</v>
+        <v>72.58567515817515</v>
       </c>
       <c r="S14" t="n">
-        <v>2290782.903806075</v>
+        <v>7703370.986652237</v>
       </c>
       <c r="T14" t="n">
-        <v>72.97901941647105</v>
+        <v>76.89476232101234</v>
       </c>
       <c r="U14" t="n">
-        <v>27.132339152076</v>
+        <v>25.62021687462864</v>
       </c>
       <c r="V14" t="n">
-        <v>181.1581510594669</v>
+        <v>179.9947546190193</v>
       </c>
       <c r="W14" t="n">
-        <v>1.097537331089963</v>
+        <v>1.244628710069886</v>
       </c>
       <c r="X14" t="n">
-        <v>74.36837504600663</v>
+        <v>73.83372556093144</v>
       </c>
       <c r="Y14" t="n">
-        <v>7397022.232153811</v>
+        <v>7794598.373440285</v>
       </c>
       <c r="Z14" t="n">
-        <v>76.53239304555093</v>
+        <v>77.41868545397958</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>22.60227272727273</v>
+        <v>27.525</v>
       </c>
       <c r="D15" t="n">
-        <v>181.5858585858586</v>
+        <v>185.1421717171717</v>
       </c>
       <c r="E15" t="n">
-        <v>1.133838383838384</v>
+        <v>1.896717171717172</v>
       </c>
       <c r="F15" t="n">
-        <v>71.59848484848484</v>
+        <v>77.20176767676767</v>
       </c>
       <c r="G15" t="n">
-        <v>9680151.515151514</v>
+        <v>13417095.95959596</v>
       </c>
       <c r="H15" t="n">
-        <v>77.65025252525253</v>
+        <v>80.03434343434343</v>
       </c>
       <c r="I15" t="n">
-        <v>26.83333333333334</v>
+        <v>25.1</v>
       </c>
       <c r="J15" t="n">
-        <v>185.5520833333334</v>
+        <v>182.3613636363636</v>
       </c>
       <c r="K15" t="n">
-        <v>1.583333333333333</v>
+        <v>1.347727272727273</v>
       </c>
       <c r="L15" t="n">
-        <v>76.02083333333334</v>
+        <v>78.36136363636363</v>
       </c>
       <c r="M15" t="n">
-        <v>10193402.77777778</v>
+        <v>23902954.54545455</v>
       </c>
       <c r="N15" t="n">
-        <v>79.05208333333334</v>
+        <v>82.50454545454545</v>
       </c>
       <c r="O15" t="n">
-        <v>23.90011244130826</v>
+        <v>25.86868147855495</v>
       </c>
       <c r="P15" t="n">
-        <v>180.0666330431694</v>
+        <v>182.6720044123328</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.069352718360071</v>
+        <v>1.648302865976846</v>
       </c>
       <c r="R15" t="n">
-        <v>70.76355177996238</v>
+        <v>75.64786412866236</v>
       </c>
       <c r="S15" t="n">
-        <v>5258564.339561583</v>
+        <v>11375708.06132591</v>
       </c>
       <c r="T15" t="n">
-        <v>76.23010311820103</v>
+        <v>80.23151670348466</v>
       </c>
       <c r="U15" t="n">
-        <v>27.58333015024192</v>
+        <v>24.04703959274898</v>
       </c>
       <c r="V15" t="n">
-        <v>182.7216257555654</v>
+        <v>178.939980804855</v>
       </c>
       <c r="W15" t="n">
-        <v>1.654365526114752</v>
+        <v>1.137846678493132</v>
       </c>
       <c r="X15" t="n">
-        <v>76.42956354790721</v>
+        <v>74.53200992371472</v>
       </c>
       <c r="Y15" t="n">
-        <v>9668185.013838071</v>
+        <v>14114314.69369685</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.19604391996032</v>
+        <v>80.67736919830742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>23.64814814814815</v>
+        <v>26.36527777777778</v>
       </c>
       <c r="D16" t="n">
-        <v>182.0972222222223</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>1.323611111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>71.25462962962963</v>
+        <v>75.78194444444445</v>
       </c>
       <c r="G16" t="n">
-        <v>4062500</v>
+        <v>11501631.94444444</v>
       </c>
       <c r="H16" t="n">
-        <v>77.19907407407408</v>
+        <v>78.8763888888889</v>
       </c>
       <c r="I16" t="n">
-        <v>24.97569444444444</v>
+        <v>25.85479797979798</v>
       </c>
       <c r="J16" t="n">
-        <v>179.671875</v>
+        <v>181.6527777777778</v>
       </c>
       <c r="K16" t="n">
-        <v>1.03125</v>
+        <v>1.709779614325069</v>
       </c>
       <c r="L16" t="n">
-        <v>74.95486111111111</v>
+        <v>79.09391643709824</v>
       </c>
       <c r="M16" t="n">
-        <v>10317013.88888889</v>
+        <v>24725918.27364555</v>
       </c>
       <c r="N16" t="n">
-        <v>78.54340277777777</v>
+        <v>82.19090909090909</v>
       </c>
       <c r="O16" t="n">
-        <v>23.59510562248236</v>
+        <v>24.43599206349206</v>
       </c>
       <c r="P16" t="n">
-        <v>180.564903875451</v>
+        <v>183.6600396825397</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="R16" t="n">
-        <v>70.74557885310955</v>
+        <v>71.80648809523809</v>
       </c>
       <c r="S16" t="n">
-        <v>3790047.160210984</v>
+        <v>5516420.138888889</v>
       </c>
       <c r="T16" t="n">
-        <v>76.35091117421052</v>
+        <v>77.29160714285715</v>
       </c>
       <c r="U16" t="n">
-        <v>26.1549926553824</v>
+        <v>24.24142583371832</v>
       </c>
       <c r="V16" t="n">
-        <v>178.4871885013627</v>
+        <v>180.4800125763564</v>
       </c>
       <c r="W16" t="n">
-        <v>1.132388921300313</v>
+        <v>1.644737179816231</v>
       </c>
       <c r="X16" t="n">
-        <v>73.26581407493497</v>
+        <v>75.16623162739764</v>
       </c>
       <c r="Y16" t="n">
-        <v>6189981.746920832</v>
+        <v>16413862.68458156</v>
       </c>
       <c r="Z16" t="n">
-        <v>75.63635020738633</v>
+        <v>80.23855744058314</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.8125</v>
+        <v>25.47561728395062</v>
       </c>
       <c r="D17" t="n">
-        <v>182.4375</v>
+        <v>182.1258417508417</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1875</v>
+        <v>2.899607182940516</v>
       </c>
       <c r="F17" t="n">
-        <v>74.4375</v>
+        <v>83.94565095398428</v>
       </c>
       <c r="G17" t="n">
-        <v>10537500</v>
+        <v>66109175.08417508</v>
       </c>
       <c r="H17" t="n">
-        <v>77.875</v>
+        <v>87.50488215488215</v>
       </c>
       <c r="I17" t="n">
-        <v>27.00925925925926</v>
+        <v>27.86631944444444</v>
       </c>
       <c r="J17" t="n">
-        <v>181.9737654320987</v>
+        <v>181.9479166666667</v>
       </c>
       <c r="K17" t="n">
-        <v>1.407407407407407</v>
+        <v>1.887152777777778</v>
       </c>
       <c r="L17" t="n">
-        <v>75.12191358024693</v>
+        <v>76.58159722222223</v>
       </c>
       <c r="M17" t="n">
-        <v>8219135.802469134</v>
+        <v>11931944.44444444</v>
       </c>
       <c r="N17" t="n">
-        <v>78.20555555555556</v>
+        <v>78.83159722222223</v>
       </c>
       <c r="O17" t="n">
-        <v>25.85128936719846</v>
+        <v>25.15651526835737</v>
       </c>
       <c r="P17" t="n">
-        <v>180.6609985973622</v>
+        <v>179.2574110830689</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.053013905286633</v>
+        <v>2.708553507895614</v>
       </c>
       <c r="R17" t="n">
-        <v>72.85710728665275</v>
+        <v>82.26296583533426</v>
       </c>
       <c r="S17" t="n">
-        <v>7892025.572281255</v>
+        <v>58603716.60503239</v>
       </c>
       <c r="T17" t="n">
-        <v>77.0212124996216</v>
+        <v>86.62627248482512</v>
       </c>
       <c r="U17" t="n">
-        <v>25.55895316804408</v>
+        <v>27.30906732156733</v>
       </c>
       <c r="V17" t="n">
-        <v>180.1654007608553</v>
+        <v>183.3382575757576</v>
       </c>
       <c r="W17" t="n">
-        <v>1.218739341466614</v>
+        <v>1.932301032301032</v>
       </c>
       <c r="X17" t="n">
-        <v>73.75978617342254</v>
+        <v>75.55436369186368</v>
       </c>
       <c r="Y17" t="n">
-        <v>7529535.123966943</v>
+        <v>10001130.25863026</v>
       </c>
       <c r="Z17" t="n">
-        <v>77.2428440246622</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27.75353535353536</v>
-      </c>
-      <c r="D18" t="n">
-        <v>185.1169191919192</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.940909090909091</v>
-      </c>
-      <c r="F18" t="n">
-        <v>77.41767676767677</v>
-      </c>
-      <c r="G18" t="n">
-        <v>13708131.31313132</v>
-      </c>
-      <c r="H18" t="n">
-        <v>80.08863636363637</v>
-      </c>
-      <c r="I18" t="n">
-        <v>25.1225</v>
-      </c>
-      <c r="J18" t="n">
-        <v>182.185</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.345</v>
-      </c>
-      <c r="L18" t="n">
-        <v>78.38499999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>24073250</v>
-      </c>
-      <c r="N18" t="n">
-        <v>82.5175</v>
-      </c>
-      <c r="O18" t="n">
-        <v>25.7703942585286</v>
-      </c>
-      <c r="P18" t="n">
-        <v>182.821148022346</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.655153985871445</v>
-      </c>
-      <c r="R18" t="n">
-        <v>75.80543988623812</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11820161.2892574</v>
-      </c>
-      <c r="T18" t="n">
-        <v>80.21834147291811</v>
-      </c>
-      <c r="U18" t="n">
-        <v>24.0748204751008</v>
-      </c>
-      <c r="V18" t="n">
-        <v>179.0032096545712</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.136246730957829</v>
-      </c>
-      <c r="X18" t="n">
-        <v>74.80828783916313</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>14677284.62460499</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>80.79895227198431</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>26.36527777777778</v>
-      </c>
-      <c r="D19" t="n">
-        <v>182.8888888888889</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.323611111111111</v>
-      </c>
-      <c r="F19" t="n">
-        <v>75.78194444444445</v>
-      </c>
-      <c r="G19" t="n">
-        <v>11501631.94444444</v>
-      </c>
-      <c r="H19" t="n">
-        <v>78.8763888888889</v>
-      </c>
-      <c r="I19" t="n">
-        <v>25.85479797979798</v>
-      </c>
-      <c r="J19" t="n">
-        <v>181.6527777777778</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.709779614325069</v>
-      </c>
-      <c r="L19" t="n">
-        <v>79.09391643709824</v>
-      </c>
-      <c r="M19" t="n">
-        <v>24725918.27364555</v>
-      </c>
-      <c r="N19" t="n">
-        <v>82.19090909090909</v>
-      </c>
-      <c r="O19" t="n">
-        <v>24.43531746031746</v>
-      </c>
-      <c r="P19" t="n">
-        <v>183.7104256854257</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.088059163059163</v>
-      </c>
-      <c r="R19" t="n">
-        <v>71.94745670995671</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5596096.23015873</v>
-      </c>
-      <c r="T19" t="n">
-        <v>77.42094155844156</v>
-      </c>
-      <c r="U19" t="n">
-        <v>24.24142583371832</v>
-      </c>
-      <c r="V19" t="n">
-        <v>180.4800125763564</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.644737179816231</v>
-      </c>
-      <c r="X19" t="n">
-        <v>75.16623162739764</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>16413862.68458156</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>80.23855744058314</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>25.47561728395062</v>
-      </c>
-      <c r="D20" t="n">
-        <v>182.1258417508417</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.899607182940516</v>
-      </c>
-      <c r="F20" t="n">
-        <v>83.94565095398428</v>
-      </c>
-      <c r="G20" t="n">
-        <v>66109175.08417508</v>
-      </c>
-      <c r="H20" t="n">
-        <v>87.50488215488215</v>
-      </c>
-      <c r="I20" t="n">
-        <v>27.86631944444444</v>
-      </c>
-      <c r="J20" t="n">
-        <v>181.9479166666667</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.887152777777778</v>
-      </c>
-      <c r="L20" t="n">
-        <v>76.58159722222223</v>
-      </c>
-      <c r="M20" t="n">
-        <v>11931944.44444444</v>
-      </c>
-      <c r="N20" t="n">
-        <v>78.83159722222223</v>
-      </c>
-      <c r="O20" t="n">
-        <v>25.15651526835737</v>
-      </c>
-      <c r="P20" t="n">
-        <v>179.2574110830689</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.708553507895614</v>
-      </c>
-      <c r="R20" t="n">
-        <v>82.26296583533426</v>
-      </c>
-      <c r="S20" t="n">
-        <v>58603716.60503239</v>
-      </c>
-      <c r="T20" t="n">
-        <v>86.62627248482512</v>
-      </c>
-      <c r="U20" t="n">
-        <v>27.30906732156733</v>
-      </c>
-      <c r="V20" t="n">
-        <v>183.3382575757576</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.932301032301032</v>
-      </c>
-      <c r="X20" t="n">
-        <v>75.55436369186368</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>10001130.25863026</v>
-      </c>
-      <c r="Z20" t="n">
         <v>79.24953657453658</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1289 +558,809 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.31527777777778</v>
+        <v>25.82291666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>183.3217592592593</v>
+        <v>181.9045138888889</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442824074074074</v>
+        <v>2.703125</v>
       </c>
       <c r="F2" t="n">
-        <v>78.59328703703703</v>
+        <v>81.27951388888889</v>
       </c>
       <c r="G2" t="n">
-        <v>22660416.66666667</v>
+        <v>44854861.1111111</v>
       </c>
       <c r="H2" t="n">
-        <v>81.97523148148149</v>
+        <v>85.62326388888889</v>
       </c>
       <c r="I2" t="n">
-        <v>22.51805555555556</v>
+        <v>25.33928571428572</v>
       </c>
       <c r="J2" t="n">
-        <v>181.4222222222222</v>
+        <v>179.718253968254</v>
       </c>
       <c r="K2" t="n">
-        <v>1.136111111111111</v>
+        <v>1.113095238095238</v>
       </c>
       <c r="L2" t="n">
-        <v>71.35833333333332</v>
+        <v>70.64484126984127</v>
       </c>
       <c r="M2" t="n">
-        <v>9669277.777777778</v>
+        <v>3187103.174603175</v>
       </c>
       <c r="N2" t="n">
-        <v>77.49305555555556</v>
+        <v>75.49603174603173</v>
       </c>
       <c r="O2" t="n">
-        <v>25.15153701918324</v>
+        <v>22.80811587373632</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7983506257021</v>
+        <v>180.9057924260285</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.367762163633916</v>
+        <v>2.075876010994068</v>
       </c>
       <c r="R2" t="n">
-        <v>75.51880875850792</v>
+        <v>76.90122958312058</v>
       </c>
       <c r="S2" t="n">
-        <v>13750483.94910977</v>
+        <v>34737872.57981312</v>
       </c>
       <c r="T2" t="n">
-        <v>80.01106502062721</v>
+        <v>83.76488280979127</v>
       </c>
       <c r="U2" t="n">
-        <v>23.99059885372157</v>
+        <v>25.46278232252497</v>
       </c>
       <c r="V2" t="n">
-        <v>180.0597035795615</v>
+        <v>180.1446627514642</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07565751093826</v>
+        <v>1.146086389101095</v>
       </c>
       <c r="X2" t="n">
-        <v>71.049415794591</v>
+        <v>69.91529882154883</v>
       </c>
       <c r="Y2" t="n">
-        <v>5473260.664803111</v>
+        <v>2625913.819126135</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.44149777396821</v>
+        <v>74.8699380888719</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.39583333333333</v>
+        <v>25.32121212121212</v>
       </c>
       <c r="D3" t="n">
-        <v>179.7638888888889</v>
+        <v>183.1578282828283</v>
       </c>
       <c r="E3" t="n">
-        <v>1.131944444444444</v>
+        <v>1.471717171717172</v>
       </c>
       <c r="F3" t="n">
-        <v>70.65972222222221</v>
+        <v>78.62449494949495</v>
       </c>
       <c r="G3" t="n">
-        <v>3273842.592592593</v>
+        <v>22862500</v>
       </c>
       <c r="H3" t="n">
-        <v>75.67129629629629</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>82.01843434343435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28.60956790123457</v>
+      </c>
+      <c r="J3" t="n">
+        <v>180.1064814814815</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.407407407407407</v>
+      </c>
+      <c r="L3" t="n">
+        <v>82.10648148148147</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32805555.55555556</v>
+      </c>
+      <c r="N3" t="n">
+        <v>83.63271604938272</v>
+      </c>
       <c r="O3" t="n">
-        <v>25.63553526093633</v>
+        <v>24.93034136700932</v>
       </c>
       <c r="P3" t="n">
-        <v>180.0669048197791</v>
+        <v>182.0943651184557</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.153685151746649</v>
+        <v>1.352363612909278</v>
       </c>
       <c r="R3" t="n">
-        <v>69.85646235078053</v>
+        <v>75.26591020778328</v>
       </c>
       <c r="S3" t="n">
-        <v>2491905.984501238</v>
+        <v>13651589.02157354</v>
       </c>
       <c r="T3" t="n">
-        <v>74.61379609695118</v>
+        <v>79.96251429598952</v>
       </c>
       <c r="U3" t="n">
-        <v>26.31697808242981</v>
+        <v>26.7667251908738</v>
       </c>
       <c r="V3" t="n">
-        <v>181.8983554757936</v>
+        <v>180.4749739768316</v>
       </c>
       <c r="W3" t="n">
-        <v>1.00933014354067</v>
+        <v>1.862720080057541</v>
       </c>
       <c r="X3" t="n">
-        <v>68.72922341871471</v>
+        <v>78.82695397138122</v>
       </c>
       <c r="Y3" t="n">
-        <v>2330586.697200211</v>
+        <v>21479809.79632682</v>
       </c>
       <c r="Z3" t="n">
-        <v>72.94502652919836</v>
+        <v>81.81274934216111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>28.56111111111111</v>
+        <v>26.71875</v>
       </c>
       <c r="D4" t="n">
-        <v>180.1458333333333</v>
+        <v>182.8541666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>2.429166666666666</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="F4" t="n">
-        <v>82.12083333333332</v>
+        <v>71.91319444444444</v>
       </c>
       <c r="G4" t="n">
-        <v>33006250</v>
+        <v>4064583.333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>83.69444444444444</v>
+        <v>75.46527777777779</v>
       </c>
       <c r="I4" t="n">
-        <v>26.71875</v>
+        <v>28.95833333333334</v>
       </c>
       <c r="J4" t="n">
-        <v>182.8541666666667</v>
+        <v>179.6027777777778</v>
       </c>
       <c r="K4" t="n">
-        <v>1.121527777777778</v>
+        <v>1.327777777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>71.91319444444444</v>
+        <v>75.41111111111111</v>
       </c>
       <c r="M4" t="n">
-        <v>4064583.333333333</v>
+        <v>6709444.444444445</v>
       </c>
       <c r="N4" t="n">
-        <v>75.46527777777779</v>
+        <v>76.59583333333333</v>
       </c>
       <c r="O4" t="n">
-        <v>26.98036155451016</v>
+        <v>26.76358065443543</v>
       </c>
       <c r="P4" t="n">
-        <v>180.7249739768316</v>
+        <v>179.4213256412705</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.908174625512087</v>
+        <v>1.056592901583711</v>
       </c>
       <c r="R4" t="n">
-        <v>78.7587721531994</v>
+        <v>71.11218924559918</v>
       </c>
       <c r="S4" t="n">
-        <v>20598900.70541774</v>
+        <v>2860065.093199285</v>
       </c>
       <c r="T4" t="n">
-        <v>81.63093116034293</v>
+        <v>74.01205272974575</v>
       </c>
       <c r="U4" t="n">
-        <v>26.79670825362001</v>
+        <v>28.75654666970457</v>
       </c>
       <c r="V4" t="n">
-        <v>179.3649695729108</v>
+        <v>179.4495727956254</v>
       </c>
       <c r="W4" t="n">
-        <v>1.060365761689291</v>
+        <v>1.345313093339409</v>
       </c>
       <c r="X4" t="n">
-        <v>71.12411297308357</v>
+        <v>74.5989481278955</v>
       </c>
       <c r="Y4" t="n">
-        <v>2849847.210523681</v>
+        <v>5503463.868003341</v>
       </c>
       <c r="Z4" t="n">
-        <v>73.94618957839545</v>
+        <v>75.47532277663858</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>25.85479797979798</v>
-      </c>
-      <c r="D5" t="n">
-        <v>181.6527777777778</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.709779614325069</v>
-      </c>
-      <c r="F5" t="n">
-        <v>79.09391643709824</v>
-      </c>
-      <c r="G5" t="n">
-        <v>24725918.27364555</v>
-      </c>
-      <c r="H5" t="n">
-        <v>82.19090909090909</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>23.64814814814815</v>
+        <v>27.6459595959596</v>
       </c>
       <c r="J5" t="n">
-        <v>182.0972222222223</v>
+        <v>183.5162457912458</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>1.295707070707071</v>
       </c>
       <c r="L5" t="n">
-        <v>71.25462962962963</v>
+        <v>75.9736531986532</v>
       </c>
       <c r="M5" t="n">
-        <v>4062500</v>
+        <v>10256649.83164983</v>
       </c>
       <c r="N5" t="n">
-        <v>77.19907407407408</v>
+        <v>77.84074074074074</v>
       </c>
       <c r="O5" t="n">
-        <v>24.24142583371832</v>
+        <v>26.29056324222732</v>
       </c>
       <c r="P5" t="n">
-        <v>180.4800125763564</v>
+        <v>181.7798417258266</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.644737179816231</v>
+        <v>1.012520885547201</v>
       </c>
       <c r="R5" t="n">
-        <v>75.16623162739764</v>
+        <v>69.02956591159959</v>
       </c>
       <c r="S5" t="n">
-        <v>16413862.68458156</v>
+        <v>2613851.297830352</v>
       </c>
       <c r="T5" t="n">
-        <v>80.23855744058314</v>
+        <v>73.15992511208262</v>
       </c>
       <c r="U5" t="n">
-        <v>23.59510562248236</v>
+        <v>27.20266343563557</v>
       </c>
       <c r="V5" t="n">
-        <v>180.564903875451</v>
+        <v>181.4422762480038</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.104136124453462</v>
       </c>
       <c r="X5" t="n">
-        <v>70.74557885310955</v>
+        <v>74.34386524208504</v>
       </c>
       <c r="Y5" t="n">
-        <v>3790047.160210984</v>
+        <v>7478769.969710372</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.35091117421052</v>
+        <v>76.48865247239861</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.1</v>
+        <v>22.64267676767677</v>
       </c>
       <c r="D6" t="n">
-        <v>182.3613636363636</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="E6" t="n">
-        <v>1.347727272727273</v>
+        <v>1.143939393939394</v>
       </c>
       <c r="F6" t="n">
-        <v>78.36136363636363</v>
+        <v>71.37626262626263</v>
       </c>
       <c r="G6" t="n">
-        <v>23902954.54545455</v>
+        <v>9642979.797979798</v>
       </c>
       <c r="H6" t="n">
-        <v>82.50454545454545</v>
+        <v>77.41792929292929</v>
       </c>
       <c r="I6" t="n">
-        <v>26.875</v>
+        <v>26.22222222222222</v>
       </c>
       <c r="J6" t="n">
-        <v>181.875</v>
+        <v>185.1064814814815</v>
       </c>
       <c r="K6" t="n">
-        <v>1.25</v>
+        <v>1.518518518518519</v>
       </c>
       <c r="L6" t="n">
-        <v>74.625</v>
+        <v>75.62037037037037</v>
       </c>
       <c r="M6" t="n">
-        <v>11100000</v>
+        <v>9920833.333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>78.84722222222223</v>
       </c>
       <c r="O6" t="n">
-        <v>24.04703959274898</v>
+        <v>23.85249339368922</v>
       </c>
       <c r="P6" t="n">
-        <v>178.939980804855</v>
+        <v>179.7547282812646</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.137846678493132</v>
+        <v>1.074908273915627</v>
       </c>
       <c r="R6" t="n">
-        <v>74.53200992371472</v>
+        <v>71.01752003393064</v>
       </c>
       <c r="S6" t="n">
-        <v>14114314.69369685</v>
+        <v>5692961.164958407</v>
       </c>
       <c r="T6" t="n">
-        <v>80.67736919830742</v>
+        <v>76.58803962613753</v>
       </c>
       <c r="U6" t="n">
-        <v>25.70784687534688</v>
+        <v>27.41855742296919</v>
       </c>
       <c r="V6" t="n">
-        <v>180.8413841713842</v>
+        <v>182.4148075737472</v>
       </c>
       <c r="W6" t="n">
-        <v>1.044029581529581</v>
+        <v>1.665729162478389</v>
       </c>
       <c r="X6" t="n">
-        <v>72.58567515817515</v>
+        <v>76.41251809336175</v>
       </c>
       <c r="Y6" t="n">
-        <v>7703370.986652237</v>
+        <v>10027275.92292898</v>
       </c>
       <c r="Z6" t="n">
-        <v>76.89476232101234</v>
+        <v>79.39490755632396</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>24.97569444444444</v>
+        <v>23.82986111111111</v>
       </c>
       <c r="D7" t="n">
-        <v>179.671875</v>
+        <v>181.9791666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>1.03125</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>74.95486111111111</v>
+        <v>71.37847222222223</v>
       </c>
       <c r="G7" t="n">
-        <v>10317013.88888889</v>
+        <v>3943750</v>
       </c>
       <c r="H7" t="n">
-        <v>78.54340277777777</v>
+        <v>76.77430555555556</v>
       </c>
       <c r="I7" t="n">
-        <v>25.47561728395062</v>
+        <v>24.88293650793651</v>
       </c>
       <c r="J7" t="n">
-        <v>182.1258417508417</v>
+        <v>179.6071428571429</v>
       </c>
       <c r="K7" t="n">
-        <v>2.899607182940516</v>
+        <v>1.035714285714286</v>
       </c>
       <c r="L7" t="n">
-        <v>83.94565095398428</v>
+        <v>74.91269841269842</v>
       </c>
       <c r="M7" t="n">
-        <v>66109175.08417508</v>
+        <v>10446230.15873016</v>
       </c>
       <c r="N7" t="n">
-        <v>87.50488215488215</v>
+        <v>78.62103174603173</v>
       </c>
       <c r="O7" t="n">
-        <v>26.1549926553824</v>
+        <v>23.67361801917658</v>
       </c>
       <c r="P7" t="n">
-        <v>178.4871885013627</v>
+        <v>180.6144906523105</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.132388921300313</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>73.26581407493497</v>
+        <v>70.69185984484508</v>
       </c>
       <c r="S7" t="n">
-        <v>6189981.746920832</v>
+        <v>3715150.465996108</v>
       </c>
       <c r="T7" t="n">
-        <v>75.63635020738633</v>
+        <v>76.18148968660722</v>
       </c>
       <c r="U7" t="n">
-        <v>25.15651526835737</v>
+        <v>26.02841922880898</v>
       </c>
       <c r="V7" t="n">
-        <v>179.2574110830689</v>
+        <v>178.308866823041</v>
       </c>
       <c r="W7" t="n">
-        <v>2.708553507895614</v>
+        <v>1.121200110111502</v>
       </c>
       <c r="X7" t="n">
-        <v>82.26296583533426</v>
+        <v>73.20462526374615</v>
       </c>
       <c r="Y7" t="n">
-        <v>58603716.60503239</v>
+        <v>6161834.893773979</v>
       </c>
       <c r="Z7" t="n">
-        <v>86.62627248482512</v>
+        <v>75.72655999759611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.99537037037037</v>
+        <v>26.9375</v>
       </c>
       <c r="D8" t="n">
-        <v>181.7623456790124</v>
+        <v>183.0486111111111</v>
       </c>
       <c r="E8" t="n">
-        <v>2.708333333333333</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>81.29012345679013</v>
+        <v>75.53472222222223</v>
       </c>
       <c r="G8" t="n">
-        <v>44161265.43209876</v>
+        <v>11327777.77777778</v>
       </c>
       <c r="H8" t="n">
-        <v>85.47067901234567</v>
+        <v>78.55555555555556</v>
       </c>
       <c r="I8" t="n">
-        <v>25.39583333333333</v>
+        <v>26.8858024691358</v>
       </c>
       <c r="J8" t="n">
-        <v>179.7638888888889</v>
+        <v>181.8256172839506</v>
       </c>
       <c r="K8" t="n">
-        <v>1.131944444444444</v>
+        <v>1.395061728395061</v>
       </c>
       <c r="L8" t="n">
-        <v>70.65972222222221</v>
+        <v>74.83796296296298</v>
       </c>
       <c r="M8" t="n">
-        <v>3273842.592592593</v>
+        <v>8129012.345679011</v>
       </c>
       <c r="N8" t="n">
-        <v>75.67129629629629</v>
+        <v>77.92160493827161</v>
       </c>
       <c r="O8" t="n">
-        <v>22.94822282560798</v>
+        <v>25.50713352304262</v>
       </c>
       <c r="P8" t="n">
-        <v>180.8801239768307</v>
+        <v>180.8558037921674</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.130421465539523</v>
+        <v>1.047602649875377</v>
       </c>
       <c r="R8" t="n">
-        <v>77.51941140130239</v>
+        <v>72.38849256803802</v>
       </c>
       <c r="S8" t="n">
-        <v>35599396.64398423</v>
+        <v>7532041.806047488</v>
       </c>
       <c r="T8" t="n">
-        <v>84.24563147289287</v>
+        <v>76.94978392819303</v>
       </c>
       <c r="U8" t="n">
-        <v>25.63553526093633</v>
+        <v>25.55841840868579</v>
       </c>
       <c r="V8" t="n">
-        <v>180.0669048197791</v>
+        <v>179.9942777662029</v>
       </c>
       <c r="W8" t="n">
-        <v>1.153685151746649</v>
+        <v>1.257776774621694</v>
       </c>
       <c r="X8" t="n">
-        <v>69.85646235078053</v>
+        <v>73.78224606647066</v>
       </c>
       <c r="Y8" t="n">
-        <v>2491905.984501238</v>
+        <v>7800925.498298493</v>
       </c>
       <c r="Z8" t="n">
-        <v>74.61379609695118</v>
+        <v>77.51129322252318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.31527777777778</v>
+        <v>27.525</v>
       </c>
       <c r="D9" t="n">
-        <v>183.3217592592593</v>
+        <v>185.1421717171717</v>
       </c>
       <c r="E9" t="n">
-        <v>1.442824074074074</v>
+        <v>1.896717171717172</v>
       </c>
       <c r="F9" t="n">
-        <v>78.59328703703703</v>
+        <v>77.20176767676767</v>
       </c>
       <c r="G9" t="n">
-        <v>22660416.66666667</v>
+        <v>13417095.95959596</v>
       </c>
       <c r="H9" t="n">
-        <v>81.97523148148149</v>
+        <v>80.03434343434343</v>
       </c>
       <c r="I9" t="n">
-        <v>28.56111111111111</v>
+        <v>25.01590909090909</v>
       </c>
       <c r="J9" t="n">
-        <v>180.1458333333333</v>
+        <v>182.6772727272727</v>
       </c>
       <c r="K9" t="n">
-        <v>2.429166666666666</v>
+        <v>1.345454545454545</v>
       </c>
       <c r="L9" t="n">
-        <v>82.12083333333332</v>
+        <v>78.25227272727274</v>
       </c>
       <c r="M9" t="n">
-        <v>33006250</v>
+        <v>23548636.36363636</v>
       </c>
       <c r="N9" t="n">
-        <v>83.69444444444444</v>
+        <v>82.47045454545454</v>
       </c>
       <c r="O9" t="n">
-        <v>25.15153701918324</v>
+        <v>25.86868147855495</v>
       </c>
       <c r="P9" t="n">
-        <v>181.7983506257021</v>
+        <v>182.6720044123328</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.367762163633916</v>
+        <v>1.648302865976846</v>
       </c>
       <c r="R9" t="n">
-        <v>75.51880875850792</v>
+        <v>75.64786412866236</v>
       </c>
       <c r="S9" t="n">
-        <v>13750483.94910977</v>
+        <v>11375708.06132591</v>
       </c>
       <c r="T9" t="n">
-        <v>80.01106502062721</v>
+        <v>80.23151670348466</v>
       </c>
       <c r="U9" t="n">
-        <v>26.98036155451016</v>
+        <v>24.43621708192646</v>
       </c>
       <c r="V9" t="n">
-        <v>180.7249739768316</v>
+        <v>178.6594613243355</v>
       </c>
       <c r="W9" t="n">
-        <v>1.908174625512087</v>
+        <v>1.156894297540751</v>
       </c>
       <c r="X9" t="n">
-        <v>78.7587721531994</v>
+        <v>74.7155597072645</v>
       </c>
       <c r="Y9" t="n">
-        <v>20598900.70541774</v>
+        <v>14043665.34304749</v>
       </c>
       <c r="Z9" t="n">
-        <v>81.63093116034293</v>
+        <v>80.51459863553686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.71875</v>
+        <v>26.36527777777778</v>
       </c>
       <c r="D10" t="n">
-        <v>182.8541666666667</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="E10" t="n">
-        <v>1.121527777777778</v>
+        <v>1.323611111111111</v>
       </c>
       <c r="F10" t="n">
-        <v>71.91319444444444</v>
+        <v>75.78194444444445</v>
       </c>
       <c r="G10" t="n">
-        <v>4064583.333333333</v>
+        <v>11501631.94444444</v>
       </c>
       <c r="H10" t="n">
-        <v>75.46527777777779</v>
+        <v>78.8763888888889</v>
       </c>
       <c r="I10" t="n">
-        <v>28.82575757575758</v>
+        <v>25.95252525252525</v>
       </c>
       <c r="J10" t="n">
-        <v>179.5025252525253</v>
+        <v>181.7573232323232</v>
       </c>
       <c r="K10" t="n">
-        <v>1.297979797979798</v>
+        <v>1.737052341597796</v>
       </c>
       <c r="L10" t="n">
-        <v>75.36237373737373</v>
+        <v>79.14391643709826</v>
       </c>
       <c r="M10" t="n">
-        <v>6719949.494949495</v>
+        <v>24805463.728191</v>
       </c>
       <c r="N10" t="n">
-        <v>76.56439393939394</v>
+        <v>82.10909090909091</v>
       </c>
       <c r="O10" t="n">
-        <v>26.79670825362001</v>
+        <v>24.43599206349206</v>
       </c>
       <c r="P10" t="n">
-        <v>179.3649695729108</v>
+        <v>183.6600396825397</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.060365761689291</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="R10" t="n">
-        <v>71.12411297308357</v>
+        <v>71.80648809523809</v>
       </c>
       <c r="S10" t="n">
-        <v>2849847.210523681</v>
+        <v>5516420.138888889</v>
       </c>
       <c r="T10" t="n">
-        <v>73.94618957839545</v>
+        <v>77.29160714285715</v>
       </c>
       <c r="U10" t="n">
-        <v>28.79897091212881</v>
+        <v>24.1032256500636</v>
       </c>
       <c r="V10" t="n">
-        <v>179.79502734108</v>
+        <v>180.5309767636843</v>
       </c>
       <c r="W10" t="n">
-        <v>1.345313093339409</v>
+        <v>1.599741771184459</v>
       </c>
       <c r="X10" t="n">
-        <v>74.6110693400167</v>
+        <v>74.80443181105237</v>
       </c>
       <c r="Y10" t="n">
-        <v>5484069.928609402</v>
+        <v>15728359.92976062</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.5116864130022</v>
+        <v>80.12652805582647</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>25.53117283950617</v>
+      </c>
+      <c r="D11" t="n">
+        <v>182.1925084175084</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.932940516273849</v>
+      </c>
+      <c r="F11" t="n">
+        <v>83.82342873176206</v>
+      </c>
+      <c r="G11" t="n">
+        <v>66195841.75084175</v>
+      </c>
+      <c r="H11" t="n">
+        <v>87.4493265993266</v>
+      </c>
       <c r="I11" t="n">
-        <v>27.6459595959596</v>
+        <v>27.79365079365079</v>
       </c>
       <c r="J11" t="n">
-        <v>183.5162457912458</v>
+        <v>182.0119047619048</v>
       </c>
       <c r="K11" t="n">
-        <v>1.295707070707071</v>
+        <v>1.871031746031746</v>
       </c>
       <c r="L11" t="n">
-        <v>75.9736531986532</v>
+        <v>76.39682539682541</v>
       </c>
       <c r="M11" t="n">
-        <v>10256649.83164983</v>
+        <v>11400793.65079365</v>
       </c>
       <c r="N11" t="n">
-        <v>77.84074074074074</v>
+        <v>78.75396825396827</v>
       </c>
       <c r="O11" t="n">
-        <v>26.31697808242981</v>
+        <v>25.08138900573111</v>
       </c>
       <c r="P11" t="n">
-        <v>181.8983554757936</v>
+        <v>179.0080423962003</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.00933014354067</v>
+        <v>2.664992901835007</v>
       </c>
       <c r="R11" t="n">
-        <v>68.72922341871471</v>
+        <v>82.2124607848292</v>
       </c>
       <c r="S11" t="n">
-        <v>2330586.697200211</v>
+        <v>58076238.70099198</v>
       </c>
       <c r="T11" t="n">
-        <v>72.94502652919836</v>
+        <v>86.54925228280491</v>
       </c>
       <c r="U11" t="n">
-        <v>27.20266343563557</v>
+        <v>27.19330738705739</v>
       </c>
       <c r="V11" t="n">
-        <v>181.4422762480038</v>
+        <v>183.1854166666667</v>
       </c>
       <c r="W11" t="n">
-        <v>1.104136124453462</v>
+        <v>1.918864468864469</v>
       </c>
       <c r="X11" t="n">
-        <v>74.34386524208504</v>
+        <v>75.56313339438339</v>
       </c>
       <c r="Y11" t="n">
-        <v>7478769.969710372</v>
+        <v>10099909.95115995</v>
       </c>
       <c r="Z11" t="n">
-        <v>76.48865247239861</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>22.51805555555556</v>
-      </c>
-      <c r="D12" t="n">
-        <v>181.4222222222222</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.136111111111111</v>
-      </c>
-      <c r="F12" t="n">
-        <v>71.35833333333332</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9669277.777777778</v>
-      </c>
-      <c r="H12" t="n">
-        <v>77.49305555555556</v>
-      </c>
-      <c r="I12" t="n">
-        <v>26.83333333333334</v>
-      </c>
-      <c r="J12" t="n">
-        <v>185.5520833333334</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.583333333333333</v>
-      </c>
-      <c r="L12" t="n">
-        <v>76.02083333333334</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10193402.77777778</v>
-      </c>
-      <c r="N12" t="n">
-        <v>79.05208333333334</v>
-      </c>
-      <c r="O12" t="n">
-        <v>23.99059885372157</v>
-      </c>
-      <c r="P12" t="n">
-        <v>180.0597035795615</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.07565751093826</v>
-      </c>
-      <c r="R12" t="n">
-        <v>71.049415794591</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5473260.664803111</v>
-      </c>
-      <c r="T12" t="n">
-        <v>76.44149777396821</v>
-      </c>
-      <c r="U12" t="n">
-        <v>27.45138597105509</v>
-      </c>
-      <c r="V12" t="n">
-        <v>182.4531569426016</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.662335065605189</v>
-      </c>
-      <c r="X12" t="n">
-        <v>76.41459991891493</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9987502.929351566</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>79.25262359329696</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>23.64814814814815</v>
-      </c>
-      <c r="D13" t="n">
-        <v>182.0972222222223</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>71.25462962962963</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4062500</v>
-      </c>
-      <c r="H13" t="n">
-        <v>77.19907407407408</v>
-      </c>
-      <c r="I13" t="n">
-        <v>24.97569444444444</v>
-      </c>
-      <c r="J13" t="n">
-        <v>179.671875</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.03125</v>
-      </c>
-      <c r="L13" t="n">
-        <v>74.95486111111111</v>
-      </c>
-      <c r="M13" t="n">
-        <v>10317013.88888889</v>
-      </c>
-      <c r="N13" t="n">
-        <v>78.54340277777777</v>
-      </c>
-      <c r="O13" t="n">
-        <v>23.59510562248236</v>
-      </c>
-      <c r="P13" t="n">
-        <v>180.564903875451</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>70.74557885310955</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3790047.160210984</v>
-      </c>
-      <c r="T13" t="n">
-        <v>76.35091117421052</v>
-      </c>
-      <c r="U13" t="n">
-        <v>26.1549926553824</v>
-      </c>
-      <c r="V13" t="n">
-        <v>178.4871885013627</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.132388921300313</v>
-      </c>
-      <c r="X13" t="n">
-        <v>73.26581407493497</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>6189981.746920832</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>75.63635020738633</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>26.875</v>
-      </c>
-      <c r="D14" t="n">
-        <v>181.875</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F14" t="n">
-        <v>74.625</v>
-      </c>
-      <c r="G14" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>78</v>
-      </c>
-      <c r="I14" t="n">
-        <v>26.93055555555555</v>
-      </c>
-      <c r="J14" t="n">
-        <v>181.8541666666667</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>74.89861111111111</v>
-      </c>
-      <c r="M14" t="n">
-        <v>8176111.11111111</v>
-      </c>
-      <c r="N14" t="n">
-        <v>77.97388888888889</v>
-      </c>
-      <c r="O14" t="n">
-        <v>25.70784687534688</v>
-      </c>
-      <c r="P14" t="n">
-        <v>180.8413841713842</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.044029581529581</v>
-      </c>
-      <c r="R14" t="n">
-        <v>72.58567515817515</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7703370.986652237</v>
-      </c>
-      <c r="T14" t="n">
-        <v>76.89476232101234</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25.62021687462864</v>
-      </c>
-      <c r="V14" t="n">
-        <v>179.9947546190193</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.244628710069886</v>
-      </c>
-      <c r="X14" t="n">
-        <v>73.83372556093144</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7794598.373440285</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>77.41868545397958</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>27.525</v>
-      </c>
-      <c r="D15" t="n">
-        <v>185.1421717171717</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.896717171717172</v>
-      </c>
-      <c r="F15" t="n">
-        <v>77.20176767676767</v>
-      </c>
-      <c r="G15" t="n">
-        <v>13417095.95959596</v>
-      </c>
-      <c r="H15" t="n">
-        <v>80.03434343434343</v>
-      </c>
-      <c r="I15" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>182.3613636363636</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.347727272727273</v>
-      </c>
-      <c r="L15" t="n">
-        <v>78.36136363636363</v>
-      </c>
-      <c r="M15" t="n">
-        <v>23902954.54545455</v>
-      </c>
-      <c r="N15" t="n">
-        <v>82.50454545454545</v>
-      </c>
-      <c r="O15" t="n">
-        <v>25.86868147855495</v>
-      </c>
-      <c r="P15" t="n">
-        <v>182.6720044123328</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.648302865976846</v>
-      </c>
-      <c r="R15" t="n">
-        <v>75.64786412866236</v>
-      </c>
-      <c r="S15" t="n">
-        <v>11375708.06132591</v>
-      </c>
-      <c r="T15" t="n">
-        <v>80.23151670348466</v>
-      </c>
-      <c r="U15" t="n">
-        <v>24.04703959274898</v>
-      </c>
-      <c r="V15" t="n">
-        <v>178.939980804855</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.137846678493132</v>
-      </c>
-      <c r="X15" t="n">
-        <v>74.53200992371472</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14114314.69369685</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>80.67736919830742</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>26.36527777777778</v>
-      </c>
-      <c r="D16" t="n">
-        <v>182.8888888888889</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.323611111111111</v>
-      </c>
-      <c r="F16" t="n">
-        <v>75.78194444444445</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11501631.94444444</v>
-      </c>
-      <c r="H16" t="n">
-        <v>78.8763888888889</v>
-      </c>
-      <c r="I16" t="n">
-        <v>25.85479797979798</v>
-      </c>
-      <c r="J16" t="n">
-        <v>181.6527777777778</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.709779614325069</v>
-      </c>
-      <c r="L16" t="n">
-        <v>79.09391643709824</v>
-      </c>
-      <c r="M16" t="n">
-        <v>24725918.27364555</v>
-      </c>
-      <c r="N16" t="n">
-        <v>82.19090909090909</v>
-      </c>
-      <c r="O16" t="n">
-        <v>24.43599206349206</v>
-      </c>
-      <c r="P16" t="n">
-        <v>183.6600396825397</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.096865079365079</v>
-      </c>
-      <c r="R16" t="n">
-        <v>71.80648809523809</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5516420.138888889</v>
-      </c>
-      <c r="T16" t="n">
-        <v>77.29160714285715</v>
-      </c>
-      <c r="U16" t="n">
-        <v>24.24142583371832</v>
-      </c>
-      <c r="V16" t="n">
-        <v>180.4800125763564</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.644737179816231</v>
-      </c>
-      <c r="X16" t="n">
-        <v>75.16623162739764</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16413862.68458156</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>80.23855744058314</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>25.47561728395062</v>
-      </c>
-      <c r="D17" t="n">
-        <v>182.1258417508417</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.899607182940516</v>
-      </c>
-      <c r="F17" t="n">
-        <v>83.94565095398428</v>
-      </c>
-      <c r="G17" t="n">
-        <v>66109175.08417508</v>
-      </c>
-      <c r="H17" t="n">
-        <v>87.50488215488215</v>
-      </c>
-      <c r="I17" t="n">
-        <v>27.86631944444444</v>
-      </c>
-      <c r="J17" t="n">
-        <v>181.9479166666667</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.887152777777778</v>
-      </c>
-      <c r="L17" t="n">
-        <v>76.58159722222223</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11931944.44444444</v>
-      </c>
-      <c r="N17" t="n">
-        <v>78.83159722222223</v>
-      </c>
-      <c r="O17" t="n">
-        <v>25.15651526835737</v>
-      </c>
-      <c r="P17" t="n">
-        <v>179.2574110830689</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.708553507895614</v>
-      </c>
-      <c r="R17" t="n">
-        <v>82.26296583533426</v>
-      </c>
-      <c r="S17" t="n">
-        <v>58603716.60503239</v>
-      </c>
-      <c r="T17" t="n">
-        <v>86.62627248482512</v>
-      </c>
-      <c r="U17" t="n">
-        <v>27.30906732156733</v>
-      </c>
-      <c r="V17" t="n">
-        <v>183.3382575757576</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.932301032301032</v>
-      </c>
-      <c r="X17" t="n">
-        <v>75.55436369186368</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10001130.25863026</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>79.24953657453658</v>
+        <v>79.26115689865689</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,808 +558,410 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.82291666666667</v>
+        <v>23.82986111111111</v>
       </c>
       <c r="D2" t="n">
-        <v>181.9045138888889</v>
+        <v>181.9791666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>2.703125</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>81.27951388888889</v>
+        <v>71.37847222222223</v>
       </c>
       <c r="G2" t="n">
-        <v>44854861.1111111</v>
+        <v>3943750</v>
       </c>
       <c r="H2" t="n">
-        <v>85.62326388888889</v>
+        <v>76.77430555555556</v>
       </c>
       <c r="I2" t="n">
-        <v>25.33928571428572</v>
+        <v>24.88293650793651</v>
       </c>
       <c r="J2" t="n">
-        <v>179.718253968254</v>
+        <v>179.6071428571429</v>
       </c>
       <c r="K2" t="n">
-        <v>1.113095238095238</v>
+        <v>1.035714285714286</v>
       </c>
       <c r="L2" t="n">
-        <v>70.64484126984127</v>
+        <v>74.91269841269842</v>
       </c>
       <c r="M2" t="n">
-        <v>3187103.174603175</v>
+        <v>10446230.15873016</v>
       </c>
       <c r="N2" t="n">
-        <v>75.49603174603173</v>
+        <v>78.62103174603173</v>
       </c>
       <c r="O2" t="n">
-        <v>22.80811587373632</v>
+        <v>23.67361801917657</v>
       </c>
       <c r="P2" t="n">
-        <v>180.9057924260285</v>
+        <v>180.6144906523105</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.075876010994068</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>76.90122958312058</v>
+        <v>70.69185984484508</v>
       </c>
       <c r="S2" t="n">
-        <v>34737872.57981312</v>
+        <v>3715150.465996108</v>
       </c>
       <c r="T2" t="n">
-        <v>83.76488280979127</v>
+        <v>76.18148968660722</v>
       </c>
       <c r="U2" t="n">
-        <v>25.46278232252497</v>
+        <v>26.02841922880898</v>
       </c>
       <c r="V2" t="n">
-        <v>180.1446627514642</v>
+        <v>178.308866823041</v>
       </c>
       <c r="W2" t="n">
-        <v>1.146086389101095</v>
+        <v>1.121200110111502</v>
       </c>
       <c r="X2" t="n">
-        <v>69.91529882154883</v>
+        <v>73.20462526374615</v>
       </c>
       <c r="Y2" t="n">
-        <v>2625913.819126135</v>
+        <v>6161834.893773979</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8699380888719</v>
+        <v>75.72655999759611</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.32121212121212</v>
+        <v>26.9375</v>
       </c>
       <c r="D3" t="n">
-        <v>183.1578282828283</v>
+        <v>183.0486111111111</v>
       </c>
       <c r="E3" t="n">
-        <v>1.471717171717172</v>
+        <v>1.180555555555555</v>
       </c>
       <c r="F3" t="n">
-        <v>78.62449494949495</v>
+        <v>75.53472222222223</v>
       </c>
       <c r="G3" t="n">
-        <v>22862500</v>
+        <v>11327777.77777778</v>
       </c>
       <c r="H3" t="n">
-        <v>82.01843434343435</v>
+        <v>78.55555555555556</v>
       </c>
       <c r="I3" t="n">
-        <v>28.60956790123457</v>
+        <v>26.8858024691358</v>
       </c>
       <c r="J3" t="n">
-        <v>180.1064814814815</v>
+        <v>181.8256172839506</v>
       </c>
       <c r="K3" t="n">
-        <v>2.407407407407407</v>
+        <v>1.395061728395061</v>
       </c>
       <c r="L3" t="n">
-        <v>82.10648148148147</v>
+        <v>74.83796296296298</v>
       </c>
       <c r="M3" t="n">
-        <v>32805555.55555556</v>
+        <v>8129012.345679011</v>
       </c>
       <c r="N3" t="n">
-        <v>83.63271604938272</v>
+        <v>77.92160493827161</v>
       </c>
       <c r="O3" t="n">
-        <v>24.93034136700932</v>
+        <v>25.50713352304262</v>
       </c>
       <c r="P3" t="n">
-        <v>182.0943651184557</v>
+        <v>180.8558037921674</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.352363612909278</v>
+        <v>1.047602649875377</v>
       </c>
       <c r="R3" t="n">
-        <v>75.26591020778328</v>
+        <v>72.38849256803802</v>
       </c>
       <c r="S3" t="n">
-        <v>13651589.02157354</v>
+        <v>7532041.806047488</v>
       </c>
       <c r="T3" t="n">
-        <v>79.96251429598952</v>
+        <v>76.94978392819303</v>
       </c>
       <c r="U3" t="n">
-        <v>26.7667251908738</v>
+        <v>25.55841840868579</v>
       </c>
       <c r="V3" t="n">
-        <v>180.4749739768316</v>
+        <v>179.9942777662029</v>
       </c>
       <c r="W3" t="n">
-        <v>1.862720080057541</v>
+        <v>1.257776774621694</v>
       </c>
       <c r="X3" t="n">
-        <v>78.82695397138122</v>
+        <v>73.78224606647066</v>
       </c>
       <c r="Y3" t="n">
-        <v>21479809.79632682</v>
+        <v>7800925.498298493</v>
       </c>
       <c r="Z3" t="n">
-        <v>81.81274934216111</v>
+        <v>77.51129322252318</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>26.71875</v>
+        <v>27.525</v>
       </c>
       <c r="D4" t="n">
-        <v>182.8541666666667</v>
+        <v>185.1421717171717</v>
       </c>
       <c r="E4" t="n">
-        <v>1.121527777777778</v>
+        <v>1.896717171717172</v>
       </c>
       <c r="F4" t="n">
-        <v>71.91319444444444</v>
+        <v>77.20176767676767</v>
       </c>
       <c r="G4" t="n">
-        <v>4064583.333333333</v>
+        <v>13417095.95959596</v>
       </c>
       <c r="H4" t="n">
-        <v>75.46527777777779</v>
+        <v>80.03434343434343</v>
       </c>
       <c r="I4" t="n">
-        <v>28.95833333333334</v>
+        <v>25.01590909090909</v>
       </c>
       <c r="J4" t="n">
-        <v>179.6027777777778</v>
+        <v>182.6772727272727</v>
       </c>
       <c r="K4" t="n">
-        <v>1.327777777777778</v>
+        <v>1.345454545454545</v>
       </c>
       <c r="L4" t="n">
-        <v>75.41111111111111</v>
+        <v>78.25227272727274</v>
       </c>
       <c r="M4" t="n">
-        <v>6709444.444444445</v>
+        <v>23548636.36363636</v>
       </c>
       <c r="N4" t="n">
-        <v>76.59583333333333</v>
+        <v>82.47045454545454</v>
       </c>
       <c r="O4" t="n">
-        <v>26.76358065443543</v>
+        <v>25.86868147855495</v>
       </c>
       <c r="P4" t="n">
-        <v>179.4213256412705</v>
+        <v>182.6720044123328</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.056592901583711</v>
+        <v>1.648302865976846</v>
       </c>
       <c r="R4" t="n">
-        <v>71.11218924559918</v>
+        <v>75.64786412866236</v>
       </c>
       <c r="S4" t="n">
-        <v>2860065.093199285</v>
+        <v>11375708.06132591</v>
       </c>
       <c r="T4" t="n">
-        <v>74.01205272974575</v>
+        <v>80.23151670348466</v>
       </c>
       <c r="U4" t="n">
-        <v>28.75654666970457</v>
+        <v>24.43621708192646</v>
       </c>
       <c r="V4" t="n">
-        <v>179.4495727956254</v>
+        <v>178.6594613243355</v>
       </c>
       <c r="W4" t="n">
-        <v>1.345313093339409</v>
+        <v>1.156894297540751</v>
       </c>
       <c r="X4" t="n">
-        <v>74.5989481278955</v>
+        <v>74.7155597072645</v>
       </c>
       <c r="Y4" t="n">
-        <v>5503463.868003341</v>
+        <v>14043665.34304749</v>
       </c>
       <c r="Z4" t="n">
-        <v>75.47532277663858</v>
+        <v>80.51459863553686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>26.36527777777778</v>
+      </c>
+      <c r="D5" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.323611111111111</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75.78194444444445</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11501631.94444444</v>
+      </c>
+      <c r="H5" t="n">
+        <v>78.8763888888889</v>
+      </c>
       <c r="I5" t="n">
-        <v>27.6459595959596</v>
+        <v>25.95252525252525</v>
       </c>
       <c r="J5" t="n">
-        <v>183.5162457912458</v>
+        <v>181.7573232323232</v>
       </c>
       <c r="K5" t="n">
-        <v>1.295707070707071</v>
+        <v>1.737052341597796</v>
       </c>
       <c r="L5" t="n">
-        <v>75.9736531986532</v>
+        <v>79.14391643709826</v>
       </c>
       <c r="M5" t="n">
-        <v>10256649.83164983</v>
+        <v>24805463.728191</v>
       </c>
       <c r="N5" t="n">
-        <v>77.84074074074074</v>
+        <v>82.10909090909091</v>
       </c>
       <c r="O5" t="n">
-        <v>26.29056324222732</v>
+        <v>24.43599206349206</v>
       </c>
       <c r="P5" t="n">
-        <v>181.7798417258266</v>
+        <v>183.6600396825397</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.012520885547201</v>
+        <v>1.096865079365079</v>
       </c>
       <c r="R5" t="n">
-        <v>69.02956591159959</v>
+        <v>71.80648809523809</v>
       </c>
       <c r="S5" t="n">
-        <v>2613851.297830352</v>
+        <v>5516420.138888889</v>
       </c>
       <c r="T5" t="n">
-        <v>73.15992511208262</v>
+        <v>77.29160714285715</v>
       </c>
       <c r="U5" t="n">
-        <v>27.20266343563557</v>
+        <v>24.1032256500636</v>
       </c>
       <c r="V5" t="n">
-        <v>181.4422762480038</v>
+        <v>180.5309767636842</v>
       </c>
       <c r="W5" t="n">
-        <v>1.104136124453462</v>
+        <v>1.599741771184459</v>
       </c>
       <c r="X5" t="n">
-        <v>74.34386524208504</v>
+        <v>74.80443181105237</v>
       </c>
       <c r="Y5" t="n">
-        <v>7478769.969710372</v>
+        <v>15728359.92976062</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.48865247239861</v>
+        <v>80.12652805582647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>22.64267676767677</v>
+        <v>25.53117283950617</v>
       </c>
       <c r="D6" t="n">
-        <v>181.5555555555555</v>
+        <v>182.1925084175084</v>
       </c>
       <c r="E6" t="n">
-        <v>1.143939393939394</v>
+        <v>2.932940516273849</v>
       </c>
       <c r="F6" t="n">
-        <v>71.37626262626263</v>
+        <v>83.82342873176206</v>
       </c>
       <c r="G6" t="n">
-        <v>9642979.797979798</v>
+        <v>66195841.75084175</v>
       </c>
       <c r="H6" t="n">
-        <v>77.41792929292929</v>
+        <v>87.4493265993266</v>
       </c>
       <c r="I6" t="n">
-        <v>26.22222222222222</v>
+        <v>27.79365079365079</v>
       </c>
       <c r="J6" t="n">
-        <v>185.1064814814815</v>
+        <v>182.0119047619048</v>
       </c>
       <c r="K6" t="n">
-        <v>1.518518518518519</v>
+        <v>1.871031746031746</v>
       </c>
       <c r="L6" t="n">
-        <v>75.62037037037037</v>
+        <v>76.39682539682541</v>
       </c>
       <c r="M6" t="n">
-        <v>9920833.333333334</v>
+        <v>11400793.65079365</v>
       </c>
       <c r="N6" t="n">
-        <v>78.84722222222223</v>
+        <v>78.75396825396827</v>
       </c>
       <c r="O6" t="n">
-        <v>23.85249339368922</v>
+        <v>25.08138900573111</v>
       </c>
       <c r="P6" t="n">
-        <v>179.7547282812646</v>
+        <v>179.0080423962003</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.074908273915627</v>
+        <v>2.664992901835007</v>
       </c>
       <c r="R6" t="n">
-        <v>71.01752003393064</v>
+        <v>82.2124607848292</v>
       </c>
       <c r="S6" t="n">
-        <v>5692961.164958407</v>
+        <v>58076238.70099198</v>
       </c>
       <c r="T6" t="n">
-        <v>76.58803962613753</v>
+        <v>86.54925228280491</v>
       </c>
       <c r="U6" t="n">
-        <v>27.41855742296919</v>
+        <v>27.19330738705739</v>
       </c>
       <c r="V6" t="n">
-        <v>182.4148075737472</v>
+        <v>183.1854166666667</v>
       </c>
       <c r="W6" t="n">
-        <v>1.665729162478389</v>
+        <v>1.918864468864469</v>
       </c>
       <c r="X6" t="n">
-        <v>76.41251809336175</v>
+        <v>75.56313339438339</v>
       </c>
       <c r="Y6" t="n">
-        <v>10027275.92292898</v>
+        <v>10099909.95115995</v>
       </c>
       <c r="Z6" t="n">
-        <v>79.39490755632396</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>23.82986111111111</v>
-      </c>
-      <c r="D7" t="n">
-        <v>181.9791666666667</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>71.37847222222223</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3943750</v>
-      </c>
-      <c r="H7" t="n">
-        <v>76.77430555555556</v>
-      </c>
-      <c r="I7" t="n">
-        <v>24.88293650793651</v>
-      </c>
-      <c r="J7" t="n">
-        <v>179.6071428571429</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.035714285714286</v>
-      </c>
-      <c r="L7" t="n">
-        <v>74.91269841269842</v>
-      </c>
-      <c r="M7" t="n">
-        <v>10446230.15873016</v>
-      </c>
-      <c r="N7" t="n">
-        <v>78.62103174603173</v>
-      </c>
-      <c r="O7" t="n">
-        <v>23.67361801917658</v>
-      </c>
-      <c r="P7" t="n">
-        <v>180.6144906523105</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>70.69185984484508</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3715150.465996108</v>
-      </c>
-      <c r="T7" t="n">
-        <v>76.18148968660722</v>
-      </c>
-      <c r="U7" t="n">
-        <v>26.02841922880898</v>
-      </c>
-      <c r="V7" t="n">
-        <v>178.308866823041</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.121200110111502</v>
-      </c>
-      <c r="X7" t="n">
-        <v>73.20462526374615</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>6161834.893773979</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>75.72655999759611</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>26.9375</v>
-      </c>
-      <c r="D8" t="n">
-        <v>183.0486111111111</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.180555555555556</v>
-      </c>
-      <c r="F8" t="n">
-        <v>75.53472222222223</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11327777.77777778</v>
-      </c>
-      <c r="H8" t="n">
-        <v>78.55555555555556</v>
-      </c>
-      <c r="I8" t="n">
-        <v>26.8858024691358</v>
-      </c>
-      <c r="J8" t="n">
-        <v>181.8256172839506</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.395061728395061</v>
-      </c>
-      <c r="L8" t="n">
-        <v>74.83796296296298</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8129012.345679011</v>
-      </c>
-      <c r="N8" t="n">
-        <v>77.92160493827161</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25.50713352304262</v>
-      </c>
-      <c r="P8" t="n">
-        <v>180.8558037921674</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.047602649875377</v>
-      </c>
-      <c r="R8" t="n">
-        <v>72.38849256803802</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7532041.806047488</v>
-      </c>
-      <c r="T8" t="n">
-        <v>76.94978392819303</v>
-      </c>
-      <c r="U8" t="n">
-        <v>25.55841840868579</v>
-      </c>
-      <c r="V8" t="n">
-        <v>179.9942777662029</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.257776774621694</v>
-      </c>
-      <c r="X8" t="n">
-        <v>73.78224606647066</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>7800925.498298493</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>77.51129322252318</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.525</v>
-      </c>
-      <c r="D9" t="n">
-        <v>185.1421717171717</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.896717171717172</v>
-      </c>
-      <c r="F9" t="n">
-        <v>77.20176767676767</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13417095.95959596</v>
-      </c>
-      <c r="H9" t="n">
-        <v>80.03434343434343</v>
-      </c>
-      <c r="I9" t="n">
-        <v>25.01590909090909</v>
-      </c>
-      <c r="J9" t="n">
-        <v>182.6772727272727</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.345454545454545</v>
-      </c>
-      <c r="L9" t="n">
-        <v>78.25227272727274</v>
-      </c>
-      <c r="M9" t="n">
-        <v>23548636.36363636</v>
-      </c>
-      <c r="N9" t="n">
-        <v>82.47045454545454</v>
-      </c>
-      <c r="O9" t="n">
-        <v>25.86868147855495</v>
-      </c>
-      <c r="P9" t="n">
-        <v>182.6720044123328</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.648302865976846</v>
-      </c>
-      <c r="R9" t="n">
-        <v>75.64786412866236</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11375708.06132591</v>
-      </c>
-      <c r="T9" t="n">
-        <v>80.23151670348466</v>
-      </c>
-      <c r="U9" t="n">
-        <v>24.43621708192646</v>
-      </c>
-      <c r="V9" t="n">
-        <v>178.6594613243355</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.156894297540751</v>
-      </c>
-      <c r="X9" t="n">
-        <v>74.7155597072645</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>14043665.34304749</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>80.51459863553686</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>26.36527777777778</v>
-      </c>
-      <c r="D10" t="n">
-        <v>182.8888888888889</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.323611111111111</v>
-      </c>
-      <c r="F10" t="n">
-        <v>75.78194444444445</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11501631.94444444</v>
-      </c>
-      <c r="H10" t="n">
-        <v>78.8763888888889</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25.95252525252525</v>
-      </c>
-      <c r="J10" t="n">
-        <v>181.7573232323232</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.737052341597796</v>
-      </c>
-      <c r="L10" t="n">
-        <v>79.14391643709826</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24805463.728191</v>
-      </c>
-      <c r="N10" t="n">
-        <v>82.10909090909091</v>
-      </c>
-      <c r="O10" t="n">
-        <v>24.43599206349206</v>
-      </c>
-      <c r="P10" t="n">
-        <v>183.6600396825397</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.096865079365079</v>
-      </c>
-      <c r="R10" t="n">
-        <v>71.80648809523809</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5516420.138888889</v>
-      </c>
-      <c r="T10" t="n">
-        <v>77.29160714285715</v>
-      </c>
-      <c r="U10" t="n">
-        <v>24.1032256500636</v>
-      </c>
-      <c r="V10" t="n">
-        <v>180.5309767636843</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.599741771184459</v>
-      </c>
-      <c r="X10" t="n">
-        <v>74.80443181105237</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>15728359.92976062</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>80.12652805582647</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>25.53117283950617</v>
-      </c>
-      <c r="D11" t="n">
-        <v>182.1925084175084</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.932940516273849</v>
-      </c>
-      <c r="F11" t="n">
-        <v>83.82342873176206</v>
-      </c>
-      <c r="G11" t="n">
-        <v>66195841.75084175</v>
-      </c>
-      <c r="H11" t="n">
-        <v>87.4493265993266</v>
-      </c>
-      <c r="I11" t="n">
-        <v>27.79365079365079</v>
-      </c>
-      <c r="J11" t="n">
-        <v>182.0119047619048</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.871031746031746</v>
-      </c>
-      <c r="L11" t="n">
-        <v>76.39682539682541</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11400793.65079365</v>
-      </c>
-      <c r="N11" t="n">
-        <v>78.75396825396827</v>
-      </c>
-      <c r="O11" t="n">
-        <v>25.08138900573111</v>
-      </c>
-      <c r="P11" t="n">
-        <v>179.0080423962003</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.664992901835007</v>
-      </c>
-      <c r="R11" t="n">
-        <v>82.2124607848292</v>
-      </c>
-      <c r="S11" t="n">
-        <v>58076238.70099198</v>
-      </c>
-      <c r="T11" t="n">
-        <v>86.54925228280491</v>
-      </c>
-      <c r="U11" t="n">
-        <v>27.19330738705739</v>
-      </c>
-      <c r="V11" t="n">
-        <v>183.1854166666667</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.918864468864469</v>
-      </c>
-      <c r="X11" t="n">
-        <v>75.56313339438339</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10099909.95115995</v>
-      </c>
-      <c r="Z11" t="n">
         <v>79.26115689865689</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,411 +558,773 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>23.82986111111111</v>
-      </c>
-      <c r="D2" t="n">
-        <v>181.9791666666667</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>71.37847222222223</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3943750</v>
-      </c>
-      <c r="H2" t="n">
-        <v>76.77430555555556</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>24.88293650793651</v>
+        <v>25.875</v>
       </c>
       <c r="J2" t="n">
-        <v>179.6071428571429</v>
+        <v>181.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1.035714285714286</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>74.91269841269842</v>
+        <v>72.5</v>
       </c>
       <c r="M2" t="n">
-        <v>10446230.15873016</v>
+        <v>5125000</v>
       </c>
       <c r="N2" t="n">
-        <v>78.62103174603173</v>
+        <v>75.5</v>
       </c>
       <c r="O2" t="n">
-        <v>23.67361801917657</v>
+        <v>22.74272786037492</v>
       </c>
       <c r="P2" t="n">
-        <v>180.6144906523105</v>
+        <v>182.7450980392157</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>1.419090713208361</v>
       </c>
       <c r="R2" t="n">
-        <v>70.69185984484508</v>
+        <v>73.19198448610213</v>
       </c>
       <c r="S2" t="n">
-        <v>3715150.465996108</v>
+        <v>7080025.856496445</v>
       </c>
       <c r="T2" t="n">
-        <v>76.18148968660722</v>
+        <v>80.73066149536737</v>
       </c>
       <c r="U2" t="n">
-        <v>26.02841922880898</v>
+        <v>25.28874269005848</v>
       </c>
       <c r="V2" t="n">
-        <v>178.308866823041</v>
+        <v>181.2408312447786</v>
       </c>
       <c r="W2" t="n">
-        <v>1.121200110111502</v>
+        <v>1.051451545530493</v>
       </c>
       <c r="X2" t="n">
-        <v>73.20462526374615</v>
+        <v>71.02565789473684</v>
       </c>
       <c r="Y2" t="n">
-        <v>6161834.893773979</v>
+        <v>4820958.385547202</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.72655999759611</v>
+        <v>74.91640559732664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.9375</v>
+        <v>27.13958333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>183.0486111111111</v>
+        <v>184.2868055555555</v>
       </c>
       <c r="E3" t="n">
-        <v>1.180555555555555</v>
+        <v>1.304166666666666</v>
       </c>
       <c r="F3" t="n">
-        <v>75.53472222222223</v>
+        <v>76.27152777777778</v>
       </c>
       <c r="G3" t="n">
-        <v>11327777.77777778</v>
+        <v>11721597.22222222</v>
       </c>
       <c r="H3" t="n">
-        <v>78.55555555555556</v>
-      </c>
-      <c r="I3" t="n">
-        <v>26.8858024691358</v>
-      </c>
-      <c r="J3" t="n">
-        <v>181.8256172839506</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.395061728395061</v>
-      </c>
-      <c r="L3" t="n">
-        <v>74.83796296296298</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8129012.345679011</v>
-      </c>
-      <c r="N3" t="n">
-        <v>77.92160493827161</v>
-      </c>
+        <v>78.44722222222222</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>25.50713352304262</v>
+        <v>27.00247082638723</v>
       </c>
       <c r="P3" t="n">
-        <v>180.8558037921674</v>
+        <v>182.4237318409145</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.047602649875377</v>
+        <v>1.08457370802572</v>
       </c>
       <c r="R3" t="n">
-        <v>72.38849256803802</v>
+        <v>73.92495236961182</v>
       </c>
       <c r="S3" t="n">
-        <v>7532041.806047488</v>
+        <v>7223532.686353894</v>
       </c>
       <c r="T3" t="n">
-        <v>76.94978392819303</v>
+        <v>76.39003334127173</v>
       </c>
       <c r="U3" t="n">
-        <v>25.55841840868579</v>
+        <v>24.7875</v>
       </c>
       <c r="V3" t="n">
-        <v>179.9942777662029</v>
+        <v>179.9625</v>
       </c>
       <c r="W3" t="n">
-        <v>1.257776774621694</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>73.78224606647066</v>
+        <v>74.97083333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>7800925.498298493</v>
+        <v>10799166.66666667</v>
       </c>
       <c r="Z3" t="n">
-        <v>77.51129322252318</v>
+        <v>80.11458333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.525</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>185.1421717171717</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="E4" t="n">
-        <v>1.896717171717172</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>77.20176767676767</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="G4" t="n">
-        <v>13417095.95959596</v>
+        <v>4500000</v>
       </c>
       <c r="H4" t="n">
-        <v>80.03434343434343</v>
+        <v>76.44444444444444</v>
       </c>
       <c r="I4" t="n">
-        <v>25.01590909090909</v>
+        <v>24.375</v>
       </c>
       <c r="J4" t="n">
-        <v>182.6772727272727</v>
+        <v>181.625</v>
       </c>
       <c r="K4" t="n">
-        <v>1.345454545454545</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>78.25227272727274</v>
+        <v>71.75</v>
       </c>
       <c r="M4" t="n">
-        <v>23548636.36363636</v>
+        <v>3587500</v>
       </c>
       <c r="N4" t="n">
-        <v>82.47045454545454</v>
+        <v>75.5</v>
       </c>
       <c r="O4" t="n">
-        <v>25.86868147855495</v>
+        <v>25.6649801179213</v>
       </c>
       <c r="P4" t="n">
-        <v>182.6720044123328</v>
+        <v>179.3413478678185</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.648302865976846</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>75.64786412866236</v>
+        <v>70.43972987796516</v>
       </c>
       <c r="S4" t="n">
-        <v>11375708.06132591</v>
+        <v>2885490.881667352</v>
       </c>
       <c r="T4" t="n">
-        <v>80.23151670348466</v>
+        <v>74.8608597285068</v>
       </c>
       <c r="U4" t="n">
-        <v>24.43621708192646</v>
+        <v>23.61105462519936</v>
       </c>
       <c r="V4" t="n">
-        <v>178.6594613243355</v>
+        <v>179.4058064194577</v>
       </c>
       <c r="W4" t="n">
-        <v>1.156894297540751</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>74.7155597072645</v>
+        <v>70.82016547049443</v>
       </c>
       <c r="Y4" t="n">
-        <v>14043665.34304749</v>
+        <v>3561355.163476874</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.51459863553686</v>
+        <v>76.12727771132376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.36527777777778</v>
+        <v>25.45833333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>182.8888888888889</v>
+        <v>185.6851851851851</v>
       </c>
       <c r="E5" t="n">
-        <v>1.323611111111111</v>
+        <v>1.504629629629629</v>
       </c>
       <c r="F5" t="n">
-        <v>75.78194444444445</v>
+        <v>75.57870370370371</v>
       </c>
       <c r="G5" t="n">
-        <v>11501631.94444444</v>
+        <v>11929166.66666667</v>
       </c>
       <c r="H5" t="n">
-        <v>78.8763888888889</v>
+        <v>79.68981481481482</v>
       </c>
       <c r="I5" t="n">
-        <v>25.95252525252525</v>
+        <v>26.69444444444445</v>
       </c>
       <c r="J5" t="n">
-        <v>181.7573232323232</v>
+        <v>180.2777777777778</v>
       </c>
       <c r="K5" t="n">
-        <v>1.737052341597796</v>
+        <v>1.347222222222222</v>
       </c>
       <c r="L5" t="n">
-        <v>79.14391643709826</v>
+        <v>74.2638888888889</v>
       </c>
       <c r="M5" t="n">
-        <v>24805463.728191</v>
+        <v>8592013.888888888</v>
       </c>
       <c r="N5" t="n">
-        <v>82.10909090909091</v>
+        <v>77.15277777777777</v>
       </c>
       <c r="O5" t="n">
-        <v>24.43599206349206</v>
+        <v>26.721875</v>
       </c>
       <c r="P5" t="n">
-        <v>183.6600396825397</v>
+        <v>180.384375</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.096865079365079</v>
+        <v>1.699652777777778</v>
       </c>
       <c r="R5" t="n">
-        <v>71.80648809523809</v>
+        <v>75.27430555555556</v>
       </c>
       <c r="S5" t="n">
-        <v>5516420.138888889</v>
+        <v>10073055.55555555</v>
       </c>
       <c r="T5" t="n">
-        <v>77.29160714285715</v>
+        <v>80.56145833333333</v>
       </c>
       <c r="U5" t="n">
-        <v>24.1032256500636</v>
+        <v>23.61699346405229</v>
       </c>
       <c r="V5" t="n">
-        <v>180.5309767636842</v>
+        <v>180.1575163398693</v>
       </c>
       <c r="W5" t="n">
-        <v>1.599741771184459</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>74.80443181105237</v>
+        <v>71.29477124183008</v>
       </c>
       <c r="Y5" t="n">
-        <v>15728359.92976062</v>
+        <v>5820285.947712419</v>
       </c>
       <c r="Z5" t="n">
-        <v>80.12652805582647</v>
+        <v>77.35653594771242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.53117283950617</v>
+        <v>26.09722222222222</v>
       </c>
       <c r="D6" t="n">
-        <v>182.1925084175084</v>
+        <v>182.03125</v>
       </c>
       <c r="E6" t="n">
-        <v>2.932940516273849</v>
+        <v>1.847222222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>83.82342873176206</v>
+        <v>79.13541666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>66195841.75084175</v>
+        <v>25463888.88888889</v>
       </c>
       <c r="H6" t="n">
-        <v>87.4493265993266</v>
+        <v>82.11805555555556</v>
       </c>
       <c r="I6" t="n">
-        <v>27.79365079365079</v>
+        <v>25.80833333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>182.0119047619048</v>
+        <v>182.9222222222222</v>
       </c>
       <c r="K6" t="n">
-        <v>1.871031746031746</v>
+        <v>3.161111111111111</v>
       </c>
       <c r="L6" t="n">
-        <v>76.39682539682541</v>
+        <v>85.18055555555556</v>
       </c>
       <c r="M6" t="n">
-        <v>11400793.65079365</v>
+        <v>73657500</v>
       </c>
       <c r="N6" t="n">
-        <v>78.75396825396827</v>
+        <v>88.18333333333334</v>
       </c>
       <c r="O6" t="n">
-        <v>25.08138900573111</v>
+        <v>23.44391339869281</v>
       </c>
       <c r="P6" t="n">
-        <v>179.0080423962003</v>
+        <v>179.921568627451</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.664992901835007</v>
+        <v>1.455841503267974</v>
       </c>
       <c r="R6" t="n">
-        <v>82.2124607848292</v>
+        <v>73.20204248366014</v>
       </c>
       <c r="S6" t="n">
-        <v>58076238.70099198</v>
+        <v>13163443.62745098</v>
       </c>
       <c r="T6" t="n">
-        <v>86.54925228280491</v>
+        <v>79.61566584967321</v>
       </c>
       <c r="U6" t="n">
-        <v>27.19330738705739</v>
+        <v>25.39720394736842</v>
       </c>
       <c r="V6" t="n">
-        <v>183.1854166666667</v>
+        <v>175.812774122807</v>
       </c>
       <c r="W6" t="n">
-        <v>1.918864468864469</v>
+        <v>2.101699561403509</v>
       </c>
       <c r="X6" t="n">
-        <v>75.56313339438339</v>
+        <v>79.36951754385964</v>
       </c>
       <c r="Y6" t="n">
-        <v>10099909.95115995</v>
+        <v>37069044.68201754</v>
       </c>
       <c r="Z6" t="n">
-        <v>79.26115689865689</v>
+        <v>84.01918859649123</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="D7" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="F7" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9362962.962962963</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.96296296296296</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25.08796296296296</v>
+      </c>
+      <c r="J7" t="n">
+        <v>179.6527777777778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="L7" t="n">
+        <v>71.20833333333333</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3592129.629629629</v>
+      </c>
+      <c r="N7" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="O7" t="n">
+        <v>26.20686274509804</v>
+      </c>
+      <c r="P7" t="n">
+        <v>179.7599673202614</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.393464052287582</v>
+      </c>
+      <c r="R7" t="n">
+        <v>73.61037581699347</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9606219.362745099</v>
+      </c>
+      <c r="T7" t="n">
+        <v>77.53267973856208</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24.18055555555556</v>
+      </c>
+      <c r="V7" t="n">
+        <v>180.5642361111111</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.059027777777778</v>
+      </c>
+      <c r="X7" t="n">
+        <v>70.41493055555556</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3553255.208333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>76.453125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.0625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>183.65625</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.34375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.34375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19359375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>25.27445054945055</v>
+      </c>
+      <c r="P8" t="n">
+        <v>179.6090659340659</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.227747252747253</v>
+      </c>
+      <c r="R8" t="n">
+        <v>74.02445054945056</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10748296.7032967</v>
+      </c>
+      <c r="T8" t="n">
+        <v>79.73324175824176</v>
+      </c>
+      <c r="U8" t="n">
+        <v>20.58004807692308</v>
+      </c>
+      <c r="V8" t="n">
+        <v>181.5259615384616</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.475721153846154</v>
+      </c>
+      <c r="X8" t="n">
+        <v>70.77980769230768</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20355420.67307692</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>80.67740384615385</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>25.51851851851852</v>
+      </c>
+      <c r="J9" t="n">
+        <v>184.2962962962963</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.37037037037037</v>
+      </c>
+      <c r="L9" t="n">
+        <v>78.03703703703704</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21592592.59259259</v>
+      </c>
+      <c r="N9" t="n">
+        <v>81.85185185185185</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.61137473637474</v>
+      </c>
+      <c r="P9" t="n">
+        <v>176.9500915750916</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.091561216561217</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73.46421633921634</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7803422.272172272</v>
+      </c>
+      <c r="T9" t="n">
+        <v>77.32693695193696</v>
+      </c>
+      <c r="U9" t="n">
+        <v>24.01118421052631</v>
+      </c>
+      <c r="V9" t="n">
+        <v>183.0503588516746</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.294557416267943</v>
+      </c>
+      <c r="X9" t="n">
+        <v>74.63947368421053</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14213175.83732058</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>80.28026315789475</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="D10" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="F10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30055555.55555556</v>
+      </c>
+      <c r="H10" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="J10" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="L10" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="N10" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26.25899552803578</v>
+      </c>
+      <c r="P10" t="n">
+        <v>179.589877880977</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.783307533539732</v>
+      </c>
+      <c r="R10" t="n">
+        <v>78.94576453388373</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24194573.44341245</v>
+      </c>
+      <c r="T10" t="n">
+        <v>82.11785345717234</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24.06954656862745</v>
+      </c>
+      <c r="V10" t="n">
+        <v>178.6974264705882</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.093872549019608</v>
+      </c>
+      <c r="X10" t="n">
+        <v>71.03063725490196</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6288776.960784314</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>76.84779411764706</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28.67592592592592</v>
+      </c>
+      <c r="D11" t="n">
+        <v>178.3796296296296</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.398148148148148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>75.3425925925926</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6887962.962962963</v>
+      </c>
+      <c r="H11" t="n">
+        <v>76.68518518518518</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="L11" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11555555.55555556</v>
+      </c>
+      <c r="N11" t="n">
+        <v>79.11111111111111</v>
+      </c>
+      <c r="O11" t="n">
+        <v>28.26666666666667</v>
+      </c>
+      <c r="P11" t="n">
+        <v>177.2083333333334</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.66666666666666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5892500</v>
+      </c>
+      <c r="T11" t="n">
+        <v>75.80000000000001</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24.71875</v>
+      </c>
+      <c r="V11" t="n">
+        <v>178.796875</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.052083333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>71.72916666666667</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6958593.75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>77.484375</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,65 +564,77 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>28.38425925925926</v>
+      </c>
+      <c r="D2" t="n">
+        <v>180.1805555555556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.921296296296297</v>
+      </c>
+      <c r="F2" t="n">
+        <v>78.21296296296296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17379629.62962963</v>
+      </c>
+      <c r="H2" t="n">
+        <v>79.26851851851852</v>
+      </c>
       <c r="I2" t="n">
-        <v>25.875</v>
+        <v>26.08680555555556</v>
       </c>
       <c r="J2" t="n">
-        <v>181.25</v>
+        <v>181.7638888888889</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.121527777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>72.5</v>
+        <v>71.98263888888889</v>
       </c>
       <c r="M2" t="n">
-        <v>5125000</v>
+        <v>3652777.777777778</v>
       </c>
       <c r="N2" t="n">
-        <v>75.5</v>
+        <v>74.89583333333333</v>
       </c>
       <c r="O2" t="n">
-        <v>22.74272786037492</v>
+        <v>23.87768440709617</v>
       </c>
       <c r="P2" t="n">
-        <v>182.7450980392157</v>
+        <v>182.5415499533146</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.419090713208361</v>
+        <v>1.640522875816993</v>
       </c>
       <c r="R2" t="n">
-        <v>73.19198448610213</v>
+        <v>76.07749766573296</v>
       </c>
       <c r="S2" t="n">
-        <v>7080025.856496445</v>
+        <v>24518394.02427638</v>
       </c>
       <c r="T2" t="n">
-        <v>80.73066149536737</v>
+        <v>82.21288515406162</v>
       </c>
       <c r="U2" t="n">
-        <v>25.28874269005848</v>
+        <v>25.32644110275689</v>
       </c>
       <c r="V2" t="n">
-        <v>181.2408312447786</v>
+        <v>181.0602756892231</v>
       </c>
       <c r="W2" t="n">
-        <v>1.051451545530493</v>
+        <v>1.049467418546366</v>
       </c>
       <c r="X2" t="n">
-        <v>71.02565789473684</v>
+        <v>71.23399122807018</v>
       </c>
       <c r="Y2" t="n">
-        <v>4820958.385547202</v>
+        <v>4977257.988721805</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.91640559732664</v>
+        <v>75.00767543859649</v>
       </c>
     </row>
     <row r="3">
@@ -635,64 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>27.13958333333333</v>
+        <v>27.20833333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>184.2868055555555</v>
+        <v>183.2833333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>1.304166666666666</v>
+        <v>1.358333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>76.27152777777778</v>
+        <v>76.18333333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>11721597.22222222</v>
+        <v>11251111.11111111</v>
       </c>
       <c r="H3" t="n">
-        <v>78.44722222222222</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>78.17777777777778</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J3" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7059375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>78.5</v>
+      </c>
       <c r="O3" t="n">
-        <v>27.00247082638723</v>
+        <v>27.0098544973545</v>
       </c>
       <c r="P3" t="n">
-        <v>182.4237318409145</v>
+        <v>181.6117063492064</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.08457370802572</v>
+        <v>1.148346560846561</v>
       </c>
       <c r="R3" t="n">
-        <v>73.92495236961182</v>
+        <v>73.97685185185185</v>
       </c>
       <c r="S3" t="n">
-        <v>7223532.686353894</v>
+        <v>7069370.37037037</v>
       </c>
       <c r="T3" t="n">
-        <v>76.39003334127173</v>
+        <v>76.31587301587301</v>
       </c>
       <c r="U3" t="n">
-        <v>24.7875</v>
+        <v>25.02579365079365</v>
       </c>
       <c r="V3" t="n">
-        <v>179.9625</v>
+        <v>181.3435913501703</v>
       </c>
       <c r="W3" t="n">
-        <v>1.566666666666667</v>
+        <v>1.539329091960671</v>
       </c>
       <c r="X3" t="n">
-        <v>74.97083333333333</v>
+        <v>74.80722639933167</v>
       </c>
       <c r="Y3" t="n">
-        <v>10799166.66666667</v>
+        <v>10027009.22980528</v>
       </c>
       <c r="Z3" t="n">
-        <v>80.11458333333333</v>
+        <v>79.65689062399589</v>
       </c>
     </row>
     <row r="4">
@@ -708,7 +732,7 @@
         <v>25.66666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>183.7777777777778</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -723,58 +747,58 @@
         <v>76.44444444444444</v>
       </c>
       <c r="I4" t="n">
-        <v>24.375</v>
+        <v>24.11805555555556</v>
       </c>
       <c r="J4" t="n">
-        <v>181.625</v>
+        <v>180.2847222222223</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>71.75</v>
+        <v>72.02083333333334</v>
       </c>
       <c r="M4" t="n">
-        <v>3587500</v>
+        <v>3806250</v>
       </c>
       <c r="N4" t="n">
-        <v>75.5</v>
+        <v>76.26388888888889</v>
       </c>
       <c r="O4" t="n">
-        <v>25.6649801179213</v>
+        <v>25.51086048454469</v>
       </c>
       <c r="P4" t="n">
-        <v>179.3413478678185</v>
+        <v>180.6975772765246</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>70.43972987796516</v>
+        <v>70.81923558897243</v>
       </c>
       <c r="S4" t="n">
-        <v>2885490.881667352</v>
+        <v>3083354.218880535</v>
       </c>
       <c r="T4" t="n">
-        <v>74.8608597285068</v>
+        <v>74.89358813700919</v>
       </c>
       <c r="U4" t="n">
-        <v>23.61105462519936</v>
+        <v>23.58056680161943</v>
       </c>
       <c r="V4" t="n">
-        <v>179.4058064194577</v>
+        <v>179.1022941970311</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>70.82016547049443</v>
+        <v>70.64209401709402</v>
       </c>
       <c r="Y4" t="n">
-        <v>3561355.163476874</v>
+        <v>3296332.799145299</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.12727771132376</v>
+        <v>76.20529689608637</v>
       </c>
     </row>
     <row r="5">
@@ -787,28 +811,28 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.45833333333333</v>
+        <v>24.80555555555556</v>
       </c>
       <c r="D5" t="n">
-        <v>185.6851851851851</v>
+        <v>185.6027777777778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.504629629629629</v>
+        <v>1.375</v>
       </c>
       <c r="F5" t="n">
-        <v>75.57870370370371</v>
+        <v>74.93611111111112</v>
       </c>
       <c r="G5" t="n">
-        <v>11929166.66666667</v>
+        <v>10536388.88888889</v>
       </c>
       <c r="H5" t="n">
-        <v>79.68981481481482</v>
+        <v>79.6888888888889</v>
       </c>
       <c r="I5" t="n">
         <v>26.69444444444445</v>
       </c>
       <c r="J5" t="n">
-        <v>180.2777777777778</v>
+        <v>180.625</v>
       </c>
       <c r="K5" t="n">
         <v>1.347222222222222</v>
@@ -823,22 +847,22 @@
         <v>77.15277777777777</v>
       </c>
       <c r="O5" t="n">
-        <v>26.721875</v>
+        <v>26.44305555555556</v>
       </c>
       <c r="P5" t="n">
-        <v>180.384375</v>
+        <v>180.6722222222222</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.699652777777778</v>
+        <v>1.588888888888889</v>
       </c>
       <c r="R5" t="n">
-        <v>75.27430555555556</v>
+        <v>75.06805555555555</v>
       </c>
       <c r="S5" t="n">
-        <v>10073055.55555555</v>
+        <v>8988333.333333332</v>
       </c>
       <c r="T5" t="n">
-        <v>80.56145833333333</v>
+        <v>79.92361111111111</v>
       </c>
       <c r="U5" t="n">
         <v>23.61699346405229</v>
@@ -869,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.09722222222222</v>
+        <v>25.75</v>
       </c>
       <c r="D6" t="n">
-        <v>182.03125</v>
+        <v>181.1111111111111</v>
       </c>
       <c r="E6" t="n">
-        <v>1.847222222222222</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="F6" t="n">
-        <v>79.13541666666667</v>
+        <v>78.83333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>25463888.88888889</v>
+        <v>24594444.44444444</v>
       </c>
       <c r="H6" t="n">
-        <v>82.11805555555556</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="I6" t="n">
-        <v>25.80833333333333</v>
+        <v>25.63636363636363</v>
       </c>
       <c r="J6" t="n">
-        <v>182.9222222222222</v>
+        <v>182.4863636363636</v>
       </c>
       <c r="K6" t="n">
-        <v>3.161111111111111</v>
+        <v>3.304545454545455</v>
       </c>
       <c r="L6" t="n">
-        <v>85.18055555555556</v>
+        <v>85.56590909090909</v>
       </c>
       <c r="M6" t="n">
-        <v>73657500</v>
+        <v>82452272.72727273</v>
       </c>
       <c r="N6" t="n">
-        <v>88.18333333333334</v>
+        <v>88.53409090909091</v>
       </c>
       <c r="O6" t="n">
-        <v>23.44391339869281</v>
+        <v>23.38780959752322</v>
       </c>
       <c r="P6" t="n">
-        <v>179.921568627451</v>
+        <v>179.453366873065</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.455841503267974</v>
+        <v>1.437383900928793</v>
       </c>
       <c r="R6" t="n">
-        <v>73.20204248366014</v>
+        <v>73.36644736842106</v>
       </c>
       <c r="S6" t="n">
-        <v>13163443.62745098</v>
+        <v>13345019.3498452</v>
       </c>
       <c r="T6" t="n">
-        <v>79.61566584967321</v>
+        <v>79.88962848297214</v>
       </c>
       <c r="U6" t="n">
-        <v>25.39720394736842</v>
+        <v>25.35194327731092</v>
       </c>
       <c r="V6" t="n">
-        <v>175.812774122807</v>
+        <v>176.7450630252101</v>
       </c>
       <c r="W6" t="n">
-        <v>2.101699561403509</v>
+        <v>2.186081932773109</v>
       </c>
       <c r="X6" t="n">
-        <v>79.36951754385964</v>
+        <v>79.68484768907562</v>
       </c>
       <c r="Y6" t="n">
-        <v>37069044.68201754</v>
+        <v>40352639.83718488</v>
       </c>
       <c r="Z6" t="n">
-        <v>84.01918859649123</v>
+        <v>83.97607668067228</v>
       </c>
     </row>
     <row r="7">
@@ -963,28 +987,28 @@
         <v>74.54629629629629</v>
       </c>
       <c r="G7" t="n">
-        <v>9362962.962962963</v>
+        <v>8969444.444444444</v>
       </c>
       <c r="H7" t="n">
         <v>77.96296296296296</v>
       </c>
       <c r="I7" t="n">
-        <v>25.08796296296296</v>
+        <v>24.59097222222222</v>
       </c>
       <c r="J7" t="n">
-        <v>179.6527777777778</v>
+        <v>181.1263888888889</v>
       </c>
       <c r="K7" t="n">
-        <v>1.041666666666667</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="L7" t="n">
-        <v>71.20833333333333</v>
+        <v>70.23888888888888</v>
       </c>
       <c r="M7" t="n">
-        <v>3592129.629629629</v>
+        <v>2895208.333333333</v>
       </c>
       <c r="N7" t="n">
-        <v>75.41666666666667</v>
+        <v>74.86388888888888</v>
       </c>
       <c r="O7" t="n">
         <v>26.20686274509804</v>
@@ -996,31 +1020,31 @@
         <v>1.393464052287582</v>
       </c>
       <c r="R7" t="n">
-        <v>73.61037581699347</v>
+        <v>73.55759803921569</v>
       </c>
       <c r="S7" t="n">
-        <v>9606219.362745099</v>
+        <v>9027134.395424839</v>
       </c>
       <c r="T7" t="n">
-        <v>77.53267973856208</v>
+        <v>77.47990196078432</v>
       </c>
       <c r="U7" t="n">
         <v>24.18055555555556</v>
       </c>
       <c r="V7" t="n">
-        <v>180.5642361111111</v>
+        <v>180.4548611111111</v>
       </c>
       <c r="W7" t="n">
         <v>1.059027777777778</v>
       </c>
       <c r="X7" t="n">
-        <v>70.41493055555556</v>
+        <v>70.35243055555556</v>
       </c>
       <c r="Y7" t="n">
-        <v>3553255.208333333</v>
+        <v>3393706.597222222</v>
       </c>
       <c r="Z7" t="n">
-        <v>76.453125</v>
+        <v>76.35763888888889</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.0625</v>
+        <v>25.18888888888889</v>
       </c>
       <c r="D8" t="n">
-        <v>183.65625</v>
+        <v>182.7222222222222</v>
       </c>
       <c r="E8" t="n">
-        <v>1.34375</v>
+        <v>1.358333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>77.34375</v>
+        <v>77.5</v>
       </c>
       <c r="G8" t="n">
-        <v>19359375</v>
+        <v>18778888.88888889</v>
       </c>
       <c r="H8" t="n">
-        <v>81.75</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>81.74444444444444</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J8" t="n">
+        <v>179</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="M8" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="N8" t="n">
+        <v>85</v>
+      </c>
       <c r="O8" t="n">
-        <v>25.27445054945055</v>
+        <v>24.9577205882353</v>
       </c>
       <c r="P8" t="n">
-        <v>179.6090659340659</v>
+        <v>179.8472338935574</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.227747252747253</v>
+        <v>1.411151960784314</v>
       </c>
       <c r="R8" t="n">
-        <v>74.02445054945056</v>
+        <v>74.35922619047619</v>
       </c>
       <c r="S8" t="n">
-        <v>10748296.7032967</v>
+        <v>10777280.28711485</v>
       </c>
       <c r="T8" t="n">
-        <v>79.73324175824176</v>
+        <v>80.0358018207283</v>
       </c>
       <c r="U8" t="n">
-        <v>20.58004807692308</v>
+        <v>20.9292239010989</v>
       </c>
       <c r="V8" t="n">
-        <v>181.5259615384616</v>
+        <v>181.4137706043956</v>
       </c>
       <c r="W8" t="n">
-        <v>1.475721153846154</v>
+        <v>1.592754120879121</v>
       </c>
       <c r="X8" t="n">
-        <v>70.77980769230768</v>
+        <v>71.75865384615385</v>
       </c>
       <c r="Y8" t="n">
-        <v>20355420.67307692</v>
+        <v>22704431.66208791</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.67740384615385</v>
+        <v>81.18619505494506</v>
       </c>
     </row>
     <row r="9">
@@ -1112,7 +1148,7 @@
         <v>25.51851851851852</v>
       </c>
       <c r="J9" t="n">
-        <v>184.2962962962963</v>
+        <v>184.1851851851852</v>
       </c>
       <c r="K9" t="n">
         <v>1.37037037037037</v>
@@ -1127,22 +1163,22 @@
         <v>81.85185185185185</v>
       </c>
       <c r="O9" t="n">
-        <v>24.61137473637474</v>
+        <v>24.65033577533578</v>
       </c>
       <c r="P9" t="n">
-        <v>176.9500915750916</v>
+        <v>177.7637362637363</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.091561216561217</v>
+        <v>1.086691086691087</v>
       </c>
       <c r="R9" t="n">
-        <v>73.46421633921634</v>
+        <v>73.43986568986568</v>
       </c>
       <c r="S9" t="n">
-        <v>7803422.272172272</v>
+        <v>7635889.804639805</v>
       </c>
       <c r="T9" t="n">
-        <v>77.32693695193696</v>
+        <v>77.33180708180709</v>
       </c>
       <c r="U9" t="n">
         <v>24.01118421052631</v>
@@ -1173,22 +1209,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>28.22222222222222</v>
+        <v>27.02777777777778</v>
       </c>
       <c r="D10" t="n">
-        <v>182.3333333333333</v>
+        <v>180.5194444444444</v>
       </c>
       <c r="E10" t="n">
-        <v>2.333333333333333</v>
+        <v>2.127777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>81.33333333333333</v>
+        <v>81.46111111111111</v>
       </c>
       <c r="G10" t="n">
-        <v>30055555.55555556</v>
+        <v>32883333.33333334</v>
       </c>
       <c r="H10" t="n">
-        <v>83.33333333333333</v>
+        <v>83.96111111111111</v>
       </c>
       <c r="I10" t="n">
         <v>22.75694444444444</v>
@@ -1209,40 +1245,40 @@
         <v>77.83333333333334</v>
       </c>
       <c r="O10" t="n">
-        <v>26.25899552803578</v>
+        <v>25.97996794871795</v>
       </c>
       <c r="P10" t="n">
-        <v>179.589877880977</v>
+        <v>179.5369551282051</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.783307533539732</v>
+        <v>1.858205128205128</v>
       </c>
       <c r="R10" t="n">
-        <v>78.94576453388373</v>
+        <v>79.55842948717948</v>
       </c>
       <c r="S10" t="n">
-        <v>24194573.44341245</v>
+        <v>27075176.28205128</v>
       </c>
       <c r="T10" t="n">
-        <v>82.11785345717234</v>
+        <v>82.59689102564101</v>
       </c>
       <c r="U10" t="n">
-        <v>24.06954656862745</v>
+        <v>24.01899509803921</v>
       </c>
       <c r="V10" t="n">
-        <v>178.6974264705882</v>
+        <v>178.865625</v>
       </c>
       <c r="W10" t="n">
-        <v>1.093872549019608</v>
+        <v>1.091115196078432</v>
       </c>
       <c r="X10" t="n">
-        <v>71.03063725490196</v>
+        <v>70.93780637254902</v>
       </c>
       <c r="Y10" t="n">
-        <v>6288776.960784314</v>
+        <v>6213064.644607844</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.84779411764706</v>
+        <v>76.846875</v>
       </c>
     </row>
     <row r="11">
@@ -1258,7 +1294,7 @@
         <v>28.67592592592592</v>
       </c>
       <c r="D11" t="n">
-        <v>178.3796296296296</v>
+        <v>178.0092592592593</v>
       </c>
       <c r="E11" t="n">
         <v>1.398148148148148</v>
@@ -1273,58 +1309,1358 @@
         <v>76.68518518518518</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>26.0125</v>
       </c>
       <c r="J11" t="n">
-        <v>184.2222222222222</v>
+        <v>182.975</v>
       </c>
       <c r="K11" t="n">
-        <v>1.111111111111111</v>
+        <v>1.1125</v>
       </c>
       <c r="L11" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27.92788461538461</v>
+      </c>
+      <c r="P11" t="n">
+        <v>176.8858173076923</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.198317307692308</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.15985576923077</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5245793.269230769</v>
+      </c>
+      <c r="T11" t="n">
+        <v>75.76201923076923</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24.44142578590141</v>
+      </c>
+      <c r="V11" t="n">
+        <v>177.73659278995</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.049561651583711</v>
+      </c>
+      <c r="X11" t="n">
+        <v>71.87296082400572</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7118900.612497023</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>77.93532314241486</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>27.20833333333333</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.2833333333333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.358333333333333</v>
+      </c>
+      <c r="F12" t="n">
+        <v>76.18333333333334</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11251111.11111111</v>
+      </c>
+      <c r="H12" t="n">
+        <v>78.17777777777778</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="L12" t="n">
+        <v>78.83333333333334</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24594444.44444444</v>
+      </c>
+      <c r="N12" t="n">
+        <v>82.33333333333334</v>
+      </c>
+      <c r="O12" t="n">
+        <v>27.0098544973545</v>
+      </c>
+      <c r="P12" t="n">
+        <v>181.6117063492064</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.148346560846561</v>
+      </c>
+      <c r="R12" t="n">
+        <v>73.97685185185185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7069370.37037037</v>
+      </c>
+      <c r="T12" t="n">
+        <v>76.31587301587301</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.38780959752322</v>
+      </c>
+      <c r="V12" t="n">
+        <v>179.453366873065</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.437383900928793</v>
+      </c>
+      <c r="X12" t="n">
+        <v>73.36644736842106</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13345019.3498452</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>79.88962848297214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.38425925925926</v>
+      </c>
+      <c r="D13" t="n">
+        <v>180.1805555555556</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.921296296296297</v>
+      </c>
+      <c r="F13" t="n">
+        <v>78.21296296296296</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17379629.62962963</v>
+      </c>
+      <c r="H13" t="n">
+        <v>79.26851851851852</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.69444444444445</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.347222222222222</v>
+      </c>
+      <c r="L13" t="n">
+        <v>74.2638888888889</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8592013.888888888</v>
+      </c>
+      <c r="N13" t="n">
+        <v>77.15277777777777</v>
+      </c>
+      <c r="O13" t="n">
+        <v>23.87768440709617</v>
+      </c>
+      <c r="P13" t="n">
+        <v>182.5415499533146</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.640522875816993</v>
+      </c>
+      <c r="R13" t="n">
+        <v>76.07749766573296</v>
+      </c>
+      <c r="S13" t="n">
+        <v>24518394.02427638</v>
+      </c>
+      <c r="T13" t="n">
+        <v>82.21288515406162</v>
+      </c>
+      <c r="U13" t="n">
+        <v>23.61699346405229</v>
+      </c>
+      <c r="V13" t="n">
+        <v>180.1575163398693</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>71.29477124183008</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5820285.947712419</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.35653594771242</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.08680555555556</v>
+      </c>
+      <c r="D14" t="n">
+        <v>181.7638888888889</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.121527777777778</v>
+      </c>
+      <c r="F14" t="n">
+        <v>71.98263888888889</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3652777.777777778</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.89583333333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.51851851851852</v>
+      </c>
+      <c r="J14" t="n">
+        <v>184.1851851851852</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.37037037037037</v>
+      </c>
+      <c r="L14" t="n">
+        <v>78.03703703703704</v>
+      </c>
+      <c r="M14" t="n">
+        <v>21592592.59259259</v>
+      </c>
+      <c r="N14" t="n">
+        <v>81.85185185185185</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25.32644110275689</v>
+      </c>
+      <c r="P14" t="n">
+        <v>181.0602756892231</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.049467418546366</v>
+      </c>
+      <c r="R14" t="n">
+        <v>71.23399122807018</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4977257.988721805</v>
+      </c>
+      <c r="T14" t="n">
+        <v>75.00767543859649</v>
+      </c>
+      <c r="U14" t="n">
+        <v>24.01118421052631</v>
+      </c>
+      <c r="V14" t="n">
+        <v>183.0503588516746</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.294557416267943</v>
+      </c>
+      <c r="X14" t="n">
+        <v>74.63947368421053</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14213175.83732058</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>80.28026315789475</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="D15" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3806250</v>
+      </c>
+      <c r="H15" t="n">
+        <v>76.26388888888889</v>
+      </c>
+      <c r="I15" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="J15" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="L15" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10536388.88888889</v>
+      </c>
+      <c r="N15" t="n">
+        <v>79.6888888888889</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23.58056680161943</v>
+      </c>
+      <c r="P15" t="n">
+        <v>179.1022941970311</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>70.64209401709402</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3296332.799145299</v>
+      </c>
+      <c r="T15" t="n">
+        <v>76.20529689608637</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.44305555555556</v>
+      </c>
+      <c r="V15" t="n">
+        <v>180.6722222222222</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.588888888888889</v>
+      </c>
+      <c r="X15" t="n">
+        <v>75.06805555555555</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8988333.333333332</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.92361111111111</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24.59097222222222</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.1263888888889</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.027777777777778</v>
+      </c>
+      <c r="F16" t="n">
+        <v>70.23888888888888</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2895208.333333333</v>
+      </c>
+      <c r="H16" t="n">
+        <v>74.86388888888888</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="L16" t="n">
+        <v>78.83333333333334</v>
+      </c>
+      <c r="M16" t="n">
+        <v>24594444.44444444</v>
+      </c>
+      <c r="N16" t="n">
+        <v>82.33333333333334</v>
+      </c>
+      <c r="O16" t="n">
+        <v>24.18055555555556</v>
+      </c>
+      <c r="P16" t="n">
+        <v>180.4548611111111</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.059027777777778</v>
+      </c>
+      <c r="R16" t="n">
+        <v>70.35243055555556</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3393706.597222222</v>
+      </c>
+      <c r="T16" t="n">
+        <v>76.35763888888889</v>
+      </c>
+      <c r="U16" t="n">
+        <v>23.38780959752322</v>
+      </c>
+      <c r="V16" t="n">
+        <v>179.453366873065</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.437383900928793</v>
+      </c>
+      <c r="X16" t="n">
+        <v>73.36644736842106</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13345019.3498452</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>79.88962848297214</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.0125</v>
+      </c>
+      <c r="D17" t="n">
+        <v>182.975</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.1125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>24.44142578590141</v>
+      </c>
+      <c r="P17" t="n">
+        <v>177.73659278995</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.049561651583711</v>
+      </c>
+      <c r="R17" t="n">
+        <v>71.87296082400572</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7118900.612497023</v>
+      </c>
+      <c r="T17" t="n">
+        <v>77.93532314241486</v>
+      </c>
+      <c r="U17" t="n">
+        <v>24.65033577533578</v>
+      </c>
+      <c r="V17" t="n">
+        <v>177.7637362637363</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.086691086691087</v>
+      </c>
+      <c r="X17" t="n">
+        <v>73.43986568986568</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7635889.804639805</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>77.33180708180709</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="H18" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25.18888888888889</v>
+      </c>
+      <c r="J18" t="n">
+        <v>182.7222222222222</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.358333333333333</v>
+      </c>
+      <c r="L18" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18778888.88888889</v>
+      </c>
+      <c r="N18" t="n">
+        <v>81.74444444444444</v>
+      </c>
+      <c r="O18" t="n">
+        <v>24.01899509803921</v>
+      </c>
+      <c r="P18" t="n">
+        <v>178.865625</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.091115196078432</v>
+      </c>
+      <c r="R18" t="n">
+        <v>70.93780637254902</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6213064.644607844</v>
+      </c>
+      <c r="T18" t="n">
+        <v>76.846875</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.9577205882353</v>
+      </c>
+      <c r="V18" t="n">
+        <v>179.8472338935574</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.411151960784314</v>
+      </c>
+      <c r="X18" t="n">
+        <v>74.35922619047619</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10777280.28711485</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>80.0358018207283</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.63636363636363</v>
+      </c>
+      <c r="D19" t="n">
+        <v>182.4863636363636</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.304545454545455</v>
+      </c>
+      <c r="F19" t="n">
+        <v>85.56590909090909</v>
+      </c>
+      <c r="G19" t="n">
+        <v>82452272.72727273</v>
+      </c>
+      <c r="H19" t="n">
+        <v>88.53409090909091</v>
+      </c>
+      <c r="I19" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="N19" t="n">
         <v>76.44444444444444</v>
       </c>
-      <c r="M11" t="n">
-        <v>11555555.55555556</v>
-      </c>
-      <c r="N11" t="n">
-        <v>79.11111111111111</v>
-      </c>
-      <c r="O11" t="n">
-        <v>28.26666666666667</v>
-      </c>
-      <c r="P11" t="n">
-        <v>177.2083333333334</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="R11" t="n">
-        <v>74.66666666666666</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5892500</v>
-      </c>
-      <c r="T11" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="U11" t="n">
-        <v>24.71875</v>
-      </c>
-      <c r="V11" t="n">
-        <v>178.796875</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.052083333333333</v>
-      </c>
-      <c r="X11" t="n">
-        <v>71.72916666666667</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>6958593.75</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>77.484375</v>
+      <c r="O19" t="n">
+        <v>25.35194327731092</v>
+      </c>
+      <c r="P19" t="n">
+        <v>176.7450630252101</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.186081932773109</v>
+      </c>
+      <c r="R19" t="n">
+        <v>79.68484768907562</v>
+      </c>
+      <c r="S19" t="n">
+        <v>40352639.83718488</v>
+      </c>
+      <c r="T19" t="n">
+        <v>83.97607668067228</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.51086048454469</v>
+      </c>
+      <c r="V19" t="n">
+        <v>180.6975772765246</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>70.81923558897243</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3083354.218880535</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>74.89358813700919</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.69444444444445</v>
+      </c>
+      <c r="D20" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.347222222222222</v>
+      </c>
+      <c r="F20" t="n">
+        <v>74.2638888888889</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8592013.888888888</v>
+      </c>
+      <c r="H20" t="n">
+        <v>77.15277777777777</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26.08680555555556</v>
+      </c>
+      <c r="J20" t="n">
+        <v>181.7638888888889</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.121527777777778</v>
+      </c>
+      <c r="L20" t="n">
+        <v>71.98263888888889</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3652777.777777778</v>
+      </c>
+      <c r="N20" t="n">
+        <v>74.89583333333333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23.61699346405229</v>
+      </c>
+      <c r="P20" t="n">
+        <v>180.1575163398693</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>71.29477124183008</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5820285.947712419</v>
+      </c>
+      <c r="T20" t="n">
+        <v>77.35653594771242</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25.32644110275689</v>
+      </c>
+      <c r="V20" t="n">
+        <v>181.0602756892231</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.049467418546366</v>
+      </c>
+      <c r="X20" t="n">
+        <v>71.23399122807018</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4977257.988721805</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>75.00767543859649</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>25.51851851851852</v>
+      </c>
+      <c r="D21" t="n">
+        <v>184.1851851851852</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.37037037037037</v>
+      </c>
+      <c r="F21" t="n">
+        <v>78.03703703703704</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21592592.59259259</v>
+      </c>
+      <c r="H21" t="n">
+        <v>81.85185185185185</v>
+      </c>
+      <c r="I21" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="J21" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="L21" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8969444.444444444</v>
+      </c>
+      <c r="N21" t="n">
+        <v>77.96296296296296</v>
+      </c>
+      <c r="O21" t="n">
+        <v>24.01118421052631</v>
+      </c>
+      <c r="P21" t="n">
+        <v>183.0503588516746</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.294557416267943</v>
+      </c>
+      <c r="R21" t="n">
+        <v>74.63947368421053</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14213175.83732058</v>
+      </c>
+      <c r="T21" t="n">
+        <v>80.28026315789475</v>
+      </c>
+      <c r="U21" t="n">
+        <v>26.20686274509804</v>
+      </c>
+      <c r="V21" t="n">
+        <v>179.7599673202614</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.393464052287582</v>
+      </c>
+      <c r="X21" t="n">
+        <v>73.55759803921569</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9027134.395424839</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>77.47990196078432</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7059375</v>
+      </c>
+      <c r="H22" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J22" t="n">
+        <v>179</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="M22" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="N22" t="n">
+        <v>85</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25.02579365079365</v>
+      </c>
+      <c r="P22" t="n">
+        <v>181.3435913501703</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.539329091960671</v>
+      </c>
+      <c r="R22" t="n">
+        <v>74.80722639933167</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10027009.22980528</v>
+      </c>
+      <c r="T22" t="n">
+        <v>79.65689062399589</v>
+      </c>
+      <c r="U22" t="n">
+        <v>20.9292239010989</v>
+      </c>
+      <c r="V22" t="n">
+        <v>181.4137706043956</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.592754120879121</v>
+      </c>
+      <c r="X22" t="n">
+        <v>71.75865384615385</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>22704431.66208791</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>81.18619505494506</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>28.67592592592592</v>
+      </c>
+      <c r="D23" t="n">
+        <v>178.0092592592593</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.398148148148148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75.3425925925926</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6887962.962962963</v>
+      </c>
+      <c r="H23" t="n">
+        <v>76.68518518518518</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.02777777777778</v>
+      </c>
+      <c r="J23" t="n">
+        <v>180.5194444444444</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.127777777777778</v>
+      </c>
+      <c r="L23" t="n">
+        <v>81.46111111111111</v>
+      </c>
+      <c r="M23" t="n">
+        <v>32883333.33333334</v>
+      </c>
+      <c r="N23" t="n">
+        <v>83.96111111111111</v>
+      </c>
+      <c r="O23" t="n">
+        <v>27.92788461538461</v>
+      </c>
+      <c r="P23" t="n">
+        <v>176.8858173076923</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.198317307692308</v>
+      </c>
+      <c r="R23" t="n">
+        <v>74.15985576923077</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5245793.269230769</v>
+      </c>
+      <c r="T23" t="n">
+        <v>75.76201923076923</v>
+      </c>
+      <c r="U23" t="n">
+        <v>25.97996794871795</v>
+      </c>
+      <c r="V23" t="n">
+        <v>179.5369551282051</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.858205128205128</v>
+      </c>
+      <c r="X23" t="n">
+        <v>79.55842948717948</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>27075176.28205128</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>82.59689102564101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>28.38425925925926</v>
+      </c>
+      <c r="D24" t="n">
+        <v>180.1805555555556</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.921296296296297</v>
+      </c>
+      <c r="F24" t="n">
+        <v>78.21296296296296</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17379629.62962963</v>
+      </c>
+      <c r="H24" t="n">
+        <v>79.26851851851852</v>
+      </c>
+      <c r="I24" t="n">
+        <v>27.20833333333333</v>
+      </c>
+      <c r="J24" t="n">
+        <v>183.2833333333333</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.358333333333333</v>
+      </c>
+      <c r="L24" t="n">
+        <v>76.18333333333334</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11251111.11111111</v>
+      </c>
+      <c r="N24" t="n">
+        <v>78.17777777777778</v>
+      </c>
+      <c r="O24" t="n">
+        <v>23.87768440709617</v>
+      </c>
+      <c r="P24" t="n">
+        <v>182.5415499533146</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.640522875816993</v>
+      </c>
+      <c r="R24" t="n">
+        <v>76.07749766573296</v>
+      </c>
+      <c r="S24" t="n">
+        <v>24518394.02427638</v>
+      </c>
+      <c r="T24" t="n">
+        <v>82.21288515406162</v>
+      </c>
+      <c r="U24" t="n">
+        <v>27.0098544973545</v>
+      </c>
+      <c r="V24" t="n">
+        <v>181.6117063492064</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.148346560846561</v>
+      </c>
+      <c r="X24" t="n">
+        <v>73.97685185185185</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>7069370.37037037</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>76.31587301587301</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="D25" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F25" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10536388.88888889</v>
+      </c>
+      <c r="H25" t="n">
+        <v>79.6888888888889</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24.59097222222222</v>
+      </c>
+      <c r="J25" t="n">
+        <v>181.1263888888889</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.027777777777778</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70.23888888888888</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2895208.333333333</v>
+      </c>
+      <c r="N25" t="n">
+        <v>74.86388888888888</v>
+      </c>
+      <c r="O25" t="n">
+        <v>26.44305555555556</v>
+      </c>
+      <c r="P25" t="n">
+        <v>180.6722222222222</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.588888888888889</v>
+      </c>
+      <c r="R25" t="n">
+        <v>75.06805555555555</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8988333.333333332</v>
+      </c>
+      <c r="T25" t="n">
+        <v>79.92361111111111</v>
+      </c>
+      <c r="U25" t="n">
+        <v>24.18055555555556</v>
+      </c>
+      <c r="V25" t="n">
+        <v>180.4548611111111</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.059027777777778</v>
+      </c>
+      <c r="X25" t="n">
+        <v>70.35243055555556</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3393706.597222222</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>76.35763888888889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="D26" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="H26" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26.0125</v>
+      </c>
+      <c r="J26" t="n">
+        <v>182.975</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.1125</v>
+      </c>
+      <c r="L26" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="N26" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="O26" t="n">
+        <v>24.01899509803921</v>
+      </c>
+      <c r="P26" t="n">
+        <v>178.865625</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.091115196078432</v>
+      </c>
+      <c r="R26" t="n">
+        <v>70.93780637254902</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6213064.644607844</v>
+      </c>
+      <c r="T26" t="n">
+        <v>76.846875</v>
+      </c>
+      <c r="U26" t="n">
+        <v>24.44142578590141</v>
+      </c>
+      <c r="V26" t="n">
+        <v>177.73659278995</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.049561651583711</v>
+      </c>
+      <c r="X26" t="n">
+        <v>71.87296082400572</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7118900.612497023</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>77.93532314241486</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>25.63636363636363</v>
+      </c>
+      <c r="D27" t="n">
+        <v>182.4863636363636</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.304545454545455</v>
+      </c>
+      <c r="F27" t="n">
+        <v>85.56590909090909</v>
+      </c>
+      <c r="G27" t="n">
+        <v>82452272.72727273</v>
+      </c>
+      <c r="H27" t="n">
+        <v>88.53409090909091</v>
+      </c>
+      <c r="I27" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="J27" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3806250</v>
+      </c>
+      <c r="N27" t="n">
+        <v>76.26388888888889</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25.35194327731092</v>
+      </c>
+      <c r="P27" t="n">
+        <v>176.7450630252101</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.186081932773109</v>
+      </c>
+      <c r="R27" t="n">
+        <v>79.68484768907562</v>
+      </c>
+      <c r="S27" t="n">
+        <v>40352639.83718488</v>
+      </c>
+      <c r="T27" t="n">
+        <v>83.97607668067228</v>
+      </c>
+      <c r="U27" t="n">
+        <v>23.58056680161943</v>
+      </c>
+      <c r="V27" t="n">
+        <v>179.1022941970311</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>70.64209401709402</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3296332.799145299</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>76.20529689608637</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,481 +558,2507 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.24074074074074</v>
+        <v>27.05555555555555</v>
       </c>
       <c r="D2" t="n">
-        <v>181.050925925926</v>
+        <v>183.2488888888889</v>
       </c>
       <c r="E2" t="n">
-        <v>1.402777777777778</v>
+        <v>1.353333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>74.54629629629629</v>
+        <v>75.88</v>
       </c>
       <c r="G2" t="n">
-        <v>8969444.444444444</v>
+        <v>10485333.33333333</v>
       </c>
       <c r="H2" t="n">
-        <v>77.96296296296296</v>
+        <v>77.96444444444444</v>
       </c>
       <c r="I2" t="n">
-        <v>24.59097222222222</v>
+        <v>25.75</v>
       </c>
       <c r="J2" t="n">
-        <v>181.1263888888889</v>
+        <v>181.1111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>1.027777777777778</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>70.23888888888888</v>
+        <v>78.83333333333334</v>
       </c>
       <c r="M2" t="n">
-        <v>2895208.333333333</v>
+        <v>24594444.44444444</v>
       </c>
       <c r="N2" t="n">
-        <v>74.86388888888888</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="O2" t="n">
-        <v>26.20686274509804</v>
+        <v>26.82455026455026</v>
       </c>
       <c r="P2" t="n">
-        <v>179.7599673202614</v>
+        <v>181.7560317460317</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.393464052287582</v>
+        <v>1.152010582010582</v>
       </c>
       <c r="R2" t="n">
-        <v>73.55759803921569</v>
+        <v>74.12314814814815</v>
       </c>
       <c r="S2" t="n">
-        <v>9027134.395424839</v>
+        <v>7623079.62962963</v>
       </c>
       <c r="T2" t="n">
-        <v>77.47990196078432</v>
+        <v>76.7276984126984</v>
       </c>
       <c r="U2" t="n">
-        <v>24.18055555555556</v>
+        <v>23.43524767801858</v>
       </c>
       <c r="V2" t="n">
-        <v>180.4548611111111</v>
+        <v>179.262693498452</v>
       </c>
       <c r="W2" t="n">
-        <v>1.059027777777778</v>
+        <v>1.399907120743034</v>
       </c>
       <c r="X2" t="n">
-        <v>70.35243055555556</v>
+        <v>73.40565789473685</v>
       </c>
       <c r="Y2" t="n">
-        <v>3393706.597222222</v>
+        <v>12621015.47987616</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.35763888888889</v>
+        <v>79.7617027863777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.18888888888889</v>
+        <v>27.75694444444444</v>
       </c>
       <c r="D3" t="n">
-        <v>182.7222222222222</v>
+        <v>180.5729166666667</v>
       </c>
       <c r="E3" t="n">
-        <v>1.358333333333333</v>
+        <v>1.815972222222222</v>
       </c>
       <c r="F3" t="n">
-        <v>77.5</v>
+        <v>77.65972222222223</v>
       </c>
       <c r="G3" t="n">
-        <v>18778888.88888889</v>
+        <v>15519097.22222222</v>
       </c>
       <c r="H3" t="n">
-        <v>81.74444444444444</v>
+        <v>79.42013888888889</v>
       </c>
       <c r="I3" t="n">
-        <v>23.875</v>
+        <v>26.83333333333334</v>
       </c>
       <c r="J3" t="n">
-        <v>179</v>
+        <v>180.40625</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>1.354166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>79.125</v>
+        <v>74.69791666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>42187500</v>
+        <v>8790885.416666666</v>
       </c>
       <c r="N3" t="n">
-        <v>85</v>
+        <v>77.36458333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>24.9577205882353</v>
+        <v>23.8687896211116</v>
       </c>
       <c r="P3" t="n">
-        <v>179.8472338935574</v>
+        <v>181.9719519386702</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.411151960784314</v>
+        <v>1.63828689370485</v>
       </c>
       <c r="R3" t="n">
-        <v>74.35922619047619</v>
+        <v>75.80812324929973</v>
       </c>
       <c r="S3" t="n">
-        <v>10777280.28711485</v>
+        <v>21211163.93925992</v>
       </c>
       <c r="T3" t="n">
-        <v>80.0358018207283</v>
+        <v>81.83071649712517</v>
       </c>
       <c r="U3" t="n">
-        <v>20.9292239010989</v>
+        <v>23.41587009803921</v>
       </c>
       <c r="V3" t="n">
-        <v>181.4137706043956</v>
+        <v>180.852512254902</v>
       </c>
       <c r="W3" t="n">
-        <v>1.592754120879121</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>71.75865384615385</v>
+        <v>70.86170343137255</v>
       </c>
       <c r="Y3" t="n">
-        <v>22704431.66208791</v>
+        <v>5480058.210784314</v>
       </c>
       <c r="Z3" t="n">
-        <v>81.18619505494506</v>
+        <v>77.39240196078433</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>xjut9IFr</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>26.29444444444444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>181.8361111111111</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.172222222222222</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72.28611111111111</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4147222.222222222</v>
+      </c>
+      <c r="H4" t="n">
+        <v>74.96666666666667</v>
+      </c>
       <c r="I4" t="n">
-        <v>25.51851851851852</v>
+        <v>25.31388888888889</v>
       </c>
       <c r="J4" t="n">
-        <v>184.1851851851852</v>
+        <v>183.9138888888889</v>
       </c>
       <c r="K4" t="n">
-        <v>1.37037037037037</v>
+        <v>1.352777777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>78.03703703703704</v>
+        <v>78.05277777777778</v>
       </c>
       <c r="M4" t="n">
-        <v>21592592.59259259</v>
+        <v>21916944.44444445</v>
       </c>
       <c r="N4" t="n">
-        <v>81.85185185185185</v>
+        <v>81.96388888888889</v>
       </c>
       <c r="O4" t="n">
-        <v>24.65033577533578</v>
+        <v>25.36115288220551</v>
       </c>
       <c r="P4" t="n">
-        <v>177.7637362637363</v>
+        <v>181.3027660059239</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.086691086691087</v>
+        <v>1.048664843928002</v>
       </c>
       <c r="R4" t="n">
-        <v>73.43986568986568</v>
+        <v>71.25992025518342</v>
       </c>
       <c r="S4" t="n">
-        <v>7635889.804639805</v>
+        <v>4979988.209159262</v>
       </c>
       <c r="T4" t="n">
-        <v>77.33180708180709</v>
+        <v>75.01523125996809</v>
       </c>
       <c r="U4" t="n">
-        <v>24.01118421052631</v>
+        <v>24.13894736842105</v>
       </c>
       <c r="V4" t="n">
-        <v>183.0503588516746</v>
+        <v>182.9902870813397</v>
       </c>
       <c r="W4" t="n">
-        <v>1.294557416267943</v>
+        <v>1.265645933014354</v>
       </c>
       <c r="X4" t="n">
-        <v>74.63947368421053</v>
+        <v>74.92157894736843</v>
       </c>
       <c r="Y4" t="n">
-        <v>14213175.83732058</v>
+        <v>14405540.66985646</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.28026315789475</v>
+        <v>80.3542105263158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>IRBb0lXA</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.02777777777778</v>
+        <v>24.11805555555556</v>
       </c>
       <c r="D5" t="n">
-        <v>180.5194444444444</v>
+        <v>180.2847222222223</v>
       </c>
       <c r="E5" t="n">
-        <v>2.127777777777778</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>81.46111111111111</v>
+        <v>72.02083333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>32883333.33333334</v>
+        <v>3806250</v>
       </c>
       <c r="H5" t="n">
-        <v>83.96111111111111</v>
+        <v>76.26388888888889</v>
       </c>
       <c r="I5" t="n">
-        <v>22.75694444444444</v>
+        <v>24.80555555555556</v>
       </c>
       <c r="J5" t="n">
-        <v>181.9583333333334</v>
+        <v>185.6027777777778</v>
       </c>
       <c r="K5" t="n">
-        <v>1.208333333333333</v>
+        <v>1.375</v>
       </c>
       <c r="L5" t="n">
-        <v>71.80555555555556</v>
+        <v>74.93611111111112</v>
       </c>
       <c r="M5" t="n">
-        <v>10669027.77777778</v>
+        <v>10536388.88888889</v>
       </c>
       <c r="N5" t="n">
-        <v>77.83333333333334</v>
+        <v>79.6888888888889</v>
       </c>
       <c r="O5" t="n">
-        <v>25.97996794871795</v>
+        <v>23.71445344129554</v>
       </c>
       <c r="P5" t="n">
-        <v>179.5369551282051</v>
+        <v>179.6018353576249</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.858205128205128</v>
+        <v>1.03</v>
       </c>
       <c r="R5" t="n">
-        <v>79.55842948717948</v>
+        <v>70.97367521367521</v>
       </c>
       <c r="S5" t="n">
-        <v>27075176.28205128</v>
+        <v>3710066.239316239</v>
       </c>
       <c r="T5" t="n">
-        <v>82.59689102564101</v>
+        <v>76.4042375168691</v>
       </c>
       <c r="U5" t="n">
-        <v>24.01899509803921</v>
+        <v>25.78301587301587</v>
       </c>
       <c r="V5" t="n">
-        <v>178.865625</v>
+        <v>180.775873015873</v>
       </c>
       <c r="W5" t="n">
-        <v>1.091115196078432</v>
+        <v>1.528253968253968</v>
       </c>
       <c r="X5" t="n">
-        <v>70.93780637254902</v>
+        <v>74.79730158730158</v>
       </c>
       <c r="Y5" t="n">
-        <v>6213064.644607844</v>
+        <v>8918285.714285713</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.846875</v>
+        <v>80.00555555555555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>28.67592592592592</v>
+        <v>24.43277777777778</v>
       </c>
       <c r="D6" t="n">
-        <v>178.0092592592593</v>
+        <v>181.3811111111111</v>
       </c>
       <c r="E6" t="n">
-        <v>1.398148148148148</v>
+        <v>1.022222222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3425925925926</v>
+        <v>70.27111111111113</v>
       </c>
       <c r="G6" t="n">
-        <v>6887962.962962963</v>
+        <v>2938166.666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>76.68518518518518</v>
+        <v>74.99111111111111</v>
       </c>
       <c r="I6" t="n">
-        <v>26.0125</v>
+        <v>25.75</v>
       </c>
       <c r="J6" t="n">
-        <v>182.975</v>
+        <v>181.1111111111111</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1125</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="L6" t="n">
-        <v>76.03749999999999</v>
+        <v>78.83333333333334</v>
       </c>
       <c r="M6" t="n">
-        <v>11375000</v>
+        <v>24594444.44444444</v>
       </c>
       <c r="N6" t="n">
-        <v>80.05</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="O6" t="n">
-        <v>27.92788461538461</v>
+        <v>24.37444444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>176.8858173076923</v>
+        <v>180.3538888888889</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.198317307692308</v>
+        <v>1.057222222222223</v>
       </c>
       <c r="R6" t="n">
-        <v>74.15985576923077</v>
+        <v>70.39194444444445</v>
       </c>
       <c r="S6" t="n">
-        <v>5245793.269230769</v>
+        <v>3327715.277777778</v>
       </c>
       <c r="T6" t="n">
-        <v>75.76201923076923</v>
+        <v>76.10611111111112</v>
       </c>
       <c r="U6" t="n">
-        <v>24.44142578590141</v>
+        <v>23.43524767801858</v>
       </c>
       <c r="V6" t="n">
-        <v>177.73659278995</v>
+        <v>179.262693498452</v>
       </c>
       <c r="W6" t="n">
-        <v>1.049561651583711</v>
+        <v>1.399907120743034</v>
       </c>
       <c r="X6" t="n">
-        <v>71.87296082400572</v>
+        <v>73.40565789473685</v>
       </c>
       <c r="Y6" t="n">
-        <v>7118900.612497023</v>
+        <v>12621015.47987616</v>
       </c>
       <c r="Z6" t="n">
-        <v>77.93532314241486</v>
+        <v>79.7617027863777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
+        <v>26.0125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>182.975</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.1125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>25.00577220766849</v>
+      </c>
+      <c r="P7" t="n">
+        <v>177.6208531793284</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.07122826863539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>72.35100023815194</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7289857.332102883</v>
+      </c>
+      <c r="T7" t="n">
+        <v>77.74825851393189</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24.84526862026862</v>
+      </c>
+      <c r="V7" t="n">
+        <v>178.398489010989</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08185286935287</v>
+      </c>
+      <c r="X7" t="n">
+        <v>73.30189255189255</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7058711.843711844</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>77.02794566544567</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="D8" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="H8" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24.90666666666667</v>
+      </c>
+      <c r="J8" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.353333333333333</v>
+      </c>
+      <c r="L8" t="n">
+        <v>77.15555555555555</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18229777.77777778</v>
+      </c>
+      <c r="N8" t="n">
+        <v>81.70666666666666</v>
+      </c>
+      <c r="O8" t="n">
+        <v>23.8374183006536</v>
+      </c>
+      <c r="P8" t="n">
+        <v>178.6258333333333</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.072892156862745</v>
+      </c>
+      <c r="R8" t="n">
+        <v>70.75024509803922</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5677396.160130719</v>
+      </c>
+      <c r="T8" t="n">
+        <v>76.81083333333333</v>
+      </c>
+      <c r="U8" t="n">
+        <v>25.13459752321982</v>
+      </c>
+      <c r="V8" t="n">
+        <v>179.6462081674775</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.444711042311662</v>
+      </c>
+      <c r="X8" t="n">
+        <v>74.79264411027569</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11310245.28232346</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>80.14443093026685</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.83636363636364</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.0981818181818</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.261818181818182</v>
+      </c>
+      <c r="F9" t="n">
+        <v>85.54363636363637</v>
+      </c>
+      <c r="G9" t="n">
+        <v>80570909.09090909</v>
+      </c>
+      <c r="H9" t="n">
+        <v>88.44545454545455</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.66337280366692</v>
+      </c>
+      <c r="P9" t="n">
+        <v>177.0505958747136</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.130683728036669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>79.03878724216959</v>
+      </c>
+      <c r="S9" t="n">
+        <v>42054839.14247517</v>
+      </c>
+      <c r="T9" t="n">
+        <v>83.94449770817418</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.59050656945394</v>
+      </c>
+      <c r="V9" t="n">
+        <v>181.0762436394015</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>70.97357028935976</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3153047.011468064</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>74.95123414597099</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="D10" t="n">
+        <v>180.40625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.354166666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>74.69791666666667</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8790885.416666666</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.36458333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>26.29444444444444</v>
+      </c>
+      <c r="J10" t="n">
+        <v>181.8361111111111</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.172222222222222</v>
+      </c>
+      <c r="L10" t="n">
+        <v>72.28611111111111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4147222.222222222</v>
+      </c>
+      <c r="N10" t="n">
+        <v>74.96666666666667</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23.41587009803921</v>
+      </c>
+      <c r="P10" t="n">
+        <v>180.852512254902</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>70.86170343137255</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5480058.210784314</v>
+      </c>
+      <c r="T10" t="n">
+        <v>77.39240196078433</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25.36115288220551</v>
+      </c>
+      <c r="V10" t="n">
+        <v>181.3027660059239</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.048664843928002</v>
+      </c>
+      <c r="X10" t="n">
+        <v>71.25992025518342</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4979988.209159262</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>75.01523125996809</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.31388888888889</v>
+      </c>
+      <c r="D11" t="n">
+        <v>183.9138888888889</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.352777777777778</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.05277777777778</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21916944.44444445</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.96388888888889</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="J11" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="L11" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8969444.444444444</v>
+      </c>
+      <c r="N11" t="n">
+        <v>77.96296296296296</v>
+      </c>
+      <c r="O11" t="n">
+        <v>24.13894736842105</v>
+      </c>
+      <c r="P11" t="n">
+        <v>182.9902870813397</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.265645933014354</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.92157894736843</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14405540.66985646</v>
+      </c>
+      <c r="T11" t="n">
+        <v>80.3542105263158</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.19049019607843</v>
+      </c>
+      <c r="V11" t="n">
+        <v>180.3579738562092</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.377271241830065</v>
+      </c>
+      <c r="X11" t="n">
+        <v>73.78357843137255</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9030457.516339872</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>77.67142156862745</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="D12" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F12" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7059375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J12" t="n">
+        <v>179</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="M12" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="N12" t="n">
+        <v>85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>25.24920634920635</v>
+      </c>
+      <c r="P12" t="n">
+        <v>180.9320159372791</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.545748987854251</v>
+      </c>
+      <c r="R12" t="n">
+        <v>75.04578111946533</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9978750.240987083</v>
+      </c>
+      <c r="T12" t="n">
+        <v>79.45408392776815</v>
+      </c>
+      <c r="U12" t="n">
+        <v>20.81480769230769</v>
+      </c>
+      <c r="V12" t="n">
+        <v>181.5738736263737</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.617060439560439</v>
+      </c>
+      <c r="X12" t="n">
+        <v>71.79263736263735</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>23059259.61538462</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>81.33467032967033</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.63194444444444</v>
+      </c>
+      <c r="D13" t="n">
+        <v>178.4756944444445</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.392361111111111</v>
+      </c>
+      <c r="F13" t="n">
+        <v>75.10069444444444</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6397222.222222222</v>
+      </c>
+      <c r="H13" t="n">
+        <v>76.67013888888889</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180.8155555555555</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.213333333333333</v>
+      </c>
+      <c r="L13" t="n">
+        <v>81.63555555555556</v>
+      </c>
+      <c r="M13" t="n">
+        <v>33506666.66666667</v>
+      </c>
+      <c r="N13" t="n">
+        <v>83.90222222222224</v>
+      </c>
+      <c r="O13" t="n">
+        <v>28.12897435897436</v>
+      </c>
+      <c r="P13" t="n">
+        <v>176.7353205128205</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.198653846153846</v>
+      </c>
+      <c r="R13" t="n">
+        <v>74.30121794871795</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5515301.282051282</v>
+      </c>
+      <c r="T13" t="n">
+        <v>75.68961538461538</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.99166666666666</v>
+      </c>
+      <c r="V13" t="n">
+        <v>179.1680256410256</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.825025641025641</v>
+      </c>
+      <c r="X13" t="n">
+        <v>79.50828205128205</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>26687064.1025641</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>82.5621282051282</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.75694444444444</v>
+      </c>
+      <c r="D14" t="n">
+        <v>180.5729166666667</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.815972222222222</v>
+      </c>
+      <c r="F14" t="n">
+        <v>77.65972222222223</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15519097.22222222</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.42013888888889</v>
+      </c>
+      <c r="I14" t="n">
         <v>27.05555555555555</v>
       </c>
-      <c r="D7" t="n">
+      <c r="J14" t="n">
         <v>183.2488888888889</v>
       </c>
-      <c r="E7" t="n">
+      <c r="K14" t="n">
         <v>1.353333333333333</v>
       </c>
-      <c r="F7" t="n">
+      <c r="L14" t="n">
         <v>75.88</v>
       </c>
-      <c r="G7" t="n">
+      <c r="M14" t="n">
         <v>10485333.33333333</v>
       </c>
-      <c r="H7" t="n">
+      <c r="N14" t="n">
         <v>77.96444444444444</v>
       </c>
-      <c r="I7" t="n">
+      <c r="O14" t="n">
+        <v>23.8687896211116</v>
+      </c>
+      <c r="P14" t="n">
+        <v>181.9719519386702</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.63828689370485</v>
+      </c>
+      <c r="R14" t="n">
+        <v>75.80812324929973</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21211163.93925992</v>
+      </c>
+      <c r="T14" t="n">
+        <v>81.83071649712517</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.82455026455026</v>
+      </c>
+      <c r="V14" t="n">
+        <v>181.7560317460317</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.152010582010582</v>
+      </c>
+      <c r="X14" t="n">
+        <v>74.12314814814815</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7623079.62962963</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>76.7276984126984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="D15" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10536388.88888889</v>
+      </c>
+      <c r="H15" t="n">
+        <v>79.6888888888889</v>
+      </c>
+      <c r="I15" t="n">
+        <v>24.43277777777778</v>
+      </c>
+      <c r="J15" t="n">
+        <v>181.3811111111111</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.022222222222222</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70.27111111111113</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2938166.666666667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>74.99111111111111</v>
+      </c>
+      <c r="O15" t="n">
+        <v>25.78301587301587</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180.775873015873</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.528253968253968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>74.79730158730158</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8918285.714285713</v>
+      </c>
+      <c r="T15" t="n">
+        <v>80.00555555555555</v>
+      </c>
+      <c r="U15" t="n">
+        <v>24.37444444444444</v>
+      </c>
+      <c r="V15" t="n">
+        <v>180.3538888888889</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.057222222222223</v>
+      </c>
+      <c r="X15" t="n">
+        <v>70.39194444444445</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3327715.277777778</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>76.10611111111112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26.0125</v>
+      </c>
+      <c r="J16" t="n">
+        <v>182.975</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.1125</v>
+      </c>
+      <c r="L16" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>23.8374183006536</v>
+      </c>
+      <c r="P16" t="n">
+        <v>178.6258333333333</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.072892156862745</v>
+      </c>
+      <c r="R16" t="n">
+        <v>70.75024509803922</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5677396.160130719</v>
+      </c>
+      <c r="T16" t="n">
+        <v>76.81083333333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.00577220766849</v>
+      </c>
+      <c r="V16" t="n">
+        <v>177.6208531793284</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07122826863539</v>
+      </c>
+      <c r="X16" t="n">
+        <v>72.35100023815194</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7289857.332102883</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>77.74825851393189</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.83636363636364</v>
+      </c>
+      <c r="D17" t="n">
+        <v>182.0981818181818</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.261818181818182</v>
+      </c>
+      <c r="F17" t="n">
+        <v>85.54363636363637</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80570909.09090909</v>
+      </c>
+      <c r="H17" t="n">
+        <v>88.44545454545455</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="J17" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3806250</v>
+      </c>
+      <c r="N17" t="n">
+        <v>76.26388888888889</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.66337280366692</v>
+      </c>
+      <c r="P17" t="n">
+        <v>177.0505958747136</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.130683728036669</v>
+      </c>
+      <c r="R17" t="n">
+        <v>79.03878724216959</v>
+      </c>
+      <c r="S17" t="n">
+        <v>42054839.14247517</v>
+      </c>
+      <c r="T17" t="n">
+        <v>83.94449770817418</v>
+      </c>
+      <c r="U17" t="n">
+        <v>23.71445344129554</v>
+      </c>
+      <c r="V17" t="n">
+        <v>179.6018353576249</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>70.97367521367521</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3710066.239316239</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>76.4042375168691</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.90666666666667</v>
+      </c>
+      <c r="D18" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.353333333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>77.15555555555555</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18229777.77777778</v>
+      </c>
+      <c r="H18" t="n">
+        <v>81.70666666666666</v>
+      </c>
+      <c r="I18" t="n">
+        <v>28.63194444444444</v>
+      </c>
+      <c r="J18" t="n">
+        <v>178.4756944444445</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.392361111111111</v>
+      </c>
+      <c r="L18" t="n">
+        <v>75.10069444444444</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6397222.222222222</v>
+      </c>
+      <c r="N18" t="n">
+        <v>76.67013888888889</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25.13459752321982</v>
+      </c>
+      <c r="P18" t="n">
+        <v>179.6462081674775</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.444711042311662</v>
+      </c>
+      <c r="R18" t="n">
+        <v>74.79264411027569</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11310245.28232346</v>
+      </c>
+      <c r="T18" t="n">
+        <v>80.14443093026685</v>
+      </c>
+      <c r="U18" t="n">
+        <v>28.12897435897436</v>
+      </c>
+      <c r="V18" t="n">
+        <v>176.7353205128205</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.198653846153846</v>
+      </c>
+      <c r="X18" t="n">
+        <v>74.30121794871795</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5515301.282051282</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>75.68961538461538</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="D19" t="n">
+        <v>179</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="H19" t="n">
+        <v>85</v>
+      </c>
+      <c r="I19" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="J19" t="n">
+        <v>180.40625</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.354166666666667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74.69791666666667</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8790885.416666666</v>
+      </c>
+      <c r="N19" t="n">
+        <v>77.36458333333333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20.81480769230769</v>
+      </c>
+      <c r="P19" t="n">
+        <v>181.5738736263737</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.617060439560439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>71.79263736263735</v>
+      </c>
+      <c r="S19" t="n">
+        <v>23059259.61538462</v>
+      </c>
+      <c r="T19" t="n">
+        <v>81.33467032967033</v>
+      </c>
+      <c r="U19" t="n">
+        <v>23.41587009803921</v>
+      </c>
+      <c r="V19" t="n">
+        <v>180.852512254902</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>70.86170343137255</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5480058.210784314</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>77.39240196078433</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="D20" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="I20" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J20" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7059375</v>
+      </c>
+      <c r="N20" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25.59050656945394</v>
+      </c>
+      <c r="P20" t="n">
+        <v>181.0762436394015</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>70.97357028935976</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3153047.011468064</v>
+      </c>
+      <c r="T20" t="n">
+        <v>74.95123414597099</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25.24920634920635</v>
+      </c>
+      <c r="V20" t="n">
+        <v>180.9320159372791</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.545748987854251</v>
+      </c>
+      <c r="X20" t="n">
+        <v>75.04578111946533</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9978750.240987083</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>79.45408392776815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>27.75694444444444</v>
+      </c>
+      <c r="J21" t="n">
+        <v>180.5729166666667</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.815972222222222</v>
+      </c>
+      <c r="L21" t="n">
+        <v>77.65972222222223</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15519097.22222222</v>
+      </c>
+      <c r="N21" t="n">
+        <v>79.42013888888889</v>
+      </c>
+      <c r="O21" t="n">
+        <v>24.84526862026862</v>
+      </c>
+      <c r="P21" t="n">
+        <v>178.398489010989</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.08185286935287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>73.30189255189255</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7058711.843711844</v>
+      </c>
+      <c r="T21" t="n">
+        <v>77.02794566544567</v>
+      </c>
+      <c r="U21" t="n">
+        <v>23.8687896211116</v>
+      </c>
+      <c r="V21" t="n">
+        <v>181.9719519386702</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.63828689370485</v>
+      </c>
+      <c r="X21" t="n">
+        <v>75.80812324929973</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21211163.93925992</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>81.83071649712517</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="D22" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="F22" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8969444.444444444</v>
+      </c>
+      <c r="H22" t="n">
+        <v>77.96296296296296</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>180.8155555555555</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.213333333333333</v>
+      </c>
+      <c r="L22" t="n">
+        <v>81.63555555555556</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33506666.66666667</v>
+      </c>
+      <c r="N22" t="n">
+        <v>83.90222222222224</v>
+      </c>
+      <c r="O22" t="n">
+        <v>26.19049019607843</v>
+      </c>
+      <c r="P22" t="n">
+        <v>180.3579738562092</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.377271241830065</v>
+      </c>
+      <c r="R22" t="n">
+        <v>73.78357843137255</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9030457.516339872</v>
+      </c>
+      <c r="T22" t="n">
+        <v>77.67142156862745</v>
+      </c>
+      <c r="U22" t="n">
+        <v>25.99166666666666</v>
+      </c>
+      <c r="V22" t="n">
+        <v>179.1680256410256</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.825025641025641</v>
+      </c>
+      <c r="X22" t="n">
+        <v>79.50828205128205</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>26687064.1025641</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>82.5621282051282</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24.43277777777778</v>
+      </c>
+      <c r="D23" t="n">
+        <v>181.3811111111111</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.022222222222222</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70.27111111111113</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2938166.666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>74.99111111111111</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.05555555555555</v>
+      </c>
+      <c r="J23" t="n">
+        <v>183.2488888888889</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.353333333333333</v>
+      </c>
+      <c r="L23" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10485333.33333333</v>
+      </c>
+      <c r="N23" t="n">
+        <v>77.96444444444444</v>
+      </c>
+      <c r="O23" t="n">
+        <v>24.37444444444444</v>
+      </c>
+      <c r="P23" t="n">
+        <v>180.3538888888889</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.057222222222223</v>
+      </c>
+      <c r="R23" t="n">
+        <v>70.39194444444445</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3327715.277777778</v>
+      </c>
+      <c r="T23" t="n">
+        <v>76.10611111111112</v>
+      </c>
+      <c r="U23" t="n">
+        <v>26.82455026455026</v>
+      </c>
+      <c r="V23" t="n">
+        <v>181.7560317460317</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.152010582010582</v>
+      </c>
+      <c r="X23" t="n">
+        <v>74.12314814814815</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7623079.62962963</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>76.7276984126984</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.83333333333334</v>
+      </c>
+      <c r="D24" t="n">
+        <v>180.40625</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.354166666666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>74.69791666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8790885.416666666</v>
+      </c>
+      <c r="H24" t="n">
+        <v>77.36458333333333</v>
+      </c>
+      <c r="I24" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="J24" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3806250</v>
+      </c>
+      <c r="N24" t="n">
+        <v>76.26388888888889</v>
+      </c>
+      <c r="O24" t="n">
+        <v>23.41587009803921</v>
+      </c>
+      <c r="P24" t="n">
+        <v>180.852512254902</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>70.86170343137255</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5480058.210784314</v>
+      </c>
+      <c r="T24" t="n">
+        <v>77.39240196078433</v>
+      </c>
+      <c r="U24" t="n">
+        <v>23.71445344129554</v>
+      </c>
+      <c r="V24" t="n">
+        <v>179.6018353576249</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>70.97367521367521</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3710066.239316239</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>76.4042375168691</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>28.63194444444444</v>
+      </c>
+      <c r="D25" t="n">
+        <v>178.4756944444445</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.392361111111111</v>
+      </c>
+      <c r="F25" t="n">
+        <v>75.10069444444444</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6397222.222222222</v>
+      </c>
+      <c r="H25" t="n">
+        <v>76.67013888888889</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26.29444444444444</v>
+      </c>
+      <c r="J25" t="n">
+        <v>181.8361111111111</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.172222222222222</v>
+      </c>
+      <c r="L25" t="n">
+        <v>72.28611111111111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4147222.222222222</v>
+      </c>
+      <c r="N25" t="n">
+        <v>74.96666666666667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>28.12897435897436</v>
+      </c>
+      <c r="P25" t="n">
+        <v>176.7353205128205</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.198653846153846</v>
+      </c>
+      <c r="R25" t="n">
+        <v>74.30121794871795</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5515301.282051282</v>
+      </c>
+      <c r="T25" t="n">
+        <v>75.68961538461538</v>
+      </c>
+      <c r="U25" t="n">
+        <v>25.36115288220551</v>
+      </c>
+      <c r="V25" t="n">
+        <v>181.3027660059239</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.048664843928002</v>
+      </c>
+      <c r="X25" t="n">
+        <v>71.25992025518342</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4979988.209159262</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>75.01523125996809</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>25.75</v>
       </c>
-      <c r="J7" t="n">
+      <c r="D26" t="n">
         <v>181.1111111111111</v>
       </c>
-      <c r="K7" t="n">
+      <c r="E26" t="n">
         <v>1.777777777777778</v>
       </c>
-      <c r="L7" t="n">
+      <c r="F26" t="n">
         <v>78.83333333333334</v>
       </c>
-      <c r="M7" t="n">
+      <c r="G26" t="n">
         <v>24594444.44444444</v>
       </c>
-      <c r="N7" t="n">
+      <c r="H26" t="n">
         <v>82.33333333333334</v>
       </c>
-      <c r="O7" t="n">
-        <v>26.82455026455026</v>
-      </c>
-      <c r="P7" t="n">
-        <v>181.7560317460318</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.152010582010582</v>
-      </c>
-      <c r="R7" t="n">
-        <v>74.12314814814815</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7623079.62962963</v>
-      </c>
-      <c r="T7" t="n">
-        <v>76.7276984126984</v>
-      </c>
-      <c r="U7" t="n">
-        <v>23.38780959752322</v>
-      </c>
-      <c r="V7" t="n">
-        <v>179.453366873065</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.437383900928793</v>
-      </c>
-      <c r="X7" t="n">
-        <v>73.36644736842106</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13345019.3498452</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>79.88962848297214</v>
+      <c r="I26" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="J26" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="L26" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10669027.77777778</v>
+      </c>
+      <c r="N26" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="O26" t="n">
+        <v>23.43524767801858</v>
+      </c>
+      <c r="P26" t="n">
+        <v>179.262693498452</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.399907120743034</v>
+      </c>
+      <c r="R26" t="n">
+        <v>73.40565789473685</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12621015.47987616</v>
+      </c>
+      <c r="T26" t="n">
+        <v>79.7617027863777</v>
+      </c>
+      <c r="U26" t="n">
+        <v>23.8374183006536</v>
+      </c>
+      <c r="V26" t="n">
+        <v>178.6258333333333</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.072892156862745</v>
+      </c>
+      <c r="X26" t="n">
+        <v>70.75024509803922</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>5677396.160130719</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>76.81083333333333</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26.0125</v>
+      </c>
+      <c r="D27" t="n">
+        <v>182.975</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.1125</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76.03749999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11375000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="J27" t="n">
+        <v>179</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="M27" t="n">
+        <v>42187500</v>
+      </c>
+      <c r="N27" t="n">
+        <v>85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25.00577220766849</v>
+      </c>
+      <c r="P27" t="n">
+        <v>177.6208531793284</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.07122826863539</v>
+      </c>
+      <c r="R27" t="n">
+        <v>72.35100023815194</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7289857.332102883</v>
+      </c>
+      <c r="T27" t="n">
+        <v>77.74825851393189</v>
+      </c>
+      <c r="U27" t="n">
+        <v>20.81480769230769</v>
+      </c>
+      <c r="V27" t="n">
+        <v>181.5738736263737</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.617060439560439</v>
+      </c>
+      <c r="X27" t="n">
+        <v>71.79263736263735</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>23059259.61538462</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>81.33467032967033</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="D28" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.402777777777778</v>
+      </c>
+      <c r="F28" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8969444.444444444</v>
+      </c>
+      <c r="H28" t="n">
+        <v>77.96296296296296</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24.90666666666667</v>
+      </c>
+      <c r="J28" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.353333333333333</v>
+      </c>
+      <c r="L28" t="n">
+        <v>77.15555555555555</v>
+      </c>
+      <c r="M28" t="n">
+        <v>18229777.77777778</v>
+      </c>
+      <c r="N28" t="n">
+        <v>81.70666666666666</v>
+      </c>
+      <c r="O28" t="n">
+        <v>26.19049019607843</v>
+      </c>
+      <c r="P28" t="n">
+        <v>180.3579738562092</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.377271241830065</v>
+      </c>
+      <c r="R28" t="n">
+        <v>73.78357843137255</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9030457.516339872</v>
+      </c>
+      <c r="T28" t="n">
+        <v>77.67142156862745</v>
+      </c>
+      <c r="U28" t="n">
+        <v>25.13459752321982</v>
+      </c>
+      <c r="V28" t="n">
+        <v>179.6462081674775</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.444711042311662</v>
+      </c>
+      <c r="X28" t="n">
+        <v>74.79264411027569</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11310245.28232346</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>80.14443093026685</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>25.31388888888889</v>
+      </c>
+      <c r="D29" t="n">
+        <v>183.9138888888889</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.352777777777778</v>
+      </c>
+      <c r="F29" t="n">
+        <v>78.05277777777778</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21916944.44444445</v>
+      </c>
+      <c r="H29" t="n">
+        <v>81.96388888888889</v>
+      </c>
+      <c r="I29" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="J29" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="L29" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10536388.88888889</v>
+      </c>
+      <c r="N29" t="n">
+        <v>79.6888888888889</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24.13894736842105</v>
+      </c>
+      <c r="P29" t="n">
+        <v>182.9902870813397</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.265645933014354</v>
+      </c>
+      <c r="R29" t="n">
+        <v>74.92157894736843</v>
+      </c>
+      <c r="S29" t="n">
+        <v>14405540.66985646</v>
+      </c>
+      <c r="T29" t="n">
+        <v>80.3542105263158</v>
+      </c>
+      <c r="U29" t="n">
+        <v>25.78301587301587</v>
+      </c>
+      <c r="V29" t="n">
+        <v>180.775873015873</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.528253968253968</v>
+      </c>
+      <c r="X29" t="n">
+        <v>74.79730158730158</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8918285.714285713</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>80.00555555555555</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>27.75694444444444</v>
+      </c>
+      <c r="D30" t="n">
+        <v>180.5729166666667</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.815972222222222</v>
+      </c>
+      <c r="F30" t="n">
+        <v>77.65972222222223</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15519097.22222222</v>
+      </c>
+      <c r="H30" t="n">
+        <v>79.42013888888889</v>
+      </c>
+      <c r="I30" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="J30" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="N30" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="O30" t="n">
+        <v>23.8687896211116</v>
+      </c>
+      <c r="P30" t="n">
+        <v>181.9719519386702</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.63828689370485</v>
+      </c>
+      <c r="R30" t="n">
+        <v>75.80812324929973</v>
+      </c>
+      <c r="S30" t="n">
+        <v>21211163.93925992</v>
+      </c>
+      <c r="T30" t="n">
+        <v>81.83071649712517</v>
+      </c>
+      <c r="U30" t="n">
+        <v>25.59050656945394</v>
+      </c>
+      <c r="V30" t="n">
+        <v>181.0762436394015</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>70.97357028935976</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3153047.011468064</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>74.95123414597099</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>180.8155555555555</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.213333333333333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>81.63555555555556</v>
+      </c>
+      <c r="G31" t="n">
+        <v>33506666.66666667</v>
+      </c>
+      <c r="H31" t="n">
+        <v>83.90222222222224</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.83636363636364</v>
+      </c>
+      <c r="J31" t="n">
+        <v>182.0981818181818</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.261818181818182</v>
+      </c>
+      <c r="L31" t="n">
+        <v>85.54363636363637</v>
+      </c>
+      <c r="M31" t="n">
+        <v>80570909.09090909</v>
+      </c>
+      <c r="N31" t="n">
+        <v>88.44545454545455</v>
+      </c>
+      <c r="O31" t="n">
+        <v>25.99166666666666</v>
+      </c>
+      <c r="P31" t="n">
+        <v>179.1680256410256</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.825025641025641</v>
+      </c>
+      <c r="R31" t="n">
+        <v>79.50828205128205</v>
+      </c>
+      <c r="S31" t="n">
+        <v>26687064.1025641</v>
+      </c>
+      <c r="T31" t="n">
+        <v>82.5621282051282</v>
+      </c>
+      <c r="U31" t="n">
+        <v>24.66337280366692</v>
+      </c>
+      <c r="V31" t="n">
+        <v>177.0505958747136</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.130683728036669</v>
+      </c>
+      <c r="X31" t="n">
+        <v>79.03878724216959</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>42054839.14247517</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>83.94449770817418</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="D32" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F32" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7059375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>25.24920634920635</v>
+      </c>
+      <c r="P32" t="n">
+        <v>180.9320159372791</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.545748987854251</v>
+      </c>
+      <c r="R32" t="n">
+        <v>75.04578111946533</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9978750.240987083</v>
+      </c>
+      <c r="T32" t="n">
+        <v>79.45408392776815</v>
+      </c>
+      <c r="U32" t="n">
+        <v>24.84526862026862</v>
+      </c>
+      <c r="V32" t="n">
+        <v>178.398489010989</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08185286935287</v>
+      </c>
+      <c r="X32" t="n">
+        <v>73.30189255189255</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7058711.843711844</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>77.02794566544567</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,593 +446,1731 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.24074074074074</v>
+        <v>27.12222222222222</v>
       </c>
       <c r="D2" t="n">
-        <v>181.050925925926</v>
+        <v>180.6472222222223</v>
       </c>
       <c r="E2" t="n">
-        <v>1.402777777777778</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>74.54629629629629</v>
+        <v>40983.33333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>8969444.444444444</v>
+        <v>27.04629629629629</v>
       </c>
       <c r="H2" t="n">
-        <v>77.96296296296296</v>
+        <v>183.274074074074</v>
       </c>
       <c r="I2" t="n">
-        <v>24.59097222222222</v>
+        <v>75.75</v>
       </c>
       <c r="J2" t="n">
-        <v>181.1263888888889</v>
+        <v>24390.74074074074</v>
       </c>
       <c r="K2" t="n">
-        <v>1.027777777777778</v>
+        <v>24.30112893642305</v>
       </c>
       <c r="L2" t="n">
-        <v>70.23888888888888</v>
+        <v>181.2384432560903</v>
       </c>
       <c r="M2" t="n">
-        <v>2895208.333333333</v>
+        <v>75.31978609625669</v>
       </c>
       <c r="N2" t="n">
-        <v>74.86388888888888</v>
+        <v>45115.86452762924</v>
       </c>
       <c r="O2" t="n">
-        <v>26.20686274509804</v>
+        <v>26.70161797408174</v>
       </c>
       <c r="P2" t="n">
-        <v>179.7599673202614</v>
+        <v>181.8401713825627</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.393464052287582</v>
+        <v>74.16784084809447</v>
       </c>
       <c r="R2" t="n">
-        <v>73.55759803921569</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9027134.395424839</v>
-      </c>
-      <c r="T2" t="n">
-        <v>77.47990196078432</v>
-      </c>
-      <c r="U2" t="n">
-        <v>24.18055555555556</v>
-      </c>
-      <c r="V2" t="n">
-        <v>180.4548611111111</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.059027777777778</v>
-      </c>
-      <c r="X2" t="n">
-        <v>70.35243055555556</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3393706.597222222</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>76.35763888888889</v>
+        <v>21963.39333640058</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.18888888888889</v>
+        <v>24.80555555555556</v>
       </c>
       <c r="D3" t="n">
-        <v>182.7222222222222</v>
+        <v>185.6027777777778</v>
       </c>
       <c r="E3" t="n">
-        <v>1.358333333333333</v>
+        <v>74.93611111111112</v>
       </c>
       <c r="F3" t="n">
-        <v>77.5</v>
+        <v>24561.11111111111</v>
       </c>
       <c r="G3" t="n">
-        <v>18778888.88888889</v>
+        <v>24.39398148148148</v>
       </c>
       <c r="H3" t="n">
-        <v>81.74444444444444</v>
+        <v>181.5175925925926</v>
       </c>
       <c r="I3" t="n">
-        <v>23.875</v>
+        <v>70.27592592592593</v>
       </c>
       <c r="J3" t="n">
-        <v>179</v>
+        <v>12455.55555555556</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>25.61547619047619</v>
       </c>
       <c r="L3" t="n">
-        <v>79.125</v>
+        <v>181.0169312169312</v>
       </c>
       <c r="M3" t="n">
-        <v>42187500</v>
+        <v>74.84960317460317</v>
       </c>
       <c r="N3" t="n">
-        <v>85</v>
+        <v>21078.96825396825</v>
       </c>
       <c r="O3" t="n">
-        <v>24.9577205882353</v>
+        <v>24.58287037037037</v>
       </c>
       <c r="P3" t="n">
-        <v>179.8472338935574</v>
+        <v>180.4303240740741</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.411151960784314</v>
+        <v>70.67037037037038</v>
       </c>
       <c r="R3" t="n">
-        <v>74.35922619047619</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10777280.28711485</v>
-      </c>
-      <c r="T3" t="n">
-        <v>80.0358018207283</v>
-      </c>
-      <c r="U3" t="n">
-        <v>20.9292239010989</v>
-      </c>
-      <c r="V3" t="n">
-        <v>181.4137706043956</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.592754120879121</v>
-      </c>
-      <c r="X3" t="n">
-        <v>71.75865384615385</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>22704431.66208791</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>81.18619505494506</v>
+        <v>14829.86111111111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="E4" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19944.44444444445</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25.88333333333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>183.2333333333333</v>
+      </c>
       <c r="I4" t="n">
-        <v>25.51851851851852</v>
+        <v>75.98333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>184.1851851851852</v>
+        <v>22850</v>
       </c>
       <c r="K4" t="n">
-        <v>1.37037037037037</v>
+        <v>23.97284858387799</v>
       </c>
       <c r="L4" t="n">
-        <v>78.03703703703704</v>
+        <v>178.7048611111111</v>
       </c>
       <c r="M4" t="n">
-        <v>21592592.59259259</v>
+        <v>71.10020424836601</v>
       </c>
       <c r="N4" t="n">
-        <v>81.85185185185185</v>
+        <v>19992.34749455338</v>
       </c>
       <c r="O4" t="n">
-        <v>24.65033577533578</v>
+        <v>25.26522683972374</v>
       </c>
       <c r="P4" t="n">
-        <v>177.7637362637363</v>
+        <v>177.340294316107</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.086691086691087</v>
+        <v>72.60500019845995</v>
       </c>
       <c r="R4" t="n">
-        <v>73.43986568986568</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7635889.804639805</v>
-      </c>
-      <c r="T4" t="n">
-        <v>77.33180708180709</v>
-      </c>
-      <c r="U4" t="n">
-        <v>24.01118421052631</v>
-      </c>
-      <c r="V4" t="n">
-        <v>183.0503588516746</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.294557416267943</v>
-      </c>
-      <c r="X4" t="n">
-        <v>74.63947368421053</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>14213175.83732058</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>80.28026315789475</v>
+        <v>18910.85923235691</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.02777777777778</v>
+        <v>25.78030303030303</v>
       </c>
       <c r="D5" t="n">
-        <v>180.5194444444444</v>
+        <v>182.0651515151515</v>
       </c>
       <c r="E5" t="n">
-        <v>2.127777777777778</v>
+        <v>85.58636363636363</v>
       </c>
       <c r="F5" t="n">
-        <v>81.46111111111111</v>
+        <v>204253.0303030303</v>
       </c>
       <c r="G5" t="n">
-        <v>32883333.33333334</v>
+        <v>24.11805555555556</v>
       </c>
       <c r="H5" t="n">
-        <v>83.96111111111111</v>
+        <v>180.2847222222223</v>
       </c>
       <c r="I5" t="n">
-        <v>22.75694444444444</v>
+        <v>72.02083333333334</v>
       </c>
       <c r="J5" t="n">
-        <v>181.9583333333334</v>
+        <v>14784.72222222223</v>
       </c>
       <c r="K5" t="n">
-        <v>1.208333333333333</v>
+        <v>24.5632273363891</v>
       </c>
       <c r="L5" t="n">
-        <v>71.80555555555556</v>
+        <v>177.7088298955946</v>
       </c>
       <c r="M5" t="n">
-        <v>10669027.77777778</v>
+        <v>79.15732270180798</v>
       </c>
       <c r="N5" t="n">
-        <v>77.83333333333334</v>
+        <v>132018.9616755793</v>
       </c>
       <c r="O5" t="n">
-        <v>25.97996794871795</v>
+        <v>23.75224061284433</v>
       </c>
       <c r="P5" t="n">
-        <v>179.5369551282051</v>
+        <v>179.6583922097854</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.858205128205128</v>
+        <v>71.0564940506117</v>
       </c>
       <c r="R5" t="n">
-        <v>79.55842948717948</v>
-      </c>
-      <c r="S5" t="n">
-        <v>27075176.28205128</v>
-      </c>
-      <c r="T5" t="n">
-        <v>82.59689102564101</v>
-      </c>
-      <c r="U5" t="n">
-        <v>24.01899509803921</v>
-      </c>
-      <c r="V5" t="n">
-        <v>178.865625</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.091115196078432</v>
-      </c>
-      <c r="X5" t="n">
-        <v>70.93780637254902</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6213064.644607844</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>76.846875</v>
+        <v>14402.46906229878</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>28.67592592592592</v>
+        <v>24.90666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>178.0092592592593</v>
+        <v>182.8666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>1.398148148148148</v>
+        <v>77.15555555555555</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3425925925926</v>
+        <v>33453.33333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>6887962.962962963</v>
+        <v>28.39444444444445</v>
       </c>
       <c r="H6" t="n">
-        <v>76.68518518518518</v>
+        <v>178.8027777777778</v>
       </c>
       <c r="I6" t="n">
-        <v>26.0125</v>
+        <v>74.925</v>
       </c>
       <c r="J6" t="n">
-        <v>182.975</v>
+        <v>17638.88888888889</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1125</v>
+        <v>25.22883126934984</v>
       </c>
       <c r="L6" t="n">
-        <v>76.03749999999999</v>
+        <v>180.1635068062312</v>
       </c>
       <c r="M6" t="n">
-        <v>11375000</v>
+        <v>75.25220342522975</v>
       </c>
       <c r="N6" t="n">
-        <v>80.05</v>
+        <v>35764.86436679935</v>
       </c>
       <c r="O6" t="n">
-        <v>27.92788461538461</v>
+        <v>28.38525641025641</v>
       </c>
       <c r="P6" t="n">
-        <v>176.8858173076923</v>
+        <v>176.6683226495726</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.198317307692308</v>
+        <v>74.43990384615385</v>
       </c>
       <c r="R6" t="n">
-        <v>74.15985576923077</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5245793.269230769</v>
-      </c>
-      <c r="T6" t="n">
-        <v>75.76201923076923</v>
-      </c>
-      <c r="U6" t="n">
-        <v>24.44142578590141</v>
-      </c>
-      <c r="V6" t="n">
-        <v>177.73659278995</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.049561651583711</v>
-      </c>
-      <c r="X6" t="n">
-        <v>71.87296082400572</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>7118900.612497023</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>77.93532314241486</v>
+        <v>17029.16666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>27.05555555555555</v>
+        <v>23.875</v>
       </c>
       <c r="D7" t="n">
-        <v>183.2488888888889</v>
+        <v>179</v>
       </c>
       <c r="E7" t="n">
-        <v>1.353333333333333</v>
+        <v>79.125</v>
       </c>
       <c r="F7" t="n">
-        <v>75.88</v>
+        <v>108000</v>
       </c>
       <c r="G7" t="n">
-        <v>10485333.33333333</v>
+        <v>26.81666666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>77.96444444444444</v>
+        <v>180.675</v>
       </c>
       <c r="I7" t="n">
-        <v>25.75</v>
+        <v>74.75833333333334</v>
       </c>
       <c r="J7" t="n">
-        <v>181.1111111111111</v>
+        <v>23313.88888888889</v>
       </c>
       <c r="K7" t="n">
-        <v>1.777777777777778</v>
+        <v>20.74249847374847</v>
       </c>
       <c r="L7" t="n">
-        <v>78.83333333333334</v>
+        <v>181.5099740537241</v>
       </c>
       <c r="M7" t="n">
-        <v>24594444.44444444</v>
+        <v>71.3271978021978</v>
       </c>
       <c r="N7" t="n">
-        <v>82.33333333333334</v>
+        <v>56073.13797313798</v>
       </c>
       <c r="O7" t="n">
-        <v>26.82455026455026</v>
+        <v>23.91676407742584</v>
       </c>
       <c r="P7" t="n">
-        <v>181.7560317460318</v>
+        <v>180.2847819255908</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.152010582010582</v>
+        <v>71.91308132227249</v>
       </c>
       <c r="R7" t="n">
-        <v>74.12314814814815</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7623079.62962963</v>
-      </c>
-      <c r="T7" t="n">
-        <v>76.7276984126984</v>
-      </c>
-      <c r="U7" t="n">
-        <v>23.38780959752322</v>
-      </c>
-      <c r="V7" t="n">
-        <v>179.453366873065</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.437383900928793</v>
-      </c>
-      <c r="X7" t="n">
-        <v>73.36644736842106</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13345019.3498452</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>79.88962848297214</v>
+        <v>22426.35746606335</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="E8" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11111.11111111111</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.25694444444444</v>
+      </c>
+      <c r="H8" t="n">
+        <v>183.6840277777778</v>
+      </c>
+      <c r="I8" t="n">
+        <v>74.61458333333333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27645.83333333334</v>
+      </c>
+      <c r="K8" t="n">
+        <v>25.51708880787828</v>
+      </c>
+      <c r="L8" t="n">
+        <v>181.4218696995013</v>
+      </c>
+      <c r="M8" t="n">
+        <v>71.20297524113313</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13362.04273309536</v>
+      </c>
+      <c r="O8" t="n">
+        <v>25.23892195767196</v>
+      </c>
+      <c r="P8" t="n">
+        <v>180.8808466143992</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>75.11106759955445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>37888.12656641604</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>27.12222222222222</v>
+      </c>
+      <c r="H9" t="n">
+        <v>180.6472222222223</v>
+      </c>
+      <c r="I9" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40983.33333333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>24.97362128612129</v>
+      </c>
+      <c r="L9" t="n">
+        <v>178.3320741758242</v>
+      </c>
+      <c r="M9" t="n">
+        <v>73.35414122914123</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20312.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.30112893642305</v>
+      </c>
+      <c r="P9" t="n">
+        <v>181.2384432560903</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75.31978609625669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>45115.86452762924</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="D10" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="E10" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21453.7037037037</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27.24074074074074</v>
+      </c>
+      <c r="H10" t="n">
+        <v>180.7907407407407</v>
+      </c>
+      <c r="I10" t="n">
+        <v>81.54814814814814</v>
+      </c>
+      <c r="J10" t="n">
+        <v>69892.59259259258</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.08374183006536</v>
+      </c>
+      <c r="L10" t="n">
+        <v>180.7816448801743</v>
+      </c>
+      <c r="M10" t="n">
+        <v>73.84464869281045</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27300</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26.11210317460317</v>
+      </c>
+      <c r="P10" t="n">
+        <v>179.2114499389499</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>79.5505525030525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>65692.73504273505</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24.39398148148148</v>
+      </c>
+      <c r="D11" t="n">
+        <v>181.5175925925926</v>
+      </c>
+      <c r="E11" t="n">
+        <v>70.27592592592593</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12455.55555555556</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27.04629629629629</v>
+      </c>
+      <c r="H11" t="n">
+        <v>183.274074074074</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24390.74074074074</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24.58287037037037</v>
+      </c>
+      <c r="L11" t="n">
+        <v>180.4303240740741</v>
+      </c>
+      <c r="M11" t="n">
+        <v>70.67037037037038</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14829.86111111111</v>
+      </c>
+      <c r="O11" t="n">
+        <v>26.70161797408174</v>
+      </c>
+      <c r="P11" t="n">
+        <v>181.8401713825627</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>74.16784084809447</v>
+      </c>
+      <c r="R11" t="n">
+        <v>21963.39333640058</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26.81666666666666</v>
+      </c>
+      <c r="D12" t="n">
+        <v>180.675</v>
+      </c>
+      <c r="E12" t="n">
+        <v>74.75833333333334</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23313.88888888889</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="H12" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="I12" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14784.72222222223</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.91676407742584</v>
+      </c>
+      <c r="L12" t="n">
+        <v>180.2847819255908</v>
+      </c>
+      <c r="M12" t="n">
+        <v>71.91308132227249</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22426.35746606335</v>
+      </c>
+      <c r="O12" t="n">
+        <v>23.75224061284433</v>
+      </c>
+      <c r="P12" t="n">
+        <v>179.6583922097854</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>71.0564940506117</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14402.46906229878</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.39444444444445</v>
+      </c>
+      <c r="D13" t="n">
+        <v>178.8027777777778</v>
+      </c>
+      <c r="E13" t="n">
+        <v>74.925</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17638.88888888889</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="H13" t="n">
+        <v>181.900462962963</v>
+      </c>
+      <c r="I13" t="n">
+        <v>72.49768518518518</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17136.57407407407</v>
+      </c>
+      <c r="K13" t="n">
+        <v>28.38525641025641</v>
+      </c>
+      <c r="L13" t="n">
+        <v>176.6683226495726</v>
+      </c>
+      <c r="M13" t="n">
+        <v>74.43990384615385</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17029.16666666667</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25.53677931889766</v>
+      </c>
+      <c r="P13" t="n">
+        <v>181.4740254079581</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>71.60387678682874</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25.53333333333334</v>
+      </c>
+      <c r="D14" t="n">
+        <v>180.8222222222223</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>38133.33333333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="H14" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="I14" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19944.44444444445</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.54124834144184</v>
+      </c>
+      <c r="L14" t="n">
+        <v>179.3179953560371</v>
+      </c>
+      <c r="M14" t="n">
+        <v>73.63439849624059</v>
+      </c>
+      <c r="N14" t="n">
+        <v>25839.68929677134</v>
+      </c>
+      <c r="O14" t="n">
+        <v>23.97284858387799</v>
+      </c>
+      <c r="P14" t="n">
+        <v>178.7048611111111</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>71.10020424836601</v>
+      </c>
+      <c r="R14" t="n">
+        <v>19992.34749455338</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25.88333333333334</v>
+      </c>
+      <c r="D15" t="n">
+        <v>183.2333333333333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75.98333333333333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22850</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="H15" t="n">
+        <v>179</v>
+      </c>
+      <c r="I15" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="J15" t="n">
+        <v>108000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25.26522683972374</v>
+      </c>
+      <c r="L15" t="n">
+        <v>177.340294316107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>72.60500019845995</v>
+      </c>
+      <c r="N15" t="n">
+        <v>18910.85923235691</v>
+      </c>
+      <c r="O15" t="n">
+        <v>20.74249847374847</v>
+      </c>
+      <c r="P15" t="n">
+        <v>181.5099740537241</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>71.3271978021978</v>
+      </c>
+      <c r="R15" t="n">
+        <v>56073.13797313798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="E16" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="F16" t="n">
+        <v>21453.7037037037</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24.90666666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>77.15555555555555</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33453.33333333334</v>
+      </c>
+      <c r="K16" t="n">
+        <v>26.08374183006536</v>
+      </c>
+      <c r="L16" t="n">
+        <v>180.7816448801743</v>
+      </c>
+      <c r="M16" t="n">
+        <v>73.84464869281045</v>
+      </c>
+      <c r="N16" t="n">
+        <v>27300</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25.22883126934984</v>
+      </c>
+      <c r="P16" t="n">
+        <v>180.1635068062312</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>75.25220342522975</v>
+      </c>
+      <c r="R16" t="n">
+        <v>35764.86436679935</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.09814814814815</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183.5537037037037</v>
+      </c>
+      <c r="E17" t="n">
+        <v>77.88703703703703</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26707.40740740741</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="H17" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="I17" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24561.11111111111</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24.2900693763394</v>
+      </c>
+      <c r="L17" t="n">
+        <v>183.1555880808741</v>
+      </c>
+      <c r="M17" t="n">
+        <v>74.95295666702989</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21823.91205285942</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25.61547619047619</v>
+      </c>
+      <c r="P17" t="n">
+        <v>181.0169312169312</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>74.84960317460317</v>
+      </c>
+      <c r="R17" t="n">
+        <v>21078.96825396825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.12222222222222</v>
+      </c>
+      <c r="D18" t="n">
+        <v>180.6472222222223</v>
+      </c>
+      <c r="E18" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40983.33333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="I18" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11111.11111111111</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24.30112893642305</v>
+      </c>
+      <c r="L18" t="n">
+        <v>181.2384432560903</v>
+      </c>
+      <c r="M18" t="n">
+        <v>75.31978609625669</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45115.86452762924</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25.51708880787828</v>
+      </c>
+      <c r="P18" t="n">
+        <v>181.4218696995013</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>71.20297524113313</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13362.04273309536</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27.24074074074074</v>
+      </c>
+      <c r="D19" t="n">
+        <v>180.7907407407407</v>
+      </c>
+      <c r="E19" t="n">
+        <v>81.54814814814814</v>
+      </c>
+      <c r="F19" t="n">
+        <v>69892.59259259258</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25.78030303030303</v>
+      </c>
+      <c r="H19" t="n">
+        <v>182.0651515151515</v>
+      </c>
+      <c r="I19" t="n">
+        <v>85.58636363636363</v>
+      </c>
+      <c r="J19" t="n">
+        <v>204253.0303030303</v>
+      </c>
+      <c r="K19" t="n">
+        <v>26.11210317460317</v>
+      </c>
+      <c r="L19" t="n">
+        <v>179.2114499389499</v>
+      </c>
+      <c r="M19" t="n">
+        <v>79.5505525030525</v>
+      </c>
+      <c r="N19" t="n">
+        <v>65692.73504273505</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24.5632273363891</v>
+      </c>
+      <c r="P19" t="n">
+        <v>177.7088298955946</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>79.15732270180798</v>
+      </c>
+      <c r="R19" t="n">
+        <v>132018.9616755793</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.25694444444444</v>
+      </c>
+      <c r="D20" t="n">
+        <v>183.6840277777778</v>
+      </c>
+      <c r="E20" t="n">
+        <v>74.61458333333333</v>
+      </c>
+      <c r="F20" t="n">
+        <v>27645.83333333334</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>25.23892195767196</v>
+      </c>
+      <c r="L20" t="n">
+        <v>180.8808466143992</v>
+      </c>
+      <c r="M20" t="n">
+        <v>75.11106759955445</v>
+      </c>
+      <c r="N20" t="n">
+        <v>37888.12656641604</v>
+      </c>
+      <c r="O20" t="n">
+        <v>24.97362128612129</v>
+      </c>
+      <c r="P20" t="n">
+        <v>178.3320741758242</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>73.35414122914123</v>
+      </c>
+      <c r="R20" t="n">
+        <v>20312.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.900462962963</v>
+      </c>
+      <c r="E21" t="n">
+        <v>72.49768518518518</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17136.57407407407</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.75694444444444</v>
+      </c>
+      <c r="H21" t="n">
+        <v>181.9583333333334</v>
+      </c>
+      <c r="I21" t="n">
+        <v>71.80555555555556</v>
+      </c>
+      <c r="J21" t="n">
+        <v>19944.44444444445</v>
+      </c>
+      <c r="K21" t="n">
+        <v>25.53677931889766</v>
+      </c>
+      <c r="L21" t="n">
+        <v>181.4740254079581</v>
+      </c>
+      <c r="M21" t="n">
+        <v>71.60387678682874</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>23.97284858387799</v>
+      </c>
+      <c r="P21" t="n">
+        <v>178.7048611111111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>71.10020424836601</v>
+      </c>
+      <c r="R21" t="n">
+        <v>19992.34749455338</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="D22" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="E22" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11111.11111111111</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27.04629629629629</v>
+      </c>
+      <c r="H22" t="n">
+        <v>183.274074074074</v>
+      </c>
+      <c r="I22" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24390.74074074074</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25.51708880787828</v>
+      </c>
+      <c r="L22" t="n">
+        <v>181.4218696995013</v>
+      </c>
+      <c r="M22" t="n">
+        <v>71.20297524113313</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13362.04273309536</v>
+      </c>
+      <c r="O22" t="n">
+        <v>26.70161797408174</v>
+      </c>
+      <c r="P22" t="n">
+        <v>181.8401713825627</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>74.16784084809447</v>
+      </c>
+      <c r="R22" t="n">
+        <v>21963.39333640058</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.81666666666666</v>
+      </c>
+      <c r="D23" t="n">
+        <v>180.675</v>
+      </c>
+      <c r="E23" t="n">
+        <v>74.75833333333334</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23313.88888888889</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25.88333333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>183.2333333333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>75.98333333333333</v>
+      </c>
+      <c r="J23" t="n">
+        <v>22850</v>
+      </c>
+      <c r="K23" t="n">
+        <v>23.91676407742584</v>
+      </c>
+      <c r="L23" t="n">
+        <v>180.2847819255908</v>
+      </c>
+      <c r="M23" t="n">
+        <v>71.91308132227249</v>
+      </c>
+      <c r="N23" t="n">
+        <v>22426.35746606335</v>
+      </c>
+      <c r="O23" t="n">
+        <v>25.26522683972374</v>
+      </c>
+      <c r="P23" t="n">
+        <v>177.340294316107</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>72.60500019845995</v>
+      </c>
+      <c r="R23" t="n">
+        <v>18910.85923235691</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="H24" t="n">
+        <v>181.050925925926</v>
+      </c>
+      <c r="I24" t="n">
+        <v>74.54629629629629</v>
+      </c>
+      <c r="J24" t="n">
+        <v>21453.7037037037</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24.97362128612129</v>
+      </c>
+      <c r="L24" t="n">
+        <v>178.3320741758242</v>
+      </c>
+      <c r="M24" t="n">
+        <v>73.35414122914123</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20312.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>26.08374183006536</v>
+      </c>
+      <c r="P24" t="n">
+        <v>180.7816448801743</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>73.84464869281045</v>
+      </c>
+      <c r="R24" t="n">
+        <v>27300</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24.39398148148148</v>
+      </c>
+      <c r="D25" t="n">
+        <v>181.5175925925926</v>
+      </c>
+      <c r="E25" t="n">
+        <v>70.27592592592593</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12455.55555555556</v>
+      </c>
+      <c r="G25" t="n">
+        <v>28.39444444444445</v>
+      </c>
+      <c r="H25" t="n">
+        <v>178.8027777777778</v>
+      </c>
+      <c r="I25" t="n">
+        <v>74.925</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17638.88888888889</v>
+      </c>
+      <c r="K25" t="n">
+        <v>24.58287037037037</v>
+      </c>
+      <c r="L25" t="n">
+        <v>180.4303240740741</v>
+      </c>
+      <c r="M25" t="n">
+        <v>70.67037037037038</v>
+      </c>
+      <c r="N25" t="n">
+        <v>14829.86111111111</v>
+      </c>
+      <c r="O25" t="n">
+        <v>28.38525641025641</v>
+      </c>
+      <c r="P25" t="n">
+        <v>176.6683226495726</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>74.43990384615385</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17029.16666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25.78030303030303</v>
+      </c>
+      <c r="D26" t="n">
+        <v>182.0651515151515</v>
+      </c>
+      <c r="E26" t="n">
+        <v>85.58636363636363</v>
+      </c>
+      <c r="F26" t="n">
+        <v>204253.0303030303</v>
+      </c>
+      <c r="G26" t="n">
+        <v>26.25694444444444</v>
+      </c>
+      <c r="H26" t="n">
+        <v>183.6840277777778</v>
+      </c>
+      <c r="I26" t="n">
+        <v>74.61458333333333</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27645.83333333334</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24.5632273363891</v>
+      </c>
+      <c r="L26" t="n">
+        <v>177.7088298955946</v>
+      </c>
+      <c r="M26" t="n">
+        <v>79.15732270180798</v>
+      </c>
+      <c r="N26" t="n">
+        <v>132018.9616755793</v>
+      </c>
+      <c r="O26" t="n">
+        <v>25.23892195767196</v>
+      </c>
+      <c r="P26" t="n">
+        <v>180.8808466143992</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>75.11106759955445</v>
+      </c>
+      <c r="R26" t="n">
+        <v>37888.12656641604</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24.90666666666667</v>
+      </c>
+      <c r="D27" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="E27" t="n">
+        <v>77.15555555555555</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33453.33333333334</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25.09814814814815</v>
+      </c>
+      <c r="H27" t="n">
+        <v>183.5537037037037</v>
+      </c>
+      <c r="I27" t="n">
+        <v>77.88703703703703</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26707.40740740741</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25.22883126934984</v>
+      </c>
+      <c r="L27" t="n">
+        <v>180.1635068062312</v>
+      </c>
+      <c r="M27" t="n">
+        <v>75.25220342522975</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35764.86436679935</v>
+      </c>
+      <c r="O27" t="n">
+        <v>24.2900693763394</v>
+      </c>
+      <c r="P27" t="n">
+        <v>183.1555880808741</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>74.95295666702989</v>
+      </c>
+      <c r="R27" t="n">
+        <v>21823.91205285942</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>24.11805555555556</v>
+      </c>
+      <c r="D28" t="n">
+        <v>180.2847222222223</v>
+      </c>
+      <c r="E28" t="n">
+        <v>72.02083333333334</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14784.72222222223</v>
+      </c>
+      <c r="G28" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>179</v>
+      </c>
+      <c r="I28" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="J28" t="n">
+        <v>108000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23.75224061284433</v>
+      </c>
+      <c r="L28" t="n">
+        <v>179.6583922097854</v>
+      </c>
+      <c r="M28" t="n">
+        <v>71.0564940506117</v>
+      </c>
+      <c r="N28" t="n">
+        <v>14402.46906229878</v>
+      </c>
+      <c r="O28" t="n">
+        <v>20.74249847374847</v>
+      </c>
+      <c r="P28" t="n">
+        <v>181.5099740537241</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>71.3271978021978</v>
+      </c>
+      <c r="R28" t="n">
+        <v>56073.13797313798</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24.80555555555556</v>
+      </c>
+      <c r="D29" t="n">
+        <v>185.6027777777778</v>
+      </c>
+      <c r="E29" t="n">
+        <v>74.93611111111112</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24561.11111111111</v>
+      </c>
+      <c r="G29" t="n">
+        <v>27.12222222222222</v>
+      </c>
+      <c r="H29" t="n">
+        <v>180.6472222222223</v>
+      </c>
+      <c r="I29" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>40983.33333333333</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25.61547619047619</v>
+      </c>
+      <c r="L29" t="n">
+        <v>181.0169312169312</v>
+      </c>
+      <c r="M29" t="n">
+        <v>74.84960317460317</v>
+      </c>
+      <c r="N29" t="n">
+        <v>21078.96825396825</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24.30112893642305</v>
+      </c>
+      <c r="P29" t="n">
+        <v>181.2384432560903</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>75.31978609625669</v>
+      </c>
+      <c r="R29" t="n">
+        <v>45115.86452762924</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>25.53333333333334</v>
+      </c>
+      <c r="D30" t="n">
+        <v>180.8222222222223</v>
+      </c>
+      <c r="E30" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38133.33333333334</v>
+      </c>
+      <c r="G30" t="n">
+        <v>27.24074074074074</v>
+      </c>
+      <c r="H30" t="n">
+        <v>180.7907407407407</v>
+      </c>
+      <c r="I30" t="n">
+        <v>81.54814814814814</v>
+      </c>
+      <c r="J30" t="n">
+        <v>69892.59259259258</v>
+      </c>
+      <c r="K30" t="n">
+        <v>23.54124834144184</v>
+      </c>
+      <c r="L30" t="n">
+        <v>179.3179953560371</v>
+      </c>
+      <c r="M30" t="n">
+        <v>73.63439849624059</v>
+      </c>
+      <c r="N30" t="n">
+        <v>25839.68929677134</v>
+      </c>
+      <c r="O30" t="n">
+        <v>26.11210317460317</v>
+      </c>
+      <c r="P30" t="n">
+        <v>179.2114499389499</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>79.5505525030525</v>
+      </c>
+      <c r="R30" t="n">
+        <v>65692.73504273505</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,523 +518,283 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.56984126984127</v>
+        <v>26.76388888888889</v>
       </c>
       <c r="D2" t="n">
-        <v>181.336507936508</v>
+        <v>180.8993055555556</v>
       </c>
       <c r="E2" t="n">
-        <v>70.39722222222223</v>
+        <v>74.90972222222223</v>
       </c>
       <c r="F2" t="n">
-        <v>12301.19047619048</v>
+        <v>24645.83333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>27.03968253968254</v>
+        <v>24.75555555555556</v>
       </c>
       <c r="H2" t="n">
-        <v>183.4349206349206</v>
+        <v>182.7722222222222</v>
       </c>
       <c r="I2" t="n">
-        <v>75.64285714285714</v>
+        <v>77.16296296296296</v>
       </c>
       <c r="J2" t="n">
-        <v>24192.06349206349</v>
+        <v>32544.44444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>24.55515873015873</v>
+        <v>26.11573475544063</v>
       </c>
       <c r="L2" t="n">
-        <v>180.4720238095238</v>
+        <v>180.5600912159736</v>
       </c>
       <c r="M2" t="n">
-        <v>70.66190476190476</v>
+        <v>73.70200657185951</v>
       </c>
       <c r="N2" t="n">
-        <v>15854.16666666667</v>
+        <v>25417.30769230769</v>
       </c>
       <c r="O2" t="n">
-        <v>26.50614873968911</v>
+        <v>25.55977745165052</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6725278517204</v>
+        <v>180.3219668728736</v>
       </c>
       <c r="Q2" t="n">
-        <v>74.07243501265241</v>
+        <v>75.33305748136574</v>
       </c>
       <c r="R2" t="n">
-        <v>21796.00381215287</v>
+        <v>36408.84478193191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.76388888888889</v>
+        <v>25.09814814814815</v>
       </c>
       <c r="D3" t="n">
-        <v>180.7291666666667</v>
+        <v>183.5537037037037</v>
       </c>
       <c r="E3" t="n">
-        <v>74.81944444444444</v>
+        <v>77.88703703703703</v>
       </c>
       <c r="F3" t="n">
-        <v>22990.74074074074</v>
+        <v>26707.40740740741</v>
       </c>
       <c r="G3" t="n">
-        <v>23.74537037037037</v>
+        <v>25.20444444444444</v>
       </c>
       <c r="H3" t="n">
-        <v>180.5601851851852</v>
+        <v>185.2222222222222</v>
       </c>
       <c r="I3" t="n">
-        <v>71.49537037037037</v>
+        <v>75.20888888888889</v>
       </c>
       <c r="J3" t="n">
-        <v>13930.55555555556</v>
+        <v>24668.88888888889</v>
       </c>
       <c r="K3" t="n">
-        <v>24.24294063779358</v>
+        <v>24.2900693763394</v>
       </c>
       <c r="L3" t="n">
-        <v>180.320289269554</v>
+        <v>183.1555880808741</v>
       </c>
       <c r="M3" t="n">
-        <v>72.3635935143288</v>
+        <v>74.95295666702989</v>
       </c>
       <c r="N3" t="n">
-        <v>22426.35746606335</v>
+        <v>21823.91205285942</v>
       </c>
       <c r="O3" t="n">
-        <v>23.97250876058925</v>
+        <v>25.39489795918368</v>
       </c>
       <c r="P3" t="n">
-        <v>179.6231597092278</v>
+        <v>180.8614512471655</v>
       </c>
       <c r="Q3" t="n">
-        <v>71.19128061481003</v>
+        <v>74.70782312925169</v>
       </c>
       <c r="R3" t="n">
-        <v>14639.09112902921</v>
+        <v>21332.99319727891</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>28.27314814814815</v>
+        <v>27.12222222222222</v>
       </c>
       <c r="D4" t="n">
-        <v>179.0208333333333</v>
+        <v>180.6472222222223</v>
       </c>
       <c r="E4" t="n">
-        <v>74.77083333333333</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>17254.62962962963</v>
+        <v>40983.33333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>26.375</v>
+        <v>25.27083333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>181.900462962963</v>
+        <v>183.2777777777777</v>
       </c>
       <c r="I4" t="n">
-        <v>72.49768518518518</v>
+        <v>72.24305555555556</v>
       </c>
       <c r="J4" t="n">
-        <v>17136.57407407407</v>
+        <v>13180.55555555555</v>
       </c>
       <c r="K4" t="n">
-        <v>28.33021978021978</v>
+        <v>24.57646427789617</v>
       </c>
       <c r="L4" t="n">
-        <v>176.4409798534798</v>
+        <v>180.9865760099894</v>
       </c>
       <c r="M4" t="n">
-        <v>74.49793956043956</v>
+        <v>74.67343743717583</v>
       </c>
       <c r="N4" t="n">
-        <v>17200.82417582417</v>
+        <v>45115.86452762924</v>
       </c>
       <c r="O4" t="n">
-        <v>25.53677931889766</v>
+        <v>25.61464754960995</v>
       </c>
       <c r="P4" t="n">
-        <v>181.4740254079581</v>
+        <v>181.7544597424296</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.60387678682874</v>
+        <v>71.30969306382841</v>
       </c>
       <c r="R4" t="n">
-        <v>12000</v>
+        <v>13731.75091408174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53333333333334</v>
+        <v>27.15873015873016</v>
       </c>
       <c r="D5" t="n">
-        <v>180.8222222222223</v>
+        <v>180.9952380952381</v>
       </c>
       <c r="E5" t="n">
-        <v>78.59999999999999</v>
+        <v>81.54920634920634</v>
       </c>
       <c r="F5" t="n">
-        <v>38133.33333333334</v>
+        <v>69606.34920634922</v>
       </c>
       <c r="G5" t="n">
-        <v>22.75555555555555</v>
+        <v>25.59090909090909</v>
       </c>
       <c r="H5" t="n">
-        <v>181.9416666666667</v>
+        <v>182.2766233766234</v>
       </c>
       <c r="I5" t="n">
-        <v>71.56944444444444</v>
+        <v>85.43766233766235</v>
       </c>
       <c r="J5" t="n">
-        <v>19955.55555555555</v>
+        <v>204307.7922077922</v>
       </c>
       <c r="K5" t="n">
-        <v>23.54124834144184</v>
+        <v>26.07568027210884</v>
       </c>
       <c r="L5" t="n">
-        <v>179.3179953560371</v>
+        <v>179.0247802197802</v>
       </c>
       <c r="M5" t="n">
-        <v>73.63439849624059</v>
+        <v>79.58754840397697</v>
       </c>
       <c r="N5" t="n">
-        <v>25839.68929677134</v>
+        <v>66471.32391418106</v>
       </c>
       <c r="O5" t="n">
-        <v>23.96312191543284</v>
+        <v>24.71490914547637</v>
       </c>
       <c r="P5" t="n">
-        <v>178.7402210884354</v>
+        <v>177.9647113390811</v>
       </c>
       <c r="Q5" t="n">
-        <v>71.23554921968788</v>
+        <v>79.38484803012113</v>
       </c>
       <c r="R5" t="n">
-        <v>20469.63118580766</v>
+        <v>132918.038579068</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.88333333333334</v>
+        <v>26.25</v>
       </c>
       <c r="D6" t="n">
-        <v>183.2333333333333</v>
+        <v>183.6361111111111</v>
       </c>
       <c r="E6" t="n">
-        <v>75.98333333333333</v>
+        <v>74.69166666666666</v>
       </c>
       <c r="F6" t="n">
-        <v>22850</v>
-      </c>
-      <c r="G6" t="n">
-        <v>23.875</v>
-      </c>
-      <c r="H6" t="n">
-        <v>179</v>
-      </c>
-      <c r="I6" t="n">
-        <v>79.125</v>
-      </c>
-      <c r="J6" t="n">
-        <v>108000</v>
-      </c>
+        <v>26250</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>25.30352776738226</v>
+        <v>25.31363378684807</v>
       </c>
       <c r="L6" t="n">
-        <v>177.4535856042822</v>
+        <v>181.0339229483967</v>
       </c>
       <c r="M6" t="n">
-        <v>72.81380969391805</v>
+        <v>74.90472460914191</v>
       </c>
       <c r="N6" t="n">
-        <v>19104.54600868688</v>
+        <v>37888.12656641604</v>
       </c>
       <c r="O6" t="n">
-        <v>20.5649986917844</v>
+        <v>25.18747370743169</v>
       </c>
       <c r="P6" t="n">
-        <v>181.4575287807431</v>
+        <v>178.2762316465048</v>
       </c>
       <c r="Q6" t="n">
-        <v>71.72943485086343</v>
+        <v>73.40438996111266</v>
       </c>
       <c r="R6" t="n">
-        <v>59858.60805860806</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26.76388888888889</v>
-      </c>
-      <c r="D7" t="n">
-        <v>180.8993055555556</v>
-      </c>
-      <c r="E7" t="n">
-        <v>74.90972222222223</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24645.83333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24.75555555555556</v>
-      </c>
-      <c r="H7" t="n">
-        <v>182.7722222222222</v>
-      </c>
-      <c r="I7" t="n">
-        <v>77.16296296296296</v>
-      </c>
-      <c r="J7" t="n">
-        <v>32544.44444444445</v>
-      </c>
-      <c r="K7" t="n">
-        <v>26.11573475544063</v>
-      </c>
-      <c r="L7" t="n">
-        <v>180.5600912159736</v>
-      </c>
-      <c r="M7" t="n">
-        <v>73.70200657185951</v>
-      </c>
-      <c r="N7" t="n">
-        <v>25417.30769230769</v>
-      </c>
-      <c r="O7" t="n">
-        <v>25.55977745165052</v>
-      </c>
-      <c r="P7" t="n">
-        <v>180.3219668728736</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>75.33305748136574</v>
-      </c>
-      <c r="R7" t="n">
-        <v>36408.84478193191</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>25.09814814814815</v>
-      </c>
-      <c r="D8" t="n">
-        <v>183.5537037037037</v>
-      </c>
-      <c r="E8" t="n">
-        <v>77.88703703703703</v>
-      </c>
-      <c r="F8" t="n">
-        <v>26707.40740740741</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25.20444444444444</v>
-      </c>
-      <c r="H8" t="n">
-        <v>185.2222222222222</v>
-      </c>
-      <c r="I8" t="n">
-        <v>75.20888888888889</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24668.88888888889</v>
-      </c>
-      <c r="K8" t="n">
-        <v>24.2900693763394</v>
-      </c>
-      <c r="L8" t="n">
-        <v>183.1555880808741</v>
-      </c>
-      <c r="M8" t="n">
-        <v>74.95295666702989</v>
-      </c>
-      <c r="N8" t="n">
-        <v>21823.91205285942</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25.39489795918368</v>
-      </c>
-      <c r="P8" t="n">
-        <v>180.8614512471655</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>74.70782312925169</v>
-      </c>
-      <c r="R8" t="n">
-        <v>21332.99319727891</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.12222222222222</v>
-      </c>
-      <c r="D9" t="n">
-        <v>180.6472222222223</v>
-      </c>
-      <c r="E9" t="n">
-        <v>77.15000000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>40983.33333333333</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.27083333333334</v>
-      </c>
-      <c r="H9" t="n">
-        <v>183.2777777777777</v>
-      </c>
-      <c r="I9" t="n">
-        <v>72.24305555555556</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13180.55555555555</v>
-      </c>
-      <c r="K9" t="n">
-        <v>24.57646427789617</v>
-      </c>
-      <c r="L9" t="n">
-        <v>180.9865760099894</v>
-      </c>
-      <c r="M9" t="n">
-        <v>74.67343743717583</v>
-      </c>
-      <c r="N9" t="n">
-        <v>45115.86452762924</v>
-      </c>
-      <c r="O9" t="n">
-        <v>25.61464754960995</v>
-      </c>
-      <c r="P9" t="n">
-        <v>181.7544597424296</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>71.30969306382841</v>
-      </c>
-      <c r="R9" t="n">
-        <v>13731.75091408174</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>27.15873015873016</v>
-      </c>
-      <c r="D10" t="n">
-        <v>180.9952380952381</v>
-      </c>
-      <c r="E10" t="n">
-        <v>81.54920634920634</v>
-      </c>
-      <c r="F10" t="n">
-        <v>69606.34920634922</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25.59090909090909</v>
-      </c>
-      <c r="H10" t="n">
-        <v>182.2766233766234</v>
-      </c>
-      <c r="I10" t="n">
-        <v>85.43766233766235</v>
-      </c>
-      <c r="J10" t="n">
-        <v>204307.7922077922</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.07568027210884</v>
-      </c>
-      <c r="L10" t="n">
-        <v>179.0247802197802</v>
-      </c>
-      <c r="M10" t="n">
-        <v>79.58754840397697</v>
-      </c>
-      <c r="N10" t="n">
-        <v>66471.32391418106</v>
-      </c>
-      <c r="O10" t="n">
-        <v>24.71490914547637</v>
-      </c>
-      <c r="P10" t="n">
-        <v>177.9647113390811</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>79.38484803012113</v>
-      </c>
-      <c r="R10" t="n">
-        <v>132918.038579068</v>
+        <v>19967.64705882353</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,345 +456,1289 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>26.76388888888889</v>
-      </c>
-      <c r="D2" t="n">
-        <v>180.8993055555556</v>
-      </c>
-      <c r="E2" t="n">
-        <v>74.90972222222223</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24645.83333333333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.75555555555556</v>
-      </c>
-      <c r="H2" t="n">
-        <v>182.7722222222222</v>
-      </c>
-      <c r="I2" t="n">
-        <v>77.16296296296296</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>32544.44444444445</v>
+        <v>23.97534722222222</v>
       </c>
       <c r="K2" t="n">
-        <v>26.11573475544063</v>
+        <v>182.2385416666667</v>
       </c>
       <c r="L2" t="n">
-        <v>180.5600912159736</v>
+        <v>76.26041666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>73.70200657185951</v>
+        <v>35870.13888888889</v>
       </c>
       <c r="N2" t="n">
-        <v>25417.30769230769</v>
+        <v>17745034.72222222</v>
       </c>
       <c r="O2" t="n">
-        <v>25.55977745165052</v>
+        <v>81.47638888888889</v>
       </c>
       <c r="P2" t="n">
-        <v>180.3219668728736</v>
+        <v>1.252777777777778</v>
       </c>
       <c r="Q2" t="n">
-        <v>75.33305748136574</v>
+        <v>26.76504211249277</v>
       </c>
       <c r="R2" t="n">
-        <v>36408.84478193191</v>
+        <v>181.3894263904955</v>
+      </c>
+      <c r="S2" t="n">
+        <v>70.97871541835357</v>
+      </c>
+      <c r="T2" t="n">
+        <v>27122.54855889724</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4440124.81624735</v>
+      </c>
+      <c r="V2" t="n">
+        <v>74.31737908473106</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05376873674571</v>
+      </c>
+      <c r="X2" t="n">
+        <v>24.30645695678591</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>178.7062651894889</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>72.23930422647527</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>27348.71981089086</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7763378.783132073</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>78.49287660438975</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.03696314650262</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09814814814815</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="D3" t="n">
-        <v>183.5537037037037</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="E3" t="n">
-        <v>77.88703703703703</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>26707.40740740741</v>
+        <v>21666.66666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>25.20444444444444</v>
+        <v>4822222.222222222</v>
       </c>
       <c r="H3" t="n">
-        <v>185.2222222222222</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="I3" t="n">
-        <v>75.20888888888889</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>24668.88888888889</v>
+        <v>27.96875</v>
       </c>
       <c r="K3" t="n">
-        <v>24.2900693763394</v>
+        <v>184.5</v>
       </c>
       <c r="L3" t="n">
-        <v>183.1555880808741</v>
+        <v>76.6875</v>
       </c>
       <c r="M3" t="n">
-        <v>74.95295666702989</v>
+        <v>31031.25</v>
       </c>
       <c r="N3" t="n">
-        <v>21823.91205285942</v>
+        <v>12071875</v>
       </c>
       <c r="O3" t="n">
-        <v>25.39489795918368</v>
+        <v>78.8125</v>
       </c>
       <c r="P3" t="n">
-        <v>180.8614512471655</v>
+        <v>1.46875</v>
       </c>
       <c r="Q3" t="n">
-        <v>74.70782312925169</v>
+        <v>26.34396603192559</v>
       </c>
       <c r="R3" t="n">
-        <v>21332.99319727891</v>
+        <v>180.7362485859728</v>
+      </c>
+      <c r="S3" t="n">
+        <v>71.24644529286074</v>
+      </c>
+      <c r="T3" t="n">
+        <v>18693.38392408245</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3449663.382981398</v>
+      </c>
+      <c r="V3" t="n">
+        <v>75.50324047888387</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>26.67126796814297</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>181.5024341977467</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>74.91635708041957</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>27472.70784770785</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9044196.775446774</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>78.15489631895883</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.263039044289044</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.12222222222222</v>
+        <v>27.66076388888889</v>
       </c>
       <c r="D4" t="n">
-        <v>180.6472222222223</v>
+        <v>181.4784722222222</v>
       </c>
       <c r="E4" t="n">
-        <v>77.15000000000001</v>
+        <v>75.20555555555555</v>
       </c>
       <c r="F4" t="n">
-        <v>40983.33333333333</v>
+        <v>28269.44444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>25.27083333333334</v>
+        <v>8076736.111111111</v>
       </c>
       <c r="H4" t="n">
-        <v>183.2777777777777</v>
+        <v>77.42743055555556</v>
       </c>
       <c r="I4" t="n">
-        <v>72.24305555555556</v>
+        <v>1.330208333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>13180.55555555555</v>
+        <v>26.89583333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>24.57646427789617</v>
+        <v>182.7870370370371</v>
       </c>
       <c r="L4" t="n">
-        <v>180.9865760099894</v>
+        <v>76.32407407407408</v>
       </c>
       <c r="M4" t="n">
-        <v>74.67343743717583</v>
+        <v>31768.51851851852</v>
       </c>
       <c r="N4" t="n">
-        <v>45115.86452762924</v>
+        <v>11187731.48148148</v>
       </c>
       <c r="O4" t="n">
-        <v>25.61464754960995</v>
+        <v>79.80092592592592</v>
       </c>
       <c r="P4" t="n">
-        <v>181.7544597424296</v>
+        <v>1.1875</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.30969306382841</v>
+        <v>25.26260369532428</v>
       </c>
       <c r="R4" t="n">
-        <v>13731.75091408174</v>
+        <v>180.5988051470588</v>
+      </c>
+      <c r="S4" t="n">
+        <v>72.33604826546002</v>
+      </c>
+      <c r="T4" t="n">
+        <v>24108.35595776773</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6700449.542797888</v>
+      </c>
+      <c r="V4" t="n">
+        <v>76.73619202488688</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.123265460030166</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26.73413812387303</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>178.3493025727498</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>72.87628722541648</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>27040.84275663707</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6413604.234710079</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>76.67258456520261</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.154596297020833</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27.15873015873016</v>
+        <v>28.075</v>
       </c>
       <c r="D5" t="n">
-        <v>180.9952380952381</v>
+        <v>180</v>
       </c>
       <c r="E5" t="n">
-        <v>81.54920634920634</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>69606.34920634922</v>
+        <v>20475</v>
       </c>
       <c r="G5" t="n">
-        <v>25.59090909090909</v>
+        <v>7222500</v>
       </c>
       <c r="H5" t="n">
-        <v>182.2766233766234</v>
+        <v>77.625</v>
       </c>
       <c r="I5" t="n">
-        <v>85.43766233766235</v>
+        <v>1.175</v>
       </c>
       <c r="J5" t="n">
-        <v>204307.7922077922</v>
+        <v>27.28968253968254</v>
       </c>
       <c r="K5" t="n">
-        <v>26.07568027210884</v>
+        <v>181.015873015873</v>
       </c>
       <c r="L5" t="n">
-        <v>179.0247802197802</v>
+        <v>73.02579365079364</v>
       </c>
       <c r="M5" t="n">
-        <v>79.58754840397697</v>
+        <v>22031.74603174603</v>
       </c>
       <c r="N5" t="n">
-        <v>66471.32391418106</v>
+        <v>6349255.952380952</v>
       </c>
       <c r="O5" t="n">
-        <v>24.71490914547637</v>
+        <v>77.0515873015873</v>
       </c>
       <c r="P5" t="n">
-        <v>177.9647113390811</v>
+        <v>1.359126984126984</v>
       </c>
       <c r="Q5" t="n">
-        <v>79.38484803012113</v>
+        <v>26.78220244238046</v>
       </c>
       <c r="R5" t="n">
-        <v>132918.038579068</v>
+        <v>178.2452114508084</v>
+      </c>
+      <c r="S5" t="n">
+        <v>72.75551094341245</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20442.78121775026</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5133576.818885449</v>
+      </c>
+      <c r="V5" t="n">
+        <v>75.10812371001032</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.102306394048848</v>
+      </c>
+      <c r="X5" t="n">
+        <v>26.46784491308485</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>180.0252243241794</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>71.42522457547612</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>21470.21024318819</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5829384.12206988</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>75.89828640786457</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.29378405070162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>26.25</v>
+        <v>26.73253968253968</v>
       </c>
       <c r="D6" t="n">
-        <v>183.6361111111111</v>
+        <v>179.797619047619</v>
       </c>
       <c r="E6" t="n">
-        <v>74.69166666666666</v>
+        <v>72.21150793650794</v>
       </c>
       <c r="F6" t="n">
-        <v>26250</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>19825.39682539683</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3350952.380952381</v>
+      </c>
+      <c r="H6" t="n">
+        <v>74.94484126984126</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.048015873015873</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.55277777777778</v>
+      </c>
       <c r="K6" t="n">
-        <v>25.31363378684807</v>
+        <v>180.3888888888889</v>
       </c>
       <c r="L6" t="n">
-        <v>181.0339229483967</v>
+        <v>74.38055555555556</v>
       </c>
       <c r="M6" t="n">
-        <v>74.90472460914191</v>
+        <v>19044.44444444445</v>
       </c>
       <c r="N6" t="n">
-        <v>37888.12656641604</v>
+        <v>5870555.555555556</v>
       </c>
       <c r="O6" t="n">
-        <v>25.18747370743169</v>
+        <v>76.45277777777778</v>
       </c>
       <c r="P6" t="n">
-        <v>178.2762316465048</v>
+        <v>1.377777777777777</v>
       </c>
       <c r="Q6" t="n">
-        <v>73.40438996111266</v>
+        <v>26.64900210084033</v>
       </c>
       <c r="R6" t="n">
-        <v>19967.64705882353</v>
+        <v>179.6858375886239</v>
+      </c>
+      <c r="S6" t="n">
+        <v>71.44100181938805</v>
+      </c>
+      <c r="T6" t="n">
+        <v>18484.9173401418</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3172305.349771488</v>
+      </c>
+      <c r="V6" t="n">
+        <v>74.77833110516934</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.054347600284133</v>
+      </c>
+      <c r="X6" t="n">
+        <v>29.2390611946533</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>177.8287045739348</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>74.8735223475355</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>20462.65272556391</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7268447.942773601</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>76.3515063700919</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.497156954887218</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.44652777777778</v>
+      </c>
+      <c r="D7" t="n">
+        <v>183.3267361111111</v>
+      </c>
+      <c r="E7" t="n">
+        <v>85.86527777777778</v>
+      </c>
+      <c r="F7" t="n">
+        <v>231505.2083333333</v>
+      </c>
+      <c r="G7" t="n">
+        <v>69389062.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>88.31666666666666</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.572222222222222</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="M7" t="n">
+        <v>36000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>80</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25.76346153846154</v>
+      </c>
+      <c r="R7" t="n">
+        <v>180.0412259615385</v>
+      </c>
+      <c r="S7" t="n">
+        <v>79.77235576923076</v>
+      </c>
+      <c r="T7" t="n">
+        <v>135960.750534188</v>
+      </c>
+      <c r="U7" t="n">
+        <v>38462514.69017094</v>
+      </c>
+      <c r="V7" t="n">
+        <v>85.16121794871793</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.226322115384616</v>
+      </c>
+      <c r="X7" t="n">
+        <v>25.96385526882818</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>180.808568508375</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>74.3223437553159</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>32067.67484321664</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8627637.036596015</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>79.3893702015219</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.519061865636943</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.26825396825397</v>
+      </c>
+      <c r="D8" t="n">
+        <v>181.436507936508</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79.14603174603174</v>
+      </c>
+      <c r="F8" t="n">
+        <v>41174.60317460318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20080158.73015873</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82.26825396825396</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.84920634920635</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.72468434343434</v>
+      </c>
+      <c r="K8" t="n">
+        <v>183.3688446969697</v>
+      </c>
+      <c r="L8" t="n">
+        <v>78.49062500000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33155.17676767677</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22844090.90909091</v>
+      </c>
+      <c r="O8" t="n">
+        <v>81.8246212121212</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.826988636363637</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>26.7350118835413</v>
+      </c>
+      <c r="R8" t="n">
+        <v>180.2538101604278</v>
+      </c>
+      <c r="S8" t="n">
+        <v>74.9854055258467</v>
+      </c>
+      <c r="T8" t="n">
+        <v>32937.76737967914</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10496012.32917409</v>
+      </c>
+      <c r="V8" t="n">
+        <v>79.70854129530599</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.400846702317291</v>
+      </c>
+      <c r="X8" t="n">
+        <v>26.69656432748538</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>182.8024488304094</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>75.9857273391813</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>30357.60233918129</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16591536.91520468</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>79.78406432748537</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.515369152046783</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25.83611111111111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>72.94722222222222</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22988.88888888889</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4515000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>76.54166666666666</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.2797619047619</v>
+      </c>
+      <c r="K9" t="n">
+        <v>180.1746031746032</v>
+      </c>
+      <c r="L9" t="n">
+        <v>81.13690476190474</v>
+      </c>
+      <c r="M9" t="n">
+        <v>119696.4285714286</v>
+      </c>
+      <c r="N9" t="n">
+        <v>40428968.25396825</v>
+      </c>
+      <c r="O9" t="n">
+        <v>86.67460317460316</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.811507936507937</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>24.91713564213564</v>
+      </c>
+      <c r="R9" t="n">
+        <v>179.9522974101922</v>
+      </c>
+      <c r="S9" t="n">
+        <v>72.23020619731146</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24307.98017771702</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4583785.363028783</v>
+      </c>
+      <c r="V9" t="n">
+        <v>76.85129205589732</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03056884635832</v>
+      </c>
+      <c r="X9" t="n">
+        <v>21.06835412394623</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>181.4228587567403</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>71.01955029619504</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>62807.47512721198</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18113949.67057796</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>81.01018217893217</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.577206273258905</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>24.76032717282717</v>
+      </c>
+      <c r="R10" t="n">
+        <v>181.8981018981019</v>
+      </c>
+      <c r="S10" t="n">
+        <v>73.47370129870129</v>
+      </c>
+      <c r="T10" t="n">
+        <v>25885.41874791875</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9693582.042957043</v>
+      </c>
+      <c r="V10" t="n">
+        <v>79.45553300865801</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.254749417249418</v>
+      </c>
+      <c r="X10" t="n">
+        <v>22.69581095987346</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>182.1355425824175</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>71.77991331585082</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>22746.76157176158</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7155141.291000666</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>80.664575008325</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.173952089577089</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="D11" t="n">
+        <v>180.9388888888889</v>
+      </c>
+      <c r="E11" t="n">
+        <v>78.37222222222222</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39994.44444444444</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22137500</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.76388888888889</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.33928571428572</v>
+      </c>
+      <c r="K11" t="n">
+        <v>181.6535714285715</v>
+      </c>
+      <c r="L11" t="n">
+        <v>82.49325396825397</v>
+      </c>
+      <c r="M11" t="n">
+        <v>81902.77777777778</v>
+      </c>
+      <c r="N11" t="n">
+        <v>31479365.07936508</v>
+      </c>
+      <c r="O11" t="n">
+        <v>83.94484126984128</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.840079365079365</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24.03705861132332</v>
+      </c>
+      <c r="R11" t="n">
+        <v>181.1414770074696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>71.52473368135134</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29130.25077455225</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11242087.8692386</v>
+      </c>
+      <c r="V11" t="n">
+        <v>78.35653860028859</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.530990578049402</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27.66172683747412</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>178.4687976425748</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>79.31899674148316</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>72452.39006916995</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>23741599.43769998</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>82.05085286090721</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.300772868435912</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.83611111111111</v>
+      </c>
+      <c r="D12" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>72.94722222222222</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22988.88888888889</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4515000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.54166666666666</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26.73253968253968</v>
+      </c>
+      <c r="K12" t="n">
+        <v>179.797619047619</v>
+      </c>
+      <c r="L12" t="n">
+        <v>72.21150793650794</v>
+      </c>
+      <c r="M12" t="n">
+        <v>19825.39682539683</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3350952.380952381</v>
+      </c>
+      <c r="O12" t="n">
+        <v>74.94484126984126</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.048015873015873</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24.91713564213564</v>
+      </c>
+      <c r="R12" t="n">
+        <v>179.9522974101922</v>
+      </c>
+      <c r="S12" t="n">
+        <v>72.23020619731146</v>
+      </c>
+      <c r="T12" t="n">
+        <v>24307.98017771702</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4583785.363028783</v>
+      </c>
+      <c r="V12" t="n">
+        <v>76.85129205589732</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03056884635832</v>
+      </c>
+      <c r="X12" t="n">
+        <v>26.64900210084033</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>179.6858375886239</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>71.44100181938805</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>18484.9173401418</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3172305.349771488</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>74.77833110516934</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.054347600284133</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.72468434343434</v>
+      </c>
+      <c r="D13" t="n">
+        <v>183.3688446969697</v>
+      </c>
+      <c r="E13" t="n">
+        <v>78.49062500000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33155.17676767677</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22844090.90909091</v>
+      </c>
+      <c r="H13" t="n">
+        <v>81.8246212121212</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.826988636363637</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="K13" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="L13" t="n">
+        <v>73</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21666.66666666667</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4822222.222222222</v>
+      </c>
+      <c r="O13" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26.69656432748538</v>
+      </c>
+      <c r="R13" t="n">
+        <v>182.8024488304094</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75.9857273391813</v>
+      </c>
+      <c r="T13" t="n">
+        <v>30357.60233918129</v>
+      </c>
+      <c r="U13" t="n">
+        <v>16591536.91520468</v>
+      </c>
+      <c r="V13" t="n">
+        <v>79.78406432748537</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.515369152046783</v>
+      </c>
+      <c r="X13" t="n">
+        <v>26.34396603192559</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>180.7362485859728</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>71.24644529286074</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>18693.38392408245</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3449663.382981398</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>75.50324047888387</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.89583333333333</v>
+      </c>
+      <c r="D14" t="n">
+        <v>182.7870370370371</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76.32407407407408</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31768.51851851852</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11187731.48148148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.80092592592592</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>26.73413812387303</v>
+      </c>
+      <c r="R14" t="n">
+        <v>178.3493025727498</v>
+      </c>
+      <c r="S14" t="n">
+        <v>72.87628722541648</v>
+      </c>
+      <c r="T14" t="n">
+        <v>27040.84275663707</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6413604.234710079</v>
+      </c>
+      <c r="V14" t="n">
+        <v>76.67258456520261</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.154596297020833</v>
+      </c>
+      <c r="X14" t="n">
+        <v>22.69581095987346</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>182.1355425824175</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>71.77991331585082</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>22746.76157176158</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7155141.291000666</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>80.664575008325</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.173952089577089</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -578,1118 +578,1104 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>26.26825396825397</v>
+      </c>
+      <c r="D2" t="n">
+        <v>181.436507936508</v>
+      </c>
+      <c r="E2" t="n">
+        <v>79.14603174603174</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41174.60317460318</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20080158.73015873</v>
+      </c>
+      <c r="H2" t="n">
+        <v>82.26825396825396</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.84920634920635</v>
+      </c>
       <c r="J2" t="n">
-        <v>23.97534722222222</v>
+        <v>26.72468434343434</v>
       </c>
       <c r="K2" t="n">
-        <v>182.2385416666667</v>
+        <v>183.3688446969697</v>
       </c>
       <c r="L2" t="n">
-        <v>76.26041666666666</v>
+        <v>78.49062500000001</v>
       </c>
       <c r="M2" t="n">
-        <v>35870.13888888889</v>
+        <v>33155.17676767677</v>
       </c>
       <c r="N2" t="n">
-        <v>17745034.72222222</v>
+        <v>22844090.90909091</v>
       </c>
       <c r="O2" t="n">
-        <v>81.47638888888889</v>
+        <v>81.8246212121212</v>
       </c>
       <c r="P2" t="n">
-        <v>1.252777777777778</v>
+        <v>1.826988636363637</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.76504211249277</v>
+        <v>26.7350118835413</v>
       </c>
       <c r="R2" t="n">
-        <v>181.3894263904955</v>
+        <v>180.2538101604278</v>
       </c>
       <c r="S2" t="n">
-        <v>70.97871541835357</v>
+        <v>74.9854055258467</v>
       </c>
       <c r="T2" t="n">
-        <v>27122.54855889724</v>
+        <v>32937.76737967914</v>
       </c>
       <c r="U2" t="n">
-        <v>4440124.81624735</v>
+        <v>10496012.32917409</v>
       </c>
       <c r="V2" t="n">
-        <v>74.31737908473106</v>
+        <v>79.70854129530599</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05376873674571</v>
+        <v>1.400846702317291</v>
       </c>
       <c r="X2" t="n">
-        <v>24.30645695678591</v>
+        <v>26.69656432748538</v>
       </c>
       <c r="Y2" t="n">
-        <v>178.7062651894889</v>
+        <v>182.8024488304094</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.23930422647527</v>
+        <v>75.9857273391813</v>
       </c>
       <c r="AA2" t="n">
-        <v>27348.71981089086</v>
+        <v>30357.60233918129</v>
       </c>
       <c r="AB2" t="n">
-        <v>7763378.783132073</v>
+        <v>16591536.91520468</v>
       </c>
       <c r="AC2" t="n">
-        <v>78.49287660438975</v>
+        <v>79.78406432748537</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.03696314650262</v>
+        <v>1.515369152046783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.55555555555556</v>
+        <v>25.83611111111111</v>
       </c>
       <c r="D3" t="n">
-        <v>182.1111111111111</v>
+        <v>181.75</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>72.94722222222222</v>
       </c>
       <c r="F3" t="n">
-        <v>21666.66666666667</v>
+        <v>22988.88888888889</v>
       </c>
       <c r="G3" t="n">
-        <v>4822222.222222222</v>
+        <v>4515000</v>
       </c>
       <c r="H3" t="n">
-        <v>76.55555555555556</v>
+        <v>76.54166666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="J3" t="n">
-        <v>27.96875</v>
+        <v>25.2797619047619</v>
       </c>
       <c r="K3" t="n">
-        <v>184.5</v>
+        <v>180.1746031746032</v>
       </c>
       <c r="L3" t="n">
-        <v>76.6875</v>
+        <v>81.13690476190474</v>
       </c>
       <c r="M3" t="n">
-        <v>31031.25</v>
+        <v>119696.4285714286</v>
       </c>
       <c r="N3" t="n">
-        <v>12071875</v>
+        <v>40428968.25396825</v>
       </c>
       <c r="O3" t="n">
-        <v>78.8125</v>
+        <v>86.67460317460316</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46875</v>
+        <v>2.811507936507937</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.34396603192559</v>
+        <v>24.91713564213564</v>
       </c>
       <c r="R3" t="n">
-        <v>180.7362485859728</v>
+        <v>179.9522974101922</v>
       </c>
       <c r="S3" t="n">
-        <v>71.24644529286074</v>
+        <v>72.23020619731146</v>
       </c>
       <c r="T3" t="n">
-        <v>18693.38392408245</v>
+        <v>24307.98017771702</v>
       </c>
       <c r="U3" t="n">
-        <v>3449663.382981398</v>
+        <v>4583785.363028783</v>
       </c>
       <c r="V3" t="n">
-        <v>75.50324047888387</v>
+        <v>76.85129205589732</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.03056884635832</v>
       </c>
       <c r="X3" t="n">
-        <v>26.67126796814297</v>
+        <v>21.06835412394623</v>
       </c>
       <c r="Y3" t="n">
-        <v>181.5024341977467</v>
+        <v>181.4228587567403</v>
       </c>
       <c r="Z3" t="n">
-        <v>74.91635708041957</v>
+        <v>71.01955029619504</v>
       </c>
       <c r="AA3" t="n">
-        <v>27472.70784770785</v>
+        <v>62807.47512721198</v>
       </c>
       <c r="AB3" t="n">
-        <v>9044196.775446774</v>
+        <v>18113949.67057796</v>
       </c>
       <c r="AC3" t="n">
-        <v>78.15489631895883</v>
+        <v>81.01018217893217</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.263039044289044</v>
+        <v>1.577206273258905</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>27.66076388888889</v>
-      </c>
-      <c r="D4" t="n">
-        <v>181.4784722222222</v>
-      </c>
-      <c r="E4" t="n">
-        <v>75.20555555555555</v>
-      </c>
-      <c r="F4" t="n">
-        <v>28269.44444444445</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8076736.111111111</v>
-      </c>
-      <c r="H4" t="n">
-        <v>77.42743055555556</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.330208333333333</v>
-      </c>
-      <c r="J4" t="n">
-        <v>26.89583333333333</v>
-      </c>
-      <c r="K4" t="n">
-        <v>182.7870370370371</v>
-      </c>
-      <c r="L4" t="n">
-        <v>76.32407407407408</v>
-      </c>
-      <c r="M4" t="n">
-        <v>31768.51851851852</v>
-      </c>
-      <c r="N4" t="n">
-        <v>11187731.48148148</v>
-      </c>
-      <c r="O4" t="n">
-        <v>79.80092592592592</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.1875</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>25.26260369532428</v>
+        <v>24.76032717282717</v>
       </c>
       <c r="R4" t="n">
-        <v>180.5988051470588</v>
+        <v>181.8981018981019</v>
       </c>
       <c r="S4" t="n">
-        <v>72.33604826546002</v>
+        <v>73.47370129870129</v>
       </c>
       <c r="T4" t="n">
-        <v>24108.35595776773</v>
+        <v>25885.41874791875</v>
       </c>
       <c r="U4" t="n">
-        <v>6700449.542797888</v>
+        <v>9693582.042957043</v>
       </c>
       <c r="V4" t="n">
-        <v>76.73619202488688</v>
+        <v>79.45553300865801</v>
       </c>
       <c r="W4" t="n">
-        <v>1.123265460030166</v>
+        <v>1.254749417249418</v>
       </c>
       <c r="X4" t="n">
-        <v>26.73413812387303</v>
+        <v>22.69581095987346</v>
       </c>
       <c r="Y4" t="n">
-        <v>178.3493025727498</v>
+        <v>182.1355425824175</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.87628722541648</v>
+        <v>71.77991331585082</v>
       </c>
       <c r="AA4" t="n">
-        <v>27040.84275663707</v>
+        <v>22746.76157176158</v>
       </c>
       <c r="AB4" t="n">
-        <v>6413604.234710079</v>
+        <v>7155141.291000666</v>
       </c>
       <c r="AC4" t="n">
-        <v>76.67258456520261</v>
+        <v>80.664575008325</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.154596297020833</v>
+        <v>1.173952089577089</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>28.075</v>
+        <v>26.625</v>
       </c>
       <c r="D5" t="n">
-        <v>180</v>
+        <v>180.9388888888889</v>
       </c>
       <c r="E5" t="n">
-        <v>75.34999999999999</v>
+        <v>78.37222222222222</v>
       </c>
       <c r="F5" t="n">
-        <v>20475</v>
+        <v>39994.44444444444</v>
       </c>
       <c r="G5" t="n">
-        <v>7222500</v>
+        <v>22137500</v>
       </c>
       <c r="H5" t="n">
-        <v>77.625</v>
+        <v>81.76388888888889</v>
       </c>
       <c r="I5" t="n">
-        <v>1.175</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>27.28968253968254</v>
+        <v>29.33928571428572</v>
       </c>
       <c r="K5" t="n">
-        <v>181.015873015873</v>
+        <v>181.6535714285715</v>
       </c>
       <c r="L5" t="n">
-        <v>73.02579365079364</v>
+        <v>82.49325396825397</v>
       </c>
       <c r="M5" t="n">
-        <v>22031.74603174603</v>
+        <v>81902.77777777778</v>
       </c>
       <c r="N5" t="n">
-        <v>6349255.952380952</v>
+        <v>31479365.07936508</v>
       </c>
       <c r="O5" t="n">
-        <v>77.0515873015873</v>
+        <v>83.94484126984128</v>
       </c>
       <c r="P5" t="n">
-        <v>1.359126984126984</v>
+        <v>2.840079365079365</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.78220244238046</v>
+        <v>24.03705861132332</v>
       </c>
       <c r="R5" t="n">
-        <v>178.2452114508084</v>
+        <v>181.1414770074696</v>
       </c>
       <c r="S5" t="n">
-        <v>72.75551094341245</v>
+        <v>71.52473368135134</v>
       </c>
       <c r="T5" t="n">
-        <v>20442.78121775026</v>
+        <v>29130.25077455225</v>
       </c>
       <c r="U5" t="n">
-        <v>5133576.818885449</v>
+        <v>11242087.8692386</v>
       </c>
       <c r="V5" t="n">
-        <v>75.10812371001032</v>
+        <v>78.35653860028859</v>
       </c>
       <c r="W5" t="n">
-        <v>1.102306394048848</v>
+        <v>1.530990578049402</v>
       </c>
       <c r="X5" t="n">
-        <v>26.46784491308485</v>
+        <v>27.66172683747412</v>
       </c>
       <c r="Y5" t="n">
-        <v>180.0252243241794</v>
+        <v>178.4687976425748</v>
       </c>
       <c r="Z5" t="n">
-        <v>71.42522457547612</v>
+        <v>79.31899674148316</v>
       </c>
       <c r="AA5" t="n">
-        <v>21470.21024318819</v>
+        <v>72452.39006916995</v>
       </c>
       <c r="AB5" t="n">
-        <v>5829384.12206988</v>
+        <v>23741599.43769998</v>
       </c>
       <c r="AC5" t="n">
-        <v>75.89828640786457</v>
+        <v>82.05085286090721</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.29378405070162</v>
+        <v>2.300772868435912</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
+        <v>25.83611111111111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72.94722222222222</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22988.88888888889</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4515000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>76.54166666666666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J6" t="n">
         <v>26.73253968253968</v>
       </c>
-      <c r="D6" t="n">
+      <c r="K6" t="n">
         <v>179.797619047619</v>
       </c>
-      <c r="E6" t="n">
+      <c r="L6" t="n">
         <v>72.21150793650794</v>
       </c>
-      <c r="F6" t="n">
+      <c r="M6" t="n">
         <v>19825.39682539683</v>
       </c>
-      <c r="G6" t="n">
+      <c r="N6" t="n">
         <v>3350952.380952381</v>
       </c>
-      <c r="H6" t="n">
+      <c r="O6" t="n">
         <v>74.94484126984126</v>
       </c>
-      <c r="I6" t="n">
+      <c r="P6" t="n">
         <v>1.048015873015873</v>
       </c>
-      <c r="J6" t="n">
-        <v>28.55277777777778</v>
-      </c>
-      <c r="K6" t="n">
-        <v>180.3888888888889</v>
-      </c>
-      <c r="L6" t="n">
-        <v>74.38055555555556</v>
-      </c>
-      <c r="M6" t="n">
-        <v>19044.44444444445</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5870555.555555556</v>
-      </c>
-      <c r="O6" t="n">
-        <v>76.45277777777778</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.377777777777777</v>
-      </c>
       <c r="Q6" t="n">
-        <v>26.64900210084033</v>
+        <v>24.91713564213564</v>
       </c>
       <c r="R6" t="n">
-        <v>179.6858375886239</v>
+        <v>179.9522974101922</v>
       </c>
       <c r="S6" t="n">
-        <v>71.44100181938805</v>
+        <v>72.23020619731146</v>
       </c>
       <c r="T6" t="n">
-        <v>18484.9173401418</v>
+        <v>24307.98017771702</v>
       </c>
       <c r="U6" t="n">
-        <v>3172305.349771488</v>
+        <v>4583785.363028783</v>
       </c>
       <c r="V6" t="n">
-        <v>74.77833110516934</v>
+        <v>76.85129205589732</v>
       </c>
       <c r="W6" t="n">
-        <v>1.054347600284133</v>
+        <v>1.03056884635832</v>
       </c>
       <c r="X6" t="n">
-        <v>29.2390611946533</v>
+        <v>26.71215645678561</v>
       </c>
       <c r="Y6" t="n">
-        <v>177.8287045739348</v>
+        <v>179.619295247859</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.8735223475355</v>
+        <v>71.44997263172657</v>
       </c>
       <c r="AA6" t="n">
-        <v>20462.65272556391</v>
+        <v>18474.51589655116</v>
       </c>
       <c r="AB6" t="n">
-        <v>7268447.942773601</v>
+        <v>3150261.760183351</v>
       </c>
       <c r="AC6" t="n">
-        <v>76.3515063700919</v>
+        <v>74.66286436401526</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.497156954887218</v>
+        <v>1.053139895904736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>27.44652777777778</v>
+        <v>26.72468434343434</v>
       </c>
       <c r="D7" t="n">
-        <v>183.3267361111111</v>
+        <v>183.3688446969697</v>
       </c>
       <c r="E7" t="n">
-        <v>85.86527777777778</v>
+        <v>78.49062500000001</v>
       </c>
       <c r="F7" t="n">
-        <v>231505.2083333333</v>
+        <v>33155.17676767677</v>
       </c>
       <c r="G7" t="n">
-        <v>69389062.5</v>
+        <v>22844090.90909091</v>
       </c>
       <c r="H7" t="n">
-        <v>88.31666666666666</v>
+        <v>81.8246212121212</v>
       </c>
       <c r="I7" t="n">
-        <v>3.572222222222222</v>
+        <v>1.826988636363637</v>
       </c>
       <c r="J7" t="n">
-        <v>29.125</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="K7" t="n">
-        <v>183.75</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="L7" t="n">
-        <v>77.875</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>21666.66666666667</v>
       </c>
       <c r="N7" t="n">
-        <v>12400000</v>
+        <v>4822222.222222222</v>
       </c>
       <c r="O7" t="n">
-        <v>80</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="P7" t="n">
-        <v>1.875</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.76346153846154</v>
+        <v>26.69656432748538</v>
       </c>
       <c r="R7" t="n">
-        <v>180.0412259615385</v>
+        <v>182.8024488304094</v>
       </c>
       <c r="S7" t="n">
-        <v>79.77235576923076</v>
+        <v>75.9857273391813</v>
       </c>
       <c r="T7" t="n">
-        <v>135960.750534188</v>
+        <v>30357.60233918129</v>
       </c>
       <c r="U7" t="n">
-        <v>38462514.69017094</v>
+        <v>16591536.91520468</v>
       </c>
       <c r="V7" t="n">
-        <v>85.16121794871793</v>
+        <v>79.78406432748537</v>
       </c>
       <c r="W7" t="n">
-        <v>2.226322115384616</v>
+        <v>1.515369152046783</v>
       </c>
       <c r="X7" t="n">
-        <v>25.96385526882818</v>
+        <v>26.30574758393386</v>
       </c>
       <c r="Y7" t="n">
-        <v>180.808568508375</v>
+        <v>180.6359246690129</v>
       </c>
       <c r="Z7" t="n">
-        <v>74.3223437553159</v>
+        <v>71.0986921121725</v>
       </c>
       <c r="AA7" t="n">
-        <v>32067.67484321664</v>
+        <v>18625.60052511033</v>
       </c>
       <c r="AB7" t="n">
-        <v>8627637.036596015</v>
+        <v>3371923.007094576</v>
       </c>
       <c r="AC7" t="n">
-        <v>79.3893702015219</v>
+        <v>75.42880635160047</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.519061865636943</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.26825396825397</v>
+        <v>26.89484126984127</v>
       </c>
       <c r="D8" t="n">
-        <v>181.436507936508</v>
+        <v>182.6904761904762</v>
       </c>
       <c r="E8" t="n">
-        <v>79.14603174603174</v>
+        <v>76.24603174603173</v>
       </c>
       <c r="F8" t="n">
-        <v>41174.60317460318</v>
+        <v>31642.85714285714</v>
       </c>
       <c r="G8" t="n">
-        <v>20080158.73015873</v>
+        <v>11010119.04761905</v>
       </c>
       <c r="H8" t="n">
-        <v>82.26825396825396</v>
+        <v>79.70238095238096</v>
       </c>
       <c r="I8" t="n">
-        <v>1.84920634920635</v>
-      </c>
-      <c r="J8" t="n">
-        <v>26.72468434343434</v>
-      </c>
-      <c r="K8" t="n">
-        <v>183.3688446969697</v>
-      </c>
-      <c r="L8" t="n">
-        <v>78.49062500000001</v>
-      </c>
-      <c r="M8" t="n">
-        <v>33155.17676767677</v>
-      </c>
-      <c r="N8" t="n">
-        <v>22844090.90909091</v>
-      </c>
-      <c r="O8" t="n">
-        <v>81.8246212121212</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.826988636363637</v>
-      </c>
+        <v>1.192460317460317</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>26.7350118835413</v>
+        <v>26.77756722122047</v>
       </c>
       <c r="R8" t="n">
-        <v>180.2538101604278</v>
+        <v>178.3035467313331</v>
       </c>
       <c r="S8" t="n">
-        <v>74.9854055258467</v>
+        <v>73.02892197814798</v>
       </c>
       <c r="T8" t="n">
-        <v>32937.76737967914</v>
+        <v>27216.86022812184</v>
       </c>
       <c r="U8" t="n">
-        <v>10496012.32917409</v>
+        <v>6607925.986408959</v>
       </c>
       <c r="V8" t="n">
-        <v>79.70854129530599</v>
+        <v>76.78535294684677</v>
       </c>
       <c r="W8" t="n">
-        <v>1.400846702317291</v>
+        <v>1.144363375129629</v>
       </c>
       <c r="X8" t="n">
-        <v>26.69656432748538</v>
+        <v>22.69581095987346</v>
       </c>
       <c r="Y8" t="n">
-        <v>182.8024488304094</v>
+        <v>182.1355425824175</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.9857273391813</v>
+        <v>71.77991331585082</v>
       </c>
       <c r="AA8" t="n">
-        <v>30357.60233918129</v>
+        <v>22746.76157176158</v>
       </c>
       <c r="AB8" t="n">
-        <v>16591536.91520468</v>
+        <v>7155141.291000666</v>
       </c>
       <c r="AC8" t="n">
-        <v>79.78406432748537</v>
+        <v>80.664575008325</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.515369152046783</v>
+        <v>1.173952089577089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25.83611111111111</v>
+        <v>26.26825396825397</v>
       </c>
       <c r="D9" t="n">
-        <v>181.75</v>
+        <v>181.436507936508</v>
       </c>
       <c r="E9" t="n">
-        <v>72.94722222222222</v>
+        <v>79.14603174603174</v>
       </c>
       <c r="F9" t="n">
-        <v>22988.88888888889</v>
+        <v>41174.60317460318</v>
       </c>
       <c r="G9" t="n">
-        <v>4515000</v>
+        <v>20080158.73015873</v>
       </c>
       <c r="H9" t="n">
-        <v>76.54166666666666</v>
+        <v>82.26825396825396</v>
       </c>
       <c r="I9" t="n">
-        <v>1.05</v>
+        <v>1.84920634920635</v>
       </c>
       <c r="J9" t="n">
-        <v>25.2797619047619</v>
+        <v>26.625</v>
       </c>
       <c r="K9" t="n">
-        <v>180.1746031746032</v>
+        <v>180.9388888888889</v>
       </c>
       <c r="L9" t="n">
-        <v>81.13690476190474</v>
+        <v>78.37222222222222</v>
       </c>
       <c r="M9" t="n">
-        <v>119696.4285714286</v>
+        <v>39994.44444444444</v>
       </c>
       <c r="N9" t="n">
-        <v>40428968.25396825</v>
+        <v>22137500</v>
       </c>
       <c r="O9" t="n">
-        <v>86.67460317460316</v>
+        <v>81.76388888888889</v>
       </c>
       <c r="P9" t="n">
-        <v>2.811507936507937</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.91713564213564</v>
+        <v>26.7350118835413</v>
       </c>
       <c r="R9" t="n">
-        <v>179.9522974101922</v>
+        <v>180.2538101604278</v>
       </c>
       <c r="S9" t="n">
-        <v>72.23020619731146</v>
+        <v>74.9854055258467</v>
       </c>
       <c r="T9" t="n">
-        <v>24307.98017771702</v>
+        <v>32937.76737967914</v>
       </c>
       <c r="U9" t="n">
-        <v>4583785.363028783</v>
+        <v>10496012.32917409</v>
       </c>
       <c r="V9" t="n">
-        <v>76.85129205589732</v>
+        <v>79.70854129530599</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03056884635832</v>
+        <v>1.400846702317291</v>
       </c>
       <c r="X9" t="n">
-        <v>21.06835412394623</v>
+        <v>24.03705861132332</v>
       </c>
       <c r="Y9" t="n">
-        <v>181.4228587567403</v>
+        <v>181.1414770074696</v>
       </c>
       <c r="Z9" t="n">
-        <v>71.01955029619504</v>
+        <v>71.52473368135134</v>
       </c>
       <c r="AA9" t="n">
-        <v>62807.47512721198</v>
+        <v>29130.25077455225</v>
       </c>
       <c r="AB9" t="n">
-        <v>18113949.67057796</v>
+        <v>11242087.8692386</v>
       </c>
       <c r="AC9" t="n">
-        <v>81.01018217893217</v>
+        <v>78.35653860028859</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.577206273258905</v>
+        <v>1.530990578049402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>27.57291666666666</v>
+      </c>
+      <c r="D10" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>73.39756944444444</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22388.88888888889</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6500043.402777778</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.22569444444444</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.383680555555555</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.44652777777778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>183.3267361111111</v>
+      </c>
+      <c r="L10" t="n">
+        <v>85.86527777777778</v>
+      </c>
+      <c r="M10" t="n">
+        <v>231505.2083333333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>69389062.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88.31666666666666</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.572222222222222</v>
+      </c>
       <c r="Q10" t="n">
-        <v>24.76032717282717</v>
+        <v>26.29946002856219</v>
       </c>
       <c r="R10" t="n">
-        <v>181.8981018981019</v>
+        <v>179.8795644786357</v>
       </c>
       <c r="S10" t="n">
-        <v>73.47370129870129</v>
+        <v>71.13988216232798</v>
       </c>
       <c r="T10" t="n">
-        <v>25885.41874791875</v>
+        <v>21169.28741193447</v>
       </c>
       <c r="U10" t="n">
-        <v>9693582.042957043</v>
+        <v>5627045.145543598</v>
       </c>
       <c r="V10" t="n">
-        <v>79.45553300865801</v>
+        <v>75.79318580169974</v>
       </c>
       <c r="W10" t="n">
-        <v>1.254749417249418</v>
+        <v>1.266432383692446</v>
       </c>
       <c r="X10" t="n">
-        <v>22.69581095987346</v>
+        <v>25.76346153846154</v>
       </c>
       <c r="Y10" t="n">
-        <v>182.1355425824175</v>
+        <v>180.0412259615385</v>
       </c>
       <c r="Z10" t="n">
-        <v>71.77991331585082</v>
+        <v>79.77235576923076</v>
       </c>
       <c r="AA10" t="n">
-        <v>22746.76157176158</v>
+        <v>135960.750534188</v>
       </c>
       <c r="AB10" t="n">
-        <v>7155141.291000666</v>
+        <v>38462514.69017094</v>
       </c>
       <c r="AC10" t="n">
-        <v>80.664575008325</v>
+        <v>85.16121794871793</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.173952089577089</v>
+        <v>2.226322115384616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.625</v>
+        <v>27.85</v>
       </c>
       <c r="D11" t="n">
-        <v>180.9388888888889</v>
+        <v>184.2</v>
       </c>
       <c r="E11" t="n">
-        <v>78.37222222222222</v>
+        <v>76.5</v>
       </c>
       <c r="F11" t="n">
-        <v>39994.44444444444</v>
+        <v>30525</v>
       </c>
       <c r="G11" t="n">
-        <v>22137500</v>
+        <v>11722500</v>
       </c>
       <c r="H11" t="n">
-        <v>81.76388888888889</v>
+        <v>78.72499999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.083333333333333</v>
+        <v>1.425</v>
       </c>
       <c r="J11" t="n">
-        <v>29.33928571428572</v>
+        <v>28.55333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>181.6535714285715</v>
+        <v>180</v>
       </c>
       <c r="L11" t="n">
-        <v>82.49325396825397</v>
+        <v>74.52666666666667</v>
       </c>
       <c r="M11" t="n">
-        <v>81902.77777777778</v>
+        <v>19257.77777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>31479365.07936508</v>
+        <v>6149777.777777778</v>
       </c>
       <c r="O11" t="n">
-        <v>83.94484126984128</v>
+        <v>76.60666666666665</v>
       </c>
       <c r="P11" t="n">
-        <v>2.840079365079365</v>
+        <v>1.391111111111111</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.03705861132332</v>
+        <v>26.57446041612708</v>
       </c>
       <c r="R11" t="n">
-        <v>181.1414770074696</v>
+        <v>181.2095711387378</v>
       </c>
       <c r="S11" t="n">
-        <v>71.52473368135134</v>
+        <v>74.8960211085211</v>
       </c>
       <c r="T11" t="n">
-        <v>29130.25077455225</v>
+        <v>27301.66623499956</v>
       </c>
       <c r="U11" t="n">
-        <v>11242087.8692386</v>
+        <v>8977804.541137874</v>
       </c>
       <c r="V11" t="n">
-        <v>78.35653860028859</v>
+        <v>78.22657450574118</v>
       </c>
       <c r="W11" t="n">
-        <v>1.530990578049402</v>
+        <v>1.256034706034706</v>
       </c>
       <c r="X11" t="n">
-        <v>27.66172683747412</v>
+        <v>29.3528497168848</v>
       </c>
       <c r="Y11" t="n">
-        <v>178.4687976425748</v>
+        <v>178.1869186856029</v>
       </c>
       <c r="Z11" t="n">
-        <v>79.31899674148316</v>
+        <v>74.90511927968068</v>
       </c>
       <c r="AA11" t="n">
-        <v>72452.39006916995</v>
+        <v>20557.44569757728</v>
       </c>
       <c r="AB11" t="n">
-        <v>23741599.43769998</v>
+        <v>7296515.13041864</v>
       </c>
       <c r="AC11" t="n">
-        <v>82.05085286090721</v>
+        <v>76.29490624709923</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.300772868435912</v>
+        <v>1.5062447786132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.83611111111111</v>
+        <v>29.33928571428572</v>
       </c>
       <c r="D12" t="n">
-        <v>181.75</v>
+        <v>181.6535714285715</v>
       </c>
       <c r="E12" t="n">
-        <v>72.94722222222222</v>
+        <v>82.49325396825397</v>
       </c>
       <c r="F12" t="n">
-        <v>22988.88888888889</v>
+        <v>81902.77777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>4515000</v>
+        <v>31479365.07936508</v>
       </c>
       <c r="H12" t="n">
-        <v>76.54166666666666</v>
+        <v>83.94484126984128</v>
       </c>
       <c r="I12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J12" t="n">
-        <v>26.73253968253968</v>
-      </c>
-      <c r="K12" t="n">
-        <v>179.797619047619</v>
-      </c>
-      <c r="L12" t="n">
-        <v>72.21150793650794</v>
-      </c>
-      <c r="M12" t="n">
-        <v>19825.39682539683</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3350952.380952381</v>
-      </c>
-      <c r="O12" t="n">
-        <v>74.94484126984126</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.048015873015873</v>
-      </c>
+        <v>2.840079365079365</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>24.91713564213564</v>
+        <v>27.66172683747412</v>
       </c>
       <c r="R12" t="n">
-        <v>179.9522974101922</v>
+        <v>178.4687976425748</v>
       </c>
       <c r="S12" t="n">
-        <v>72.23020619731146</v>
+        <v>79.31899674148316</v>
       </c>
       <c r="T12" t="n">
-        <v>24307.98017771702</v>
+        <v>72452.39006916995</v>
       </c>
       <c r="U12" t="n">
-        <v>4583785.363028783</v>
+        <v>23741599.43769998</v>
       </c>
       <c r="V12" t="n">
-        <v>76.85129205589732</v>
+        <v>82.05085286090721</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03056884635832</v>
+        <v>2.300772868435912</v>
       </c>
       <c r="X12" t="n">
-        <v>26.64900210084033</v>
+        <v>26.80966706295654</v>
       </c>
       <c r="Y12" t="n">
-        <v>179.6858375886239</v>
+        <v>181.3739345693293</v>
       </c>
       <c r="Z12" t="n">
-        <v>71.44100181938805</v>
+        <v>70.84219148298095</v>
       </c>
       <c r="AA12" t="n">
-        <v>18484.9173401418</v>
+        <v>26849.67279309385</v>
       </c>
       <c r="AB12" t="n">
-        <v>3172305.349771488</v>
+        <v>4187981.318145792</v>
       </c>
       <c r="AC12" t="n">
-        <v>74.77833110516934</v>
+        <v>74.13396659383501</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.054347600284133</v>
+        <v>1.047794432662854</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.72468434343434</v>
+        <v>29.125</v>
       </c>
       <c r="D13" t="n">
-        <v>183.3688446969697</v>
+        <v>183.75</v>
       </c>
       <c r="E13" t="n">
-        <v>78.49062500000001</v>
+        <v>77.875</v>
       </c>
       <c r="F13" t="n">
-        <v>33155.17676767677</v>
+        <v>36000</v>
       </c>
       <c r="G13" t="n">
-        <v>22844090.90909091</v>
+        <v>12400000</v>
       </c>
       <c r="H13" t="n">
-        <v>81.8246212121212</v>
+        <v>80</v>
       </c>
       <c r="I13" t="n">
-        <v>1.826988636363637</v>
+        <v>1.875</v>
       </c>
       <c r="J13" t="n">
-        <v>26.55555555555556</v>
+        <v>27.7108024691358</v>
       </c>
       <c r="K13" t="n">
-        <v>182.1111111111111</v>
+        <v>181.3882716049383</v>
       </c>
       <c r="L13" t="n">
-        <v>73</v>
+        <v>75.30617283950617</v>
       </c>
       <c r="M13" t="n">
-        <v>21666.66666666667</v>
+        <v>28387.65432098765</v>
       </c>
       <c r="N13" t="n">
-        <v>4822222.222222222</v>
+        <v>8170679.012345678</v>
       </c>
       <c r="O13" t="n">
-        <v>76.55555555555556</v>
+        <v>77.47870370370372</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>1.330555555555555</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.69656432748538</v>
+        <v>25.96385526882818</v>
       </c>
       <c r="R13" t="n">
-        <v>182.8024488304094</v>
+        <v>180.808568508375</v>
       </c>
       <c r="S13" t="n">
-        <v>75.9857273391813</v>
+        <v>74.3223437553159</v>
       </c>
       <c r="T13" t="n">
-        <v>30357.60233918129</v>
+        <v>32067.67484321664</v>
       </c>
       <c r="U13" t="n">
-        <v>16591536.91520468</v>
+        <v>8627637.036596015</v>
       </c>
       <c r="V13" t="n">
-        <v>79.78406432748537</v>
+        <v>79.3893702015219</v>
       </c>
       <c r="W13" t="n">
-        <v>1.515369152046783</v>
+        <v>1.519061865636943</v>
       </c>
       <c r="X13" t="n">
-        <v>26.34396603192559</v>
+        <v>25.31367242053516</v>
       </c>
       <c r="Y13" t="n">
-        <v>180.7362485859728</v>
+        <v>180.779184822077</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.24644529286074</v>
+        <v>72.10735154460644</v>
       </c>
       <c r="AA13" t="n">
-        <v>18693.38392408245</v>
+        <v>23794.00033517681</v>
       </c>
       <c r="AB13" t="n">
-        <v>3449663.382981398</v>
+        <v>6596232.926931456</v>
       </c>
       <c r="AC13" t="n">
-        <v>75.50324047888387</v>
+        <v>76.4877262443439</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>1.134260655829283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>26.89583333333333</v>
+        <v>25.2797619047619</v>
       </c>
       <c r="D14" t="n">
-        <v>182.7870370370371</v>
+        <v>180.1746031746032</v>
       </c>
       <c r="E14" t="n">
-        <v>76.32407407407408</v>
+        <v>81.13690476190474</v>
       </c>
       <c r="F14" t="n">
-        <v>31768.51851851852</v>
+        <v>119696.4285714286</v>
       </c>
       <c r="G14" t="n">
-        <v>11187731.48148148</v>
+        <v>40428968.25396825</v>
       </c>
       <c r="H14" t="n">
-        <v>79.80092592592592</v>
+        <v>86.67460317460316</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1875</v>
+        <v>2.811507936507937</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1699,46 +1685,46 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>26.73413812387303</v>
+        <v>21.06835412394623</v>
       </c>
       <c r="R14" t="n">
-        <v>178.3493025727498</v>
+        <v>181.4228587567403</v>
       </c>
       <c r="S14" t="n">
-        <v>72.87628722541648</v>
+        <v>71.01955029619504</v>
       </c>
       <c r="T14" t="n">
-        <v>27040.84275663707</v>
+        <v>62807.47512721198</v>
       </c>
       <c r="U14" t="n">
-        <v>6413604.234710079</v>
+        <v>18113949.67057796</v>
       </c>
       <c r="V14" t="n">
-        <v>76.67258456520261</v>
+        <v>81.01018217893217</v>
       </c>
       <c r="W14" t="n">
-        <v>1.154596297020833</v>
+        <v>1.577206273258905</v>
       </c>
       <c r="X14" t="n">
-        <v>22.69581095987346</v>
+        <v>24.76032717282717</v>
       </c>
       <c r="Y14" t="n">
-        <v>182.1355425824175</v>
+        <v>181.8981018981019</v>
       </c>
       <c r="Z14" t="n">
-        <v>71.77991331585082</v>
+        <v>73.47370129870129</v>
       </c>
       <c r="AA14" t="n">
-        <v>22746.76157176158</v>
+        <v>25885.41874791875</v>
       </c>
       <c r="AB14" t="n">
-        <v>7155141.291000666</v>
+        <v>9693582.042957043</v>
       </c>
       <c r="AC14" t="n">
-        <v>80.664575008325</v>
+        <v>79.45553300865801</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.173952089577089</v>
+        <v>1.254749417249418</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,207 +578,221 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.26825396825397</v>
+        <v>25.75231481481481</v>
       </c>
       <c r="D2" t="n">
-        <v>181.436507936508</v>
+        <v>181.7361111111111</v>
       </c>
       <c r="E2" t="n">
-        <v>79.14603174603174</v>
+        <v>72.91898148148148</v>
       </c>
       <c r="F2" t="n">
-        <v>41174.60317460318</v>
+        <v>22638.88888888889</v>
       </c>
       <c r="G2" t="n">
-        <v>20080158.73015873</v>
+        <v>4527314.814814814</v>
       </c>
       <c r="H2" t="n">
-        <v>82.26825396825396</v>
+        <v>76.58101851851852</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84920634920635</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>26.72468434343434</v>
+        <v>26.73253968253968</v>
       </c>
       <c r="K2" t="n">
-        <v>183.3688446969697</v>
+        <v>179.797619047619</v>
       </c>
       <c r="L2" t="n">
-        <v>78.49062500000001</v>
+        <v>72.21150793650794</v>
       </c>
       <c r="M2" t="n">
-        <v>33155.17676767677</v>
+        <v>19825.39682539683</v>
       </c>
       <c r="N2" t="n">
-        <v>22844090.90909091</v>
+        <v>3350952.380952381</v>
       </c>
       <c r="O2" t="n">
-        <v>81.8246212121212</v>
+        <v>74.94484126984126</v>
       </c>
       <c r="P2" t="n">
-        <v>1.826988636363637</v>
+        <v>1.048015873015873</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.7350118835413</v>
+        <v>24.97263908930576</v>
       </c>
       <c r="R2" t="n">
-        <v>180.2538101604278</v>
+        <v>180.152042142393</v>
       </c>
       <c r="S2" t="n">
-        <v>74.9854055258467</v>
+        <v>72.35277587909167</v>
       </c>
       <c r="T2" t="n">
-        <v>32937.76737967914</v>
+        <v>24523.76015797068</v>
       </c>
       <c r="U2" t="n">
-        <v>10496012.32917409</v>
+        <v>4804105.507877437</v>
       </c>
       <c r="V2" t="n">
-        <v>79.70854129530599</v>
+        <v>76.93262997561243</v>
       </c>
       <c r="W2" t="n">
-        <v>1.400846702317291</v>
+        <v>1.05495008565184</v>
       </c>
       <c r="X2" t="n">
-        <v>26.69656432748538</v>
+        <v>26.71215645678561</v>
       </c>
       <c r="Y2" t="n">
-        <v>182.8024488304094</v>
+        <v>179.619295247859</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.9857273391813</v>
+        <v>71.44997263172657</v>
       </c>
       <c r="AA2" t="n">
-        <v>30357.60233918129</v>
+        <v>18474.51589655117</v>
       </c>
       <c r="AB2" t="n">
-        <v>16591536.91520468</v>
+        <v>3150261.760183351</v>
       </c>
       <c r="AC2" t="n">
-        <v>79.78406432748537</v>
+        <v>74.66286436401526</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.515369152046783</v>
+        <v>1.053139895904736</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.83611111111111</v>
+        <v>26.79968434343434</v>
       </c>
       <c r="D3" t="n">
-        <v>181.75</v>
+        <v>183.2188446969697</v>
       </c>
       <c r="E3" t="n">
-        <v>72.94722222222222</v>
+        <v>78.56562500000001</v>
       </c>
       <c r="F3" t="n">
-        <v>22988.88888888889</v>
+        <v>33155.17676767677</v>
       </c>
       <c r="G3" t="n">
-        <v>4515000</v>
+        <v>22962840.90909091</v>
       </c>
       <c r="H3" t="n">
-        <v>76.54166666666666</v>
+        <v>81.84962121212121</v>
       </c>
       <c r="I3" t="n">
-        <v>1.05</v>
+        <v>1.851988636363636</v>
       </c>
       <c r="J3" t="n">
-        <v>25.2797619047619</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="K3" t="n">
-        <v>180.1746031746032</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="L3" t="n">
-        <v>81.13690476190474</v>
+        <v>73</v>
       </c>
       <c r="M3" t="n">
-        <v>119696.4285714286</v>
+        <v>21666.66666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>40428968.25396825</v>
+        <v>4822222.222222222</v>
       </c>
       <c r="O3" t="n">
-        <v>86.67460317460316</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="P3" t="n">
-        <v>2.811507936507937</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.91713564213564</v>
+        <v>26.69617733058136</v>
       </c>
       <c r="R3" t="n">
-        <v>179.9522974101922</v>
+        <v>182.6735788613691</v>
       </c>
       <c r="S3" t="n">
-        <v>72.23020619731146</v>
+        <v>75.61111433608531</v>
       </c>
       <c r="T3" t="n">
-        <v>24307.98017771702</v>
+        <v>29851.79738562092</v>
       </c>
       <c r="U3" t="n">
-        <v>4583785.363028783</v>
+        <v>15005314.00498796</v>
       </c>
       <c r="V3" t="n">
-        <v>76.85129205589732</v>
+        <v>79.62075163398693</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03056884635832</v>
+        <v>1.448418687650499</v>
       </c>
       <c r="X3" t="n">
-        <v>21.06835412394623</v>
+        <v>26.30574758393386</v>
       </c>
       <c r="Y3" t="n">
-        <v>181.4228587567403</v>
+        <v>180.6359246690129</v>
       </c>
       <c r="Z3" t="n">
-        <v>71.01955029619504</v>
+        <v>71.0986921121725</v>
       </c>
       <c r="AA3" t="n">
-        <v>62807.47512721198</v>
+        <v>18625.60052511033</v>
       </c>
       <c r="AB3" t="n">
-        <v>18113949.67057796</v>
+        <v>3371923.007094576</v>
       </c>
       <c r="AC3" t="n">
-        <v>81.01018217893217</v>
+        <v>75.42880635160047</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.577206273258905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>26.89484126984127</v>
+      </c>
+      <c r="D4" t="n">
+        <v>182.6904761904762</v>
+      </c>
+      <c r="E4" t="n">
+        <v>76.24603174603173</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31642.85714285714</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11010119.04761905</v>
+      </c>
+      <c r="H4" t="n">
+        <v>79.70238095238096</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.192460317460317</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -787,359 +801,359 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>24.76032717282717</v>
+        <v>26.77756722122047</v>
       </c>
       <c r="R4" t="n">
-        <v>181.8981018981019</v>
+        <v>178.3035467313331</v>
       </c>
       <c r="S4" t="n">
-        <v>73.47370129870129</v>
+        <v>73.02892197814798</v>
       </c>
       <c r="T4" t="n">
-        <v>25885.41874791875</v>
+        <v>27216.86022812184</v>
       </c>
       <c r="U4" t="n">
-        <v>9693582.042957043</v>
+        <v>6607925.986408959</v>
       </c>
       <c r="V4" t="n">
-        <v>79.45553300865801</v>
+        <v>76.78535294684677</v>
       </c>
       <c r="W4" t="n">
-        <v>1.254749417249418</v>
+        <v>1.144363375129629</v>
       </c>
       <c r="X4" t="n">
-        <v>22.69581095987346</v>
+        <v>22.98747762654013</v>
       </c>
       <c r="Y4" t="n">
-        <v>182.1355425824175</v>
+        <v>181.8022092490842</v>
       </c>
       <c r="Z4" t="n">
-        <v>71.77991331585082</v>
+        <v>71.66532998251748</v>
       </c>
       <c r="AA4" t="n">
-        <v>22746.76157176158</v>
+        <v>23298.84490509491</v>
       </c>
       <c r="AB4" t="n">
-        <v>7155141.291000666</v>
+        <v>6826495.457667332</v>
       </c>
       <c r="AC4" t="n">
-        <v>80.664575008325</v>
+        <v>80.40415834165833</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.173952089577089</v>
+        <v>1.215618756243756</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>26.12962962962963</v>
+      </c>
+      <c r="D5" t="n">
+        <v>181.5925925925926</v>
+      </c>
+      <c r="E5" t="n">
+        <v>79.17037037037036</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40753.70370370371</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20435185.18518519</v>
+      </c>
+      <c r="H5" t="n">
+        <v>82.37962962962963</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.874074074074074</v>
+      </c>
+      <c r="J5" t="n">
         <v>26.625</v>
       </c>
-      <c r="D5" t="n">
+      <c r="K5" t="n">
         <v>180.9388888888889</v>
       </c>
-      <c r="E5" t="n">
+      <c r="L5" t="n">
         <v>78.37222222222222</v>
       </c>
-      <c r="F5" t="n">
+      <c r="M5" t="n">
         <v>39994.44444444444</v>
       </c>
-      <c r="G5" t="n">
+      <c r="N5" t="n">
         <v>22137500</v>
       </c>
-      <c r="H5" t="n">
+      <c r="O5" t="n">
         <v>81.76388888888889</v>
       </c>
-      <c r="I5" t="n">
+      <c r="P5" t="n">
         <v>2.083333333333333</v>
       </c>
-      <c r="J5" t="n">
-        <v>29.33928571428572</v>
-      </c>
-      <c r="K5" t="n">
-        <v>181.6535714285715</v>
-      </c>
-      <c r="L5" t="n">
-        <v>82.49325396825397</v>
-      </c>
-      <c r="M5" t="n">
-        <v>81902.77777777778</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31479365.07936508</v>
-      </c>
-      <c r="O5" t="n">
-        <v>83.94484126984128</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.840079365079365</v>
-      </c>
       <c r="Q5" t="n">
-        <v>24.03705861132332</v>
+        <v>26.82161319073084</v>
       </c>
       <c r="R5" t="n">
-        <v>181.1414770074696</v>
+        <v>180.3873885918003</v>
       </c>
       <c r="S5" t="n">
-        <v>71.52473368135134</v>
+        <v>75.27339572192513</v>
       </c>
       <c r="T5" t="n">
-        <v>29130.25077455225</v>
+        <v>33451.24777183601</v>
       </c>
       <c r="U5" t="n">
-        <v>11242087.8692386</v>
+        <v>10761657.75401069</v>
       </c>
       <c r="V5" t="n">
-        <v>78.35653860028859</v>
+        <v>79.73877005347593</v>
       </c>
       <c r="W5" t="n">
-        <v>1.530990578049402</v>
+        <v>1.381238859180036</v>
       </c>
       <c r="X5" t="n">
-        <v>27.66172683747412</v>
+        <v>24.07334502824699</v>
       </c>
       <c r="Y5" t="n">
-        <v>178.4687976425748</v>
+        <v>181.4085856228013</v>
       </c>
       <c r="Z5" t="n">
-        <v>79.31899674148316</v>
+        <v>71.53713700968602</v>
       </c>
       <c r="AA5" t="n">
-        <v>72452.39006916995</v>
+        <v>29226.88957737977</v>
       </c>
       <c r="AB5" t="n">
-        <v>23741599.43769998</v>
+        <v>11202815.47972725</v>
       </c>
       <c r="AC5" t="n">
-        <v>82.05085286090721</v>
+        <v>78.2765191598525</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.300772868435912</v>
+        <v>1.552799705740882</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.83611111111111</v>
+        <v>27.57291666666666</v>
       </c>
       <c r="D6" t="n">
-        <v>181.75</v>
+        <v>181.1666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>72.94722222222222</v>
+        <v>73.39756944444444</v>
       </c>
       <c r="F6" t="n">
-        <v>22988.88888888889</v>
+        <v>22388.88888888889</v>
       </c>
       <c r="G6" t="n">
-        <v>4515000</v>
+        <v>6500043.402777778</v>
       </c>
       <c r="H6" t="n">
-        <v>76.54166666666666</v>
+        <v>77.22569444444444</v>
       </c>
       <c r="I6" t="n">
-        <v>1.05</v>
+        <v>1.383680555555556</v>
       </c>
       <c r="J6" t="n">
-        <v>26.73253968253968</v>
+        <v>27.43395061728395</v>
       </c>
       <c r="K6" t="n">
-        <v>179.797619047619</v>
+        <v>183.2533950617284</v>
       </c>
       <c r="L6" t="n">
-        <v>72.21150793650794</v>
+        <v>85.84320987654321</v>
       </c>
       <c r="M6" t="n">
-        <v>19825.39682539683</v>
+        <v>230658.9506172839</v>
       </c>
       <c r="N6" t="n">
-        <v>3350952.380952381</v>
+        <v>69586574.07407409</v>
       </c>
       <c r="O6" t="n">
-        <v>74.94484126984126</v>
+        <v>88.31851851851852</v>
       </c>
       <c r="P6" t="n">
-        <v>1.048015873015873</v>
+        <v>3.545679012345679</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.91713564213564</v>
+        <v>26.29946002856219</v>
       </c>
       <c r="R6" t="n">
-        <v>179.9522974101922</v>
+        <v>179.8795644786357</v>
       </c>
       <c r="S6" t="n">
-        <v>72.23020619731146</v>
+        <v>71.13988216232798</v>
       </c>
       <c r="T6" t="n">
-        <v>24307.98017771702</v>
+        <v>21169.28741193447</v>
       </c>
       <c r="U6" t="n">
-        <v>4583785.363028783</v>
+        <v>5627045.145543598</v>
       </c>
       <c r="V6" t="n">
-        <v>76.85129205589732</v>
+        <v>75.79318580169974</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03056884635832</v>
+        <v>1.266432383692446</v>
       </c>
       <c r="X6" t="n">
-        <v>26.71215645678561</v>
+        <v>25.57446581196582</v>
       </c>
       <c r="Y6" t="n">
-        <v>179.619295247859</v>
+        <v>180.1547008547008</v>
       </c>
       <c r="Z6" t="n">
-        <v>71.44997263172657</v>
+        <v>79.73514957264956</v>
       </c>
       <c r="AA6" t="n">
-        <v>18474.51589655116</v>
+        <v>135756.7782526116</v>
       </c>
       <c r="AB6" t="n">
-        <v>3150261.760183351</v>
+        <v>39158346.39126305</v>
       </c>
       <c r="AC6" t="n">
-        <v>74.66286436401526</v>
+        <v>85.22663817663816</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.053139895904736</v>
+        <v>2.228952991452992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.72468434343434</v>
+        <v>27.85</v>
       </c>
       <c r="D7" t="n">
-        <v>183.3688446969697</v>
+        <v>184.2</v>
       </c>
       <c r="E7" t="n">
-        <v>78.49062500000001</v>
+        <v>76.5</v>
       </c>
       <c r="F7" t="n">
-        <v>33155.17676767677</v>
+        <v>30525</v>
       </c>
       <c r="G7" t="n">
-        <v>22844090.90909091</v>
+        <v>11722500</v>
       </c>
       <c r="H7" t="n">
-        <v>81.8246212121212</v>
+        <v>78.72499999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.826988636363637</v>
+        <v>1.425</v>
       </c>
       <c r="J7" t="n">
-        <v>26.55555555555556</v>
+        <v>28.55333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>182.1111111111111</v>
+        <v>180.0000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>74.52666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>21666.66666666667</v>
+        <v>19257.77777777778</v>
       </c>
       <c r="N7" t="n">
-        <v>4822222.222222222</v>
+        <v>6149777.777777778</v>
       </c>
       <c r="O7" t="n">
-        <v>76.55555555555556</v>
+        <v>76.60666666666665</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.391111111111111</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.69656432748538</v>
+        <v>26.57446041612708</v>
       </c>
       <c r="R7" t="n">
-        <v>182.8024488304094</v>
+        <v>181.2095711387378</v>
       </c>
       <c r="S7" t="n">
-        <v>75.9857273391813</v>
+        <v>74.8960211085211</v>
       </c>
       <c r="T7" t="n">
-        <v>30357.60233918129</v>
+        <v>27301.66623499956</v>
       </c>
       <c r="U7" t="n">
-        <v>16591536.91520468</v>
+        <v>8977804.541137874</v>
       </c>
       <c r="V7" t="n">
-        <v>79.78406432748537</v>
+        <v>78.22657450574118</v>
       </c>
       <c r="W7" t="n">
-        <v>1.515369152046783</v>
+        <v>1.256034706034706</v>
       </c>
       <c r="X7" t="n">
-        <v>26.30574758393386</v>
+        <v>29.3528497168848</v>
       </c>
       <c r="Y7" t="n">
-        <v>180.6359246690129</v>
+        <v>178.1869186856029</v>
       </c>
       <c r="Z7" t="n">
-        <v>71.0986921121725</v>
+        <v>74.90511927968068</v>
       </c>
       <c r="AA7" t="n">
-        <v>18625.60052511033</v>
+        <v>20557.44569757728</v>
       </c>
       <c r="AB7" t="n">
-        <v>3371923.007094576</v>
+        <v>7296515.13041864</v>
       </c>
       <c r="AC7" t="n">
-        <v>75.42880635160047</v>
+        <v>76.29490624709923</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>1.5062447786132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.89484126984127</v>
+        <v>29.35243055555556</v>
       </c>
       <c r="D8" t="n">
-        <v>182.6904761904762</v>
+        <v>181.5163194444445</v>
       </c>
       <c r="E8" t="n">
-        <v>76.24603174603173</v>
+        <v>82.40381944444445</v>
       </c>
       <c r="F8" t="n">
-        <v>31642.85714285714</v>
+        <v>81734.375</v>
       </c>
       <c r="G8" t="n">
-        <v>11010119.04761905</v>
+        <v>30995833.33333333</v>
       </c>
       <c r="H8" t="n">
-        <v>79.70238095238096</v>
+        <v>83.86840277777779</v>
       </c>
       <c r="I8" t="n">
-        <v>1.192460317460317</v>
+        <v>2.818402777777778</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1149,359 +1163,345 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>26.77756722122047</v>
+        <v>27.66009705814693</v>
       </c>
       <c r="R8" t="n">
-        <v>178.3035467313331</v>
+        <v>178.743506401243</v>
       </c>
       <c r="S8" t="n">
-        <v>73.02892197814798</v>
+        <v>79.35544808393274</v>
       </c>
       <c r="T8" t="n">
-        <v>27216.86022812184</v>
+        <v>72722.38594383736</v>
       </c>
       <c r="U8" t="n">
-        <v>6607925.986408959</v>
+        <v>23940245.25181175</v>
       </c>
       <c r="V8" t="n">
-        <v>76.78535294684677</v>
+        <v>82.05173849074104</v>
       </c>
       <c r="W8" t="n">
-        <v>1.144363375129629</v>
+        <v>2.300033399394013</v>
       </c>
       <c r="X8" t="n">
-        <v>22.69581095987346</v>
+        <v>26.80966706295654</v>
       </c>
       <c r="Y8" t="n">
-        <v>182.1355425824175</v>
+        <v>181.3739345693293</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.77991331585082</v>
+        <v>70.84219148298095</v>
       </c>
       <c r="AA8" t="n">
-        <v>22746.76157176158</v>
+        <v>26849.67279309385</v>
       </c>
       <c r="AB8" t="n">
-        <v>7155141.291000666</v>
+        <v>4187981.318145792</v>
       </c>
       <c r="AC8" t="n">
-        <v>80.664575008325</v>
+        <v>74.13396659383501</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.173952089577089</v>
+        <v>1.047794432662854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.26825396825397</v>
+        <v>29.125</v>
       </c>
       <c r="D9" t="n">
-        <v>181.436507936508</v>
+        <v>183.75</v>
       </c>
       <c r="E9" t="n">
-        <v>79.14603174603174</v>
+        <v>77.875</v>
       </c>
       <c r="F9" t="n">
-        <v>41174.60317460318</v>
+        <v>36000</v>
       </c>
       <c r="G9" t="n">
-        <v>20080158.73015873</v>
+        <v>12400000</v>
       </c>
       <c r="H9" t="n">
-        <v>82.26825396825396</v>
+        <v>80</v>
       </c>
       <c r="I9" t="n">
-        <v>1.84920634920635</v>
+        <v>1.875</v>
       </c>
       <c r="J9" t="n">
-        <v>26.625</v>
+        <v>27.73715277777778</v>
       </c>
       <c r="K9" t="n">
-        <v>180.9388888888889</v>
+        <v>181.4493055555556</v>
       </c>
       <c r="L9" t="n">
-        <v>78.37222222222222</v>
+        <v>75.39444444444445</v>
       </c>
       <c r="M9" t="n">
-        <v>39994.44444444444</v>
+        <v>28398.61111111111</v>
       </c>
       <c r="N9" t="n">
-        <v>22137500</v>
+        <v>8162326.388888889</v>
       </c>
       <c r="O9" t="n">
-        <v>81.76388888888889</v>
+        <v>77.55104166666666</v>
       </c>
       <c r="P9" t="n">
-        <v>2.083333333333333</v>
+        <v>1.334375</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.7350118835413</v>
+        <v>26.02015893176884</v>
       </c>
       <c r="R9" t="n">
-        <v>180.2538101604278</v>
+        <v>180.6925837721504</v>
       </c>
       <c r="S9" t="n">
-        <v>74.9854055258467</v>
+        <v>74.38456699818929</v>
       </c>
       <c r="T9" t="n">
-        <v>32937.76737967914</v>
+        <v>32345.98019369692</v>
       </c>
       <c r="U9" t="n">
-        <v>10496012.32917409</v>
+        <v>8564435.535797765</v>
       </c>
       <c r="V9" t="n">
-        <v>79.70854129530599</v>
+        <v>79.38532253207177</v>
       </c>
       <c r="W9" t="n">
-        <v>1.400846702317291</v>
+        <v>1.526747802134799</v>
       </c>
       <c r="X9" t="n">
-        <v>24.03705861132332</v>
+        <v>25.36538147310206</v>
       </c>
       <c r="Y9" t="n">
-        <v>181.1414770074696</v>
+        <v>180.9265829248366</v>
       </c>
       <c r="Z9" t="n">
-        <v>71.52473368135134</v>
+        <v>72.05827048768225</v>
       </c>
       <c r="AA9" t="n">
-        <v>29130.25077455225</v>
+        <v>23872.80040221217</v>
       </c>
       <c r="AB9" t="n">
-        <v>11242087.8692386</v>
+        <v>6810762.042797888</v>
       </c>
       <c r="AC9" t="n">
-        <v>78.35653860028859</v>
+        <v>76.44869202488688</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.530990578049402</v>
+        <v>1.151043237807944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>27.57291666666666</v>
+        <v>25.02604166666666</v>
       </c>
       <c r="D10" t="n">
-        <v>181.1666666666667</v>
+        <v>180.0902777777778</v>
       </c>
       <c r="E10" t="n">
-        <v>73.39756944444444</v>
+        <v>80.71354166666666</v>
       </c>
       <c r="F10" t="n">
-        <v>22388.88888888889</v>
+        <v>117109.375</v>
       </c>
       <c r="G10" t="n">
-        <v>6500043.402777778</v>
+        <v>39473784.72222222</v>
       </c>
       <c r="H10" t="n">
-        <v>77.22569444444444</v>
+        <v>86.55902777777777</v>
       </c>
       <c r="I10" t="n">
-        <v>1.383680555555555</v>
-      </c>
-      <c r="J10" t="n">
-        <v>27.44652777777778</v>
-      </c>
-      <c r="K10" t="n">
-        <v>183.3267361111111</v>
-      </c>
-      <c r="L10" t="n">
-        <v>85.86527777777778</v>
-      </c>
-      <c r="M10" t="n">
-        <v>231505.2083333333</v>
-      </c>
-      <c r="N10" t="n">
-        <v>69389062.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88.31666666666666</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.572222222222222</v>
-      </c>
+        <v>2.756944444444445</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>26.29946002856219</v>
+        <v>21.28298144350776</v>
       </c>
       <c r="R10" t="n">
-        <v>179.8795644786357</v>
+        <v>181.4437756850037</v>
       </c>
       <c r="S10" t="n">
-        <v>71.13988216232798</v>
+        <v>71.5976249546425</v>
       </c>
       <c r="T10" t="n">
-        <v>21169.28741193447</v>
+        <v>66631.33591554646</v>
       </c>
       <c r="U10" t="n">
-        <v>5627045.145543598</v>
+        <v>20068881.18866189</v>
       </c>
       <c r="V10" t="n">
-        <v>75.79318580169974</v>
+        <v>81.24979156645823</v>
       </c>
       <c r="W10" t="n">
-        <v>1.266432383692446</v>
+        <v>1.65504755153878</v>
       </c>
       <c r="X10" t="n">
-        <v>25.76346153846154</v>
+        <v>24.83457653457653</v>
       </c>
       <c r="Y10" t="n">
-        <v>180.0412259615385</v>
+        <v>181.7665667665668</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.77235576923076</v>
+        <v>73.53217893217892</v>
       </c>
       <c r="AA10" t="n">
-        <v>135960.750534188</v>
+        <v>25977.51507751508</v>
       </c>
       <c r="AB10" t="n">
-        <v>38462514.69017094</v>
+        <v>9638739.593739593</v>
       </c>
       <c r="AC10" t="n">
-        <v>85.16121794871793</v>
+        <v>79.43666426166426</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.226322115384616</v>
+        <v>1.226443926443927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>27.85</v>
+        <v>24.0891975308642</v>
       </c>
       <c r="D11" t="n">
-        <v>184.2</v>
+        <v>182.3342592592593</v>
       </c>
       <c r="E11" t="n">
-        <v>76.5</v>
+        <v>76.22037037037038</v>
       </c>
       <c r="F11" t="n">
-        <v>30525</v>
+        <v>35962.34567901235</v>
       </c>
       <c r="G11" t="n">
-        <v>11722500</v>
+        <v>17576697.5308642</v>
       </c>
       <c r="H11" t="n">
-        <v>78.72499999999999</v>
+        <v>81.32345679012344</v>
       </c>
       <c r="I11" t="n">
-        <v>1.425</v>
+        <v>1.246913580246914</v>
       </c>
       <c r="J11" t="n">
-        <v>28.55333333333333</v>
+        <v>28.075</v>
       </c>
       <c r="K11" t="n">
         <v>180</v>
       </c>
       <c r="L11" t="n">
-        <v>74.52666666666667</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>19257.77777777778</v>
+        <v>20475</v>
       </c>
       <c r="N11" t="n">
-        <v>6149777.777777778</v>
+        <v>7222500</v>
       </c>
       <c r="O11" t="n">
-        <v>76.60666666666665</v>
+        <v>77.625</v>
       </c>
       <c r="P11" t="n">
-        <v>1.391111111111111</v>
+        <v>1.175</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.57446041612708</v>
+        <v>24.24859666000017</v>
       </c>
       <c r="R11" t="n">
-        <v>181.2095711387378</v>
+        <v>178.445251597006</v>
       </c>
       <c r="S11" t="n">
-        <v>74.8960211085211</v>
+        <v>72.34763550289865</v>
       </c>
       <c r="T11" t="n">
-        <v>27301.66623499956</v>
+        <v>27468.70332396648</v>
       </c>
       <c r="U11" t="n">
-        <v>8977804.541137874</v>
+        <v>8009908.124688826</v>
       </c>
       <c r="V11" t="n">
-        <v>78.22657450574118</v>
+        <v>78.66827126739408</v>
       </c>
       <c r="W11" t="n">
-        <v>1.256034706034706</v>
+        <v>1.032856130224551</v>
       </c>
       <c r="X11" t="n">
-        <v>29.3528497168848</v>
+        <v>26.86751328211596</v>
       </c>
       <c r="Y11" t="n">
-        <v>178.1869186856029</v>
+        <v>178.2457435118297</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.90511927968068</v>
+        <v>72.71045417192219</v>
       </c>
       <c r="AA11" t="n">
-        <v>20557.44569757728</v>
+        <v>20442.78121775026</v>
       </c>
       <c r="AB11" t="n">
-        <v>7296515.13041864</v>
+        <v>5056790.505675955</v>
       </c>
       <c r="AC11" t="n">
-        <v>76.29490624709923</v>
+        <v>74.97944329778696</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5062447786132</v>
+        <v>1.107605683598976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>29.33928571428572</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="D12" t="n">
-        <v>181.6535714285715</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="E12" t="n">
-        <v>82.49325396825397</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>81902.77777777778</v>
+        <v>21666.66666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>31479365.07936508</v>
+        <v>4822222.222222222</v>
       </c>
       <c r="H12" t="n">
-        <v>83.94484126984128</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="I12" t="n">
-        <v>2.840079365079365</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1511,220 +1511,864 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>27.66172683747412</v>
+        <v>26.30574758393386</v>
       </c>
       <c r="R12" t="n">
-        <v>178.4687976425748</v>
+        <v>180.6359246690129</v>
       </c>
       <c r="S12" t="n">
-        <v>79.31899674148316</v>
+        <v>71.0986921121725</v>
       </c>
       <c r="T12" t="n">
-        <v>72452.39006916995</v>
+        <v>18625.60052511033</v>
       </c>
       <c r="U12" t="n">
-        <v>23741599.43769998</v>
+        <v>3371923.007094576</v>
       </c>
       <c r="V12" t="n">
-        <v>82.05085286090721</v>
+        <v>75.42880635160047</v>
       </c>
       <c r="W12" t="n">
-        <v>2.300772868435912</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>26.80966706295654</v>
+        <v>24.83457653457653</v>
       </c>
       <c r="Y12" t="n">
-        <v>181.3739345693293</v>
+        <v>181.7665667665668</v>
       </c>
       <c r="Z12" t="n">
-        <v>70.84219148298095</v>
+        <v>73.53217893217892</v>
       </c>
       <c r="AA12" t="n">
-        <v>26849.67279309385</v>
+        <v>25977.51507751508</v>
       </c>
       <c r="AB12" t="n">
-        <v>4187981.318145792</v>
+        <v>9638739.593739593</v>
       </c>
       <c r="AC12" t="n">
-        <v>74.13396659383501</v>
+        <v>79.43666426166426</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.047794432662854</v>
+        <v>1.226443926443927</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
+        <v>26.73253968253968</v>
+      </c>
+      <c r="D13" t="n">
+        <v>179.797619047619</v>
+      </c>
+      <c r="E13" t="n">
+        <v>72.21150793650794</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19825.39682539683</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3350952.380952381</v>
+      </c>
+      <c r="H13" t="n">
+        <v>74.94484126984126</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.048015873015873</v>
+      </c>
+      <c r="J13" t="n">
         <v>29.125</v>
       </c>
-      <c r="D13" t="n">
+      <c r="K13" t="n">
         <v>183.75</v>
       </c>
-      <c r="E13" t="n">
+      <c r="L13" t="n">
         <v>77.875</v>
       </c>
-      <c r="F13" t="n">
+      <c r="M13" t="n">
         <v>36000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="N13" t="n">
         <v>12400000</v>
       </c>
-      <c r="H13" t="n">
+      <c r="O13" t="n">
         <v>80</v>
       </c>
-      <c r="I13" t="n">
+      <c r="P13" t="n">
         <v>1.875</v>
       </c>
-      <c r="J13" t="n">
-        <v>27.7108024691358</v>
-      </c>
-      <c r="K13" t="n">
-        <v>181.3882716049383</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75.30617283950617</v>
-      </c>
-      <c r="M13" t="n">
-        <v>28387.65432098765</v>
-      </c>
-      <c r="N13" t="n">
-        <v>8170679.012345678</v>
-      </c>
-      <c r="O13" t="n">
-        <v>77.47870370370372</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.330555555555555</v>
-      </c>
       <c r="Q13" t="n">
-        <v>25.96385526882818</v>
+        <v>26.71215645678561</v>
       </c>
       <c r="R13" t="n">
-        <v>180.808568508375</v>
+        <v>179.619295247859</v>
       </c>
       <c r="S13" t="n">
-        <v>74.3223437553159</v>
+        <v>71.44997263172657</v>
       </c>
       <c r="T13" t="n">
-        <v>32067.67484321664</v>
+        <v>18474.51589655117</v>
       </c>
       <c r="U13" t="n">
-        <v>8627637.036596015</v>
+        <v>3150261.760183351</v>
       </c>
       <c r="V13" t="n">
-        <v>79.3893702015219</v>
+        <v>74.66286436401526</v>
       </c>
       <c r="W13" t="n">
-        <v>1.519061865636943</v>
+        <v>1.053139895904736</v>
       </c>
       <c r="X13" t="n">
-        <v>25.31367242053516</v>
+        <v>26.02015893176884</v>
       </c>
       <c r="Y13" t="n">
-        <v>180.779184822077</v>
+        <v>180.6925837721504</v>
       </c>
       <c r="Z13" t="n">
-        <v>72.10735154460644</v>
+        <v>74.38456699818929</v>
       </c>
       <c r="AA13" t="n">
-        <v>23794.00033517681</v>
+        <v>32345.98019369692</v>
       </c>
       <c r="AB13" t="n">
-        <v>6596232.926931456</v>
+        <v>8564435.535797765</v>
       </c>
       <c r="AC13" t="n">
-        <v>76.4877262443439</v>
+        <v>79.38532253207177</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.134260655829283</v>
+        <v>1.526747802134799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.2797619047619</v>
+        <v>28.55333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>180.1746031746032</v>
+        <v>180.0000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>81.13690476190474</v>
+        <v>74.52666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>119696.4285714286</v>
+        <v>19257.77777777778</v>
       </c>
       <c r="G14" t="n">
-        <v>40428968.25396825</v>
+        <v>6149777.777777778</v>
       </c>
       <c r="H14" t="n">
-        <v>86.67460317460316</v>
+        <v>76.60666666666665</v>
       </c>
       <c r="I14" t="n">
-        <v>2.811507936507937</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>1.391111111111111</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.75231481481481</v>
+      </c>
+      <c r="K14" t="n">
+        <v>181.7361111111111</v>
+      </c>
+      <c r="L14" t="n">
+        <v>72.91898148148148</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22638.88888888889</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4527314.814814814</v>
+      </c>
+      <c r="O14" t="n">
+        <v>76.58101851851852</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.041666666666667</v>
+      </c>
       <c r="Q14" t="n">
-        <v>21.06835412394623</v>
+        <v>29.3528497168848</v>
       </c>
       <c r="R14" t="n">
-        <v>181.4228587567403</v>
+        <v>178.1869186856029</v>
       </c>
       <c r="S14" t="n">
-        <v>71.01955029619504</v>
+        <v>74.90511927968068</v>
       </c>
       <c r="T14" t="n">
-        <v>62807.47512721198</v>
+        <v>20557.44569757728</v>
       </c>
       <c r="U14" t="n">
-        <v>18113949.67057796</v>
+        <v>7296515.13041864</v>
       </c>
       <c r="V14" t="n">
-        <v>81.01018217893217</v>
+        <v>76.29490624709923</v>
       </c>
       <c r="W14" t="n">
-        <v>1.577206273258905</v>
+        <v>1.5062447786132</v>
       </c>
       <c r="X14" t="n">
-        <v>24.76032717282717</v>
+        <v>24.97263908930576</v>
       </c>
       <c r="Y14" t="n">
-        <v>181.8981018981019</v>
+        <v>180.152042142393</v>
       </c>
       <c r="Z14" t="n">
-        <v>73.47370129870129</v>
+        <v>72.35277587909167</v>
       </c>
       <c r="AA14" t="n">
-        <v>25885.41874791875</v>
+        <v>24523.76015797068</v>
       </c>
       <c r="AB14" t="n">
-        <v>9693582.042957043</v>
+        <v>4804105.507877437</v>
       </c>
       <c r="AC14" t="n">
-        <v>79.45553300865801</v>
+        <v>76.93262997561243</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.254749417249418</v>
+        <v>1.05495008565184</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28.075</v>
+      </c>
+      <c r="D15" t="n">
+        <v>180</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20475</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7222500</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.12962962962963</v>
+      </c>
+      <c r="K15" t="n">
+        <v>181.5925925925926</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79.17037037037036</v>
+      </c>
+      <c r="M15" t="n">
+        <v>40753.70370370371</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20435185.18518519</v>
+      </c>
+      <c r="O15" t="n">
+        <v>82.37962962962963</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.874074074074074</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>26.86751328211596</v>
+      </c>
+      <c r="R15" t="n">
+        <v>178.2457435118297</v>
+      </c>
+      <c r="S15" t="n">
+        <v>72.71045417192219</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20442.78121775026</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5056790.505675955</v>
+      </c>
+      <c r="V15" t="n">
+        <v>74.97944329778696</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.107605683598976</v>
+      </c>
+      <c r="X15" t="n">
+        <v>26.82161319073084</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>180.3873885918003</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75.27339572192513</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>33451.24777183601</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10761657.75401069</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>79.73877005347593</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.381238859180036</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>27.43395061728395</v>
+      </c>
+      <c r="D16" t="n">
+        <v>183.2533950617284</v>
+      </c>
+      <c r="E16" t="n">
+        <v>85.84320987654321</v>
+      </c>
+      <c r="F16" t="n">
+        <v>230658.9506172839</v>
+      </c>
+      <c r="G16" t="n">
+        <v>69586574.07407409</v>
+      </c>
+      <c r="H16" t="n">
+        <v>88.31851851851852</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.545679012345679</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.02604166666666</v>
+      </c>
+      <c r="K16" t="n">
+        <v>180.0902777777778</v>
+      </c>
+      <c r="L16" t="n">
+        <v>80.71354166666666</v>
+      </c>
+      <c r="M16" t="n">
+        <v>117109.375</v>
+      </c>
+      <c r="N16" t="n">
+        <v>39473784.72222222</v>
+      </c>
+      <c r="O16" t="n">
+        <v>86.55902777777777</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.756944444444445</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25.57446581196582</v>
+      </c>
+      <c r="R16" t="n">
+        <v>180.1547008547008</v>
+      </c>
+      <c r="S16" t="n">
+        <v>79.73514957264956</v>
+      </c>
+      <c r="T16" t="n">
+        <v>135756.7782526116</v>
+      </c>
+      <c r="U16" t="n">
+        <v>39158346.39126305</v>
+      </c>
+      <c r="V16" t="n">
+        <v>85.22663817663816</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.228952991452992</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21.28298144350776</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>181.4437756850037</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>71.5976249546425</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>66631.33591554646</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>20068881.18866189</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>81.24979156645823</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.65504755153878</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>27.57291666666666</v>
+      </c>
+      <c r="K17" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="L17" t="n">
+        <v>73.39756944444444</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22388.88888888889</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6500043.402777778</v>
+      </c>
+      <c r="O17" t="n">
+        <v>77.22569444444444</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.383680555555556</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>26.80966706295654</v>
+      </c>
+      <c r="R17" t="n">
+        <v>181.3739345693293</v>
+      </c>
+      <c r="S17" t="n">
+        <v>70.84219148298095</v>
+      </c>
+      <c r="T17" t="n">
+        <v>26849.67279309385</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4187981.318145792</v>
+      </c>
+      <c r="V17" t="n">
+        <v>74.13396659383501</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.047794432662854</v>
+      </c>
+      <c r="X17" t="n">
+        <v>26.29946002856219</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>179.8795644786357</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>71.13988216232798</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>21169.28741193447</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5627045.145543598</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>75.79318580169974</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.266432383692446</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.73715277777778</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181.4493055555556</v>
+      </c>
+      <c r="E18" t="n">
+        <v>75.39444444444445</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28398.61111111111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8162326.388888889</v>
+      </c>
+      <c r="H18" t="n">
+        <v>77.55104166666666</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.334375</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.0891975308642</v>
+      </c>
+      <c r="K18" t="n">
+        <v>182.3342592592593</v>
+      </c>
+      <c r="L18" t="n">
+        <v>76.22037037037038</v>
+      </c>
+      <c r="M18" t="n">
+        <v>35962.34567901235</v>
+      </c>
+      <c r="N18" t="n">
+        <v>17576697.5308642</v>
+      </c>
+      <c r="O18" t="n">
+        <v>81.32345679012344</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.246913580246914</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25.36538147310206</v>
+      </c>
+      <c r="R18" t="n">
+        <v>180.9265829248366</v>
+      </c>
+      <c r="S18" t="n">
+        <v>72.05827048768225</v>
+      </c>
+      <c r="T18" t="n">
+        <v>23872.80040221217</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6810762.042797888</v>
+      </c>
+      <c r="V18" t="n">
+        <v>76.44869202488688</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.151043237807944</v>
+      </c>
+      <c r="X18" t="n">
+        <v>24.24859666000017</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>178.445251597006</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>72.34763550289865</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>27468.70332396648</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8009908.124688826</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>78.66827126739408</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.032856130224551</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>29.35243055555556</v>
+      </c>
+      <c r="K19" t="n">
+        <v>181.5163194444445</v>
+      </c>
+      <c r="L19" t="n">
+        <v>82.40381944444445</v>
+      </c>
+      <c r="M19" t="n">
+        <v>81734.375</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30995833.33333333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>83.86840277777779</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.818402777777778</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22.98747762654013</v>
+      </c>
+      <c r="R19" t="n">
+        <v>181.8022092490842</v>
+      </c>
+      <c r="S19" t="n">
+        <v>71.66532998251748</v>
+      </c>
+      <c r="T19" t="n">
+        <v>23298.84490509491</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6826495.457667332</v>
+      </c>
+      <c r="V19" t="n">
+        <v>80.40415834165833</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.215618756243756</v>
+      </c>
+      <c r="X19" t="n">
+        <v>27.66009705814693</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>178.743506401243</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>79.35544808393274</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>72722.38594383736</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23940245.25181175</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>82.05173849074104</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.300033399394013</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="D20" t="n">
+        <v>180.9388888888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.37222222222222</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39994.44444444444</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22137500</v>
+      </c>
+      <c r="H20" t="n">
+        <v>81.76388888888889</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26.89484126984127</v>
+      </c>
+      <c r="K20" t="n">
+        <v>182.6904761904762</v>
+      </c>
+      <c r="L20" t="n">
+        <v>76.24603174603173</v>
+      </c>
+      <c r="M20" t="n">
+        <v>31642.85714285714</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11010119.04761905</v>
+      </c>
+      <c r="O20" t="n">
+        <v>79.70238095238096</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.192460317460317</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>24.07334502824699</v>
+      </c>
+      <c r="R20" t="n">
+        <v>181.4085856228013</v>
+      </c>
+      <c r="S20" t="n">
+        <v>71.53713700968602</v>
+      </c>
+      <c r="T20" t="n">
+        <v>29226.88957737977</v>
+      </c>
+      <c r="U20" t="n">
+        <v>11202815.47972725</v>
+      </c>
+      <c r="V20" t="n">
+        <v>78.2765191598525</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.552799705740882</v>
+      </c>
+      <c r="X20" t="n">
+        <v>26.77756722122047</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>178.3035467313331</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>73.02892197814798</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>27216.86022812184</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6607925.986408959</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>76.78535294684677</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.144363375129629</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="D21" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30525</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11722500</v>
+      </c>
+      <c r="H21" t="n">
+        <v>78.72499999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.79968434343434</v>
+      </c>
+      <c r="K21" t="n">
+        <v>183.2188446969697</v>
+      </c>
+      <c r="L21" t="n">
+        <v>78.56562500000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>33155.17676767677</v>
+      </c>
+      <c r="N21" t="n">
+        <v>22962840.90909091</v>
+      </c>
+      <c r="O21" t="n">
+        <v>81.84962121212121</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.851988636363636</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>26.57446041612708</v>
+      </c>
+      <c r="R21" t="n">
+        <v>181.2095711387378</v>
+      </c>
+      <c r="S21" t="n">
+        <v>74.8960211085211</v>
+      </c>
+      <c r="T21" t="n">
+        <v>27301.66623499956</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8977804.541137874</v>
+      </c>
+      <c r="V21" t="n">
+        <v>78.22657450574118</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.256034706034706</v>
+      </c>
+      <c r="X21" t="n">
+        <v>26.69617733058136</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>182.6735788613691</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>75.61111433608531</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>29851.79738562092</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15005314.00498796</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>79.62075163398693</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.448418687650499</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,86 @@
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -585,25 +665,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.75231481481481</v>
+        <v>25.85277777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>181.7361111111111</v>
+        <v>182.2583333333334</v>
       </c>
       <c r="E2" t="n">
-        <v>72.91898148148148</v>
+        <v>72.85277777777779</v>
       </c>
       <c r="F2" t="n">
-        <v>22638.88888888889</v>
+        <v>22116.66666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>4527314.814814814</v>
+        <v>4475277.777777778</v>
       </c>
       <c r="H2" t="n">
-        <v>76.58101851851852</v>
+        <v>76.44722222222222</v>
       </c>
       <c r="I2" t="n">
-        <v>1.041666666666667</v>
+        <v>1.05</v>
       </c>
       <c r="J2" t="n">
         <v>26.73253968253968</v>
@@ -627,25 +707,25 @@
         <v>1.048015873015873</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.97263908930576</v>
+        <v>24.93632423862687</v>
       </c>
       <c r="R2" t="n">
-        <v>180.152042142393</v>
+        <v>180.0855210944027</v>
       </c>
       <c r="S2" t="n">
-        <v>72.35277587909167</v>
+        <v>72.52187286397813</v>
       </c>
       <c r="T2" t="n">
-        <v>24523.76015797068</v>
+        <v>24681.33544087491</v>
       </c>
       <c r="U2" t="n">
-        <v>4804105.507877437</v>
+        <v>4977151.59109896</v>
       </c>
       <c r="V2" t="n">
-        <v>76.93262997561243</v>
+        <v>77.08210345940608</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05495008565184</v>
+        <v>1.06181884635832</v>
       </c>
       <c r="X2" t="n">
         <v>26.71215645678561</v>
@@ -668,6 +748,38 @@
       <c r="AD2" t="n">
         <v>1.053139895904736</v>
       </c>
+      <c r="AE2" t="n">
+        <v>25.91666666666667</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>180.9166666666667</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>83</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>21833.33333333333</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3283333.333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -761,6 +873,38 @@
       </c>
       <c r="AD3" t="n">
         <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>28.18518518518519</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>180.4074074074074</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>115.4444444444444</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>30111.11111111111</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6777777.777777778</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>115.5555555555556</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.555555555555556</v>
       </c>
     </row>
     <row r="4">
@@ -801,25 +945,25 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>26.77756722122047</v>
+        <v>26.86741018269656</v>
       </c>
       <c r="R4" t="n">
-        <v>178.3035467313331</v>
+        <v>178.6061959551027</v>
       </c>
       <c r="S4" t="n">
-        <v>73.02892197814798</v>
+        <v>72.9516548724753</v>
       </c>
       <c r="T4" t="n">
-        <v>27216.86022812184</v>
+        <v>27001.32069781354</v>
       </c>
       <c r="U4" t="n">
-        <v>6607925.986408959</v>
+        <v>6369762.322945373</v>
       </c>
       <c r="V4" t="n">
-        <v>76.78535294684677</v>
+        <v>76.61146324167319</v>
       </c>
       <c r="W4" t="n">
-        <v>1.144363375129629</v>
+        <v>1.155055855844362</v>
       </c>
       <c r="X4" t="n">
         <v>22.98747762654013</v>
@@ -842,6 +986,22 @@
       <c r="AD4" t="n">
         <v>1.215618756243756</v>
       </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -936,6 +1096,22 @@
       <c r="AD5" t="n">
         <v>1.552799705740882</v>
       </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -947,25 +1123,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>27.57291666666666</v>
+        <v>27.54761904761904</v>
       </c>
       <c r="D6" t="n">
-        <v>181.1666666666667</v>
+        <v>181.3690476190476</v>
       </c>
       <c r="E6" t="n">
-        <v>73.39756944444444</v>
+        <v>73.11507936507937</v>
       </c>
       <c r="F6" t="n">
-        <v>22388.88888888889</v>
+        <v>22123.01587301588</v>
       </c>
       <c r="G6" t="n">
-        <v>6500043.402777778</v>
+        <v>6289335.317460318</v>
       </c>
       <c r="H6" t="n">
-        <v>77.22569444444444</v>
+        <v>77.09722222222221</v>
       </c>
       <c r="I6" t="n">
-        <v>1.383680555555556</v>
+        <v>1.384920634920635</v>
       </c>
       <c r="J6" t="n">
         <v>27.43395061728395</v>
@@ -989,25 +1165,25 @@
         <v>3.545679012345679</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.29946002856219</v>
+        <v>26.38802889576883</v>
       </c>
       <c r="R6" t="n">
-        <v>179.8795644786357</v>
+        <v>179.7167827657379</v>
       </c>
       <c r="S6" t="n">
-        <v>71.13988216232798</v>
+        <v>71.33350379625534</v>
       </c>
       <c r="T6" t="n">
-        <v>21169.28741193447</v>
+        <v>21326.81197478992</v>
       </c>
       <c r="U6" t="n">
-        <v>5627045.145543598</v>
+        <v>5721050.788736547</v>
       </c>
       <c r="V6" t="n">
-        <v>75.79318580169974</v>
+        <v>75.96619766327584</v>
       </c>
       <c r="W6" t="n">
-        <v>1.266432383692446</v>
+        <v>1.277009158926729</v>
       </c>
       <c r="X6" t="n">
         <v>25.57446581196582</v>
@@ -1030,6 +1206,22 @@
       <c r="AD6" t="n">
         <v>2.228952991452992</v>
       </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1123,6 +1315,54 @@
       </c>
       <c r="AD7" t="n">
         <v>1.5062447786132</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23.40740740740741</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>178.0185185185185</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>170.5555555555555</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>56444.44444444445</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18011111.11111111</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>179.2037037037037</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>152.2222222222222</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>36666.66666666666</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9327777.777777778</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>167.2222222222222</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1184,25 +1424,73 @@
         <v>2.300033399394013</v>
       </c>
       <c r="X8" t="n">
-        <v>26.80966706295654</v>
+        <v>26.75702929197995</v>
       </c>
       <c r="Y8" t="n">
-        <v>181.3739345693293</v>
+        <v>180.9975994674186</v>
       </c>
       <c r="Z8" t="n">
-        <v>70.84219148298095</v>
+        <v>70.6782346491228</v>
       </c>
       <c r="AA8" t="n">
-        <v>26849.67279309385</v>
+        <v>26455.88189223058</v>
       </c>
       <c r="AB8" t="n">
-        <v>4187981.318145792</v>
+        <v>4007152.059837093</v>
       </c>
       <c r="AC8" t="n">
-        <v>74.13396659383501</v>
+        <v>74.10263549498745</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.047794432662854</v>
+        <v>1.044153352130326</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>165.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>123500</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>37275000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>173.125</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -1297,6 +1585,54 @@
       </c>
       <c r="AD9" t="n">
         <v>1.151043237807944</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>28.26041666666667</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>183.15625</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>156625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>65062500</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>289.625</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>181.2083333333333</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>133</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9833333.333333334</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1358,25 +1694,73 @@
         <v>1.65504755153878</v>
       </c>
       <c r="X10" t="n">
-        <v>24.83457653457653</v>
+        <v>24.9388986013986</v>
       </c>
       <c r="Y10" t="n">
-        <v>181.7665667665668</v>
+        <v>181.6748876123876</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.53217893217892</v>
+        <v>73.6612012987013</v>
       </c>
       <c r="AA10" t="n">
-        <v>25977.51507751508</v>
+        <v>26203.87112887113</v>
       </c>
       <c r="AB10" t="n">
-        <v>9638739.593739593</v>
+        <v>9506082.042957043</v>
       </c>
       <c r="AC10" t="n">
-        <v>79.43666426166426</v>
+        <v>79.34541396103896</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.226443926443927</v>
+        <v>1.233916083916084</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24.71666666666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>180.6166666666667</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>331.875</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>533250</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>222700000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>13.375</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>185.0625</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>97.625</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>41250</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>19875000</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1410,25 +1794,25 @@
         <v>1.246913580246914</v>
       </c>
       <c r="J11" t="n">
-        <v>28.075</v>
+        <v>28.15625</v>
       </c>
       <c r="K11" t="n">
-        <v>180</v>
+        <v>179.9375</v>
       </c>
       <c r="L11" t="n">
-        <v>75.34999999999999</v>
+        <v>75.34375</v>
       </c>
       <c r="M11" t="n">
-        <v>20475</v>
+        <v>20625</v>
       </c>
       <c r="N11" t="n">
-        <v>7222500</v>
+        <v>7131250</v>
       </c>
       <c r="O11" t="n">
-        <v>77.625</v>
+        <v>77.46875</v>
       </c>
       <c r="P11" t="n">
-        <v>1.175</v>
+        <v>1.1875</v>
       </c>
       <c r="Q11" t="n">
         <v>24.24859666000017</v>
@@ -1452,25 +1836,73 @@
         <v>1.032856130224551</v>
       </c>
       <c r="X11" t="n">
-        <v>26.86751328211596</v>
+        <v>26.88428577571379</v>
       </c>
       <c r="Y11" t="n">
-        <v>178.2457435118297</v>
+        <v>178.3181281174751</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.71045417192219</v>
+        <v>72.67426094341246</v>
       </c>
       <c r="AA11" t="n">
-        <v>20442.78121775026</v>
+        <v>20436.80985552116</v>
       </c>
       <c r="AB11" t="n">
-        <v>5056790.505675955</v>
+        <v>5093889.318885449</v>
       </c>
       <c r="AC11" t="n">
-        <v>74.97944329778696</v>
+        <v>74.98520704334365</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.107605683598976</v>
+        <v>1.112723060715514</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>27.17592592592593</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.777777777777778</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>291.7777777777778</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>148222.2222222222</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>53411111.11111111</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>298.2222222222222</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>27.77083333333334</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>181.0833333333333</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>50250</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14700000</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.125</v>
       </c>
     </row>
     <row r="12">
@@ -1532,25 +1964,73 @@
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>24.83457653457653</v>
+        <v>24.9388986013986</v>
       </c>
       <c r="Y12" t="n">
-        <v>181.7665667665668</v>
+        <v>181.6748876123876</v>
       </c>
       <c r="Z12" t="n">
-        <v>73.53217893217892</v>
+        <v>73.6612012987013</v>
       </c>
       <c r="AA12" t="n">
-        <v>25977.51507751508</v>
+        <v>26203.87112887113</v>
       </c>
       <c r="AB12" t="n">
-        <v>9638739.593739593</v>
+        <v>9506082.042957043</v>
       </c>
       <c r="AC12" t="n">
-        <v>79.43666426166426</v>
+        <v>79.34541396103896</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.226443926443927</v>
+        <v>1.233916083916084</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>28.18518518518519</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>180.4074074074074</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>115.4444444444444</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>30111.11111111111</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>6777777.777777778</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>115.5555555555556</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>185.0625</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>97.625</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>41250</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19875000</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1646,6 +2126,54 @@
       <c r="AD13" t="n">
         <v>1.526747802134799</v>
       </c>
+      <c r="AE13" t="n">
+        <v>28.52777777777778</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>177.6481481481482</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>123.5555555555556</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>31111.11111111111</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2841666.666666667</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>125.6666666666667</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>28.26041666666667</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>183.15625</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>156625</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>65062500</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>289.625</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.625</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1678,25 +2206,25 @@
         <v>1.391111111111111</v>
       </c>
       <c r="J14" t="n">
-        <v>25.75231481481481</v>
+        <v>25.85277777777778</v>
       </c>
       <c r="K14" t="n">
-        <v>181.7361111111111</v>
+        <v>182.2583333333334</v>
       </c>
       <c r="L14" t="n">
-        <v>72.91898148148148</v>
+        <v>72.85277777777779</v>
       </c>
       <c r="M14" t="n">
-        <v>22638.88888888889</v>
+        <v>22116.66666666667</v>
       </c>
       <c r="N14" t="n">
-        <v>4527314.814814814</v>
+        <v>4475277.777777778</v>
       </c>
       <c r="O14" t="n">
-        <v>76.58101851851852</v>
+        <v>76.44722222222222</v>
       </c>
       <c r="P14" t="n">
-        <v>1.041666666666667</v>
+        <v>1.05</v>
       </c>
       <c r="Q14" t="n">
         <v>29.3528497168848</v>
@@ -1720,25 +2248,73 @@
         <v>1.5062447786132</v>
       </c>
       <c r="X14" t="n">
-        <v>24.97263908930576</v>
+        <v>24.93632423862687</v>
       </c>
       <c r="Y14" t="n">
-        <v>180.152042142393</v>
+        <v>180.0855210944027</v>
       </c>
       <c r="Z14" t="n">
-        <v>72.35277587909167</v>
+        <v>72.52187286397813</v>
       </c>
       <c r="AA14" t="n">
-        <v>24523.76015797068</v>
+        <v>24681.33544087491</v>
       </c>
       <c r="AB14" t="n">
-        <v>4804105.507877437</v>
+        <v>4977151.59109896</v>
       </c>
       <c r="AC14" t="n">
-        <v>76.93262997561243</v>
+        <v>77.08210345940608</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05495008565184</v>
+        <v>1.06181884635832</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>179.2037037037037</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>152.2222222222222</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>36666.66666666666</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>9327777.777777778</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>167.2222222222222</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>25.91666666666667</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>180.9166666666667</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>83</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>21833.33333333333</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3283333.333333333</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>88</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -1751,25 +2327,25 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>28.075</v>
+        <v>28.15625</v>
       </c>
       <c r="D15" t="n">
-        <v>180</v>
+        <v>179.9375</v>
       </c>
       <c r="E15" t="n">
-        <v>75.34999999999999</v>
+        <v>75.34375</v>
       </c>
       <c r="F15" t="n">
-        <v>20475</v>
+        <v>20625</v>
       </c>
       <c r="G15" t="n">
-        <v>7222500</v>
+        <v>7131250</v>
       </c>
       <c r="H15" t="n">
-        <v>77.625</v>
+        <v>77.46875</v>
       </c>
       <c r="I15" t="n">
-        <v>1.175</v>
+        <v>1.1875</v>
       </c>
       <c r="J15" t="n">
         <v>26.12962962962963</v>
@@ -1793,25 +2369,25 @@
         <v>1.874074074074074</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.86751328211596</v>
+        <v>26.88428577571379</v>
       </c>
       <c r="R15" t="n">
-        <v>178.2457435118297</v>
+        <v>178.3181281174751</v>
       </c>
       <c r="S15" t="n">
-        <v>72.71045417192219</v>
+        <v>72.67426094341246</v>
       </c>
       <c r="T15" t="n">
-        <v>20442.78121775026</v>
+        <v>20436.80985552116</v>
       </c>
       <c r="U15" t="n">
-        <v>5056790.505675955</v>
+        <v>5093889.318885449</v>
       </c>
       <c r="V15" t="n">
-        <v>74.97944329778696</v>
+        <v>74.98520704334365</v>
       </c>
       <c r="W15" t="n">
-        <v>1.107605683598976</v>
+        <v>1.112723060715514</v>
       </c>
       <c r="X15" t="n">
         <v>26.82161319073084</v>
@@ -1833,6 +2409,54 @@
       </c>
       <c r="AD15" t="n">
         <v>1.381238859180036</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>27.77083333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>181.0833333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50250</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>14700000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>179.7708333333333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>194.25</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>54875</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14462500</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>225.625</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -1927,6 +2551,54 @@
       </c>
       <c r="AD16" t="n">
         <v>1.65504755153878</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>23.12037037037037</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>180.5740740740741</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>186.4444444444445</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>417666.6666666667</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>177511111.1111111</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>197.5555555555555</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>7.555555555555555</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>24.71666666666667</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>180.6166666666667</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>331.875</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>533250</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>222700000</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13.375</v>
       </c>
     </row>
     <row r="17">
@@ -1946,67 +2618,115 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>27.57291666666666</v>
+        <v>27.54761904761904</v>
       </c>
       <c r="K17" t="n">
-        <v>181.1666666666667</v>
+        <v>181.3690476190476</v>
       </c>
       <c r="L17" t="n">
-        <v>73.39756944444444</v>
+        <v>73.11507936507937</v>
       </c>
       <c r="M17" t="n">
-        <v>22388.88888888889</v>
+        <v>22123.01587301588</v>
       </c>
       <c r="N17" t="n">
-        <v>6500043.402777778</v>
+        <v>6289335.317460318</v>
       </c>
       <c r="O17" t="n">
-        <v>77.22569444444444</v>
+        <v>77.09722222222221</v>
       </c>
       <c r="P17" t="n">
-        <v>1.383680555555556</v>
+        <v>1.384920634920635</v>
       </c>
       <c r="Q17" t="n">
-        <v>26.80966706295654</v>
+        <v>26.75702929197995</v>
       </c>
       <c r="R17" t="n">
-        <v>181.3739345693293</v>
+        <v>180.9975994674186</v>
       </c>
       <c r="S17" t="n">
-        <v>70.84219148298095</v>
+        <v>70.6782346491228</v>
       </c>
       <c r="T17" t="n">
-        <v>26849.67279309385</v>
+        <v>26455.88189223058</v>
       </c>
       <c r="U17" t="n">
-        <v>4187981.318145792</v>
+        <v>4007152.059837093</v>
       </c>
       <c r="V17" t="n">
-        <v>74.13396659383501</v>
+        <v>74.10263549498745</v>
       </c>
       <c r="W17" t="n">
-        <v>1.047794432662854</v>
+        <v>1.044153352130326</v>
       </c>
       <c r="X17" t="n">
-        <v>26.29946002856219</v>
+        <v>26.38802889576883</v>
       </c>
       <c r="Y17" t="n">
-        <v>179.8795644786357</v>
+        <v>179.7167827657379</v>
       </c>
       <c r="Z17" t="n">
-        <v>71.13988216232798</v>
+        <v>71.33350379625534</v>
       </c>
       <c r="AA17" t="n">
-        <v>21169.28741193447</v>
+        <v>21326.81197478992</v>
       </c>
       <c r="AB17" t="n">
-        <v>5627045.145543598</v>
+        <v>5721050.788736547</v>
       </c>
       <c r="AC17" t="n">
-        <v>75.79318580169974</v>
+        <v>75.96619766327584</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.266432383692446</v>
+        <v>1.277009158926729</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>27.08125</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>178.4958333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>226.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>66625</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11368750</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.375</v>
       </c>
     </row>
     <row r="18">
@@ -2101,6 +2821,54 @@
       </c>
       <c r="AD18" t="n">
         <v>1.032856130224551</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>181.2083333333333</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>133</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>9833333.333333334</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>27.17592592592593</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>181.4166666666667</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.777777777777778</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>291.7777777777778</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>148222.2222222222</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>53411111.11111111</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>298.2222222222222</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -2182,6 +2950,54 @@
       <c r="AD19" t="n">
         <v>2.300033399394013</v>
       </c>
+      <c r="AE19" t="n">
+        <v>29.9625</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>181.2625</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>315.625</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>129375</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>47306250</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>165.75</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>123500</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>37275000</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>173.125</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.875</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2256,25 +3072,73 @@
         <v>1.552799705740882</v>
       </c>
       <c r="X20" t="n">
-        <v>26.77756722122047</v>
+        <v>26.86741018269656</v>
       </c>
       <c r="Y20" t="n">
-        <v>178.3035467313331</v>
+        <v>178.6061959551027</v>
       </c>
       <c r="Z20" t="n">
-        <v>73.02892197814798</v>
+        <v>72.9516548724753</v>
       </c>
       <c r="AA20" t="n">
-        <v>27216.86022812184</v>
+        <v>27001.32069781354</v>
       </c>
       <c r="AB20" t="n">
-        <v>6607925.986408959</v>
+        <v>6369762.322945373</v>
       </c>
       <c r="AC20" t="n">
-        <v>76.78535294684677</v>
+        <v>76.61146324167319</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.144363375129629</v>
+        <v>1.155055855844362</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>26.00925925925926</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.888888888888889</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>224</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>106000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>47855555.55555555</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>237.3333333333333</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>4.555555555555555</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>27.54166666666666</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>178</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>43500</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>112.625</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
@@ -2369,6 +3233,54 @@
       </c>
       <c r="AD21" t="n">
         <v>1.448418687650499</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>23.40740740740741</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>178.0185185185185</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>170.5555555555555</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>56444.44444444445</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>18011111.11111111</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>184.4444444444445</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>27.17916666666667</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>183.79375</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>129000</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>116887500</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>301.625</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.125</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -986,14 +986,30 @@
       <c r="AD4" t="n">
         <v>1.215618756243756</v>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>27.54166666666666</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>178</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>43500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>112.625</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
@@ -1316,54 +1332,22 @@
       <c r="AD7" t="n">
         <v>1.5062447786132</v>
       </c>
-      <c r="AE7" t="n">
-        <v>23.40740740740741</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>178.0185185185185</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>170.5555555555555</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>56444.44444444445</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18011111.11111111</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>184.4444444444445</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>179.2037037037037</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.222222222222222</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>152.2222222222222</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>36666.66666666666</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>9327777.777777778</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>167.2222222222222</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3</v>
-      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1645,25 +1629,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.02604166666666</v>
+        <v>24.94047619047619</v>
       </c>
       <c r="D10" t="n">
-        <v>180.0902777777778</v>
+        <v>180.031746031746</v>
       </c>
       <c r="E10" t="n">
-        <v>80.71354166666666</v>
+        <v>80.72619047619047</v>
       </c>
       <c r="F10" t="n">
-        <v>117109.375</v>
+        <v>117035.7142857143</v>
       </c>
       <c r="G10" t="n">
-        <v>39473784.72222222</v>
+        <v>40066468.25396825</v>
       </c>
       <c r="H10" t="n">
-        <v>86.55902777777777</v>
+        <v>86.56746031746032</v>
       </c>
       <c r="I10" t="n">
-        <v>2.756944444444445</v>
+        <v>2.757936507936508</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1673,25 +1657,25 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>21.28298144350776</v>
+        <v>21.24196523505734</v>
       </c>
       <c r="R10" t="n">
-        <v>181.4437756850037</v>
+        <v>181.3048032011848</v>
       </c>
       <c r="S10" t="n">
-        <v>71.5976249546425</v>
+        <v>71.38760585175058</v>
       </c>
       <c r="T10" t="n">
-        <v>66631.33591554646</v>
+        <v>65488.03068276752</v>
       </c>
       <c r="U10" t="n">
-        <v>20068881.18866189</v>
+        <v>19147977.44835574</v>
       </c>
       <c r="V10" t="n">
-        <v>81.24979156645823</v>
+        <v>81.2324044011544</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65504755153878</v>
+        <v>1.632761828814461</v>
       </c>
       <c r="X10" t="n">
         <v>24.9388986013986</v>
@@ -1715,28 +1699,28 @@
         <v>1.233916083916084</v>
       </c>
       <c r="AE10" t="n">
-        <v>24.71666666666667</v>
+        <v>24.9047619047619</v>
       </c>
       <c r="AF10" t="n">
-        <v>180.6166666666667</v>
+        <v>180.7619047619048</v>
       </c>
       <c r="AG10" t="n">
-        <v>4</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="AH10" t="n">
-        <v>331.875</v>
+        <v>322.7142857142857</v>
       </c>
       <c r="AI10" t="n">
-        <v>533250</v>
+        <v>524428.5714285715</v>
       </c>
       <c r="AJ10" t="n">
-        <v>222700000</v>
+        <v>220285714.2857143</v>
       </c>
       <c r="AK10" t="n">
-        <v>348.5</v>
+        <v>337.1428571428572</v>
       </c>
       <c r="AL10" t="n">
-        <v>13.375</v>
+        <v>13.28571428571429</v>
       </c>
       <c r="AM10" t="n">
         <v>27.25</v>
@@ -1773,25 +1757,25 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>24.0891975308642</v>
+        <v>24.21284722222222</v>
       </c>
       <c r="D11" t="n">
-        <v>182.3342592592593</v>
+        <v>182.3010416666667</v>
       </c>
       <c r="E11" t="n">
-        <v>76.22037037037038</v>
+        <v>76.19791666666666</v>
       </c>
       <c r="F11" t="n">
-        <v>35962.34567901235</v>
+        <v>36007.63888888889</v>
       </c>
       <c r="G11" t="n">
-        <v>17576697.5308642</v>
+        <v>17368784.72222222</v>
       </c>
       <c r="H11" t="n">
-        <v>81.32345679012344</v>
+        <v>81.15138888888889</v>
       </c>
       <c r="I11" t="n">
-        <v>1.246913580246914</v>
+        <v>1.240277777777778</v>
       </c>
       <c r="J11" t="n">
         <v>28.15625</v>
@@ -1815,25 +1799,25 @@
         <v>1.1875</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.24859666000017</v>
+        <v>24.26651334776335</v>
       </c>
       <c r="R11" t="n">
-        <v>178.445251597006</v>
+        <v>178.2969606782107</v>
       </c>
       <c r="S11" t="n">
-        <v>72.34763550289865</v>
+        <v>72.52924783549784</v>
       </c>
       <c r="T11" t="n">
-        <v>27468.70332396648</v>
+        <v>27790.44913419913</v>
       </c>
       <c r="U11" t="n">
-        <v>8009908.124688826</v>
+        <v>8289765.061327561</v>
       </c>
       <c r="V11" t="n">
-        <v>78.66827126739408</v>
+        <v>78.79127886002885</v>
       </c>
       <c r="W11" t="n">
-        <v>1.032856130224551</v>
+        <v>1.030384199134199</v>
       </c>
       <c r="X11" t="n">
         <v>26.88428577571379</v>
@@ -1857,28 +1841,28 @@
         <v>1.112723060715514</v>
       </c>
       <c r="AE11" t="n">
-        <v>27.17592592592593</v>
+        <v>27.10416666666667</v>
       </c>
       <c r="AF11" t="n">
-        <v>181.4166666666667</v>
+        <v>181.65625</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.777777777777778</v>
+        <v>3.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>291.7777777777778</v>
+        <v>290</v>
       </c>
       <c r="AI11" t="n">
-        <v>148222.2222222222</v>
+        <v>147750</v>
       </c>
       <c r="AJ11" t="n">
-        <v>53411111.11111111</v>
+        <v>54562500</v>
       </c>
       <c r="AK11" t="n">
-        <v>298.2222222222222</v>
+        <v>296.875</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.666666666666667</v>
+        <v>6.625</v>
       </c>
       <c r="AM11" t="n">
         <v>27.77083333333334</v>
@@ -2490,25 +2474,25 @@
         <v>3.545679012345679</v>
       </c>
       <c r="J16" t="n">
-        <v>25.02604166666666</v>
+        <v>24.94047619047619</v>
       </c>
       <c r="K16" t="n">
-        <v>180.0902777777778</v>
+        <v>180.031746031746</v>
       </c>
       <c r="L16" t="n">
-        <v>80.71354166666666</v>
+        <v>80.72619047619047</v>
       </c>
       <c r="M16" t="n">
-        <v>117109.375</v>
+        <v>117035.7142857143</v>
       </c>
       <c r="N16" t="n">
-        <v>39473784.72222222</v>
+        <v>40066468.25396825</v>
       </c>
       <c r="O16" t="n">
-        <v>86.55902777777777</v>
+        <v>86.56746031746032</v>
       </c>
       <c r="P16" t="n">
-        <v>2.756944444444445</v>
+        <v>2.757936507936508</v>
       </c>
       <c r="Q16" t="n">
         <v>25.57446581196582</v>
@@ -2532,25 +2516,25 @@
         <v>2.228952991452992</v>
       </c>
       <c r="X16" t="n">
-        <v>21.28298144350776</v>
+        <v>21.24196523505734</v>
       </c>
       <c r="Y16" t="n">
-        <v>181.4437756850037</v>
+        <v>181.3048032011848</v>
       </c>
       <c r="Z16" t="n">
-        <v>71.5976249546425</v>
+        <v>71.38760585175058</v>
       </c>
       <c r="AA16" t="n">
-        <v>66631.33591554646</v>
+        <v>65488.03068276752</v>
       </c>
       <c r="AB16" t="n">
-        <v>20068881.18866189</v>
+        <v>19147977.44835574</v>
       </c>
       <c r="AC16" t="n">
-        <v>81.24979156645823</v>
+        <v>81.2324044011544</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65504755153878</v>
+        <v>1.632761828814461</v>
       </c>
       <c r="AE16" t="n">
         <v>23.12037037037037</v>
@@ -2577,28 +2561,28 @@
         <v>7.555555555555555</v>
       </c>
       <c r="AM16" t="n">
-        <v>24.71666666666667</v>
+        <v>24.9047619047619</v>
       </c>
       <c r="AN16" t="n">
-        <v>180.6166666666667</v>
+        <v>180.7619047619048</v>
       </c>
       <c r="AO16" t="n">
-        <v>4</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="AP16" t="n">
-        <v>331.875</v>
+        <v>322.7142857142857</v>
       </c>
       <c r="AQ16" t="n">
-        <v>533250</v>
+        <v>524428.5714285715</v>
       </c>
       <c r="AR16" t="n">
-        <v>222700000</v>
+        <v>220285714.2857143</v>
       </c>
       <c r="AS16" t="n">
-        <v>348.5</v>
+        <v>337.1428571428572</v>
       </c>
       <c r="AT16" t="n">
-        <v>13.375</v>
+        <v>13.28571428571429</v>
       </c>
     </row>
     <row r="17">
@@ -2760,25 +2744,25 @@
         <v>1.334375</v>
       </c>
       <c r="J18" t="n">
-        <v>24.0891975308642</v>
+        <v>24.21284722222222</v>
       </c>
       <c r="K18" t="n">
-        <v>182.3342592592593</v>
+        <v>182.3010416666667</v>
       </c>
       <c r="L18" t="n">
-        <v>76.22037037037038</v>
+        <v>76.19791666666666</v>
       </c>
       <c r="M18" t="n">
-        <v>35962.34567901235</v>
+        <v>36007.63888888889</v>
       </c>
       <c r="N18" t="n">
-        <v>17576697.5308642</v>
+        <v>17368784.72222222</v>
       </c>
       <c r="O18" t="n">
-        <v>81.32345679012344</v>
+        <v>81.15138888888889</v>
       </c>
       <c r="P18" t="n">
-        <v>1.246913580246914</v>
+        <v>1.240277777777778</v>
       </c>
       <c r="Q18" t="n">
         <v>25.36538147310206</v>
@@ -2802,25 +2786,25 @@
         <v>1.151043237807944</v>
       </c>
       <c r="X18" t="n">
-        <v>24.24859666000017</v>
+        <v>24.26651334776335</v>
       </c>
       <c r="Y18" t="n">
-        <v>178.445251597006</v>
+        <v>178.2969606782107</v>
       </c>
       <c r="Z18" t="n">
-        <v>72.34763550289865</v>
+        <v>72.52924783549784</v>
       </c>
       <c r="AA18" t="n">
-        <v>27468.70332396648</v>
+        <v>27790.44913419913</v>
       </c>
       <c r="AB18" t="n">
-        <v>8009908.124688826</v>
+        <v>8289765.061327561</v>
       </c>
       <c r="AC18" t="n">
-        <v>78.66827126739408</v>
+        <v>78.79127886002885</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.032856130224551</v>
+        <v>1.030384199134199</v>
       </c>
       <c r="AE18" t="n">
         <v>26.16666666666667</v>
@@ -2847,28 +2831,28 @@
         <v>2.333333333333333</v>
       </c>
       <c r="AM18" t="n">
-        <v>27.17592592592593</v>
+        <v>27.10416666666667</v>
       </c>
       <c r="AN18" t="n">
-        <v>181.4166666666667</v>
+        <v>181.65625</v>
       </c>
       <c r="AO18" t="n">
-        <v>3.777777777777778</v>
+        <v>3.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>291.7777777777778</v>
+        <v>290</v>
       </c>
       <c r="AQ18" t="n">
-        <v>148222.2222222222</v>
+        <v>147750</v>
       </c>
       <c r="AR18" t="n">
-        <v>53411111.11111111</v>
+        <v>54562500</v>
       </c>
       <c r="AS18" t="n">
-        <v>298.2222222222222</v>
+        <v>296.875</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.666666666666667</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="19">

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,40 +576,80 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -618,500 +658,2758 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="D2" t="n">
-        <v>184.03125</v>
-      </c>
-      <c r="E2" t="n">
-        <v>76.375</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30281.25</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11446875</v>
-      </c>
-      <c r="H2" t="n">
-        <v>78.6875</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.40625</v>
-      </c>
-      <c r="J2" t="n">
-        <v>28.55333333333333</v>
-      </c>
-      <c r="K2" t="n">
-        <v>180.0000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>74.52666666666667</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19257.77777777778</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6149777.777777778</v>
-      </c>
-      <c r="O2" t="n">
-        <v>76.60666666666665</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.391111111111111</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>26.54399524087024</v>
+        <v>26.65759943578571</v>
       </c>
       <c r="R2" t="n">
-        <v>181.2016766219891</v>
+        <v>180.8637024467907</v>
       </c>
       <c r="S2" t="n">
-        <v>74.97393283799533</v>
+        <v>71.40054396402437</v>
       </c>
       <c r="T2" t="n">
-        <v>27328.01087801088</v>
+        <v>18857.08200659181</v>
       </c>
       <c r="U2" t="n">
-        <v>9207984.654234655</v>
+        <v>3385071.155242724</v>
       </c>
       <c r="V2" t="n">
-        <v>78.35716904623155</v>
+        <v>75.3232507960449</v>
       </c>
       <c r="W2" t="n">
-        <v>1.265311771561772</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>29.51005116959065</v>
+        <v>24.82531727531727</v>
       </c>
       <c r="Y2" t="n">
-        <v>178.0376644736842</v>
+        <v>181.3036038036038</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.12540204678362</v>
+        <v>73.39329004329004</v>
       </c>
       <c r="AA2" t="n">
-        <v>21019.98355263158</v>
+        <v>25829.36692936693</v>
       </c>
       <c r="AB2" t="n">
-        <v>7682984.283625731</v>
+        <v>9276702.556702558</v>
       </c>
       <c r="AC2" t="n">
-        <v>76.36153143274854</v>
+        <v>79.2885161135161</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.557620614035088</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>1.235703185703186</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>28.12962962962963</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>180.3518518518518</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>124</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>32777.77777777778</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8166666.666666667</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>124.2222222222222</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>185.0625</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>97.625</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>41250</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19875000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>29.33134920634921</v>
+        <v>26.81296296296297</v>
       </c>
       <c r="D3" t="n">
-        <v>181.4900793650794</v>
+        <v>180.0347222222222</v>
       </c>
       <c r="E3" t="n">
-        <v>82.49007936507937</v>
+        <v>72.14259259259259</v>
       </c>
       <c r="F3" t="n">
-        <v>82410.71428571429</v>
+        <v>19733.7962962963</v>
       </c>
       <c r="G3" t="n">
-        <v>31488095.23809524</v>
+        <v>3307361.111111111</v>
       </c>
       <c r="H3" t="n">
-        <v>83.90674603174602</v>
+        <v>74.78981481481482</v>
       </c>
       <c r="I3" t="n">
-        <v>2.83531746031746</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>1.056018518518518</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.22916666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>183.7638888888889</v>
+      </c>
+      <c r="L3" t="n">
+        <v>77.15972222222223</v>
+      </c>
+      <c r="M3" t="n">
+        <v>33333.33333333334</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10850000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>79.83333333333334</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.715277777777778</v>
+      </c>
       <c r="Q3" t="n">
-        <v>27.66652223389356</v>
+        <v>26.76400830863746</v>
       </c>
       <c r="R3" t="n">
-        <v>178.5973142666157</v>
+        <v>180.1384310503281</v>
       </c>
       <c r="S3" t="n">
-        <v>79.26944431181565</v>
+        <v>71.57836769345496</v>
       </c>
       <c r="T3" t="n">
-        <v>72774.64070855615</v>
+        <v>18575.13318050178</v>
       </c>
       <c r="U3" t="n">
-        <v>23635493.29959257</v>
+        <v>3193008.673763598</v>
       </c>
       <c r="V3" t="n">
-        <v>81.95494493251846</v>
+        <v>74.75854337636093</v>
       </c>
       <c r="W3" t="n">
-        <v>2.277754965622613</v>
+        <v>1.047584340349181</v>
       </c>
       <c r="X3" t="n">
-        <v>26.75702929197995</v>
+        <v>25.90904782065773</v>
       </c>
       <c r="Y3" t="n">
-        <v>180.9975994674186</v>
+        <v>180.6277689573355</v>
       </c>
       <c r="Z3" t="n">
-        <v>70.6782346491228</v>
+        <v>74.0456781093004</v>
       </c>
       <c r="AA3" t="n">
-        <v>26455.88189223058</v>
+        <v>32976.358316606</v>
       </c>
       <c r="AB3" t="n">
-        <v>4007152.059837093</v>
+        <v>8261842.943205171</v>
       </c>
       <c r="AC3" t="n">
-        <v>74.10263549498745</v>
+        <v>79.23347068021991</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.044153352130326</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+        <v>1.515636691023688</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>28.30555555555556</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>177.4814814814815</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>139.1111111111111</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>35777.77777777778</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3322222.222222222</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>142.1111111111111</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>28.38541666666667</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>183.0625</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>295.875</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>164750</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>68750000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>29.125</v>
+        <v>28.49814814814815</v>
       </c>
       <c r="D4" t="n">
-        <v>183.75</v>
+        <v>180</v>
       </c>
       <c r="E4" t="n">
-        <v>77.875</v>
+        <v>74.58703703703704</v>
       </c>
       <c r="F4" t="n">
-        <v>36000</v>
+        <v>19362.96296296296</v>
       </c>
       <c r="G4" t="n">
-        <v>12400000</v>
+        <v>6308148.148148149</v>
       </c>
       <c r="H4" t="n">
-        <v>80</v>
+        <v>76.67222222222222</v>
       </c>
       <c r="I4" t="n">
-        <v>1.875</v>
+        <v>1.381481481481481</v>
       </c>
       <c r="J4" t="n">
-        <v>27.73715277777778</v>
+        <v>25.91898148148148</v>
       </c>
       <c r="K4" t="n">
-        <v>181.4493055555556</v>
+        <v>182.1944444444445</v>
       </c>
       <c r="L4" t="n">
-        <v>75.39444444444445</v>
+        <v>72.98148148148148</v>
       </c>
       <c r="M4" t="n">
-        <v>28398.61111111111</v>
+        <v>22159.72222222222</v>
       </c>
       <c r="N4" t="n">
-        <v>8162326.388888889</v>
+        <v>4558564.814814814</v>
       </c>
       <c r="O4" t="n">
-        <v>77.55104166666666</v>
+        <v>76.43518518518518</v>
       </c>
       <c r="P4" t="n">
-        <v>1.334375</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.31434546490661</v>
+        <v>29.55864197530864</v>
       </c>
       <c r="R4" t="n">
-        <v>180.5708234103358</v>
+        <v>178.302485380117</v>
       </c>
       <c r="S4" t="n">
-        <v>74.45763787296295</v>
+        <v>75.09392462638077</v>
       </c>
       <c r="T4" t="n">
-        <v>32976.358316606</v>
+        <v>21146.41812865497</v>
       </c>
       <c r="U4" t="n">
-        <v>8371656.644439152</v>
+        <v>7653295.971410006</v>
       </c>
       <c r="V4" t="n">
-        <v>79.24182118191408</v>
+        <v>76.31551332033787</v>
       </c>
       <c r="W4" t="n">
-        <v>1.559257944068316</v>
+        <v>1.559990253411306</v>
       </c>
       <c r="X4" t="n">
-        <v>25.36538147310206</v>
+        <v>24.93170341679114</v>
       </c>
       <c r="Y4" t="n">
-        <v>180.9265829248366</v>
+        <v>179.9473637798199</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.05827048768225</v>
+        <v>72.55745424166477</v>
       </c>
       <c r="AA4" t="n">
-        <v>23872.80040221217</v>
+        <v>25050.07594744437</v>
       </c>
       <c r="AB4" t="n">
-        <v>6810762.042797888</v>
+        <v>5045187.379222467</v>
       </c>
       <c r="AC4" t="n">
-        <v>76.44869202488688</v>
+        <v>77.06713289958904</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.151043237807944</v>
+        <v>1.072493945300963</v>
       </c>
       <c r="AE4" t="n">
-        <v>26.16666666666667</v>
+        <v>24.94444444444444</v>
       </c>
       <c r="AF4" t="n">
-        <v>181.2083333333333</v>
+        <v>178.7592592592592</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="AH4" t="n">
-        <v>133</v>
+        <v>152.3333333333333</v>
       </c>
       <c r="AI4" t="n">
-        <v>33000</v>
+        <v>36555.55555555555</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9833333.333333334</v>
+        <v>9216666.666666666</v>
       </c>
       <c r="AK4" t="n">
-        <v>142.5</v>
+        <v>167.3333333333333</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>23857.14285714286</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3542857.142857143</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>97.14285714285714</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.285714285714286</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.94047619047619</v>
+        <v>28.15625</v>
       </c>
       <c r="D5" t="n">
-        <v>180.031746031746</v>
+        <v>179.9375</v>
       </c>
       <c r="E5" t="n">
-        <v>80.72619047619047</v>
+        <v>75.34375</v>
       </c>
       <c r="F5" t="n">
-        <v>117035.7142857143</v>
+        <v>20625</v>
       </c>
       <c r="G5" t="n">
-        <v>40066468.25396825</v>
+        <v>7131250</v>
       </c>
       <c r="H5" t="n">
-        <v>86.56746031746032</v>
+        <v>77.46875</v>
       </c>
       <c r="I5" t="n">
-        <v>2.757936507936508</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>1.1875</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.12962962962963</v>
+      </c>
+      <c r="K5" t="n">
+        <v>181.5925925925926</v>
+      </c>
+      <c r="L5" t="n">
+        <v>79.17037037037036</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40753.70370370371</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20435185.18518519</v>
+      </c>
+      <c r="O5" t="n">
+        <v>82.37962962962963</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.874074074074074</v>
+      </c>
       <c r="Q5" t="n">
-        <v>21.24196523505734</v>
+        <v>26.84158735619004</v>
       </c>
       <c r="R5" t="n">
-        <v>181.3048032011848</v>
+        <v>178.505002771089</v>
       </c>
       <c r="S5" t="n">
-        <v>71.38760585175058</v>
+        <v>72.62156528303329</v>
       </c>
       <c r="T5" t="n">
-        <v>65488.03068276752</v>
+        <v>20189.44788441693</v>
       </c>
       <c r="U5" t="n">
-        <v>19147977.44835574</v>
+        <v>5037901.616787066</v>
       </c>
       <c r="V5" t="n">
-        <v>81.2324044011544</v>
+        <v>74.99796181630546</v>
       </c>
       <c r="W5" t="n">
-        <v>1.632761828814461</v>
+        <v>1.11130938730268</v>
       </c>
       <c r="X5" t="n">
-        <v>24.9388986013986</v>
+        <v>27.12714823303059</v>
       </c>
       <c r="Y5" t="n">
-        <v>181.6748876123876</v>
+        <v>180.9316470022353</v>
       </c>
       <c r="Z5" t="n">
-        <v>73.6612012987013</v>
+        <v>75.03666921313979</v>
       </c>
       <c r="AA5" t="n">
-        <v>26203.87112887113</v>
+        <v>32036.02976544153</v>
       </c>
       <c r="AB5" t="n">
-        <v>9506082.042957043</v>
+        <v>10021076.73372379</v>
       </c>
       <c r="AC5" t="n">
-        <v>79.34541396103896</v>
+        <v>79.48208131737543</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.233916083916084</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+        <v>1.386498033556857</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>27.64814814814815</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.444444444444445</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>51222.22222222222</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>14355555.55555556</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>187.2222222222222</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.111111111111111</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>22.11111111111111</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>179.6604938271605</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3.555555555555555</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>245.6666666666667</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>85111.11111111111</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>22544444.44444444</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>280.4444444444445</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.666666666666667</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.21284722222222</v>
+        <v>27.32283950617284</v>
       </c>
       <c r="D6" t="n">
-        <v>182.3010416666667</v>
+        <v>183.5635802469136</v>
       </c>
       <c r="E6" t="n">
-        <v>76.19791666666666</v>
+        <v>85.70123456790124</v>
       </c>
       <c r="F6" t="n">
-        <v>36007.63888888889</v>
+        <v>226368.8271604938</v>
       </c>
       <c r="G6" t="n">
-        <v>17368784.72222222</v>
+        <v>69250154.32098764</v>
       </c>
       <c r="H6" t="n">
-        <v>81.15138888888889</v>
+        <v>88.23518518518519</v>
       </c>
       <c r="I6" t="n">
-        <v>1.240277777777778</v>
+        <v>3.528703703703703</v>
       </c>
       <c r="J6" t="n">
+        <v>24.80902777777778</v>
+      </c>
+      <c r="K6" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="L6" t="n">
+        <v>80.62152777777777</v>
+      </c>
+      <c r="M6" t="n">
+        <v>116156.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>39969270.83333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>86.55208333333334</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.746527777777778</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25.76867283950617</v>
+      </c>
+      <c r="R6" t="n">
+        <v>179.9614434947768</v>
+      </c>
+      <c r="S6" t="n">
+        <v>80.26174026590694</v>
+      </c>
+      <c r="T6" t="n">
+        <v>143946.2369420703</v>
+      </c>
+      <c r="U6" t="n">
+        <v>41491774.69135802</v>
+      </c>
+      <c r="V6" t="n">
+        <v>85.51961063627729</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.309199905033239</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21.31449541361822</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>181.0838016759069</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>71.81237479219936</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>67732.050665384</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20584751.88391855</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>81.42880391213724</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.679414023273673</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>23.89814814814815</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>179.4074074074074</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>195.8888888888889</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>447666.6666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>179400000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>206.6666666666667</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7.888888888888889</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>25.54166666666666</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>303.875</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>497000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>203687500</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12.625</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>25750</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.6875</v>
+      </c>
+      <c r="K7" t="n">
+        <v>181.4618055555555</v>
+      </c>
+      <c r="L7" t="n">
+        <v>73.37847222222223</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22288.19444444445</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6392057.291666667</v>
+      </c>
+      <c r="O7" t="n">
+        <v>77.16840277777777</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.392361111111111</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>26.61230886559834</v>
+      </c>
+      <c r="R7" t="n">
+        <v>180.7554419508367</v>
+      </c>
+      <c r="S7" t="n">
+        <v>70.43115807194755</v>
+      </c>
+      <c r="T7" t="n">
+        <v>25890.07683349789</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3789690.719855193</v>
+      </c>
+      <c r="V7" t="n">
+        <v>74.00032246019087</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.039247424115845</v>
+      </c>
+      <c r="X7" t="n">
+        <v>26.22851245761462</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>179.4995740986453</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>70.96311448556031</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>20978.33022097728</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5490537.209035661</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>75.69482120333514</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.256812374072436</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>33500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>112</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27.51666666666667</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>178.2740740740741</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>218.4444444444445</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>66222.22222222222</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12050000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>223.6666666666667</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.444444444444445</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.79104938271605</v>
+      </c>
+      <c r="D8" t="n">
+        <v>181.3993827160494</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.52345679012348</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28588.88888888889</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8267746.913580247</v>
+      </c>
+      <c r="H8" t="n">
+        <v>77.5638888888889</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.334259259259259</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.25864197530864</v>
+      </c>
+      <c r="K8" t="n">
+        <v>182.4342592592592</v>
+      </c>
+      <c r="L8" t="n">
+        <v>76.10648148148147</v>
+      </c>
+      <c r="M8" t="n">
+        <v>36173.45679012345</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17406280.86419753</v>
+      </c>
+      <c r="O8" t="n">
+        <v>80.9679012345679</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.241358024691358</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>25.4112032847327</v>
+      </c>
+      <c r="R8" t="n">
+        <v>181.0705428467683</v>
+      </c>
+      <c r="S8" t="n">
+        <v>71.56414166806323</v>
+      </c>
+      <c r="T8" t="n">
+        <v>23872.80040221217</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6288887.247919111</v>
+      </c>
+      <c r="V8" t="n">
+        <v>76.10254105915871</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.134260655829283</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24.34296135962803</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>178.349823633157</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>72.81387686387686</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>28308.68205868206</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8738124.498957833</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>78.99628827962161</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.057311207311207</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>181.3214285714286</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>125.2857142857143</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>34285.71428571428</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>11357142.85714286</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>133.5714285714286</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>26.87037037037037</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>181.9166666666667</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>282.5555555555555</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>141000</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>51211111.11111111</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>290</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.333333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>29.32743055555556</v>
+      </c>
+      <c r="K9" t="n">
+        <v>181.3788194444444</v>
+      </c>
+      <c r="L9" t="n">
+        <v>82.39131944444443</v>
+      </c>
+      <c r="M9" t="n">
+        <v>82321.875</v>
+      </c>
+      <c r="N9" t="n">
+        <v>31008333.33333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>83.79340277777777</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.805902777777778</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23.03331344581345</v>
+      </c>
+      <c r="R9" t="n">
+        <v>181.6686304436304</v>
+      </c>
+      <c r="S9" t="n">
+        <v>71.68029331779331</v>
+      </c>
+      <c r="T9" t="n">
+        <v>23221.19547119547</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6721884.851259851</v>
+      </c>
+      <c r="V9" t="n">
+        <v>80.39258519258519</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.22499444999445</v>
+      </c>
+      <c r="X9" t="n">
+        <v>27.55737648860714</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>178.4549226229567</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>79.26289786781273</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>72355.23618538323</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23682426.79262029</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>82.01843058329126</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.270285115641153</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>30.02222222222223</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>181.1222222222222</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.111111111111111</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>315.7777777777778</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48883333.33333334</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>324.8888888888889</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>178</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>167.375</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>130625</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>40075000</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>174.125</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.55902777777778</v>
+      </c>
+      <c r="D10" t="n">
+        <v>180.6736111111111</v>
+      </c>
+      <c r="E10" t="n">
+        <v>78.60416666666666</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40076.38888888889</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22380208.33333334</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81.95486111111111</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.076388888888889</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.89409722222222</v>
+      </c>
+      <c r="K10" t="n">
+        <v>182.6180555555556</v>
+      </c>
+      <c r="L10" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="M10" t="n">
+        <v>31548.61111111112</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10876909.72222222</v>
+      </c>
+      <c r="O10" t="n">
+        <v>79.62847222222223</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.196180555555555</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24.15722302388969</v>
+      </c>
+      <c r="R10" t="n">
+        <v>181.5498347150308</v>
+      </c>
+      <c r="S10" t="n">
+        <v>71.59487121447904</v>
+      </c>
+      <c r="T10" t="n">
+        <v>29572.56858972545</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11461339.44486886</v>
+      </c>
+      <c r="V10" t="n">
+        <v>78.21733252223447</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.570228899640665</v>
+      </c>
+      <c r="X10" t="n">
+        <v>26.90553419748466</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>178.4803613168164</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>73.0213540386915</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>27071.34939220853</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6456747.795834484</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>76.61369832008376</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.143675380633585</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>25.98148148148148</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>180.3888888888889</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>230.1111111111111</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>105222.2222222222</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42155555.55555555</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>244.6666666666667</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>27.48148148148148</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>108.1111111111111</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>41888.88888888889</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>9044444.444444444</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>108.4444444444444</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.444444444444444</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="D11" t="n">
+        <v>184.065</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30205</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11457500</v>
+      </c>
+      <c r="H11" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.84214365881033</v>
+      </c>
+      <c r="K11" t="n">
+        <v>183.0733164983165</v>
+      </c>
+      <c r="L11" t="n">
+        <v>78.57348484848485</v>
+      </c>
+      <c r="M11" t="n">
+        <v>33198.54096520763</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22935656.56565656</v>
+      </c>
+      <c r="O11" t="n">
+        <v>81.82592592592592</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.838131313131313</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>26.51529735696402</v>
+      </c>
+      <c r="R11" t="n">
+        <v>181.1554585846253</v>
+      </c>
+      <c r="S11" t="n">
+        <v>74.93714664964665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>27267.75570108903</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9179319.692653026</v>
+      </c>
+      <c r="V11" t="n">
+        <v>78.38097566014233</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25964220964221</v>
+      </c>
+      <c r="X11" t="n">
+        <v>26.60493540496121</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>182.3973478767726</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75.63349052096471</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>29798.8198983297</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>15115140.22665596</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>79.71844589687728</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.461094389022665</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>23.70833333333334</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>178.5208333333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>61625</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>19837500</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>197.375</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>27.1037037037037</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>184.3444444444444</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>295.7777777777778</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>117900000</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>305</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.111111111111111</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.91898148148148</v>
+      </c>
+      <c r="D12" t="n">
+        <v>182.1944444444445</v>
+      </c>
+      <c r="E12" t="n">
+        <v>72.98148148148148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22159.72222222222</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4558564.814814814</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.43518518518518</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="K12" t="n">
+        <v>184.065</v>
+      </c>
+      <c r="L12" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30205</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11457500</v>
+      </c>
+      <c r="O12" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24.93170341679114</v>
+      </c>
+      <c r="R12" t="n">
+        <v>179.9473637798199</v>
+      </c>
+      <c r="S12" t="n">
+        <v>72.55745424166477</v>
+      </c>
+      <c r="T12" t="n">
+        <v>25050.07594744437</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5045187.379222467</v>
+      </c>
+      <c r="V12" t="n">
+        <v>77.06713289958904</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.072493945300963</v>
+      </c>
+      <c r="X12" t="n">
+        <v>26.51529735696402</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>181.1554585846253</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>74.93714664964665</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>27267.75570108903</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9179319.692653026</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>78.38097566014233</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.25964220964221</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>23857.14285714286</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3542857.142857143</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>97.14285714285714</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>23.70833333333334</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>178.5208333333333</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>61625</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19837500</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>197.375</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.89409722222222</v>
+      </c>
+      <c r="D13" t="n">
+        <v>182.6180555555556</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31548.61111111112</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10876909.72222222</v>
+      </c>
+      <c r="H13" t="n">
+        <v>79.62847222222223</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.196180555555555</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.81296296296297</v>
+      </c>
+      <c r="K13" t="n">
+        <v>180.0347222222222</v>
+      </c>
+      <c r="L13" t="n">
+        <v>72.14259259259259</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19733.7962962963</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3307361.111111111</v>
+      </c>
+      <c r="O13" t="n">
+        <v>74.78981481481482</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.056018518518518</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26.90553419748466</v>
+      </c>
+      <c r="R13" t="n">
+        <v>178.4803613168164</v>
+      </c>
+      <c r="S13" t="n">
+        <v>73.0213540386915</v>
+      </c>
+      <c r="T13" t="n">
+        <v>27071.34939220853</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6456747.795834484</v>
+      </c>
+      <c r="V13" t="n">
+        <v>76.61369832008376</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.143675380633585</v>
+      </c>
+      <c r="X13" t="n">
+        <v>26.76400830863746</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>180.1384310503281</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>71.57836769345496</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>18575.13318050178</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3193008.673763598</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>74.75854337636093</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.047584340349181</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27.48148148148148</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>108.1111111111111</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>41888.88888888889</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>9044444.444444444</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>108.4444444444444</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>28.30555555555556</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>177.4814814814815</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>139.1111111111111</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>35777.77777777778</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3322222.222222222</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>142.1111111111111</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.12962962962963</v>
+      </c>
+      <c r="D14" t="n">
+        <v>181.5925925925926</v>
+      </c>
+      <c r="E14" t="n">
+        <v>79.17037037037036</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40753.70370370371</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20435185.18518519</v>
+      </c>
+      <c r="H14" t="n">
+        <v>82.37962962962963</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.874074074074074</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27</v>
+      </c>
+      <c r="K14" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25750</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>27.12714823303059</v>
+      </c>
+      <c r="R14" t="n">
+        <v>180.9316470022353</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.03666921313979</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32036.02976544153</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10021076.73372379</v>
+      </c>
+      <c r="V14" t="n">
+        <v>79.48208131737543</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.386498033556857</v>
+      </c>
+      <c r="X14" t="n">
+        <v>26.61230886559834</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>180.7554419508367</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>70.43115807194755</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25890.07683349789</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3789690.719855193</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>74.00032246019087</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.039247424115845</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>22.11111111111111</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>179.6604938271605</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.555555555555555</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>245.6666666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85111.11111111111</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22544444.44444444</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>280.4444444444445</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>33500</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28.22916666666666</v>
+      </c>
+      <c r="D15" t="n">
+        <v>183.7638888888889</v>
+      </c>
+      <c r="E15" t="n">
+        <v>77.15972222222223</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33333.33333333334</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10850000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>79.83333333333334</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.715277777777778</v>
+      </c>
+      <c r="J15" t="n">
+        <v>28.49814814814815</v>
+      </c>
+      <c r="K15" t="n">
+        <v>180</v>
+      </c>
+      <c r="L15" t="n">
+        <v>74.58703703703704</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19362.96296296296</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6308148.148148149</v>
+      </c>
+      <c r="O15" t="n">
+        <v>76.67222222222222</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.381481481481481</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>25.90904782065773</v>
+      </c>
+      <c r="R15" t="n">
+        <v>180.6277689573355</v>
+      </c>
+      <c r="S15" t="n">
+        <v>74.0456781093004</v>
+      </c>
+      <c r="T15" t="n">
+        <v>32976.358316606</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8261842.943205171</v>
+      </c>
+      <c r="V15" t="n">
+        <v>79.23347068021991</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.515636691023688</v>
+      </c>
+      <c r="X15" t="n">
+        <v>29.55864197530864</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>178.302485380117</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75.09392462638077</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>21146.41812865497</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7653295.971410006</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>76.31551332033787</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.559990253411306</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>28.38541666666667</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>183.0625</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>295.875</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>164750</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>68750000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>300</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>24.94444444444444</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>178.7592592592592</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>152.3333333333333</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>36555.55555555555</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9216666.666666666</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>167.3333333333333</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24.25864197530864</v>
+      </c>
+      <c r="D16" t="n">
+        <v>182.4342592592592</v>
+      </c>
+      <c r="E16" t="n">
+        <v>76.10648148148147</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36173.45679012345</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17406280.86419753</v>
+      </c>
+      <c r="H16" t="n">
+        <v>80.9679012345679</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.241358024691358</v>
+      </c>
+      <c r="J16" t="n">
+        <v>27.32283950617284</v>
+      </c>
+      <c r="K16" t="n">
+        <v>183.5635802469136</v>
+      </c>
+      <c r="L16" t="n">
+        <v>85.70123456790124</v>
+      </c>
+      <c r="M16" t="n">
+        <v>226368.8271604938</v>
+      </c>
+      <c r="N16" t="n">
+        <v>69250154.32098764</v>
+      </c>
+      <c r="O16" t="n">
+        <v>88.23518518518519</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.528703703703703</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>24.34296135962803</v>
+      </c>
+      <c r="R16" t="n">
+        <v>178.349823633157</v>
+      </c>
+      <c r="S16" t="n">
+        <v>72.81387686387686</v>
+      </c>
+      <c r="T16" t="n">
+        <v>28308.68205868206</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8738124.498957833</v>
+      </c>
+      <c r="V16" t="n">
+        <v>78.99628827962161</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.057311207311207</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25.76867283950617</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>179.9614434947768</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.26174026590694</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>143946.2369420703</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>41491774.69135802</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>85.51961063627729</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.309199905033239</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>26.87037037037037</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>181.9166666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>282.5555555555555</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>141000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>51211111.11111111</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>23.89814814814815</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>179.4074074074074</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>195.8888888888889</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>447666.6666666667</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>179400000</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>206.6666666666667</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.888888888888889</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>29.32743055555556</v>
+      </c>
+      <c r="D17" t="n">
+        <v>181.3788194444444</v>
+      </c>
+      <c r="E17" t="n">
+        <v>82.39131944444443</v>
+      </c>
+      <c r="F17" t="n">
+        <v>82321.875</v>
+      </c>
+      <c r="G17" t="n">
+        <v>31008333.33333333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>83.79340277777777</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.805902777777778</v>
+      </c>
+      <c r="J17" t="n">
         <v>28.15625</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K17" t="n">
         <v>179.9375</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L17" t="n">
         <v>75.34375</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M17" t="n">
         <v>20625</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N17" t="n">
         <v>7131250</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O17" t="n">
         <v>77.46875</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P17" t="n">
         <v>1.1875</v>
       </c>
-      <c r="Q6" t="n">
-        <v>24.26651334776335</v>
-      </c>
-      <c r="R6" t="n">
-        <v>178.2969606782107</v>
-      </c>
-      <c r="S6" t="n">
-        <v>72.52924783549784</v>
-      </c>
-      <c r="T6" t="n">
-        <v>27790.44913419913</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8289765.061327561</v>
-      </c>
-      <c r="V6" t="n">
-        <v>78.79127886002885</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.030384199134199</v>
-      </c>
-      <c r="X6" t="n">
-        <v>26.88428577571379</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>178.3181281174751</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>72.67426094341246</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>20436.80985552116</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5093889.318885449</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>74.98520704334365</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.112723060715514</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>27.55737648860714</v>
+      </c>
+      <c r="R17" t="n">
+        <v>178.4549226229567</v>
+      </c>
+      <c r="S17" t="n">
+        <v>79.26289786781273</v>
+      </c>
+      <c r="T17" t="n">
+        <v>72355.23618538323</v>
+      </c>
+      <c r="U17" t="n">
+        <v>23682426.79262029</v>
+      </c>
+      <c r="V17" t="n">
+        <v>82.01843058329126</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.270285115641153</v>
+      </c>
+      <c r="X17" t="n">
+        <v>26.84158735619004</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>178.505002771089</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>72.62156528303329</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>20189.44788441693</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5037901.616787066</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>74.99796181630546</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.11130938730268</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>178</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>167.375</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130625</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>40075000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>174.125</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>27.64814814814815</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.444444444444445</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>51222.22222222222</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14355555.55555556</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>187.2222222222222</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.111111111111111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.80902777777778</v>
+      </c>
+      <c r="D18" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="E18" t="n">
+        <v>80.62152777777777</v>
+      </c>
+      <c r="F18" t="n">
+        <v>116156.25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39969270.83333333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>86.55208333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.746527777777778</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>21.31449541361822</v>
+      </c>
+      <c r="R18" t="n">
+        <v>181.0838016759069</v>
+      </c>
+      <c r="S18" t="n">
+        <v>71.81237479219936</v>
+      </c>
+      <c r="T18" t="n">
+        <v>67732.050665384</v>
+      </c>
+      <c r="U18" t="n">
+        <v>20584751.88391855</v>
+      </c>
+      <c r="V18" t="n">
+        <v>81.42880391213724</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.679414023273673</v>
+      </c>
+      <c r="X18" t="n">
+        <v>26.65759943578571</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>180.8637024467907</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>71.40054396402437</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>18857.08200659181</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3385071.155242724</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>75.3232507960449</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>25.54166666666666</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>303.875</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>497000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>203687500</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>12.625</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>28.12962962962963</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>180.3518518518518</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>124</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>32777.77777777778</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8166666.666666667</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>124.2222222222222</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>26.55902777777778</v>
+      </c>
+      <c r="K19" t="n">
+        <v>180.6736111111111</v>
+      </c>
+      <c r="L19" t="n">
+        <v>78.60416666666666</v>
+      </c>
+      <c r="M19" t="n">
+        <v>40076.38888888889</v>
+      </c>
+      <c r="N19" t="n">
+        <v>22380208.33333334</v>
+      </c>
+      <c r="O19" t="n">
+        <v>81.95486111111111</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.076388888888889</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>24.82531727531727</v>
+      </c>
+      <c r="R19" t="n">
+        <v>181.3036038036038</v>
+      </c>
+      <c r="S19" t="n">
+        <v>73.39329004329004</v>
+      </c>
+      <c r="T19" t="n">
+        <v>25829.36692936693</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9276702.556702558</v>
+      </c>
+      <c r="V19" t="n">
+        <v>79.2885161135161</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.235703185703186</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.15722302388969</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>181.5498347150308</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>71.59487121447904</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>29572.56858972545</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11461339.44486886</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>78.21733252223447</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.570228899640665</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>185.0625</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>97.625</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>41250</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>19875000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>25.98148148148148</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>180.3888888888889</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>230.1111111111111</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>105222.2222222222</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>42155555.55555555</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>244.6666666666667</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.84214365881033</v>
+      </c>
+      <c r="D20" t="n">
+        <v>183.0733164983165</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.57348484848485</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33198.54096520763</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22935656.56565656</v>
+      </c>
+      <c r="H20" t="n">
+        <v>81.82592592592592</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.838131313131313</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>26.60493540496121</v>
+      </c>
+      <c r="R20" t="n">
+        <v>182.3973478767726</v>
+      </c>
+      <c r="S20" t="n">
+        <v>75.63349052096471</v>
+      </c>
+      <c r="T20" t="n">
+        <v>29798.8198983297</v>
+      </c>
+      <c r="U20" t="n">
+        <v>15115140.22665596</v>
+      </c>
+      <c r="V20" t="n">
+        <v>79.71844589687728</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.461094389022665</v>
+      </c>
+      <c r="X20" t="n">
+        <v>23.03331344581345</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>181.6686304436304</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>71.68029331779331</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>23221.19547119547</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6721884.851259851</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>80.39258519258519</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22499444999445</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>27.1037037037037</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>184.3444444444444</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>295.7777777777778</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>117900000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>305</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>8.111111111111111</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>30.02222222222223</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>181.1222222222222</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4.111111111111111</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>315.7777777777778</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>48883333.33333334</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>324.8888888888889</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>27.6875</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.4618055555555</v>
+      </c>
+      <c r="E21" t="n">
+        <v>73.37847222222223</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22288.19444444445</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6392057.291666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77.16840277777777</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.392361111111111</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.79104938271605</v>
+      </c>
+      <c r="K21" t="n">
+        <v>181.3993827160494</v>
+      </c>
+      <c r="L21" t="n">
+        <v>75.52345679012348</v>
+      </c>
+      <c r="M21" t="n">
+        <v>28588.88888888889</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8267746.913580247</v>
+      </c>
+      <c r="O21" t="n">
+        <v>77.5638888888889</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.334259259259259</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>26.22851245761462</v>
+      </c>
+      <c r="R21" t="n">
+        <v>179.4995740986453</v>
+      </c>
+      <c r="S21" t="n">
+        <v>70.96311448556031</v>
+      </c>
+      <c r="T21" t="n">
+        <v>20978.33022097728</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5490537.209035661</v>
+      </c>
+      <c r="V21" t="n">
+        <v>75.69482120333514</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.256812374072436</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25.4112032847327</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>181.0705428467683</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>71.56414166806323</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>23872.80040221217</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6288887.247919111</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>76.10254105915871</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.134260655829283</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>27.51666666666667</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>178.2740740740741</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>218.4444444444445</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>66222.22222222222</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>12050000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>223.6666666666667</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3.444444444444445</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>181.3214285714286</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>125.2857142857143</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>34285.71428571428</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>11357142.85714286</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>133.5714285714286</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.285714285714286</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,765 +658,987 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>25.99166666666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>182.2333333333333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>73.15555555555555</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22502.77777777778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4770277.777777778</v>
+      </c>
+      <c r="H2" t="n">
+        <v>76.65555555555555</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>184.06875</v>
+      </c>
+      <c r="L2" t="n">
+        <v>75.91249999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>29075</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10646875</v>
+      </c>
+      <c r="O2" t="n">
+        <v>78.65625</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.35625</v>
+      </c>
       <c r="Q2" t="n">
-        <v>26.62868825414781</v>
+        <v>25.01721396293765</v>
       </c>
       <c r="R2" t="n">
-        <v>181.0758319193062</v>
+        <v>180.2526890142022</v>
       </c>
       <c r="S2" t="n">
-        <v>71.48533418174964</v>
+        <v>72.64201697425381</v>
       </c>
       <c r="T2" t="n">
-        <v>19290.60614630468</v>
+        <v>24939.07353611301</v>
       </c>
       <c r="U2" t="n">
-        <v>3492927.271870286</v>
+        <v>5333454.849244323</v>
       </c>
       <c r="V2" t="n">
-        <v>75.44699047888386</v>
+        <v>77.14040546441862</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>1.108341402749297</v>
       </c>
       <c r="X2" t="n">
-        <v>24.55348193473193</v>
+        <v>26.39599740537241</v>
       </c>
       <c r="Y2" t="n">
-        <v>181.0801906426906</v>
+        <v>180.8784893925519</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.98790584415585</v>
+        <v>75.06565361721611</v>
       </c>
       <c r="AA2" t="n">
-        <v>25035.31052281052</v>
+        <v>27420.54334554334</v>
       </c>
       <c r="AB2" t="n">
-        <v>8689699.467199467</v>
+        <v>9516223.29059829</v>
       </c>
       <c r="AC2" t="n">
-        <v>79.26776244588744</v>
+        <v>78.64545367826618</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.196984265734266</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>1.266529304029304</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>181.4047619047619</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>111.5714285714286</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28714.28571428571</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4457142.857142857</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>119.5714285714286</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.571428571428571</v>
+      </c>
       <c r="AM2" t="n">
-        <v>27</v>
+        <v>24.61111111111111</v>
       </c>
       <c r="AN2" t="n">
-        <v>185.2142857142857</v>
+        <v>180.0277777777777</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.285714285714286</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>100.4285714285714</v>
+        <v>221.3333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>42142.85714285714</v>
+        <v>77166.66666666667</v>
       </c>
       <c r="AR2" t="n">
-        <v>20785714.28571429</v>
+        <v>25316666.66666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>102.5714285714286</v>
+        <v>236.1666666666667</v>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.65555555555556</v>
+        <v>26.89484126984127</v>
       </c>
       <c r="D3" t="n">
-        <v>180.0416666666667</v>
+        <v>182.1349206349207</v>
       </c>
       <c r="E3" t="n">
-        <v>72.11111111111111</v>
+        <v>76.21428571428571</v>
       </c>
       <c r="F3" t="n">
-        <v>19580.55555555555</v>
+        <v>31515.87301587302</v>
       </c>
       <c r="G3" t="n">
-        <v>3320833.333333333</v>
+        <v>10805357.14285714</v>
       </c>
       <c r="H3" t="n">
-        <v>74.82777777777778</v>
+        <v>79.60714285714286</v>
       </c>
       <c r="I3" t="n">
-        <v>1.047222222222222</v>
+        <v>1.192460317460317</v>
       </c>
       <c r="J3" t="n">
-        <v>28.22916666666666</v>
+        <v>26.72569444444444</v>
       </c>
       <c r="K3" t="n">
-        <v>183.7638888888889</v>
+        <v>180.3020833333333</v>
       </c>
       <c r="L3" t="n">
-        <v>77.15972222222223</v>
+        <v>72.07638888888889</v>
       </c>
       <c r="M3" t="n">
-        <v>33333.33333333334</v>
+        <v>19756.94444444445</v>
       </c>
       <c r="N3" t="n">
-        <v>10850000</v>
+        <v>3301041.666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>79.83333333333334</v>
+        <v>74.69097222222223</v>
       </c>
       <c r="P3" t="n">
-        <v>1.715277777777778</v>
+        <v>1.059027777777778</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.80803875898185</v>
+        <v>27.14564904909332</v>
       </c>
       <c r="R3" t="n">
-        <v>180.310146696325</v>
+        <v>178.246335968598</v>
       </c>
       <c r="S3" t="n">
-        <v>71.54036953748978</v>
+        <v>73.28027329352793</v>
       </c>
       <c r="T3" t="n">
-        <v>18639.67188688803</v>
+        <v>27586.67832264485</v>
       </c>
       <c r="U3" t="n">
-        <v>3138274.463866401</v>
+        <v>6487963.86646764</v>
       </c>
       <c r="V3" t="n">
-        <v>74.73571423958253</v>
+        <v>76.6343208665045</v>
       </c>
       <c r="W3" t="n">
-        <v>1.046179441716358</v>
+        <v>1.125737367315347</v>
       </c>
       <c r="X3" t="n">
-        <v>25.38806341362456</v>
+        <v>27.06428875898186</v>
       </c>
       <c r="Y3" t="n">
-        <v>180.2543170000794</v>
+        <v>180.5754876054159</v>
       </c>
       <c r="Z3" t="n">
-        <v>73.74369556527066</v>
+        <v>71.70514226476251</v>
       </c>
       <c r="AA3" t="n">
-        <v>32959.59752321982</v>
+        <v>18891.37643234258</v>
       </c>
       <c r="AB3" t="n">
-        <v>8189765.618798126</v>
+        <v>3148274.463866401</v>
       </c>
       <c r="AC3" t="n">
-        <v>79.12803913063202</v>
+        <v>74.66412333049162</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43586050817088</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+        <v>1.04674762353454</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27.3125</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>178.3125</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>85.125</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>34375</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>9187500</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>28.03125</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>179.1041666666667</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>156.625</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>40750</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3778125</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>160.625</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>28.49814814814815</v>
+        <v>26.09722222222222</v>
       </c>
       <c r="D4" t="n">
+        <v>181.6833333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79.05277777777778</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40230.55555555556</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20101388.88888889</v>
+      </c>
+      <c r="H4" t="n">
+        <v>82.35833333333332</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.863888888888889</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.1875</v>
+      </c>
+      <c r="K4" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="L4" t="n">
+        <v>72.4375</v>
+      </c>
+      <c r="M4" t="n">
+        <v>27250</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>75.5625</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>27.32931627196333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>181.5595407860114</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75.31249469484763</v>
+      </c>
+      <c r="T4" t="n">
+        <v>30929.42237501061</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10095341.22740005</v>
+      </c>
+      <c r="V4" t="n">
+        <v>79.52355063237417</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.456869111280876</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26.5925812400319</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>180.767999900319</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>70.20020434609251</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>24618.81479266348</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3271949.13775917</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>73.81562250797448</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.026891447368421</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>22.54166666666666</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>179.2055555555556</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>129500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>36912500</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>23.07142857142857</v>
+      </c>
+      <c r="AN4" t="n">
         <v>180</v>
       </c>
-      <c r="E4" t="n">
-        <v>74.58703703703704</v>
-      </c>
-      <c r="F4" t="n">
-        <v>19362.96296296296</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6308148.148148149</v>
-      </c>
-      <c r="H4" t="n">
-        <v>76.67222222222222</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.381481481481481</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25.91898148148148</v>
-      </c>
-      <c r="K4" t="n">
-        <v>182.1944444444445</v>
-      </c>
-      <c r="L4" t="n">
-        <v>72.98148148148148</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22159.72222222222</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4558564.814814814</v>
-      </c>
-      <c r="O4" t="n">
-        <v>76.43518518518518</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.041666666666667</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>29.77978801169591</v>
-      </c>
-      <c r="R4" t="n">
-        <v>178.5310855263158</v>
-      </c>
-      <c r="S4" t="n">
-        <v>75.14513888888888</v>
-      </c>
-      <c r="T4" t="n">
-        <v>21210.77302631579</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7624431.652046784</v>
-      </c>
-      <c r="V4" t="n">
-        <v>76.23653143274854</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.57077850877193</v>
-      </c>
-      <c r="X4" t="n">
-        <v>24.98149967722336</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>180.1991175856307</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>72.66880268853953</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>24823.00210754158</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5231669.134958608</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>77.16719117870434</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.081555688463583</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>94.42857142857143</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>31571.42857142857</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2242857.142857143</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>106.7142857142857</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.428571428571429</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>YFePBifU</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>28.08333333333333</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>179.8333333333333</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="E5" t="n">
-        <v>75.33333333333333</v>
+        <v>76.44444444444444</v>
       </c>
       <c r="F5" t="n">
-        <v>20625</v>
+        <v>30666.66666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>7250000</v>
+        <v>9300000</v>
       </c>
       <c r="H5" t="n">
-        <v>77.58333333333333</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>1.208333333333333</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J5" t="n">
-        <v>26.05555555555555</v>
+        <v>28.33769841269842</v>
       </c>
       <c r="K5" t="n">
-        <v>181.5911111111111</v>
+        <v>179.9107142857143</v>
       </c>
       <c r="L5" t="n">
-        <v>79.06444444444443</v>
+        <v>74.53888888888889</v>
       </c>
       <c r="M5" t="n">
-        <v>39784.44444444445</v>
+        <v>19489.68253968254</v>
       </c>
       <c r="N5" t="n">
-        <v>20192222.22222222</v>
+        <v>6394484.126984128</v>
       </c>
       <c r="O5" t="n">
-        <v>82.37555555555555</v>
+        <v>76.71904761904761</v>
       </c>
       <c r="P5" t="n">
-        <v>1.868888888888889</v>
+        <v>1.380555555555555</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.88796224630203</v>
+        <v>25.48806341362456</v>
       </c>
       <c r="R5" t="n">
-        <v>178.6048928233574</v>
+        <v>179.8850862308486</v>
       </c>
       <c r="S5" t="n">
-        <v>72.56690800223598</v>
+        <v>73.78119556527065</v>
       </c>
       <c r="T5" t="n">
-        <v>20398.57456140351</v>
+        <v>33881.39239501469</v>
       </c>
       <c r="U5" t="n">
-        <v>4944845.20123839</v>
+        <v>7915438.695721203</v>
       </c>
       <c r="V5" t="n">
-        <v>74.89476586687306</v>
+        <v>79.00880836140124</v>
       </c>
       <c r="W5" t="n">
-        <v>1.117870119539044</v>
+        <v>1.427206662017034</v>
       </c>
       <c r="X5" t="n">
-        <v>27.37833587980647</v>
+        <v>29.96381578947368</v>
       </c>
       <c r="Y5" t="n">
-        <v>181.1436911128088</v>
+        <v>178.403307748538</v>
       </c>
       <c r="Z5" t="n">
-        <v>75.35007639419403</v>
+        <v>75.37222222222222</v>
       </c>
       <c r="AA5" t="n">
-        <v>32834.65113318055</v>
+        <v>21739.93969298246</v>
       </c>
       <c r="AB5" t="n">
-        <v>10247976.03132162</v>
+        <v>7985959.429824562</v>
       </c>
       <c r="AC5" t="n">
-        <v>79.46145912910619</v>
+        <v>76.36430921052632</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.405398523045582</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>1.599250730994152</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28.61190476190476</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>183.1000000000001</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>327.5714285714286</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>185857.1428571429</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>77428571.42857143</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>331.8571428571428</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>177.2916666666667</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>156.625</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10331250</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.125</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>zHmSVfun</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>27.42569444444445</v>
+        <v>24.35347222222222</v>
       </c>
       <c r="D6" t="n">
-        <v>183.5715277777778</v>
+        <v>182.2635416666667</v>
       </c>
       <c r="E6" t="n">
-        <v>85.71076388888889</v>
+        <v>76.27291666666666</v>
       </c>
       <c r="F6" t="n">
-        <v>225680.5555555556</v>
+        <v>36829.51388888889</v>
       </c>
       <c r="G6" t="n">
-        <v>69257986.1111111</v>
+        <v>17766128.47222222</v>
       </c>
       <c r="H6" t="n">
-        <v>88.12395833333333</v>
+        <v>81.02013888888888</v>
       </c>
       <c r="I6" t="n">
-        <v>3.547916666666667</v>
+        <v>1.259027777777778</v>
       </c>
       <c r="J6" t="n">
-        <v>24.67460317460317</v>
+        <v>27.05069444444445</v>
       </c>
       <c r="K6" t="n">
-        <v>179.75</v>
+        <v>183.8076388888889</v>
       </c>
       <c r="L6" t="n">
-        <v>80.24603174603173</v>
+        <v>85.66909722222222</v>
       </c>
       <c r="M6" t="n">
-        <v>114107.1428571429</v>
+        <v>224916.6666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>38902380.95238095</v>
+        <v>71507986.1111111</v>
       </c>
       <c r="O6" t="n">
-        <v>86.36309523809526</v>
+        <v>88.24895833333332</v>
       </c>
       <c r="P6" t="n">
-        <v>2.692460317460317</v>
+        <v>3.506250000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.66684027777778</v>
+        <v>24.50909992784993</v>
       </c>
       <c r="R6" t="n">
-        <v>180.1857905982906</v>
+        <v>178.2031836219336</v>
       </c>
       <c r="S6" t="n">
-        <v>80.37779113247863</v>
+        <v>72.95533008658009</v>
       </c>
       <c r="T6" t="n">
-        <v>145366.5998931624</v>
+        <v>28253.11147186147</v>
       </c>
       <c r="U6" t="n">
-        <v>42812621.52777778</v>
+        <v>8439793.47041847</v>
       </c>
       <c r="V6" t="n">
-        <v>85.58456196581196</v>
+        <v>79.0317821067821</v>
       </c>
       <c r="W6" t="n">
-        <v>2.29576655982906</v>
+        <v>1.065340909090909</v>
       </c>
       <c r="X6" t="n">
-        <v>21.42672400698716</v>
+        <v>25.89695391414141</v>
       </c>
       <c r="Y6" t="n">
-        <v>180.8755268853953</v>
+        <v>180.0714440073815</v>
       </c>
       <c r="Z6" t="n">
-        <v>72.40350497455761</v>
+        <v>80.51273431429681</v>
       </c>
       <c r="AA6" t="n">
-        <v>70844.39033189033</v>
+        <v>145594.5828477078</v>
       </c>
       <c r="AB6" t="n">
-        <v>22272950.03607504</v>
+        <v>42123630.05050505</v>
       </c>
       <c r="AC6" t="n">
-        <v>81.90948773448773</v>
+        <v>85.62149378399378</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.764340776182882</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>2.385965423465424</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>26.53541666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>182.69375</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>140250</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>56212500</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>24.92708333333334</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>178.7916666666667</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>199.25</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>458625</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>160262500</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>209.25</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.875</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>29.47539682539682</v>
       </c>
       <c r="D7" t="n">
-        <v>183.75</v>
+        <v>181.1849206349206</v>
       </c>
       <c r="E7" t="n">
-        <v>72.375</v>
+        <v>82.48690476190475</v>
       </c>
       <c r="F7" t="n">
-        <v>25750</v>
+        <v>83338.09523809524</v>
       </c>
       <c r="G7" t="n">
-        <v>4750000</v>
+        <v>31114682.53968254</v>
       </c>
       <c r="H7" t="n">
-        <v>75.875</v>
+        <v>83.71825396825398</v>
       </c>
       <c r="I7" t="n">
-        <v>1.125</v>
+        <v>2.845634920634921</v>
       </c>
       <c r="J7" t="n">
-        <v>28</v>
+        <v>27.8125</v>
       </c>
       <c r="K7" t="n">
-        <v>181.4920634920635</v>
+        <v>180.125</v>
       </c>
       <c r="L7" t="n">
-        <v>73.53968253968254</v>
+        <v>75.125</v>
       </c>
       <c r="M7" t="n">
-        <v>22507.93650793651</v>
+        <v>20250</v>
       </c>
       <c r="N7" t="n">
-        <v>6358333.333333334</v>
+        <v>7075000</v>
       </c>
       <c r="O7" t="n">
-        <v>77.03174603174602</v>
+        <v>77.625</v>
       </c>
       <c r="P7" t="n">
-        <v>1.412698412698413</v>
+        <v>1.1875</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.63884747379813</v>
+        <v>27.43061997825446</v>
       </c>
       <c r="R7" t="n">
-        <v>180.7915388613579</v>
+        <v>178.1551862192245</v>
       </c>
       <c r="S7" t="n">
-        <v>70.39338616427432</v>
+        <v>79.06605230908153</v>
       </c>
       <c r="T7" t="n">
-        <v>25743.00310435179</v>
+        <v>71424.80304621848</v>
       </c>
       <c r="U7" t="n">
-        <v>3647152.059837092</v>
+        <v>23126225.8126935</v>
       </c>
       <c r="V7" t="n">
-        <v>73.95036276771475</v>
+        <v>81.84784479581307</v>
       </c>
       <c r="W7" t="n">
-        <v>1.035820018796992</v>
+        <v>2.216949542975085</v>
       </c>
       <c r="X7" t="n">
-        <v>26.13207651481645</v>
+        <v>26.96884459924321</v>
       </c>
       <c r="Y7" t="n">
-        <v>179.4578541943093</v>
+        <v>178.6195987057104</v>
       </c>
       <c r="Z7" t="n">
-        <v>70.906420462922</v>
+        <v>72.79484917870657</v>
       </c>
       <c r="AA7" t="n">
-        <v>20866.24649859944</v>
+        <v>20495.3302373581</v>
       </c>
       <c r="AB7" t="n">
-        <v>5477896.026831785</v>
+        <v>5169477.554179566</v>
       </c>
       <c r="AC7" t="n">
-        <v>75.75042385375203</v>
+        <v>75.04917763157894</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24203892083149</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+        <v>1.117870119539044</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>27.82142857142857</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>179.6428571428571</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>203.4285714285714</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>164857.1428571429</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>49357142.85714286</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>211.8571428571429</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27.14583333333334</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>180.3541666666667</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>44750</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13712500</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>174</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.85243055555556</v>
+        <v>24.51984126984127</v>
       </c>
       <c r="D8" t="n">
-        <v>181.3993055555555</v>
+        <v>179.3988095238095</v>
       </c>
       <c r="E8" t="n">
-        <v>75.70138888888889</v>
+        <v>80.09126984126985</v>
       </c>
       <c r="F8" t="n">
-        <v>28750</v>
+        <v>113267.8571428571</v>
       </c>
       <c r="G8" t="n">
-        <v>8377777.777777778</v>
+        <v>38744642.85714286</v>
       </c>
       <c r="H8" t="n">
-        <v>77.671875</v>
+        <v>86.40476190476191</v>
       </c>
       <c r="I8" t="n">
-        <v>1.338541666666667</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24.40347222222222</v>
-      </c>
-      <c r="K8" t="n">
-        <v>182.4135416666666</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76.06979166666666</v>
-      </c>
-      <c r="M8" t="n">
-        <v>36245.13888888889</v>
-      </c>
-      <c r="N8" t="n">
-        <v>17177065.97222222</v>
-      </c>
-      <c r="O8" t="n">
-        <v>80.7513888888889</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.234027777777778</v>
-      </c>
+        <v>2.654761904761905</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>25.48343702865762</v>
+        <v>21.60076246852563</v>
       </c>
       <c r="R8" t="n">
-        <v>181.3085273692811</v>
+        <v>180.4755268853953</v>
       </c>
       <c r="S8" t="n">
-        <v>71.53049270990448</v>
+        <v>73.44869728224992</v>
       </c>
       <c r="T8" t="n">
-        <v>23924.33383609854</v>
+        <v>76762.65956265955</v>
       </c>
       <c r="U8" t="n">
-        <v>6351300.237242333</v>
+        <v>26050305.80530581</v>
       </c>
       <c r="V8" t="n">
-        <v>76.02160869155355</v>
+        <v>82.56814158064158</v>
       </c>
       <c r="W8" t="n">
-        <v>1.151043237807944</v>
+        <v>1.919148468490574</v>
       </c>
       <c r="X8" t="n">
-        <v>24.27219516594516</v>
+        <v>26.44486472473605</v>
       </c>
       <c r="Y8" t="n">
-        <v>178.1662788600289</v>
+        <v>181.1052436840121</v>
       </c>
       <c r="Z8" t="n">
-        <v>73.00652056277056</v>
+        <v>71.52209888763198</v>
       </c>
       <c r="AA8" t="n">
-        <v>28387.04004329004</v>
+        <v>19930.31202865762</v>
       </c>
       <c r="AB8" t="n">
-        <v>9017605.97041847</v>
+        <v>3656162.565987933</v>
       </c>
       <c r="AC8" t="n">
-        <v>79.23446067821067</v>
+        <v>75.57934342006033</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05879329004329</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.69047619047619</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>277.5714285714286</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>464714.2857142857</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182000000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>287.4285714285714</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>11.85714285714286</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>27.70833333333334</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>180.3958333333333</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>130.125</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9062500</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1430,335 +1652,1763 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>29.42777777777778</v>
+        <v>26.11805555555556</v>
       </c>
       <c r="K9" t="n">
-        <v>181.4865079365079</v>
+        <v>180.8472222222223</v>
       </c>
       <c r="L9" t="n">
-        <v>82.37579365079364</v>
+        <v>78.09722222222223</v>
       </c>
       <c r="M9" t="n">
-        <v>82242.85714285714</v>
+        <v>38486.11111111111</v>
       </c>
       <c r="N9" t="n">
-        <v>30598809.52380953</v>
+        <v>21582638.88888889</v>
       </c>
       <c r="O9" t="n">
-        <v>83.63888888888889</v>
+        <v>81.96527777777777</v>
       </c>
       <c r="P9" t="n">
-        <v>2.813888888888889</v>
+        <v>1.930555555555556</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.09997762654013</v>
+        <v>24.59098193473194</v>
       </c>
       <c r="R9" t="n">
-        <v>181.6272092490842</v>
+        <v>180.9968573093573</v>
       </c>
       <c r="S9" t="n">
-        <v>71.72366331585081</v>
+        <v>73.02123917748918</v>
       </c>
       <c r="T9" t="n">
-        <v>23915.51157176157</v>
+        <v>24929.06052281052</v>
       </c>
       <c r="U9" t="n">
-        <v>6779828.791000666</v>
+        <v>8673449.467199467</v>
       </c>
       <c r="V9" t="n">
-        <v>80.33749167499167</v>
+        <v>79.16984577922076</v>
       </c>
       <c r="W9" t="n">
-        <v>1.211452089577089</v>
+        <v>1.213650932400933</v>
       </c>
       <c r="X9" t="n">
-        <v>27.50204854968303</v>
+        <v>24.43602994227994</v>
       </c>
       <c r="Y9" t="n">
-        <v>178.2504243144626</v>
+        <v>181.436272387743</v>
       </c>
       <c r="Z9" t="n">
-        <v>79.24462373765294</v>
+        <v>72.23046749002631</v>
       </c>
       <c r="AA9" t="n">
-        <v>72496.23161764705</v>
+        <v>30773.4010270775</v>
       </c>
       <c r="AB9" t="n">
-        <v>23751821.05078874</v>
+        <v>12418130.92850777</v>
       </c>
       <c r="AC9" t="n">
-        <v>82.02641622438449</v>
+        <v>78.37486524912995</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.258616209641751</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+        <v>1.622252461590697</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>91.16666666666667</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38166.66666666666</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19416666.66666667</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>26.08333333333334</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>179.9166666666666</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>247.875</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>112500</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>43387500</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.375</v>
+        <v>26.85625</v>
       </c>
       <c r="D10" t="n">
-        <v>180.6018518518519</v>
+        <v>182.9661931818182</v>
       </c>
       <c r="E10" t="n">
-        <v>78.69444444444444</v>
+        <v>78.65198863636364</v>
       </c>
       <c r="F10" t="n">
-        <v>40027.77777777777</v>
+        <v>33335.22727272727</v>
       </c>
       <c r="G10" t="n">
-        <v>23184722.22222222</v>
+        <v>23170681.81818182</v>
       </c>
       <c r="H10" t="n">
-        <v>82.19907407407408</v>
+        <v>81.8215909090909</v>
       </c>
       <c r="I10" t="n">
-        <v>2.064814814814815</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26.86309523809524</v>
-      </c>
-      <c r="K10" t="n">
-        <v>182.468253968254</v>
-      </c>
-      <c r="L10" t="n">
-        <v>76.16666666666667</v>
-      </c>
-      <c r="M10" t="n">
-        <v>31468.25396825397</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10789484.12698413</v>
-      </c>
-      <c r="O10" t="n">
-        <v>79.59126984126985</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.192460317460317</v>
-      </c>
+        <v>1.805397727272727</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>24.18255772005772</v>
+        <v>26.87370709248612</v>
       </c>
       <c r="R10" t="n">
-        <v>181.6185640544096</v>
+        <v>182.0990996947024</v>
       </c>
       <c r="S10" t="n">
-        <v>71.54991193447076</v>
+        <v>76.08023635989483</v>
       </c>
       <c r="T10" t="n">
-        <v>29507.7760270775</v>
+        <v>30179.32714752568</v>
       </c>
       <c r="U10" t="n">
-        <v>11191308.0118411</v>
+        <v>15029235.13594034</v>
       </c>
       <c r="V10" t="n">
-        <v>78.14222636024107</v>
+        <v>79.94069211017741</v>
       </c>
       <c r="W10" t="n">
-        <v>1.556280239368475</v>
+        <v>1.488671663840975</v>
       </c>
       <c r="X10" t="n">
-        <v>26.97064904909332</v>
+        <v>23.16579207829208</v>
       </c>
       <c r="Y10" t="n">
-        <v>178.1942526352646</v>
+        <v>181.4293142043142</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.14902329352793</v>
+        <v>71.66889730639731</v>
       </c>
       <c r="AA10" t="n">
-        <v>27378.34498931152</v>
+        <v>23241.13849113849</v>
       </c>
       <c r="AB10" t="n">
-        <v>6619370.11646764</v>
+        <v>6576087.130462131</v>
       </c>
       <c r="AC10" t="n">
-        <v>76.73848753317117</v>
+        <v>80.27435157435158</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.142404033982014</v>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+        <v>1.222145447145447</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>27.08541666666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>185.54375</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>264</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>118375</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>116300000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>272</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>30.52592592592593</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>180.8259259259259</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>303.2222222222222</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>130444.4444444444</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>51311111.11111111</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>309</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.777777777777779</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>27.4625</v>
+        <v>28.55753968253968</v>
       </c>
       <c r="D11" t="n">
-        <v>183.8625</v>
+        <v>181.8432539682539</v>
       </c>
       <c r="E11" t="n">
-        <v>76.175</v>
+        <v>74.15476190476191</v>
       </c>
       <c r="F11" t="n">
-        <v>29881.25</v>
+        <v>23228.17460317461</v>
       </c>
       <c r="G11" t="n">
-        <v>11115625</v>
+        <v>6659722.222222222</v>
       </c>
       <c r="H11" t="n">
-        <v>78.71875</v>
+        <v>77.3888888888889</v>
       </c>
       <c r="I11" t="n">
-        <v>1.38125</v>
+        <v>1.488095238095238</v>
       </c>
       <c r="J11" t="n">
-        <v>26.84513888888889</v>
+        <v>27.90216049382716</v>
       </c>
       <c r="K11" t="n">
-        <v>183.0370265151515</v>
+        <v>181.3549382716049</v>
       </c>
       <c r="L11" t="n">
-        <v>78.57698863636364</v>
+        <v>75.69012345679012</v>
       </c>
       <c r="M11" t="n">
-        <v>33007.4494949495</v>
+        <v>28644.44444444445</v>
       </c>
       <c r="N11" t="n">
-        <v>22671931.81818182</v>
+        <v>8368024.691358025</v>
       </c>
       <c r="O11" t="n">
-        <v>81.83825757575757</v>
+        <v>77.55277777777776</v>
       </c>
       <c r="P11" t="n">
-        <v>1.817897727272727</v>
+        <v>1.334259259259259</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.4774367993118</v>
+        <v>25.84918177797434</v>
       </c>
       <c r="R11" t="n">
-        <v>181.1407999986125</v>
+        <v>179.4381173522041</v>
       </c>
       <c r="S11" t="n">
-        <v>75.02019907176157</v>
+        <v>70.39984151555359</v>
       </c>
       <c r="T11" t="n">
-        <v>27289.86152736153</v>
+        <v>20307.03597228365</v>
       </c>
       <c r="U11" t="n">
-        <v>9434689.199689198</v>
+        <v>5032994.711042311</v>
       </c>
       <c r="V11" t="n">
-        <v>78.53087034493285</v>
+        <v>75.41489753796255</v>
       </c>
       <c r="W11" t="n">
-        <v>1.269370213120213</v>
+        <v>1.202565236620964</v>
       </c>
       <c r="X11" t="n">
-        <v>26.63055233058136</v>
+        <v>25.6122614857909</v>
       </c>
       <c r="Y11" t="n">
-        <v>182.3095163613691</v>
+        <v>181.4805957568213</v>
       </c>
       <c r="Z11" t="n">
-        <v>75.76892683608531</v>
+        <v>71.40012050404208</v>
       </c>
       <c r="AA11" t="n">
-        <v>29961.17238562092</v>
+        <v>22410.89564030741</v>
       </c>
       <c r="AB11" t="n">
-        <v>15487032.75498796</v>
+        <v>5963457.353739216</v>
       </c>
       <c r="AC11" t="n">
-        <v>79.75825163398693</v>
+        <v>75.88428709090473</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.449981187650499</v>
+        <v>1.134260655829283</v>
       </c>
       <c r="AE11" t="n">
-        <v>24.0952380952381</v>
+        <v>27.58125</v>
       </c>
       <c r="AF11" t="n">
-        <v>179.1666666666667</v>
+        <v>178.6833333333333</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.714285714285714</v>
+        <v>3.125</v>
       </c>
       <c r="AH11" t="n">
-        <v>199.5714285714286</v>
+        <v>227.125</v>
       </c>
       <c r="AI11" t="n">
-        <v>68285.71428571429</v>
+        <v>68875</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22185714.28571429</v>
+        <v>12643750</v>
       </c>
       <c r="AK11" t="n">
-        <v>214</v>
+        <v>232.75</v>
       </c>
       <c r="AL11" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>181.3214285714286</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>125.2857142857143</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>34285.71428571428</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11357142.85714286</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>133.5714285714286</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.285714285714286</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>28.33769841269842</v>
+      </c>
+      <c r="D12" t="n">
+        <v>179.9107142857143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>74.53888888888889</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19489.68253968254</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6394484.126984128</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.71904761904761</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.380555555555555</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27.8125</v>
+      </c>
+      <c r="K12" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="L12" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20250</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7075000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>29.96381578947368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>178.403307748538</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75.37222222222222</v>
+      </c>
+      <c r="T12" t="n">
+        <v>21739.93969298246</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7985959.429824562</v>
+      </c>
+      <c r="V12" t="n">
+        <v>76.36430921052632</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.599250730994152</v>
+      </c>
+      <c r="X12" t="n">
+        <v>26.96884459924321</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>178.6195987057104</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>72.79484917870657</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>20495.3302373581</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5169477.554179566</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>75.04917763157894</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.117870119539044</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>177.2916666666667</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>156.625</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10331250</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>27.14583333333334</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>180.3541666666667</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>44750</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13712500</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>174</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>27.05069444444445</v>
+      </c>
+      <c r="D13" t="n">
+        <v>183.8076388888889</v>
+      </c>
+      <c r="E13" t="n">
+        <v>85.66909722222222</v>
+      </c>
+      <c r="F13" t="n">
+        <v>224916.6666666667</v>
+      </c>
+      <c r="G13" t="n">
+        <v>71507986.1111111</v>
+      </c>
+      <c r="H13" t="n">
+        <v>88.24895833333332</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.506250000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.89484126984127</v>
+      </c>
+      <c r="K13" t="n">
+        <v>182.1349206349207</v>
+      </c>
+      <c r="L13" t="n">
+        <v>76.21428571428571</v>
+      </c>
+      <c r="M13" t="n">
+        <v>31515.87301587302</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10805357.14285714</v>
+      </c>
+      <c r="O13" t="n">
+        <v>79.60714285714286</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.192460317460317</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25.89695391414141</v>
+      </c>
+      <c r="R13" t="n">
+        <v>180.0714440073815</v>
+      </c>
+      <c r="S13" t="n">
+        <v>80.51273431429681</v>
+      </c>
+      <c r="T13" t="n">
+        <v>145594.5828477078</v>
+      </c>
+      <c r="U13" t="n">
+        <v>42123630.05050505</v>
+      </c>
+      <c r="V13" t="n">
+        <v>85.62149378399378</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.385965423465424</v>
+      </c>
+      <c r="X13" t="n">
+        <v>27.14564904909332</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>178.246335968598</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>73.28027329352793</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>27586.67832264485</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6487963.86646764</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>76.6343208665045</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.125737367315347</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>24.92708333333334</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>178.7916666666667</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>199.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>458625</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>160262500</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>209.25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>27.3125</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>178.3125</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>85.125</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>34375</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9187500</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="D14" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30666.66666666667</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9300000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.66666666666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.99166666666666</v>
+      </c>
+      <c r="K14" t="n">
+        <v>182.2333333333333</v>
+      </c>
+      <c r="L14" t="n">
+        <v>73.15555555555555</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22502.77777777778</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4770277.777777778</v>
+      </c>
+      <c r="O14" t="n">
+        <v>76.65555555555555</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>25.48806341362456</v>
+      </c>
+      <c r="R14" t="n">
+        <v>179.8850862308486</v>
+      </c>
+      <c r="S14" t="n">
+        <v>73.78119556527065</v>
+      </c>
+      <c r="T14" t="n">
+        <v>33881.39239501469</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7915438.695721203</v>
+      </c>
+      <c r="V14" t="n">
+        <v>79.00880836140124</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.427206662017034</v>
+      </c>
+      <c r="X14" t="n">
+        <v>25.01721396293765</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>180.2526890142022</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>72.64201697425381</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>24939.07353611301</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5333454.849244323</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>77.14040546441862</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.108341402749297</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28.61190476190476</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>183.1000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>327.5714285714286</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>185857.1428571429</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>77428571.42857143</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>331.8571428571428</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>181.4047619047619</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>111.5714285714286</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>28714.28571428571</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4457142.857142857</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>119.5714285714286</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.571428571428571</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jFGHcfig</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>24.35347222222222</v>
+      </c>
+      <c r="K15" t="n">
+        <v>182.2635416666667</v>
+      </c>
+      <c r="L15" t="n">
+        <v>76.27291666666666</v>
+      </c>
+      <c r="M15" t="n">
+        <v>36829.51388888889</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17766128.47222222</v>
+      </c>
+      <c r="O15" t="n">
+        <v>81.02013888888888</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.259027777777778</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>26.44486472473605</v>
+      </c>
+      <c r="R15" t="n">
+        <v>181.1052436840121</v>
+      </c>
+      <c r="S15" t="n">
+        <v>71.52209888763198</v>
+      </c>
+      <c r="T15" t="n">
+        <v>19930.31202865762</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3656162.565987933</v>
+      </c>
+      <c r="V15" t="n">
+        <v>75.57934342006033</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>24.50909992784993</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>178.2031836219336</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>72.95533008658009</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>28253.11147186147</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8439793.47041847</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>79.0317821067821</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.065340909090909</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>27.70833333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>180.3958333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>130.125</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>9062500</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>26.53541666666667</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>182.69375</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>140250</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>56212500</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>27.90216049382716</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.3549382716049</v>
+      </c>
+      <c r="E16" t="n">
+        <v>75.69012345679012</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28644.44444444445</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8368024.691358025</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.55277777777776</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.334259259259259</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.09722222222222</v>
+      </c>
+      <c r="K16" t="n">
+        <v>181.6833333333333</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79.05277777777778</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40230.55555555556</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20101388.88888889</v>
+      </c>
+      <c r="O16" t="n">
+        <v>82.35833333333332</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.863888888888889</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25.6122614857909</v>
+      </c>
+      <c r="R16" t="n">
+        <v>181.4805957568213</v>
+      </c>
+      <c r="S16" t="n">
+        <v>71.40012050404208</v>
+      </c>
+      <c r="T16" t="n">
+        <v>22410.89564030741</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5963457.353739216</v>
+      </c>
+      <c r="V16" t="n">
+        <v>75.88428709090473</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.134260655829283</v>
+      </c>
+      <c r="X16" t="n">
+        <v>27.32931627196333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>181.5595407860114</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>75.31249469484763</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>30929.42237501061</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10095341.22740005</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>79.52355063237417</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.456869111280876</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>181.3214285714286</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>125.2857142857143</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>34285.71428571428</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>11357142.85714286</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>133.5714285714286</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>22.54166666666666</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>179.2055555555556</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>129500</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>36912500</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>28.55753968253968</v>
+      </c>
+      <c r="K17" t="n">
+        <v>181.8432539682539</v>
+      </c>
+      <c r="L17" t="n">
+        <v>74.15476190476191</v>
+      </c>
+      <c r="M17" t="n">
+        <v>23228.17460317461</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6659722.222222222</v>
+      </c>
+      <c r="O17" t="n">
+        <v>77.3888888888889</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23.16579207829208</v>
+      </c>
+      <c r="R17" t="n">
+        <v>181.4293142043142</v>
+      </c>
+      <c r="S17" t="n">
+        <v>71.66889730639731</v>
+      </c>
+      <c r="T17" t="n">
+        <v>23241.13849113849</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6576087.130462131</v>
+      </c>
+      <c r="V17" t="n">
+        <v>80.27435157435158</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.222145447145447</v>
+      </c>
+      <c r="X17" t="n">
+        <v>25.84918177797434</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>179.4381173522041</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70.39984151555359</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>20307.03597228365</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5032994.711042311</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>75.41489753796255</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.202565236620964</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>30.52592592592593</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>180.8259259259259</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>303.2222222222222</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>130444.4444444444</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>51311111.11111111</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>309</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>8.777777777777779</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>27.58125</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>178.6833333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>227.125</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>68875</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12643750</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>184.06875</v>
+      </c>
+      <c r="E18" t="n">
+        <v>75.91249999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>29075</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10646875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>78.65625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.35625</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29.47539682539682</v>
+      </c>
+      <c r="K18" t="n">
+        <v>181.1849206349206</v>
+      </c>
+      <c r="L18" t="n">
+        <v>82.48690476190475</v>
+      </c>
+      <c r="M18" t="n">
+        <v>83338.09523809524</v>
+      </c>
+      <c r="N18" t="n">
+        <v>31114682.53968254</v>
+      </c>
+      <c r="O18" t="n">
+        <v>83.71825396825398</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.845634920634921</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26.39599740537241</v>
+      </c>
+      <c r="R18" t="n">
+        <v>180.8784893925519</v>
+      </c>
+      <c r="S18" t="n">
+        <v>75.06565361721611</v>
+      </c>
+      <c r="T18" t="n">
+        <v>27420.54334554334</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9516223.29059829</v>
+      </c>
+      <c r="V18" t="n">
+        <v>78.64545367826618</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.266529304029304</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27.43061997825446</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>178.1551862192245</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>79.06605230908153</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>71424.80304621848</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23126225.8126935</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>81.84784479581307</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.216949542975085</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>24.61111111111111</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>180.0277777777777</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>221.3333333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>77166.66666666667</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>25316666.66666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>236.1666666666667</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>27.82142857142857</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>179.6428571428571</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>203.4285714285714</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>164857.1428571429</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>49357142.85714286</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>211.8571428571429</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.142857142857143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>27.1875</v>
+      </c>
+      <c r="D19" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="E19" t="n">
+        <v>72.4375</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27250</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>75.5625</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>26.5925812400319</v>
+      </c>
+      <c r="R19" t="n">
+        <v>180.767999900319</v>
+      </c>
+      <c r="S19" t="n">
+        <v>70.20020434609251</v>
+      </c>
+      <c r="T19" t="n">
+        <v>24618.81479266348</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3271949.13775917</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73.81562250797448</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.026891447368421</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.59098193473194</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>180.9968573093573</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>73.02123917748918</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>24929.06052281052</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8673449.467199467</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>79.16984577922076</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.213650932400933</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>23.07142857142857</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>94.42857142857143</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>31571.42857142857</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2242857.142857143</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>106.7142857142857</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>26.91666666666667</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>91.16666666666667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>38166.66666666666</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19416666.66666667</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.833333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.72569444444444</v>
+      </c>
+      <c r="D20" t="n">
+        <v>180.3020833333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>72.07638888888889</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19756.94444444445</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3301041.666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>74.69097222222223</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.059027777777778</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26.85625</v>
+      </c>
+      <c r="K20" t="n">
+        <v>182.9661931818182</v>
+      </c>
+      <c r="L20" t="n">
+        <v>78.65198863636364</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33335.22727272727</v>
+      </c>
+      <c r="N20" t="n">
+        <v>23170681.81818182</v>
+      </c>
+      <c r="O20" t="n">
+        <v>81.8215909090909</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.805397727272727</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>27.06428875898186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>180.5754876054159</v>
+      </c>
+      <c r="S20" t="n">
+        <v>71.70514226476251</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18891.37643234258</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3148274.463866401</v>
+      </c>
+      <c r="V20" t="n">
+        <v>74.66412333049162</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04674762353454</v>
+      </c>
+      <c r="X20" t="n">
+        <v>26.87370709248612</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>182.0990996947024</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>76.08023635989483</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>30179.32714752568</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>15029235.13594034</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>79.94069211017741</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.488671663840975</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>28.03125</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>179.1041666666667</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>156.625</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>40750</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3778125</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>160.625</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>27.08541666666667</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>185.54375</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>264</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>118375</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>116300000</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>272</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>26.11805555555556</v>
+      </c>
+      <c r="D21" t="n">
+        <v>180.8472222222223</v>
+      </c>
+      <c r="E21" t="n">
+        <v>78.09722222222223</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38486.11111111111</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21582638.88888889</v>
+      </c>
+      <c r="H21" t="n">
+        <v>81.96527777777777</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.930555555555556</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24.51984126984127</v>
+      </c>
+      <c r="K21" t="n">
+        <v>179.3988095238095</v>
+      </c>
+      <c r="L21" t="n">
+        <v>80.09126984126985</v>
+      </c>
+      <c r="M21" t="n">
+        <v>113267.8571428571</v>
+      </c>
+      <c r="N21" t="n">
+        <v>38744642.85714286</v>
+      </c>
+      <c r="O21" t="n">
+        <v>86.40476190476191</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.654761904761905</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>24.43602994227994</v>
+      </c>
+      <c r="R21" t="n">
+        <v>181.436272387743</v>
+      </c>
+      <c r="S21" t="n">
+        <v>72.23046749002631</v>
+      </c>
+      <c r="T21" t="n">
+        <v>30773.4010270775</v>
+      </c>
+      <c r="U21" t="n">
+        <v>12418130.92850777</v>
+      </c>
+      <c r="V21" t="n">
+        <v>78.37486524912995</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.622252461590697</v>
+      </c>
+      <c r="X21" t="n">
+        <v>21.60076246852563</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>180.4755268853953</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>73.44869728224992</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>76762.65956265955</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>26050305.80530581</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>82.56814158064158</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.919148468490574</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>26.08333333333334</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>179.9166666666666</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>247.875</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>112500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>43387500</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>26.69047619047619</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="AO21" t="n">
         <v>3.285714285714286</v>
       </c>
-      <c r="AM11" t="n">
-        <v>27.30416666666667</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>184.66875</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>3.625</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>293.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>131125</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>120987500</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>302</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.375</v>
+      <c r="AP21" t="n">
+        <v>277.5714285714286</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>464714.2857142857</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>182000000</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>287.4285714285714</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>11.85714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT9"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,504 +658,586 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.99166666666666</v>
+        <v>28.33769841269842</v>
       </c>
       <c r="D2" t="n">
-        <v>182.2333333333333</v>
+        <v>179.9107142857143</v>
       </c>
       <c r="E2" t="n">
-        <v>73.15555555555555</v>
+        <v>74.53888888888889</v>
       </c>
       <c r="F2" t="n">
-        <v>22502.77777777778</v>
+        <v>19489.68253968254</v>
       </c>
       <c r="G2" t="n">
-        <v>4770277.777777778</v>
+        <v>6394484.126984128</v>
       </c>
       <c r="H2" t="n">
-        <v>76.65555555555555</v>
+        <v>76.71904761904761</v>
       </c>
       <c r="I2" t="n">
-        <v>1.05</v>
+        <v>1.380555555555555</v>
       </c>
       <c r="J2" t="n">
-        <v>27.3</v>
+        <v>27.04166666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>184.06875</v>
+        <v>179.7916666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>75.91249999999999</v>
+        <v>74.125</v>
       </c>
       <c r="M2" t="n">
-        <v>29075</v>
+        <v>19541.66666666667</v>
       </c>
       <c r="N2" t="n">
-        <v>10646875</v>
+        <v>6600000</v>
       </c>
       <c r="O2" t="n">
-        <v>78.65625</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="P2" t="n">
-        <v>1.35625</v>
+        <v>1.125</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.24747712083239</v>
+        <v>29.72475328947368</v>
       </c>
       <c r="R2" t="n">
-        <v>180.3645311194653</v>
+        <v>178.604870248538</v>
       </c>
       <c r="S2" t="n">
-        <v>72.75385907951697</v>
+        <v>74.92690972222222</v>
       </c>
       <c r="T2" t="n">
-        <v>24662.75774663933</v>
+        <v>21152.43969298246</v>
       </c>
       <c r="U2" t="n">
-        <v>5366349.586086428</v>
+        <v>7606037.554824562</v>
       </c>
       <c r="V2" t="n">
-        <v>76.95619493810284</v>
+        <v>76.25962171052632</v>
       </c>
       <c r="W2" t="n">
-        <v>1.108341402749297</v>
+        <v>1.566438230994152</v>
       </c>
       <c r="X2" t="n">
-        <v>26.24621925693354</v>
+        <v>27.15680923441501</v>
       </c>
       <c r="Y2" t="n">
-        <v>180.9643053375196</v>
+        <v>178.3120848144326</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.00360413396128</v>
+        <v>72.89622558575087</v>
       </c>
       <c r="AA2" t="n">
-        <v>27163.16064887493</v>
+        <v>20377.68747850017</v>
       </c>
       <c r="AB2" t="n">
-        <v>9441556.776556777</v>
+        <v>5053143.059855521</v>
       </c>
       <c r="AC2" t="n">
-        <v>78.7217883307169</v>
+        <v>74.94795321637427</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.256985871271585</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+        <v>1.117858234911899</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>176.6190476190476</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>170.4285714285714</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>43285.71428571428</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>11728571.42857143</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>46750</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15312500</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>185</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.875</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.87731481481481</v>
+        <v>26.95079365079365</v>
       </c>
       <c r="D3" t="n">
-        <v>182.0833333333333</v>
+        <v>183.7623015873016</v>
       </c>
       <c r="E3" t="n">
-        <v>76.13888888888889</v>
+        <v>85.56825396825397</v>
       </c>
       <c r="F3" t="n">
-        <v>31361.11111111111</v>
+        <v>221690.4761904762</v>
       </c>
       <c r="G3" t="n">
-        <v>10654398.14814815</v>
+        <v>71776984.12698412</v>
       </c>
       <c r="H3" t="n">
-        <v>79.54166666666667</v>
+        <v>88.23095238095236</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1875</v>
+        <v>3.489285714285714</v>
       </c>
       <c r="J3" t="n">
-        <v>26.73611111111111</v>
+        <v>26.9265873015873</v>
       </c>
       <c r="K3" t="n">
-        <v>181.15625</v>
+        <v>182.1031746031746</v>
       </c>
       <c r="L3" t="n">
-        <v>72.10416666666667</v>
+        <v>76.16666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>19427.08333333333</v>
+        <v>31388.88888888889</v>
       </c>
       <c r="N3" t="n">
-        <v>3403125</v>
+        <v>10652976.19047619</v>
       </c>
       <c r="O3" t="n">
-        <v>74.84722222222223</v>
+        <v>79.55952380952382</v>
       </c>
       <c r="P3" t="n">
-        <v>1.059027777777778</v>
+        <v>1.176587301587302</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.24916282302394</v>
+        <v>25.77234293484293</v>
       </c>
       <c r="R3" t="n">
-        <v>178.3567147911797</v>
+        <v>180.3234085359085</v>
       </c>
       <c r="S3" t="n">
-        <v>73.41053789937028</v>
+        <v>80.62993811743812</v>
       </c>
       <c r="T3" t="n">
-        <v>27843.42184242118</v>
+        <v>146492.7100677101</v>
       </c>
       <c r="U3" t="n">
-        <v>6608800.809797603</v>
+        <v>43656676.10167611</v>
       </c>
       <c r="V3" t="n">
-        <v>76.6422313662307</v>
+        <v>85.72126762126763</v>
       </c>
       <c r="W3" t="n">
-        <v>1.128662254375434</v>
+        <v>2.375169275169275</v>
       </c>
       <c r="X3" t="n">
-        <v>27.12411018755328</v>
+        <v>27.21801747014595</v>
       </c>
       <c r="Y3" t="n">
-        <v>180.0228090339874</v>
+        <v>178.2730629422822</v>
       </c>
       <c r="Z3" t="n">
-        <v>71.6613922647625</v>
+        <v>73.445158161949</v>
       </c>
       <c r="AA3" t="n">
-        <v>18992.26928948544</v>
+        <v>27917.68161211853</v>
       </c>
       <c r="AB3" t="n">
-        <v>3069078.035294972</v>
+        <v>6715513.208572903</v>
       </c>
       <c r="AC3" t="n">
-        <v>74.55162333049162</v>
+        <v>76.67132744545188</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.04049762353454</v>
+        <v>1.143829472578505</v>
       </c>
       <c r="AE3" t="n">
+        <v>25.48809523809524</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>178.047619047619</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>203</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>462714.2857142857</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>147728571.4285714</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>212.8571428571429</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>7.857142857142857</v>
+      </c>
+      <c r="AM3" t="n">
         <v>27.35714285714286</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AN3" t="n">
         <v>178.2142857142857</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AO3" t="n">
         <v>1.142857142857143</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AP3" t="n">
         <v>86.57142857142857</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AQ3" t="n">
         <v>35142.85714285714</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AR3" t="n">
         <v>9642857.142857144</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AS3" t="n">
         <v>87</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AT3" t="n">
         <v>1.285714285714286</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>27.89285714285714</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>179.8333333333333</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>169.1428571428571</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>44142.85714285714</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4117857.142857143</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>173.7142857142857</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.428571428571428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.96296296296296</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>181.7777777777778</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="E4" t="n">
-        <v>79.03703703703702</v>
+        <v>76.44444444444444</v>
       </c>
       <c r="F4" t="n">
-        <v>38740.74074074074</v>
+        <v>30666.66666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>20251851.85185185</v>
+        <v>9300000</v>
       </c>
       <c r="H4" t="n">
-        <v>82.44444444444444</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>1.851851851851852</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J4" t="n">
-        <v>27.1875</v>
+        <v>25.99305555555555</v>
       </c>
       <c r="K4" t="n">
-        <v>183.125</v>
+        <v>182.0486111111111</v>
       </c>
       <c r="L4" t="n">
-        <v>72.4375</v>
+        <v>73.04629629629629</v>
       </c>
       <c r="M4" t="n">
-        <v>27250</v>
+        <v>22168.98148148148</v>
       </c>
       <c r="N4" t="n">
-        <v>4750000</v>
+        <v>4618981.481481481</v>
       </c>
       <c r="O4" t="n">
-        <v>75.5625</v>
+        <v>76.46296296296296</v>
       </c>
       <c r="P4" t="n">
-        <v>1.125</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.28624904507257</v>
+        <v>25.7059205564817</v>
       </c>
       <c r="R4" t="n">
-        <v>181.9093307019778</v>
+        <v>180.3642528975153</v>
       </c>
       <c r="S4" t="n">
-        <v>75.49211654358713</v>
+        <v>74.30679080336587</v>
       </c>
       <c r="T4" t="n">
-        <v>31535.5148119854</v>
+        <v>33403.09824334592</v>
       </c>
       <c r="U4" t="n">
-        <v>10581029.25261013</v>
+        <v>8540022.029054537</v>
       </c>
       <c r="V4" t="n">
-        <v>79.70317248111365</v>
+        <v>79.1409512185441</v>
       </c>
       <c r="W4" t="n">
-        <v>1.491532976827094</v>
+        <v>1.424230471540843</v>
       </c>
       <c r="X4" t="n">
-        <v>26.5472687400319</v>
+        <v>25.33109077407323</v>
       </c>
       <c r="Y4" t="n">
-        <v>180.547687400319</v>
+        <v>180.4573609950803</v>
       </c>
       <c r="Z4" t="n">
-        <v>69.87207934609251</v>
+        <v>72.79602288549657</v>
       </c>
       <c r="AA4" t="n">
-        <v>23596.93979266348</v>
+        <v>24766.89577479051</v>
       </c>
       <c r="AB4" t="n">
-        <v>3059371.01275917</v>
+        <v>5338977.409854602</v>
       </c>
       <c r="AC4" t="n">
-        <v>73.54843500797448</v>
+        <v>76.87217327831362</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.019078947368421</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>1.103710876517894</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>28.71388888888889</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>183.3388888888889</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>303.6666666666667</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>174833.3333333333</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>72500000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>307.1666666666667</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>181.4791666666667</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>26875</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4287500</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>29.08784722222222</v>
-      </c>
-      <c r="D5" t="n">
-        <v>181.1930555555556</v>
-      </c>
-      <c r="E5" t="n">
-        <v>81.67604166666666</v>
-      </c>
-      <c r="F5" t="n">
-        <v>79936.45833333333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29262847.22222222</v>
-      </c>
-      <c r="H5" t="n">
-        <v>83.34722222222223</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.755555555555556</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>27.04166666666667</v>
+        <v>24.40396825396826</v>
       </c>
       <c r="K5" t="n">
-        <v>179.7916666666667</v>
+        <v>182.5154761904762</v>
       </c>
       <c r="L5" t="n">
-        <v>74.125</v>
+        <v>76.25476190476191</v>
       </c>
       <c r="M5" t="n">
-        <v>19541.66666666667</v>
+        <v>36905.15873015874</v>
       </c>
       <c r="N5" t="n">
-        <v>6600000</v>
+        <v>17741289.68253968</v>
       </c>
       <c r="O5" t="n">
-        <v>77.16666666666667</v>
+        <v>80.98015873015872</v>
       </c>
       <c r="P5" t="n">
-        <v>1.125</v>
+        <v>1.267460317460318</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.50204854968303</v>
+        <v>26.42185333729451</v>
       </c>
       <c r="R5" t="n">
-        <v>177.9647100287483</v>
+        <v>181.1222989700931</v>
       </c>
       <c r="S5" t="n">
-        <v>79.1374808805101</v>
+        <v>71.38017181620123</v>
       </c>
       <c r="T5" t="n">
-        <v>71972.42209383754</v>
+        <v>19782.65498118439</v>
       </c>
       <c r="U5" t="n">
-        <v>23521463.9079316</v>
+        <v>3576728.80768469</v>
       </c>
       <c r="V5" t="n">
-        <v>81.87760670057497</v>
+        <v>75.59811101208159</v>
       </c>
       <c r="W5" t="n">
-        <v>2.240759066784608</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>27.1500945992432</v>
+        <v>24.3889713461142</v>
       </c>
       <c r="Y5" t="n">
-        <v>178.3774112057104</v>
+        <v>177.6679241393527</v>
       </c>
       <c r="Z5" t="n">
-        <v>72.77141167870657</v>
+        <v>72.94180581323438</v>
       </c>
       <c r="AA5" t="n">
-        <v>20495.3302373581</v>
+        <v>28324.98453927025</v>
       </c>
       <c r="AB5" t="n">
-        <v>4905180.679179566</v>
+        <v>8645121.10904968</v>
       </c>
       <c r="AC5" t="n">
-        <v>74.78355263157894</v>
+        <v>79.18632240775098</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.119432619539044</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>1.053246753246753</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>27.08333333333334</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>179.9375</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>35125</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>9875000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>141.625</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>26.32619047619048</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>183.0071428571428</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>298</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>147285.7142857143</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>59171428.57142857</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>308.1428571428572</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.285714285714286</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.42129629629629</v>
+        <v>27.38425925925926</v>
       </c>
       <c r="D6" t="n">
-        <v>179.3356481481482</v>
+        <v>182.75</v>
       </c>
       <c r="E6" t="n">
-        <v>79.90277777777777</v>
+        <v>72.32870370370371</v>
       </c>
       <c r="F6" t="n">
-        <v>112127.3148148148</v>
+        <v>26981.48148148149</v>
       </c>
       <c r="G6" t="n">
-        <v>38144675.92592593</v>
+        <v>4607407.407407408</v>
       </c>
       <c r="H6" t="n">
-        <v>86.32407407407408</v>
+        <v>75.33796296296296</v>
       </c>
       <c r="I6" t="n">
-        <v>2.615740740740741</v>
+        <v>1.12037037037037</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1165,68 +1247,100 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>21.60866360039293</v>
+        <v>26.27433989012936</v>
       </c>
       <c r="R6" t="n">
-        <v>180.5824203365557</v>
+        <v>180.456530214425</v>
       </c>
       <c r="S6" t="n">
-        <v>73.68162806283108</v>
+        <v>69.61356547935495</v>
       </c>
       <c r="T6" t="n">
-        <v>78456.02651316936</v>
+        <v>22863.94648236754</v>
       </c>
       <c r="U6" t="n">
-        <v>27411388.45281702</v>
+        <v>2943178.273967748</v>
       </c>
       <c r="V6" t="n">
-        <v>82.61034362462934</v>
+        <v>73.69961899698741</v>
       </c>
       <c r="W6" t="n">
-        <v>1.959546301651565</v>
+        <v>1.016959064327485</v>
       </c>
       <c r="X6" t="n">
-        <v>26.29276682263815</v>
+        <v>24.62405464905465</v>
       </c>
       <c r="Y6" t="n">
-        <v>181.0694045231729</v>
+        <v>181.2090751840752</v>
       </c>
       <c r="Z6" t="n">
-        <v>71.38223874777184</v>
+        <v>73.12670755170755</v>
       </c>
       <c r="AA6" t="n">
-        <v>19823.66867201426</v>
+        <v>24892.75076775077</v>
       </c>
       <c r="AB6" t="n">
-        <v>3656774.454099822</v>
+        <v>8763545.991045991</v>
       </c>
       <c r="AC6" t="n">
-        <v>75.69560216131907</v>
+        <v>79.19011544011545</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>1.21440688940689</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2512500</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>111.875</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>103.3333333333333</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>39333.33333333334</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19566666.66666667</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>106.8333333333333</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.833333333333333</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1240,321 +1354,683 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>26.125</v>
+        <v>28.70659722222222</v>
       </c>
       <c r="K7" t="n">
-        <v>180.25</v>
+        <v>181.0746527777778</v>
       </c>
       <c r="L7" t="n">
-        <v>77.75</v>
+        <v>74.14409722222223</v>
       </c>
       <c r="M7" t="n">
-        <v>37750</v>
+        <v>23078.125</v>
       </c>
       <c r="N7" t="n">
-        <v>19587500</v>
+        <v>6403472.222222222</v>
       </c>
       <c r="O7" t="n">
-        <v>81.375</v>
+        <v>77.00694444444446</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.454861111111111</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.62393648018648</v>
+        <v>23.61697305145835</v>
       </c>
       <c r="R7" t="n">
-        <v>181.0945845820846</v>
+        <v>181.2079042770955</v>
       </c>
       <c r="S7" t="n">
-        <v>73.126920995671</v>
+        <v>71.92364219114219</v>
       </c>
       <c r="T7" t="n">
-        <v>24894.96961371962</v>
+        <v>23731.0800718889</v>
       </c>
       <c r="U7" t="n">
-        <v>8657426.739926741</v>
+        <v>6555134.243207773</v>
       </c>
       <c r="V7" t="n">
-        <v>79.19825487012987</v>
+        <v>80.08755555718793</v>
       </c>
       <c r="W7" t="n">
-        <v>1.194332750582751</v>
+        <v>1.279201264421853</v>
       </c>
       <c r="X7" t="n">
-        <v>24.41895485466913</v>
+        <v>25.86303449254946</v>
       </c>
       <c r="Y7" t="n">
-        <v>181.4827239986904</v>
+        <v>179.5528363392141</v>
       </c>
       <c r="Z7" t="n">
-        <v>72.36656602034753</v>
+        <v>70.45708497824081</v>
       </c>
       <c r="AA7" t="n">
-        <v>31010.87101507269</v>
+        <v>20336.46480034509</v>
       </c>
       <c r="AB7" t="n">
-        <v>12797506.77543745</v>
+        <v>5026460.077208271</v>
       </c>
       <c r="AC7" t="n">
-        <v>78.48397298313265</v>
+        <v>75.41563877012793</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.639717098960796</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+        <v>1.216005700525824</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>30.6462962962963</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>180.8351851851852</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.777777777777778</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>297.1111111111111</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>53461111.11111111</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27.175</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>178.9958333333333</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>232.875</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>68250</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12062500</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>242</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>26.79675324675324</v>
+        <v>27.3</v>
       </c>
       <c r="D8" t="n">
-        <v>182.8964285714286</v>
+        <v>184.06875</v>
       </c>
       <c r="E8" t="n">
-        <v>78.49837662337663</v>
+        <v>75.91249999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>33032.46753246753</v>
+        <v>29075</v>
       </c>
       <c r="G8" t="n">
-        <v>22772987.01298701</v>
+        <v>10646875</v>
       </c>
       <c r="H8" t="n">
-        <v>81.74415584415583</v>
+        <v>78.65625</v>
       </c>
       <c r="I8" t="n">
-        <v>1.751623376623377</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>1.35625</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.91141975308642</v>
+      </c>
+      <c r="K8" t="n">
+        <v>180.8604938271605</v>
+      </c>
+      <c r="L8" t="n">
+        <v>81.56759259259259</v>
+      </c>
+      <c r="M8" t="n">
+        <v>79543.51851851851</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29066975.30864198</v>
+      </c>
+      <c r="O8" t="n">
+        <v>83.37530864197531</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.704938271604938</v>
+      </c>
       <c r="Q8" t="n">
-        <v>26.94852239141271</v>
+        <v>26.33308890864038</v>
       </c>
       <c r="R8" t="n">
-        <v>181.99897107966</v>
+        <v>181.4467083468002</v>
       </c>
       <c r="S8" t="n">
-        <v>76.25598441130839</v>
+        <v>75.04727126427494</v>
       </c>
       <c r="T8" t="n">
-        <v>30333.51674002935</v>
+        <v>27407.47145011851</v>
       </c>
       <c r="U8" t="n">
-        <v>15303411.58393182</v>
+        <v>9773862.17948718</v>
       </c>
       <c r="V8" t="n">
-        <v>80.02507669734561</v>
+        <v>78.71980008349493</v>
       </c>
       <c r="W8" t="n">
-        <v>1.508481901532543</v>
+        <v>1.298392049127343</v>
       </c>
       <c r="X8" t="n">
-        <v>23.4371595996596</v>
+        <v>27.64732357855423</v>
       </c>
       <c r="Y8" t="n">
-        <v>181.3486518111518</v>
+        <v>178.2649274329615</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.80404687904689</v>
+        <v>79.27035337526823</v>
       </c>
       <c r="AA8" t="n">
-        <v>23805.77524327524</v>
+        <v>72150.08948023655</v>
       </c>
       <c r="AB8" t="n">
-        <v>6641979.224479225</v>
+        <v>23580454.69064819</v>
       </c>
       <c r="AC8" t="n">
-        <v>80.11035584785584</v>
+        <v>81.90178796664866</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.257936045436046</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+        <v>2.261627106983144</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>24.94444444444445</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>181.5277777777777</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>222.1666666666667</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>78166.66666666667</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>26250000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>236.3333333333333</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>28.05208333333334</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>179.5208333333333</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>171375</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>51625000</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>216</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>28.50595238095238</v>
+        <v>28.01944444444445</v>
       </c>
       <c r="D9" t="n">
-        <v>181.1805555555555</v>
+        <v>181.3043209876543</v>
       </c>
       <c r="E9" t="n">
-        <v>73.8313492063492</v>
+        <v>75.70987654320987</v>
       </c>
       <c r="F9" t="n">
-        <v>22803.57142857143</v>
+        <v>28516.04938271605</v>
       </c>
       <c r="G9" t="n">
-        <v>6272222.222222222</v>
+        <v>8373148.148148149</v>
       </c>
       <c r="H9" t="n">
-        <v>76.94444444444444</v>
+        <v>77.5108024691358</v>
       </c>
       <c r="I9" t="n">
-        <v>1.44047619047619</v>
+        <v>1.330555555555555</v>
       </c>
       <c r="J9" t="n">
-        <v>27.959375</v>
+        <v>26.00347222222222</v>
       </c>
       <c r="K9" t="n">
-        <v>181.3298611111111</v>
+        <v>182.4583333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>75.8736111111111</v>
+        <v>78.46527777777777</v>
       </c>
       <c r="M9" t="n">
-        <v>28780.55555555555</v>
+        <v>37211.80555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>8443541.666666668</v>
+        <v>19075607.63888889</v>
       </c>
       <c r="O9" t="n">
-        <v>77.64965277777777</v>
+        <v>82.02083333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>1.334375</v>
+        <v>1.826388888888889</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.80424713745147</v>
+        <v>25.74298044003926</v>
       </c>
       <c r="R9" t="n">
-        <v>179.4969408816158</v>
+        <v>181.5655630770827</v>
       </c>
       <c r="S9" t="n">
-        <v>70.31283171163201</v>
+        <v>71.36744076547998</v>
       </c>
       <c r="T9" t="n">
-        <v>20135.46734483267</v>
+        <v>21728.54269913094</v>
       </c>
       <c r="U9" t="n">
-        <v>4894177.309081527</v>
+        <v>5788293.955046405</v>
       </c>
       <c r="V9" t="n">
-        <v>75.41203806083837</v>
+        <v>75.68820865953219</v>
       </c>
       <c r="W9" t="n">
-        <v>1.215228635313775</v>
+        <v>1.140796603541702</v>
       </c>
       <c r="X9" t="n">
-        <v>25.79908828916182</v>
+        <v>27.82587216704864</v>
       </c>
       <c r="Y9" t="n">
-        <v>181.4524349323062</v>
+        <v>182.268611417631</v>
       </c>
       <c r="Z9" t="n">
-        <v>71.52366497881204</v>
+        <v>75.46918295937904</v>
       </c>
       <c r="AA9" t="n">
-        <v>22484.20778567838</v>
+        <v>34237.91792811401</v>
       </c>
       <c r="AB9" t="n">
-        <v>6112749.817074265</v>
+        <v>10090676.79597091</v>
       </c>
       <c r="AC9" t="n">
-        <v>75.75952885962077</v>
+        <v>79.45043903083121</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.151043237807944</v>
+        <v>1.532156296862179</v>
       </c>
       <c r="AE9" t="n">
-        <v>27.62857142857143</v>
+        <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>178.9952380952381</v>
+        <v>181.4642857142857</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>127</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>39285.71428571428</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>14157142.85714286</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>135.4285714285714</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22.90277777777778</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>178.9902777777778</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>383.125</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>152375</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>49575000</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>428</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.73611111111111</v>
+      </c>
+      <c r="D10" t="n">
+        <v>181.15625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>72.10416666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19427.08333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3403125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>74.84722222222223</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.059027777777778</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.79715909090909</v>
+      </c>
+      <c r="K10" t="n">
+        <v>182.896875</v>
+      </c>
+      <c r="L10" t="n">
+        <v>78.67357954545454</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33103.40909090909</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23251363.63636363</v>
+      </c>
+      <c r="O10" t="n">
+        <v>81.91363636363636</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.782670454545455</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>27.23897513747427</v>
+      </c>
+      <c r="R10" t="n">
+        <v>180.119689901556</v>
+      </c>
+      <c r="S10" t="n">
+        <v>71.64053581429181</v>
+      </c>
+      <c r="T10" t="n">
+        <v>19045.75983626776</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2998829.598624771</v>
+      </c>
+      <c r="V10" t="n">
+        <v>74.42600436394576</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.035997887586257</v>
+      </c>
+      <c r="X10" t="n">
+        <v>27.07995709248612</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>181.9464681157551</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>76.19109162305273</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>30377.35346331515</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14993116.71488771</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>79.85088947859846</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.517290084893607</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>27.65625</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>180.6458333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>45625</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4743750</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>26.89791666666667</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>186.48125</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>254</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>113500</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>114112500</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>262</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="D11" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37750</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19587500</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24.25396825396825</v>
+      </c>
+      <c r="K11" t="n">
+        <v>179.359126984127</v>
+      </c>
+      <c r="L11" t="n">
+        <v>79.59523809523809</v>
+      </c>
+      <c r="M11" t="n">
+        <v>110251.9841269841</v>
+      </c>
+      <c r="N11" t="n">
+        <v>37379365.07936508</v>
+      </c>
+      <c r="O11" t="n">
+        <v>86.24206349206349</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.581349206349207</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24.46182359307359</v>
+      </c>
+      <c r="R11" t="n">
+        <v>181.3152406417112</v>
+      </c>
+      <c r="S11" t="n">
+        <v>72.26717383923267</v>
+      </c>
+      <c r="T11" t="n">
+        <v>30795.2264239029</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12379812.47612682</v>
+      </c>
+      <c r="V11" t="n">
+        <v>78.26871445547917</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.619276271114507</v>
+      </c>
+      <c r="X11" t="n">
+        <v>21.69508065034381</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>180.3596177944862</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>74.23392455497719</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>81867.77319902318</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>29764652.39621489</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>82.89030067155068</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.039603013945119</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>25.80208333333334</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>179.6666666666666</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>254.375</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110125</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>39750000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>273.875</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>27.58333333333333</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>183.8690476190476</v>
+      </c>
+      <c r="AO11" t="n">
         <v>3</v>
       </c>
-      <c r="AH9" t="n">
-        <v>217.7142857142857</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>66000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>12178571.42857143</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>223.2857142857143</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.571428571428572</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>25.83333333333333</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>181.375</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>38833.33333333334</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13100000</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>144.6666666666667</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.5</v>
+      <c r="AP11" t="n">
+        <v>255</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>434857.1428571428</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>162857142.8571429</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>262.5714285714286</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>11.14285714285714</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -1357,7 +1357,7 @@
         <v>28.70659722222222</v>
       </c>
       <c r="K7" t="n">
-        <v>181.0746527777778</v>
+        <v>181.0746527777777</v>
       </c>
       <c r="L7" t="n">
         <v>74.14409722222223</v>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AT15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,54 +748,22 @@
       <c r="AD2" t="n">
         <v>1.117858234911899</v>
       </c>
-      <c r="AE2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>176.6190476190476</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>170.4285714285714</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>43285.71428571428</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>11728571.42857143</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>183.7142857142857</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>3.428571428571428</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26.8125</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>180.125</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>176.75</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>46750</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15312500</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>185</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.875</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -890,30 +858,14 @@
       <c r="AD3" t="n">
         <v>1.143829472578505</v>
       </c>
-      <c r="AE3" t="n">
-        <v>25.48809523809524</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>178.047619047619</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>203</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>462714.2857142857</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>147728571.4285714</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>212.8571428571429</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>7.857142857142857</v>
-      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>27.35714285714286</v>
       </c>
@@ -1032,1005 +984,1367 @@
       <c r="AD4" t="n">
         <v>1.103710876517894</v>
       </c>
-      <c r="AE4" t="n">
-        <v>28.71388888888889</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>183.3388888888889</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>303.6666666666667</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>174833.3333333333</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>72500000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>307.1666666666667</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>24.625</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>181.4791666666667</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>106.25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>26875</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4287500</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>24.40396825396826</v>
-      </c>
-      <c r="K5" t="n">
-        <v>182.5154761904762</v>
-      </c>
-      <c r="L5" t="n">
-        <v>76.25476190476191</v>
-      </c>
-      <c r="M5" t="n">
-        <v>36905.15873015874</v>
-      </c>
-      <c r="N5" t="n">
-        <v>17741289.68253968</v>
-      </c>
-      <c r="O5" t="n">
-        <v>80.98015873015872</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.267460317460318</v>
-      </c>
+      <c r="C5" t="n">
+        <v>27.38425925925926</v>
+      </c>
+      <c r="D5" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72.32870370370371</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26981.48148148149</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4607407.407407408</v>
+      </c>
+      <c r="H5" t="n">
+        <v>75.33796296296296</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.12037037037037</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>26.42185333729451</v>
+        <v>26.27433989012936</v>
       </c>
       <c r="R5" t="n">
-        <v>181.1222989700931</v>
+        <v>180.456530214425</v>
       </c>
       <c r="S5" t="n">
-        <v>71.38017181620123</v>
+        <v>69.61356547935495</v>
       </c>
       <c r="T5" t="n">
-        <v>19782.65498118439</v>
+        <v>22863.94648236754</v>
       </c>
       <c r="U5" t="n">
-        <v>3576728.80768469</v>
+        <v>2943178.273967748</v>
       </c>
       <c r="V5" t="n">
-        <v>75.59811101208159</v>
+        <v>73.69961899698741</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.016959064327485</v>
       </c>
       <c r="X5" t="n">
-        <v>24.3889713461142</v>
+        <v>24.62405464905465</v>
       </c>
       <c r="Y5" t="n">
-        <v>177.6679241393527</v>
+        <v>181.2090751840752</v>
       </c>
       <c r="Z5" t="n">
-        <v>72.94180581323438</v>
+        <v>73.12670755170755</v>
       </c>
       <c r="AA5" t="n">
-        <v>28324.98453927025</v>
+        <v>24892.75076775077</v>
       </c>
       <c r="AB5" t="n">
-        <v>8645121.10904968</v>
+        <v>8763545.991045991</v>
       </c>
       <c r="AC5" t="n">
-        <v>79.18632240775098</v>
+        <v>79.19011544011545</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.053246753246753</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>27.08333333333334</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>179.9375</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>138.75</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>35125</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>9875000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>141.625</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>26.32619047619048</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>183.0071428571428</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>3.857142857142857</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>298</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>147285.7142857143</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>59171428.57142857</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>308.1428571428572</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.285714285714286</v>
-      </c>
+        <v>1.21440688940689</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>27.38425925925926</v>
-      </c>
-      <c r="D6" t="n">
-        <v>182.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>72.32870370370371</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26981.48148148149</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4607407.407407408</v>
-      </c>
-      <c r="H6" t="n">
-        <v>75.33796296296296</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.12037037037037</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>28.70659722222222</v>
+      </c>
+      <c r="K6" t="n">
+        <v>181.0746527777777</v>
+      </c>
+      <c r="L6" t="n">
+        <v>74.14409722222223</v>
+      </c>
+      <c r="M6" t="n">
+        <v>23078.125</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6403472.222222222</v>
+      </c>
+      <c r="O6" t="n">
+        <v>77.00694444444446</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.454861111111111</v>
+      </c>
       <c r="Q6" t="n">
-        <v>26.27433989012936</v>
+        <v>23.61697305145835</v>
       </c>
       <c r="R6" t="n">
-        <v>180.456530214425</v>
+        <v>181.2079042770955</v>
       </c>
       <c r="S6" t="n">
-        <v>69.61356547935495</v>
+        <v>71.92364219114219</v>
       </c>
       <c r="T6" t="n">
-        <v>22863.94648236754</v>
+        <v>23731.0800718889</v>
       </c>
       <c r="U6" t="n">
-        <v>2943178.273967748</v>
+        <v>6555134.243207773</v>
       </c>
       <c r="V6" t="n">
-        <v>73.69961899698741</v>
+        <v>80.08755555718793</v>
       </c>
       <c r="W6" t="n">
-        <v>1.016959064327485</v>
+        <v>1.279201264421853</v>
       </c>
       <c r="X6" t="n">
-        <v>24.62405464905465</v>
+        <v>25.86303449254946</v>
       </c>
       <c r="Y6" t="n">
-        <v>181.2090751840752</v>
+        <v>179.5528363392141</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.12670755170755</v>
+        <v>70.45708497824081</v>
       </c>
       <c r="AA6" t="n">
-        <v>24892.75076775077</v>
+        <v>20336.46480034509</v>
       </c>
       <c r="AB6" t="n">
-        <v>8763545.991045991</v>
+        <v>5026460.077208271</v>
       </c>
       <c r="AC6" t="n">
-        <v>79.19011544011545</v>
+        <v>75.41563877012793</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21440688940689</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>23.3125</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>34000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2512500</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>111.875</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>186.6666666666667</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>103.3333333333333</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>39333.33333333334</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19566666.66666667</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>106.8333333333333</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.833333333333333</v>
-      </c>
+        <v>1.216005700525824</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>184.06875</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75.91249999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29075</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10646875</v>
+      </c>
+      <c r="H7" t="n">
+        <v>78.65625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.35625</v>
+      </c>
       <c r="J7" t="n">
-        <v>28.70659722222222</v>
+        <v>28.91141975308642</v>
       </c>
       <c r="K7" t="n">
-        <v>181.0746527777777</v>
+        <v>180.8604938271605</v>
       </c>
       <c r="L7" t="n">
-        <v>74.14409722222223</v>
+        <v>81.56759259259259</v>
       </c>
       <c r="M7" t="n">
-        <v>23078.125</v>
+        <v>79543.51851851851</v>
       </c>
       <c r="N7" t="n">
-        <v>6403472.222222222</v>
+        <v>29066975.30864198</v>
       </c>
       <c r="O7" t="n">
-        <v>77.00694444444446</v>
+        <v>83.37530864197531</v>
       </c>
       <c r="P7" t="n">
-        <v>1.454861111111111</v>
+        <v>2.704938271604938</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.61697305145835</v>
+        <v>26.33308890864038</v>
       </c>
       <c r="R7" t="n">
-        <v>181.2079042770955</v>
+        <v>181.4467083468002</v>
       </c>
       <c r="S7" t="n">
-        <v>71.92364219114219</v>
+        <v>75.04727126427494</v>
       </c>
       <c r="T7" t="n">
-        <v>23731.0800718889</v>
+        <v>27407.47145011851</v>
       </c>
       <c r="U7" t="n">
-        <v>6555134.243207773</v>
+        <v>9773862.17948718</v>
       </c>
       <c r="V7" t="n">
-        <v>80.08755555718793</v>
+        <v>78.71980008349493</v>
       </c>
       <c r="W7" t="n">
-        <v>1.279201264421853</v>
+        <v>1.298392049127343</v>
       </c>
       <c r="X7" t="n">
-        <v>25.86303449254946</v>
+        <v>27.64732357855423</v>
       </c>
       <c r="Y7" t="n">
-        <v>179.5528363392141</v>
+        <v>178.2649274329615</v>
       </c>
       <c r="Z7" t="n">
-        <v>70.45708497824081</v>
+        <v>79.27035337526823</v>
       </c>
       <c r="AA7" t="n">
-        <v>20336.46480034509</v>
+        <v>72150.08948023655</v>
       </c>
       <c r="AB7" t="n">
-        <v>5026460.077208271</v>
+        <v>23580454.69064819</v>
       </c>
       <c r="AC7" t="n">
-        <v>75.41563877012793</v>
+        <v>81.90178796664866</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.216005700525824</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>30.6462962962963</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>180.8351851851852</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.777777777777778</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>297.1111111111111</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>130000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>53461111.11111111</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>301.6666666666667</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>8.444444444444445</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>27.175</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>178.9958333333333</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>232.875</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>68250</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12062500</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>242</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.75</v>
-      </c>
+        <v>2.261627106983144</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.3</v>
+        <v>28.01944444444445</v>
       </c>
       <c r="D8" t="n">
-        <v>184.06875</v>
+        <v>181.3043209876543</v>
       </c>
       <c r="E8" t="n">
-        <v>75.91249999999999</v>
+        <v>75.70987654320987</v>
       </c>
       <c r="F8" t="n">
-        <v>29075</v>
+        <v>28516.04938271605</v>
       </c>
       <c r="G8" t="n">
-        <v>10646875</v>
+        <v>8373148.148148149</v>
       </c>
       <c r="H8" t="n">
-        <v>78.65625</v>
+        <v>77.5108024691358</v>
       </c>
       <c r="I8" t="n">
-        <v>1.35625</v>
+        <v>1.330555555555555</v>
       </c>
       <c r="J8" t="n">
-        <v>28.91141975308642</v>
+        <v>26.00347222222222</v>
       </c>
       <c r="K8" t="n">
-        <v>180.8604938271605</v>
+        <v>182.4583333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>81.56759259259259</v>
+        <v>78.46527777777777</v>
       </c>
       <c r="M8" t="n">
-        <v>79543.51851851851</v>
+        <v>37211.80555555556</v>
       </c>
       <c r="N8" t="n">
-        <v>29066975.30864198</v>
+        <v>19075607.63888889</v>
       </c>
       <c r="O8" t="n">
-        <v>83.37530864197531</v>
+        <v>82.02083333333333</v>
       </c>
       <c r="P8" t="n">
-        <v>2.704938271604938</v>
+        <v>1.826388888888889</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.33308890864038</v>
+        <v>25.74298044003926</v>
       </c>
       <c r="R8" t="n">
-        <v>181.4467083468002</v>
+        <v>181.5655630770827</v>
       </c>
       <c r="S8" t="n">
-        <v>75.04727126427494</v>
+        <v>71.36744076547998</v>
       </c>
       <c r="T8" t="n">
-        <v>27407.47145011851</v>
+        <v>21728.54269913094</v>
       </c>
       <c r="U8" t="n">
-        <v>9773862.17948718</v>
+        <v>5788293.955046405</v>
       </c>
       <c r="V8" t="n">
-        <v>78.71980008349493</v>
+        <v>75.68820865953219</v>
       </c>
       <c r="W8" t="n">
-        <v>1.298392049127343</v>
+        <v>1.140796603541702</v>
       </c>
       <c r="X8" t="n">
-        <v>27.64732357855423</v>
+        <v>27.82587216704864</v>
       </c>
       <c r="Y8" t="n">
-        <v>178.2649274329615</v>
+        <v>182.268611417631</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.27035337526823</v>
+        <v>75.46918295937904</v>
       </c>
       <c r="AA8" t="n">
-        <v>72150.08948023655</v>
+        <v>34237.91792811401</v>
       </c>
       <c r="AB8" t="n">
-        <v>23580454.69064819</v>
+        <v>10090676.79597091</v>
       </c>
       <c r="AC8" t="n">
-        <v>81.90178796664866</v>
+        <v>79.45043903083121</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.261627106983144</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>24.94444444444445</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>181.5277777777777</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>222.1666666666667</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>78166.66666666667</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>26250000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>236.3333333333333</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>28.05208333333334</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>179.5208333333333</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>208.25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>171375</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>51625000</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>216</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.5</v>
-      </c>
+        <v>1.532156296862179</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>28.01944444444445</v>
+        <v>26.73611111111111</v>
       </c>
       <c r="D9" t="n">
-        <v>181.3043209876543</v>
+        <v>181.15625</v>
       </c>
       <c r="E9" t="n">
-        <v>75.70987654320987</v>
+        <v>72.10416666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>28516.04938271605</v>
+        <v>19427.08333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>8373148.148148149</v>
+        <v>3403125</v>
       </c>
       <c r="H9" t="n">
-        <v>77.5108024691358</v>
+        <v>74.84722222222223</v>
       </c>
       <c r="I9" t="n">
-        <v>1.330555555555555</v>
+        <v>1.059027777777778</v>
       </c>
       <c r="J9" t="n">
-        <v>26.00347222222222</v>
+        <v>26.79715909090909</v>
       </c>
       <c r="K9" t="n">
-        <v>182.4583333333333</v>
+        <v>182.896875</v>
       </c>
       <c r="L9" t="n">
-        <v>78.46527777777777</v>
+        <v>78.67357954545454</v>
       </c>
       <c r="M9" t="n">
-        <v>37211.80555555556</v>
+        <v>33103.40909090909</v>
       </c>
       <c r="N9" t="n">
-        <v>19075607.63888889</v>
+        <v>23251363.63636363</v>
       </c>
       <c r="O9" t="n">
-        <v>82.02083333333333</v>
+        <v>81.91363636363636</v>
       </c>
       <c r="P9" t="n">
-        <v>1.826388888888889</v>
+        <v>1.782670454545455</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.74298044003926</v>
+        <v>27.23897513747427</v>
       </c>
       <c r="R9" t="n">
-        <v>181.5655630770827</v>
+        <v>180.119689901556</v>
       </c>
       <c r="S9" t="n">
-        <v>71.36744076547998</v>
+        <v>71.64053581429181</v>
       </c>
       <c r="T9" t="n">
-        <v>21728.54269913094</v>
+        <v>19045.75983626776</v>
       </c>
       <c r="U9" t="n">
-        <v>5788293.955046405</v>
+        <v>2998829.598624771</v>
       </c>
       <c r="V9" t="n">
-        <v>75.68820865953219</v>
+        <v>74.42600436394576</v>
       </c>
       <c r="W9" t="n">
-        <v>1.140796603541702</v>
+        <v>1.035997887586257</v>
       </c>
       <c r="X9" t="n">
-        <v>27.82587216704864</v>
+        <v>27.07995709248612</v>
       </c>
       <c r="Y9" t="n">
-        <v>182.268611417631</v>
+        <v>181.9464681157551</v>
       </c>
       <c r="Z9" t="n">
-        <v>75.46918295937904</v>
+        <v>76.19109162305273</v>
       </c>
       <c r="AA9" t="n">
-        <v>34237.91792811401</v>
+        <v>30377.35346331515</v>
       </c>
       <c r="AB9" t="n">
-        <v>10090676.79597091</v>
+        <v>14993116.71488771</v>
       </c>
       <c r="AC9" t="n">
-        <v>79.45043903083121</v>
+        <v>79.85088947859846</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.532156296862179</v>
+        <v>1.517290084893607</v>
       </c>
       <c r="AE9" t="n">
-        <v>26</v>
+        <v>27.65625</v>
       </c>
       <c r="AF9" t="n">
-        <v>181.4642857142857</v>
+        <v>180.6458333333333</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.857142857142857</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>127</v>
+        <v>174.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>39285.71428571428</v>
+        <v>45625</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14157142.85714286</v>
+        <v>4743750</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.4285714285714</v>
+        <v>180</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.428571428571428</v>
+        <v>2.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>22.90277777777778</v>
+        <v>26.89791666666667</v>
       </c>
       <c r="AN9" t="n">
-        <v>178.9902777777778</v>
+        <v>186.48125</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.375</v>
+        <v>3.125</v>
       </c>
       <c r="AP9" t="n">
-        <v>383.125</v>
+        <v>254</v>
       </c>
       <c r="AQ9" t="n">
-        <v>152375</v>
+        <v>113500</v>
       </c>
       <c r="AR9" t="n">
-        <v>49575000</v>
+        <v>114112500</v>
       </c>
       <c r="AS9" t="n">
-        <v>428</v>
+        <v>262</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26.73611111111111</v>
+        <v>26.125</v>
       </c>
       <c r="D10" t="n">
-        <v>181.15625</v>
+        <v>180.25</v>
       </c>
       <c r="E10" t="n">
-        <v>72.10416666666667</v>
+        <v>77.75</v>
       </c>
       <c r="F10" t="n">
-        <v>19427.08333333333</v>
+        <v>37750</v>
       </c>
       <c r="G10" t="n">
-        <v>3403125</v>
+        <v>19587500</v>
       </c>
       <c r="H10" t="n">
-        <v>74.84722222222223</v>
+        <v>81.375</v>
       </c>
       <c r="I10" t="n">
-        <v>1.059027777777778</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>26.79715909090909</v>
+        <v>24.25396825396825</v>
       </c>
       <c r="K10" t="n">
-        <v>182.896875</v>
+        <v>179.359126984127</v>
       </c>
       <c r="L10" t="n">
-        <v>78.67357954545454</v>
+        <v>79.59523809523809</v>
       </c>
       <c r="M10" t="n">
-        <v>33103.40909090909</v>
+        <v>110251.9841269841</v>
       </c>
       <c r="N10" t="n">
-        <v>23251363.63636363</v>
+        <v>37379365.07936508</v>
       </c>
       <c r="O10" t="n">
-        <v>81.91363636363636</v>
+        <v>86.24206349206349</v>
       </c>
       <c r="P10" t="n">
-        <v>1.782670454545455</v>
+        <v>2.581349206349207</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.23897513747427</v>
+        <v>24.46182359307359</v>
       </c>
       <c r="R10" t="n">
-        <v>180.119689901556</v>
+        <v>181.3152406417112</v>
       </c>
       <c r="S10" t="n">
-        <v>71.64053581429181</v>
+        <v>72.26717383923267</v>
       </c>
       <c r="T10" t="n">
-        <v>19045.75983626776</v>
+        <v>30795.2264239029</v>
       </c>
       <c r="U10" t="n">
-        <v>2998829.598624771</v>
+        <v>12379812.47612682</v>
       </c>
       <c r="V10" t="n">
-        <v>74.42600436394576</v>
+        <v>78.26871445547917</v>
       </c>
       <c r="W10" t="n">
-        <v>1.035997887586257</v>
+        <v>1.619276271114507</v>
       </c>
       <c r="X10" t="n">
-        <v>27.07995709248612</v>
+        <v>21.69508065034381</v>
       </c>
       <c r="Y10" t="n">
-        <v>181.9464681157551</v>
+        <v>180.3596177944862</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.19109162305273</v>
+        <v>74.23392455497719</v>
       </c>
       <c r="AA10" t="n">
-        <v>30377.35346331515</v>
+        <v>81867.77319902318</v>
       </c>
       <c r="AB10" t="n">
-        <v>14993116.71488771</v>
+        <v>29764652.39621489</v>
       </c>
       <c r="AC10" t="n">
-        <v>79.85088947859846</v>
+        <v>82.89030067155068</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.517290084893607</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27.65625</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>180.6458333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>45625</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>4743750</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>26.89791666666667</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>186.48125</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>254</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>113500</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>114112500</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>262</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.75</v>
-      </c>
+        <v>2.039603013945119</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.125</v>
+        <v>28.01944444444445</v>
       </c>
       <c r="D11" t="n">
-        <v>180.25</v>
+        <v>181.3043209876543</v>
       </c>
       <c r="E11" t="n">
-        <v>77.75</v>
+        <v>75.70987654320987</v>
       </c>
       <c r="F11" t="n">
-        <v>37750</v>
+        <v>28516.04938271605</v>
       </c>
       <c r="G11" t="n">
-        <v>19587500</v>
+        <v>8373148.148148149</v>
       </c>
       <c r="H11" t="n">
-        <v>81.375</v>
+        <v>77.5108024691358</v>
       </c>
       <c r="I11" t="n">
-        <v>1.75</v>
+        <v>1.330555555555555</v>
       </c>
       <c r="J11" t="n">
-        <v>24.25396825396825</v>
+        <v>26.73611111111111</v>
       </c>
       <c r="K11" t="n">
-        <v>179.359126984127</v>
+        <v>181.15625</v>
       </c>
       <c r="L11" t="n">
-        <v>79.59523809523809</v>
+        <v>72.10416666666667</v>
       </c>
       <c r="M11" t="n">
-        <v>110251.9841269841</v>
+        <v>19427.08333333333</v>
       </c>
       <c r="N11" t="n">
-        <v>37379365.07936508</v>
+        <v>3403125</v>
       </c>
       <c r="O11" t="n">
-        <v>86.24206349206349</v>
+        <v>74.84722222222223</v>
       </c>
       <c r="P11" t="n">
-        <v>2.581349206349207</v>
+        <v>1.059027777777778</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.46182359307359</v>
+        <v>25.74298044003926</v>
       </c>
       <c r="R11" t="n">
-        <v>181.3152406417112</v>
+        <v>181.5655630770827</v>
       </c>
       <c r="S11" t="n">
-        <v>72.26717383923267</v>
+        <v>71.36744076547998</v>
       </c>
       <c r="T11" t="n">
-        <v>30795.2264239029</v>
+        <v>21728.54269913094</v>
       </c>
       <c r="U11" t="n">
-        <v>12379812.47612682</v>
+        <v>5788293.955046405</v>
       </c>
       <c r="V11" t="n">
-        <v>78.26871445547917</v>
+        <v>75.68820865953219</v>
       </c>
       <c r="W11" t="n">
-        <v>1.619276271114507</v>
+        <v>1.140796603541702</v>
       </c>
       <c r="X11" t="n">
-        <v>21.69508065034381</v>
+        <v>27.23897513747427</v>
       </c>
       <c r="Y11" t="n">
-        <v>180.3596177944862</v>
+        <v>180.119689901556</v>
       </c>
       <c r="Z11" t="n">
-        <v>74.23392455497719</v>
+        <v>71.64053581429181</v>
       </c>
       <c r="AA11" t="n">
-        <v>81867.77319902318</v>
+        <v>19045.75983626776</v>
       </c>
       <c r="AB11" t="n">
-        <v>29764652.39621489</v>
+        <v>2998829.598624771</v>
       </c>
       <c r="AC11" t="n">
-        <v>82.89030067155068</v>
+        <v>74.42600436394576</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.039603013945119</v>
+        <v>1.035997887586257</v>
       </c>
       <c r="AE11" t="n">
-        <v>25.80208333333334</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>179.6666666666666</v>
+        <v>181.4642857142857</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.375</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AH11" t="n">
-        <v>254.375</v>
+        <v>127</v>
       </c>
       <c r="AI11" t="n">
-        <v>110125</v>
+        <v>39285.71428571428</v>
       </c>
       <c r="AJ11" t="n">
-        <v>39750000</v>
+        <v>14157142.85714286</v>
       </c>
       <c r="AK11" t="n">
-        <v>273.875</v>
+        <v>135.4285714285714</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.25</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="AM11" t="n">
-        <v>27.58333333333333</v>
+        <v>27.65625</v>
       </c>
       <c r="AN11" t="n">
-        <v>183.8690476190476</v>
+        <v>180.6458333333333</v>
       </c>
       <c r="AO11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>45625</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4743750</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.40396825396826</v>
+      </c>
+      <c r="D12" t="n">
+        <v>182.5154761904762</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76.25476190476191</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36905.15873015874</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17741289.68253968</v>
+      </c>
+      <c r="H12" t="n">
+        <v>80.98015873015872</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.267460317460318</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>24.3889713461142</v>
+      </c>
+      <c r="R12" t="n">
+        <v>177.6679241393527</v>
+      </c>
+      <c r="S12" t="n">
+        <v>72.94180581323438</v>
+      </c>
+      <c r="T12" t="n">
+        <v>28324.98453927025</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8645121.10904968</v>
+      </c>
+      <c r="V12" t="n">
+        <v>79.18632240775098</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.053246753246753</v>
+      </c>
+      <c r="X12" t="n">
+        <v>23.61697305145835</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>181.2079042770955</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>71.92364219114219</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>23731.0800718889</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6555134.243207773</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>80.08755555718793</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.279201264421853</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>26.32619047619048</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>183.0071428571428</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>298</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>147285.7142857143</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>59171428.57142857</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>308.1428571428572</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>6.285714285714286</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>30.6462962962963</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>180.8351851851852</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.777777777777778</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>297.1111111111111</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>53461111.11111111</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.444444444444445</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28.91141975308642</v>
+      </c>
+      <c r="D13" t="n">
+        <v>180.8604938271605</v>
+      </c>
+      <c r="E13" t="n">
+        <v>81.56759259259259</v>
+      </c>
+      <c r="F13" t="n">
+        <v>79543.51851851851</v>
+      </c>
+      <c r="G13" t="n">
+        <v>29066975.30864198</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83.37530864197531</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.704938271604938</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.99305555555555</v>
+      </c>
+      <c r="K13" t="n">
+        <v>182.0486111111111</v>
+      </c>
+      <c r="L13" t="n">
+        <v>73.04629629629629</v>
+      </c>
+      <c r="M13" t="n">
+        <v>22168.98148148148</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4618981.481481481</v>
+      </c>
+      <c r="O13" t="n">
+        <v>76.46296296296296</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>27.64732357855423</v>
+      </c>
+      <c r="R13" t="n">
+        <v>178.2649274329615</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79.27035337526823</v>
+      </c>
+      <c r="T13" t="n">
+        <v>72150.08948023655</v>
+      </c>
+      <c r="U13" t="n">
+        <v>23580454.69064819</v>
+      </c>
+      <c r="V13" t="n">
+        <v>81.90178796664866</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.261627106983144</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25.33109077407323</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>180.4573609950803</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>72.79602288549657</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>24766.89577479051</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5338977.409854602</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>76.87217327831362</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.103710876517894</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28.05208333333334</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>179.5208333333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>171375</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>51625000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>216</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>181.4791666666667</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>26875</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4287500</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26.00347222222222</v>
+      </c>
+      <c r="D14" t="n">
+        <v>182.4583333333333</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.46527777777777</v>
+      </c>
+      <c r="F14" t="n">
+        <v>37211.80555555556</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19075607.63888889</v>
+      </c>
+      <c r="H14" t="n">
+        <v>82.02083333333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.826388888888889</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>27.82587216704864</v>
+      </c>
+      <c r="R14" t="n">
+        <v>182.268611417631</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.46918295937904</v>
+      </c>
+      <c r="T14" t="n">
+        <v>34237.91792811401</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10090676.79597091</v>
+      </c>
+      <c r="V14" t="n">
+        <v>79.45043903083121</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.532156296862179</v>
+      </c>
+      <c r="X14" t="n">
+        <v>26.42185333729451</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>181.1222989700931</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>71.38017181620123</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>19782.65498118439</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3576728.80768469</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>75.59811101208159</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>22.90277777777778</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>178.9902777777778</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>383.125</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>152375</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>49575000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>428</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>27.08333333333334</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>179.9375</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>35125</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9875000</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>141.625</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27.04166666666667</v>
+      </c>
+      <c r="D15" t="n">
+        <v>179.7916666666667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19541.66666666667</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>184.06875</v>
+      </c>
+      <c r="L15" t="n">
+        <v>75.91249999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29075</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10646875</v>
+      </c>
+      <c r="O15" t="n">
+        <v>78.65625</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.35625</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>27.15680923441501</v>
+      </c>
+      <c r="R15" t="n">
+        <v>178.3120848144326</v>
+      </c>
+      <c r="S15" t="n">
+        <v>72.89622558575087</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20377.68747850017</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5053143.059855521</v>
+      </c>
+      <c r="V15" t="n">
+        <v>74.94795321637427</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.117858234911899</v>
+      </c>
+      <c r="X15" t="n">
+        <v>26.33308890864038</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>181.4467083468002</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75.04727126427494</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>27407.47145011851</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9773862.17948718</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>78.71980008349493</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.298392049127343</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>26.8125</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>46750</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>15312500</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>185</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>24.94444444444445</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>181.5277777777777</v>
+      </c>
+      <c r="AO15" t="n">
         <v>3</v>
       </c>
-      <c r="AP11" t="n">
-        <v>255</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>434857.1428571428</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>162857142.8571429</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>262.5714285714286</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11.14285714285714</v>
+      <c r="AP15" t="n">
+        <v>222.1666666666667</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>78166.66666666667</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>26250000</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>236.3333333333333</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.666666666666667</v>
       </c>
     </row>
   </sheetData>
